--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="175">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,291 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Japanese J League 2</t>
+  </si>
+  <si>
+    <t>Japanese J League 3</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Slovenian 2 SNL</t>
+  </si>
+  <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Uruguayan Segunda Division</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Canadian Premier League</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>04:00:00</t>
+  </si>
+  <si>
+    <t>05:00:00</t>
+  </si>
+  <si>
+    <t>06:00:00</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>17:45:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Vanraure Hachinohe</t>
+  </si>
+  <si>
+    <t>Sapporo</t>
+  </si>
+  <si>
+    <t>Blaublitz Akita</t>
+  </si>
+  <si>
+    <t>Kamatamare Sanuki</t>
+  </si>
+  <si>
+    <t>Sendai</t>
+  </si>
+  <si>
+    <t>FC Petrzalka</t>
+  </si>
+  <si>
+    <t>Kagoshima Utd</t>
+  </si>
+  <si>
+    <t>Tegevajaro Miyazaki</t>
+  </si>
+  <si>
+    <t>BK Olympic</t>
+  </si>
+  <si>
+    <t>Vasalunds IF</t>
+  </si>
+  <si>
+    <t>Sociedad B</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>NK Slovenska Bistrica</t>
+  </si>
+  <si>
+    <t>Danubio</t>
+  </si>
+  <si>
+    <t>Ilirija Extra-Lux</t>
+  </si>
+  <si>
+    <t>NK Bilje</t>
+  </si>
+  <si>
+    <t>Sporting Gijon</t>
+  </si>
+  <si>
+    <t>Umea FC</t>
+  </si>
+  <si>
+    <t>Triglav</t>
+  </si>
+  <si>
+    <t>Krka</t>
+  </si>
+  <si>
+    <t>Boston River</t>
+  </si>
+  <si>
+    <t>Centro Atletico Fenix</t>
+  </si>
+  <si>
+    <t>Las Palmas</t>
+  </si>
+  <si>
+    <t>CD Castellon</t>
+  </si>
+  <si>
+    <t>CA Huracan</t>
+  </si>
+  <si>
+    <t>Deportivo Pasto</t>
+  </si>
+  <si>
+    <t>Girona</t>
+  </si>
+  <si>
+    <t>Cerro</t>
+  </si>
+  <si>
+    <t>Talleres</t>
+  </si>
+  <si>
+    <t>FC Supra du Quebec</t>
+  </si>
+  <si>
+    <t>Yokohama FC</t>
+  </si>
+  <si>
+    <t>Iwaki SC</t>
+  </si>
+  <si>
+    <t>Tosu</t>
+  </si>
+  <si>
+    <t>Tochigi SC</t>
+  </si>
+  <si>
+    <t>Iwata</t>
+  </si>
+  <si>
+    <t>Malzenice</t>
+  </si>
+  <si>
+    <t>Fukushima Utd</t>
+  </si>
+  <si>
+    <t>Omiya</t>
+  </si>
+  <si>
+    <t>Trelleborgs</t>
+  </si>
+  <si>
+    <t>FC Arlanda</t>
+  </si>
+  <si>
+    <t>Granada</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Rudar</t>
+  </si>
+  <si>
+    <t>Cerro Largo FC</t>
+  </si>
+  <si>
+    <t>Beltinci</t>
+  </si>
+  <si>
+    <t>NK Jadran Dekani</t>
+  </si>
+  <si>
+    <t>Celta Vigo B</t>
+  </si>
+  <si>
+    <t>Hammarby TFF</t>
+  </si>
+  <si>
+    <t>Jesenice</t>
+  </si>
+  <si>
+    <t>Tabor Sezana</t>
+  </si>
+  <si>
+    <t>Juventud De Las Piedras</t>
+  </si>
+  <si>
+    <t>Uruguay Montevideo FC</t>
+  </si>
+  <si>
+    <t>Valladolid</t>
+  </si>
+  <si>
+    <t>AD Ceuta FC</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Fortaleza FC</t>
+  </si>
+  <si>
+    <t>Mallorca</t>
+  </si>
+  <si>
+    <t>Wanderers (Uru)</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Pacific</t>
+  </si>
+  <si>
+    <t>2026-10-02 02:12:51</t>
   </si>
 </sst>
 </file>
@@ -585,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1113,7508 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>5.9</v>
+      </c>
+      <c r="H2">
+        <v>1.72</v>
+      </c>
+      <c r="I2">
+        <v>1.97</v>
+      </c>
+      <c r="J2">
+        <v>3.45</v>
+      </c>
+      <c r="K2">
+        <v>4.7</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.02</v>
+      </c>
+      <c r="N2">
+        <v>3.25</v>
+      </c>
+      <c r="O2">
+        <v>1.33</v>
+      </c>
+      <c r="P2">
+        <v>1.78</v>
+      </c>
+      <c r="Q2">
+        <v>1.94</v>
+      </c>
+      <c r="R2">
+        <v>1.28</v>
+      </c>
+      <c r="S2">
+        <v>3.2</v>
+      </c>
+      <c r="T2">
+        <v>1.79</v>
+      </c>
+      <c r="U2">
+        <v>1.91</v>
+      </c>
+      <c r="V2">
+        <v>2.02</v>
+      </c>
+      <c r="W2">
+        <v>1.2</v>
+      </c>
+      <c r="X2">
+        <v>42</v>
+      </c>
+      <c r="Y2">
+        <v>12</v>
+      </c>
+      <c r="Z2">
+        <v>18</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>12.5</v>
+      </c>
+      <c r="AD2">
+        <v>16.5</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.38</v>
+      </c>
+      <c r="AQ2">
+        <v>6</v>
+      </c>
+      <c r="AR2">
+        <v>7.2</v>
+      </c>
+      <c r="AS2">
+        <v>1.43</v>
+      </c>
+      <c r="AT2">
+        <v>8.6</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>7</v>
+      </c>
+      <c r="AW2">
+        <v>1.43</v>
+      </c>
+      <c r="AX2">
+        <v>1.43</v>
+      </c>
+      <c r="AY2">
+        <v>1.43</v>
+      </c>
+      <c r="AZ2">
+        <v>1.43</v>
+      </c>
+      <c r="BA2">
+        <v>1.43</v>
+      </c>
+      <c r="BB2">
+        <v>1.43</v>
+      </c>
+      <c r="BC2">
+        <v>1.43</v>
+      </c>
+      <c r="BD2">
+        <v>1.43</v>
+      </c>
+      <c r="BE2">
+        <v>1.43</v>
+      </c>
+      <c r="BF2">
+        <v>1.43</v>
+      </c>
+      <c r="BG2">
+        <v>1.43</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>2.64</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3">
+        <v>2.24</v>
+      </c>
+      <c r="G3">
+        <v>2.56</v>
+      </c>
+      <c r="H3">
+        <v>2.82</v>
+      </c>
+      <c r="I3">
+        <v>3.3</v>
+      </c>
+      <c r="J3">
+        <v>3.8</v>
+      </c>
+      <c r="K3">
+        <v>5.1</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>4.1</v>
+      </c>
+      <c r="O3">
+        <v>1.24</v>
+      </c>
+      <c r="P3">
+        <v>2.12</v>
+      </c>
+      <c r="Q3">
+        <v>1.7</v>
+      </c>
+      <c r="R3">
+        <v>1.4</v>
+      </c>
+      <c r="S3">
+        <v>2.72</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>1.43</v>
+      </c>
+      <c r="W3">
+        <v>1.64</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3">
+        <v>1.03</v>
+      </c>
+      <c r="AR3">
+        <v>1.03</v>
+      </c>
+      <c r="AS3">
+        <v>1.03</v>
+      </c>
+      <c r="AT3">
+        <v>1.03</v>
+      </c>
+      <c r="AU3">
+        <v>1.03</v>
+      </c>
+      <c r="AV3">
+        <v>1.03</v>
+      </c>
+      <c r="AW3">
+        <v>1.03</v>
+      </c>
+      <c r="AX3">
+        <v>1.03</v>
+      </c>
+      <c r="AY3">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3">
+        <v>1.03</v>
+      </c>
+      <c r="BA3">
+        <v>1.03</v>
+      </c>
+      <c r="BB3">
+        <v>1.03</v>
+      </c>
+      <c r="BC3">
+        <v>1.03</v>
+      </c>
+      <c r="BD3">
+        <v>1.03</v>
+      </c>
+      <c r="BE3">
+        <v>1.03</v>
+      </c>
+      <c r="BF3">
+        <v>1.01</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4">
+        <v>3.25</v>
+      </c>
+      <c r="G4">
+        <v>3.85</v>
+      </c>
+      <c r="H4">
+        <v>2.3</v>
+      </c>
+      <c r="I4">
+        <v>2.58</v>
+      </c>
+      <c r="J4">
+        <v>2.82</v>
+      </c>
+      <c r="K4">
+        <v>3.45</v>
+      </c>
+      <c r="L4">
+        <v>1.38</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>2.86</v>
+      </c>
+      <c r="O4">
+        <v>1.01</v>
+      </c>
+      <c r="P4">
+        <v>1.65</v>
+      </c>
+      <c r="Q4">
+        <v>2.2</v>
+      </c>
+      <c r="R4">
+        <v>1.22</v>
+      </c>
+      <c r="S4">
+        <v>3.9</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.63</v>
+      </c>
+      <c r="W4">
+        <v>1.35</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>11</v>
+      </c>
+      <c r="Z4">
+        <v>19</v>
+      </c>
+      <c r="AA4">
+        <v>44</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>9.4</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>38</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>19.5</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>90</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>80</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>36</v>
+      </c>
+      <c r="AP4">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4">
+        <v>1.01</v>
+      </c>
+      <c r="AR4">
+        <v>10</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>8</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>20</v>
+      </c>
+      <c r="AX4">
+        <v>16</v>
+      </c>
+      <c r="AY4">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>32</v>
+      </c>
+      <c r="BB4">
+        <v>1.01</v>
+      </c>
+      <c r="BC4">
+        <v>32</v>
+      </c>
+      <c r="BD4">
+        <v>42</v>
+      </c>
+      <c r="BE4">
+        <v>85</v>
+      </c>
+      <c r="BF4">
+        <v>38</v>
+      </c>
+      <c r="BG4">
+        <v>19</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5">
+        <v>1.1</v>
+      </c>
+      <c r="G5">
+        <v>600</v>
+      </c>
+      <c r="H5">
+        <v>1.1</v>
+      </c>
+      <c r="I5">
+        <v>870</v>
+      </c>
+      <c r="J5">
+        <v>1.12</v>
+      </c>
+      <c r="K5">
+        <v>950</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>1.24</v>
+      </c>
+      <c r="O5">
+        <v>1.01</v>
+      </c>
+      <c r="P5">
+        <v>1.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.02</v>
+      </c>
+      <c r="R5">
+        <v>1.18</v>
+      </c>
+      <c r="S5">
+        <v>1.02</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>1.01</v>
+      </c>
+      <c r="W5">
+        <v>1.01</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5">
+        <v>1.01</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>1.01</v>
+      </c>
+      <c r="AU5">
+        <v>1.01</v>
+      </c>
+      <c r="AV5">
+        <v>1.01</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>1.01</v>
+      </c>
+      <c r="AY5">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5">
+        <v>1.01</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>1.01</v>
+      </c>
+      <c r="BC5">
+        <v>1.01</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6">
+        <v>2.2</v>
+      </c>
+      <c r="G6">
+        <v>2.5</v>
+      </c>
+      <c r="H6">
+        <v>3.15</v>
+      </c>
+      <c r="I6">
+        <v>3.85</v>
+      </c>
+      <c r="J6">
+        <v>3.45</v>
+      </c>
+      <c r="K6">
+        <v>3.7</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.76</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7">
+        <v>1.1</v>
+      </c>
+      <c r="G7">
+        <v>600</v>
+      </c>
+      <c r="H7">
+        <v>1.1</v>
+      </c>
+      <c r="I7">
+        <v>870</v>
+      </c>
+      <c r="J7">
+        <v>1.12</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.03</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8">
+        <v>1.1</v>
+      </c>
+      <c r="G8">
+        <v>600</v>
+      </c>
+      <c r="H8">
+        <v>1.1</v>
+      </c>
+      <c r="I8">
+        <v>870</v>
+      </c>
+      <c r="J8">
+        <v>1.12</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.24</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9">
+        <v>2.52</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>2.54</v>
+      </c>
+      <c r="I9">
+        <v>3.15</v>
+      </c>
+      <c r="J9">
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <v>4.8</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.98</v>
+      </c>
+      <c r="Q9">
+        <v>1.78</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10">
+        <v>2.92</v>
+      </c>
+      <c r="G10">
+        <v>3.7</v>
+      </c>
+      <c r="H10">
+        <v>2.1</v>
+      </c>
+      <c r="I10">
+        <v>2.46</v>
+      </c>
+      <c r="J10">
+        <v>3.55</v>
+      </c>
+      <c r="K10">
+        <v>5.6</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.4</v>
+      </c>
+      <c r="Q10">
+        <v>1.5</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11">
+        <v>2.64</v>
+      </c>
+      <c r="G11">
+        <v>2.86</v>
+      </c>
+      <c r="H11">
+        <v>2.74</v>
+      </c>
+      <c r="I11">
+        <v>2.98</v>
+      </c>
+      <c r="J11">
+        <v>3.15</v>
+      </c>
+      <c r="K11">
+        <v>3.5</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2.1</v>
+      </c>
+      <c r="Q11">
+        <v>1.51</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12">
+        <v>2.62</v>
+      </c>
+      <c r="G12">
+        <v>2.76</v>
+      </c>
+      <c r="H12">
+        <v>2.8</v>
+      </c>
+      <c r="I12">
+        <v>2.9</v>
+      </c>
+      <c r="J12">
+        <v>3.4</v>
+      </c>
+      <c r="K12">
+        <v>3.65</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.86</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13">
+        <v>2.36</v>
+      </c>
+      <c r="G13">
+        <v>2.78</v>
+      </c>
+      <c r="H13">
+        <v>2.62</v>
+      </c>
+      <c r="I13">
+        <v>3.15</v>
+      </c>
+      <c r="J13">
+        <v>3.75</v>
+      </c>
+      <c r="K13">
+        <v>5.2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.4</v>
+      </c>
+      <c r="Q13">
+        <v>1.53</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14">
+        <v>1.79</v>
+      </c>
+      <c r="G14">
+        <v>1.97</v>
+      </c>
+      <c r="H14">
+        <v>3.9</v>
+      </c>
+      <c r="I14">
+        <v>4.6</v>
+      </c>
+      <c r="J14">
+        <v>4.1</v>
+      </c>
+      <c r="K14">
+        <v>4.9</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.04</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2.56</v>
+      </c>
+      <c r="Q14">
+        <v>1.52</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15">
+        <v>1.1</v>
+      </c>
+      <c r="G15">
+        <v>600</v>
+      </c>
+      <c r="H15">
+        <v>1.1</v>
+      </c>
+      <c r="I15">
+        <v>870</v>
+      </c>
+      <c r="J15">
+        <v>1.12</v>
+      </c>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.24</v>
+      </c>
+      <c r="Q15">
+        <v>1.02</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>2.18</v>
+      </c>
+      <c r="H16">
+        <v>4.3</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>3.2</v>
+      </c>
+      <c r="K16">
+        <v>3.5</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>1.11</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.58</v>
+      </c>
+      <c r="Q16">
+        <v>1.11</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17">
+        <v>1.1</v>
+      </c>
+      <c r="G17">
+        <v>600</v>
+      </c>
+      <c r="H17">
+        <v>1.1</v>
+      </c>
+      <c r="I17">
+        <v>870</v>
+      </c>
+      <c r="J17">
+        <v>1.12</v>
+      </c>
+      <c r="K17">
+        <v>950</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.24</v>
+      </c>
+      <c r="Q17">
+        <v>1.02</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18">
+        <v>1.1</v>
+      </c>
+      <c r="G18">
+        <v>600</v>
+      </c>
+      <c r="H18">
+        <v>1.1</v>
+      </c>
+      <c r="I18">
+        <v>870</v>
+      </c>
+      <c r="J18">
+        <v>1.12</v>
+      </c>
+      <c r="K18">
+        <v>950</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.24</v>
+      </c>
+      <c r="Q18">
+        <v>1.02</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19">
+        <v>1.56</v>
+      </c>
+      <c r="G19">
+        <v>1.67</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19">
+        <v>7.4</v>
+      </c>
+      <c r="J19">
+        <v>4.2</v>
+      </c>
+      <c r="K19">
+        <v>4.7</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2.04</v>
+      </c>
+      <c r="Q19">
+        <v>1.02</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20">
+        <v>3.8</v>
+      </c>
+      <c r="G20">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>1.55</v>
+      </c>
+      <c r="I20">
+        <v>1.96</v>
+      </c>
+      <c r="J20">
+        <v>3.6</v>
+      </c>
+      <c r="K20">
+        <v>11</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>2.06</v>
+      </c>
+      <c r="Q20">
+        <v>1.51</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F21">
+        <v>1.38</v>
+      </c>
+      <c r="G21">
+        <v>600</v>
+      </c>
+      <c r="H21">
+        <v>1.38</v>
+      </c>
+      <c r="I21">
+        <v>870</v>
+      </c>
+      <c r="J21">
+        <v>1.38</v>
+      </c>
+      <c r="K21">
+        <v>950</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1.45</v>
+      </c>
+      <c r="Q21">
+        <v>1.03</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22">
+        <v>1.1</v>
+      </c>
+      <c r="G22">
+        <v>600</v>
+      </c>
+      <c r="H22">
+        <v>1.1</v>
+      </c>
+      <c r="I22">
+        <v>870</v>
+      </c>
+      <c r="J22">
+        <v>1.12</v>
+      </c>
+      <c r="K22">
+        <v>950</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1.24</v>
+      </c>
+      <c r="Q22">
+        <v>1.02</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23">
+        <v>2.78</v>
+      </c>
+      <c r="G23">
+        <v>3.05</v>
+      </c>
+      <c r="H23">
+        <v>2.62</v>
+      </c>
+      <c r="I23">
+        <v>2.98</v>
+      </c>
+      <c r="J23">
+        <v>3.3</v>
+      </c>
+      <c r="K23">
+        <v>3.6</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.08</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.83</v>
+      </c>
+      <c r="Q23">
+        <v>2.02</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>165</v>
+      </c>
+      <c r="F24">
+        <v>1.45</v>
+      </c>
+      <c r="G24">
+        <v>1.82</v>
+      </c>
+      <c r="H24">
+        <v>4.9</v>
+      </c>
+      <c r="I24">
+        <v>1000</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
+        <v>9.6</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.54</v>
+      </c>
+      <c r="Q24">
+        <v>2.02</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25">
+        <v>2.24</v>
+      </c>
+      <c r="G25">
+        <v>2.42</v>
+      </c>
+      <c r="H25">
+        <v>3.4</v>
+      </c>
+      <c r="I25">
+        <v>3.75</v>
+      </c>
+      <c r="J25">
+        <v>3.3</v>
+      </c>
+      <c r="K25">
+        <v>3.6</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.25</v>
+      </c>
+      <c r="Q25">
+        <v>2.04</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>167</v>
+      </c>
+      <c r="F26">
+        <v>1.28</v>
+      </c>
+      <c r="G26">
+        <v>1.31</v>
+      </c>
+      <c r="H26">
+        <v>11.5</v>
+      </c>
+      <c r="I26">
+        <v>15</v>
+      </c>
+      <c r="J26">
+        <v>6.4</v>
+      </c>
+      <c r="K26">
+        <v>7.4</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>1.26</v>
+      </c>
+      <c r="Q26">
+        <v>1.4</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27">
+        <v>1.73</v>
+      </c>
+      <c r="G27">
+        <v>1.79</v>
+      </c>
+      <c r="H27">
+        <v>6</v>
+      </c>
+      <c r="I27">
+        <v>6.8</v>
+      </c>
+      <c r="J27">
+        <v>3.5</v>
+      </c>
+      <c r="K27">
+        <v>3.7</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.12</v>
+      </c>
+      <c r="N27">
+        <v>2.62</v>
+      </c>
+      <c r="O27">
+        <v>1.55</v>
+      </c>
+      <c r="P27">
+        <v>1.56</v>
+      </c>
+      <c r="Q27">
+        <v>2.6</v>
+      </c>
+      <c r="R27">
+        <v>1.2</v>
+      </c>
+      <c r="S27">
+        <v>5.4</v>
+      </c>
+      <c r="T27">
+        <v>2.44</v>
+      </c>
+      <c r="U27">
+        <v>1.64</v>
+      </c>
+      <c r="V27">
+        <v>1.17</v>
+      </c>
+      <c r="W27">
+        <v>2.26</v>
+      </c>
+      <c r="X27">
+        <v>9</v>
+      </c>
+      <c r="Y27">
+        <v>17</v>
+      </c>
+      <c r="Z27">
+        <v>60</v>
+      </c>
+      <c r="AA27">
+        <v>260</v>
+      </c>
+      <c r="AB27">
+        <v>5.9</v>
+      </c>
+      <c r="AC27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD27">
+        <v>32</v>
+      </c>
+      <c r="AE27">
+        <v>160</v>
+      </c>
+      <c r="AF27">
+        <v>9</v>
+      </c>
+      <c r="AG27">
+        <v>11.5</v>
+      </c>
+      <c r="AH27">
+        <v>36</v>
+      </c>
+      <c r="AI27">
+        <v>160</v>
+      </c>
+      <c r="AJ27">
+        <v>22</v>
+      </c>
+      <c r="AK27">
+        <v>30</v>
+      </c>
+      <c r="AL27">
+        <v>70</v>
+      </c>
+      <c r="AM27">
+        <v>290</v>
+      </c>
+      <c r="AN27">
+        <v>19.5</v>
+      </c>
+      <c r="AO27">
+        <v>290</v>
+      </c>
+      <c r="AP27">
+        <v>8</v>
+      </c>
+      <c r="AQ27">
+        <v>12.5</v>
+      </c>
+      <c r="AR27">
+        <v>8.6</v>
+      </c>
+      <c r="AS27">
+        <v>9</v>
+      </c>
+      <c r="AT27">
+        <v>5.4</v>
+      </c>
+      <c r="AU27">
+        <v>7.8</v>
+      </c>
+      <c r="AV27">
+        <v>7.4</v>
+      </c>
+      <c r="AW27">
+        <v>9.4</v>
+      </c>
+      <c r="AX27">
+        <v>8</v>
+      </c>
+      <c r="AY27">
+        <v>10</v>
+      </c>
+      <c r="AZ27">
+        <v>7.8</v>
+      </c>
+      <c r="BA27">
+        <v>9.4</v>
+      </c>
+      <c r="BB27">
+        <v>15.5</v>
+      </c>
+      <c r="BC27">
+        <v>21</v>
+      </c>
+      <c r="BD27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE27">
+        <v>9</v>
+      </c>
+      <c r="BF27">
+        <v>15.5</v>
+      </c>
+      <c r="BG27">
+        <v>9</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.01</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28">
+        <v>2.02</v>
+      </c>
+      <c r="G28">
+        <v>2.24</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>4.8</v>
+      </c>
+      <c r="J28">
+        <v>3.15</v>
+      </c>
+      <c r="K28">
+        <v>3.7</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1.54</v>
+      </c>
+      <c r="Q28">
+        <v>2.14</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29">
+        <v>2.34</v>
+      </c>
+      <c r="G29">
+        <v>2.42</v>
+      </c>
+      <c r="H29">
+        <v>3.2</v>
+      </c>
+      <c r="I29">
+        <v>3.25</v>
+      </c>
+      <c r="J29">
+        <v>3.55</v>
+      </c>
+      <c r="K29">
+        <v>3.8</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29">
+        <v>1.02</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30">
+        <v>2.92</v>
+      </c>
+      <c r="G30">
+        <v>3.75</v>
+      </c>
+      <c r="H30">
+        <v>2.44</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <v>3.1</v>
+      </c>
+      <c r="K30">
+        <v>4.1</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1.01</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1.51</v>
+      </c>
+      <c r="Q30">
+        <v>2.14</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30">
+        <v>0</v>
+      </c>
+      <c r="AW30">
+        <v>0</v>
+      </c>
+      <c r="AX30">
+        <v>0</v>
+      </c>
+      <c r="AY30">
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+      <c r="BG30">
+        <v>0</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+      <c r="BI30">
+        <v>0</v>
+      </c>
+      <c r="BJ30">
+        <v>0</v>
+      </c>
+      <c r="BK30">
+        <v>0</v>
+      </c>
+      <c r="BL30">
+        <v>0</v>
+      </c>
+      <c r="BM30">
+        <v>0</v>
+      </c>
+      <c r="BN30">
+        <v>0</v>
+      </c>
+      <c r="BO30">
+        <v>0</v>
+      </c>
+      <c r="BP30">
+        <v>0</v>
+      </c>
+      <c r="BQ30">
+        <v>0</v>
+      </c>
+      <c r="BR30">
+        <v>0</v>
+      </c>
+      <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
+        <v>0</v>
+      </c>
+      <c r="BU30">
+        <v>0</v>
+      </c>
+      <c r="BV30">
+        <v>0</v>
+      </c>
+      <c r="BW30">
+        <v>0</v>
+      </c>
+      <c r="BX30">
+        <v>0</v>
+      </c>
+      <c r="BY30">
+        <v>0</v>
+      </c>
+      <c r="BZ30">
+        <v>0</v>
+      </c>
+      <c r="CA30">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31">
+        <v>2.62</v>
+      </c>
+      <c r="G31">
+        <v>2.94</v>
+      </c>
+      <c r="H31">
+        <v>2.98</v>
+      </c>
+      <c r="I31">
+        <v>3.4</v>
+      </c>
+      <c r="J31">
+        <v>2.9</v>
+      </c>
+      <c r="K31">
+        <v>3.55</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>1.48</v>
+      </c>
+      <c r="Q31">
+        <v>2.58</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>0</v>
+      </c>
+      <c r="AV31">
+        <v>0</v>
+      </c>
+      <c r="AW31">
+        <v>0</v>
+      </c>
+      <c r="AX31">
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31">
+        <v>0</v>
+      </c>
+      <c r="BG31">
+        <v>0</v>
+      </c>
+      <c r="BH31">
+        <v>0</v>
+      </c>
+      <c r="BI31">
+        <v>0</v>
+      </c>
+      <c r="BJ31">
+        <v>0</v>
+      </c>
+      <c r="BK31">
+        <v>0</v>
+      </c>
+      <c r="BL31">
+        <v>0</v>
+      </c>
+      <c r="BM31">
+        <v>0</v>
+      </c>
+      <c r="BN31">
+        <v>0</v>
+      </c>
+      <c r="BO31">
+        <v>0</v>
+      </c>
+      <c r="BP31">
+        <v>0</v>
+      </c>
+      <c r="BQ31">
+        <v>0</v>
+      </c>
+      <c r="BR31">
+        <v>0</v>
+      </c>
+      <c r="BS31">
+        <v>0</v>
+      </c>
+      <c r="BT31">
+        <v>0</v>
+      </c>
+      <c r="BU31">
+        <v>0</v>
+      </c>
+      <c r="BV31">
+        <v>0</v>
+      </c>
+      <c r="BW31">
+        <v>0</v>
+      </c>
+      <c r="BX31">
+        <v>0</v>
+      </c>
+      <c r="BY31">
+        <v>0</v>
+      </c>
+      <c r="BZ31">
+        <v>0</v>
+      </c>
+      <c r="CA31">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32">
+        <v>1.5</v>
+      </c>
+      <c r="G32">
+        <v>1.91</v>
+      </c>
+      <c r="H32">
+        <v>4.1</v>
+      </c>
+      <c r="I32">
+        <v>870</v>
+      </c>
+      <c r="J32">
+        <v>3.7</v>
+      </c>
+      <c r="K32">
+        <v>11.5</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>2.36</v>
+      </c>
+      <c r="Q32">
+        <v>1.38</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -538,7 +538,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 02:12:51</t>
+    <t>2026-10-02 04:29:15</t>
   </si>
 </sst>
 </file>
@@ -1138,13 +1138,13 @@
         <v>5.9</v>
       </c>
       <c r="H2">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="I2">
         <v>1.97</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
         <v>4.7</v>
@@ -1189,10 +1189,10 @@
         <v>42</v>
       </c>
       <c r="Y2">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z2">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1204,7 +1204,7 @@
         <v>12.5</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE2">
         <v>1000</v>
@@ -1237,10 +1237,10 @@
         <v>1000</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP2">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ2">
         <v>6</v>
@@ -1249,7 +1249,7 @@
         <v>7.2</v>
       </c>
       <c r="AS2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AT2">
         <v>8.6</v>
@@ -1261,34 +1261,34 @@
         <v>7</v>
       </c>
       <c r="AW2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AX2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AY2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AZ2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="BA2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="BB2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="BC2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="BD2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="BE2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="BF2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="BG2">
         <v>1.43</v>
@@ -1374,13 +1374,13 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="I3">
         <v>3.3</v>
@@ -1389,7 +1389,7 @@
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1407,10 +1407,10 @@
         <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
         <v>2.72</v>
@@ -1422,10 +1422,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1652,7 +1652,7 @@
         <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
         <v>3.9</v>
@@ -1724,28 +1724,28 @@
         <v>36</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AR4">
         <v>10</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AT4">
         <v>8</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AV4">
         <v>8.199999999999999</v>
       </c>
       <c r="AW4">
-        <v>20</v>
+        <v>1.62</v>
       </c>
       <c r="AX4">
         <v>16</v>
@@ -1754,25 +1754,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BA4">
-        <v>32</v>
+        <v>1.67</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BC4">
-        <v>32</v>
+        <v>1.67</v>
       </c>
       <c r="BD4">
-        <v>42</v>
+        <v>1.63</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>1.67</v>
       </c>
       <c r="BF4">
-        <v>38</v>
+        <v>1.67</v>
       </c>
       <c r="BG4">
         <v>19</v>
@@ -1885,19 +1885,19 @@
         <v>1.24</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P5">
         <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.02</v>
+        <v>2.6</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1906,10 +1906,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1966,52 +1966,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -2100,226 +2100,226 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I6">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q6">
         <v>2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>174</v>
@@ -3794,13 +3794,13 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G13">
         <v>2.78</v>
       </c>
       <c r="H13">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I13">
         <v>3.15</v>
@@ -3809,7 +3809,7 @@
         <v>3.75</v>
       </c>
       <c r="K13">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="G14">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="H14">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="I14">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J14">
         <v>4.1</v>
       </c>
       <c r="K14">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q14">
         <v>1.52</v>
@@ -4520,19 +4520,19 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G16">
         <v>2.18</v>
       </c>
       <c r="H16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
         <v>3.5</v>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>1.56</v>
       </c>
       <c r="G19">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H19">
         <v>6</v>
@@ -5276,10 +5276,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q19">
-        <v>1.02</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -6220,7 +6220,7 @@
         <v>3.05</v>
       </c>
       <c r="H23">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I23">
         <v>2.98</v>
@@ -6710,7 +6710,7 @@
         <v>3.75</v>
       </c>
       <c r="J25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K25">
         <v>3.6</v>
@@ -7206,7 +7206,7 @@
         <v>1.12</v>
       </c>
       <c r="N27">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O27">
         <v>1.55</v>
@@ -7215,7 +7215,7 @@
         <v>1.56</v>
       </c>
       <c r="Q27">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R27">
         <v>1.2</v>
@@ -7272,7 +7272,7 @@
         <v>160</v>
       </c>
       <c r="AJ27">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK27">
         <v>30</v>
@@ -7284,7 +7284,7 @@
         <v>290</v>
       </c>
       <c r="AN27">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO27">
         <v>290</v>
@@ -7296,10 +7296,10 @@
         <v>12.5</v>
       </c>
       <c r="AR27">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS27">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT27">
         <v>5.4</v>
@@ -7308,7 +7308,7 @@
         <v>7.8</v>
       </c>
       <c r="AV27">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW27">
         <v>9.4</v>
@@ -7320,7 +7320,7 @@
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA27">
         <v>9.4</v>
@@ -7332,16 +7332,16 @@
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF27">
         <v>15.5</v>
       </c>
       <c r="BG27">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7424,7 +7424,7 @@
         <v>169</v>
       </c>
       <c r="F28">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>2.24</v>
@@ -7439,7 +7439,7 @@
         <v>3.15</v>
       </c>
       <c r="K28">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7457,7 +7457,7 @@
         <v>1.54</v>
       </c>
       <c r="Q28">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7681,7 +7681,7 @@
         <v>3.55</v>
       </c>
       <c r="K29">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7699,7 +7699,7 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -7908,22 +7908,22 @@
         <v>171</v>
       </c>
       <c r="F30">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="G30">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H30">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J30">
         <v>3.1</v>
       </c>
       <c r="K30">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8150,7 +8150,7 @@
         <v>172</v>
       </c>
       <c r="F31">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G31">
         <v>2.94</v>
@@ -8162,10 +8162,10 @@
         <v>3.4</v>
       </c>
       <c r="J31">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K31">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8183,7 +8183,7 @@
         <v>1.48</v>
       </c>
       <c r="Q31">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R31">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -538,7 +538,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 04:29:15</t>
+    <t>2026-10-02 06:45:32</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1132,7 @@
         <v>143</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G2">
         <v>5.9</v>
@@ -1144,7 +1144,7 @@
         <v>1.97</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
         <v>4.7</v>
@@ -1162,16 +1162,16 @@
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R2">
         <v>1.28</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
         <v>1.79</v>
@@ -1180,7 +1180,7 @@
         <v>1.91</v>
       </c>
       <c r="V2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W2">
         <v>1.2</v>
@@ -1252,7 +1252,7 @@
         <v>1.49</v>
       </c>
       <c r="AT2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU2">
         <v>6</v>
@@ -1297,7 +1297,7 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
@@ -1407,7 +1407,7 @@
         <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R3">
         <v>1.41</v>
@@ -1416,7 +1416,7 @@
         <v>2.72</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U3">
         <v>1.01</v>
@@ -1616,25 +1616,25 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I4">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J4">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
         <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.01</v>
@@ -1643,7 +1643,7 @@
         <v>2.86</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4">
         <v>1.65</v>
@@ -1655,19 +1655,19 @@
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U4">
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1882,16 +1882,16 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O5">
         <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -2100,22 +2100,22 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
         <v>2.48</v>
       </c>
       <c r="H6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J6">
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
         <v>1.34</v>
@@ -2124,22 +2124,22 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="T6">
         <v>1.82</v>
@@ -2223,7 +2223,7 @@
         <v>1.09</v>
       </c>
       <c r="AU6">
-        <v>5.6</v>
+        <v>1.06</v>
       </c>
       <c r="AV6">
         <v>1.16</v>
@@ -2360,208 +2360,208 @@
         <v>950</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
+        <v>1.07</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>1.07</v>
+      </c>
+      <c r="S7">
+        <v>1.01</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
         <v>1.03</v>
       </c>
-      <c r="Q7">
-        <v>1.01</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>174</v>
@@ -2602,208 +2602,208 @@
         <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P8">
         <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>174</v>
@@ -2829,16 +2829,16 @@
         <v>2.52</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H9">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I9">
         <v>3.15</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>4.8</v>
@@ -3310,19 +3310,19 @@
         <v>152</v>
       </c>
       <c r="F11">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="G11">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="H11">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="I11">
-        <v>2.98</v>
+        <v>4.6</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K11">
         <v>3.5</v>
@@ -3340,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3552,13 +3552,13 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G12">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="H12">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I12">
         <v>2.9</v>
@@ -3582,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="Q12">
         <v>2</v>
@@ -3800,7 +3800,7 @@
         <v>2.78</v>
       </c>
       <c r="H13">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I13">
         <v>3.15</v>
@@ -4039,25 +4039,25 @@
         <v>1.87</v>
       </c>
       <c r="G14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H14">
         <v>3.65</v>
       </c>
       <c r="I14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K14">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>2.58</v>
       </c>
       <c r="Q14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4281,16 +4281,16 @@
         <v>1.1</v>
       </c>
       <c r="G15">
-        <v>600</v>
+        <v>2.58</v>
       </c>
       <c r="H15">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="I15">
         <v>870</v>
       </c>
       <c r="J15">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4520,19 +4520,19 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H16">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J16">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K16">
         <v>3.5</v>
@@ -5246,22 +5246,22 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G19">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H19">
         <v>6</v>
       </c>
       <c r="I19">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5276,10 +5276,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5488,22 +5488,22 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H20">
         <v>1.55</v>
       </c>
       <c r="I20">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="J20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5518,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q20">
         <v>1.51</v>
@@ -5730,19 +5730,19 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G21">
         <v>600</v>
       </c>
       <c r="H21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="I21">
         <v>870</v>
       </c>
       <c r="J21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q21">
         <v>1.03</v>
@@ -6214,16 +6214,16 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G23">
+        <v>3.2</v>
+      </c>
+      <c r="H23">
+        <v>2.62</v>
+      </c>
+      <c r="I23">
         <v>3.05</v>
-      </c>
-      <c r="H23">
-        <v>2.58</v>
-      </c>
-      <c r="I23">
-        <v>2.98</v>
       </c>
       <c r="J23">
         <v>3.3</v>
@@ -6456,22 +6456,22 @@
         <v>165</v>
       </c>
       <c r="F24">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G24">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H24">
         <v>4.9</v>
       </c>
       <c r="I24">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K24">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6486,10 +6486,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q24">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6701,19 +6701,19 @@
         <v>2.24</v>
       </c>
       <c r="G25">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H25">
         <v>3.4</v>
       </c>
       <c r="I25">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J25">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6946,7 +6946,7 @@
         <v>1.31</v>
       </c>
       <c r="H26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I26">
         <v>15</v>
@@ -6955,7 +6955,7 @@
         <v>6.4</v>
       </c>
       <c r="K26">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6973,7 +6973,7 @@
         <v>1.26</v>
       </c>
       <c r="Q26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>168</v>
       </c>
       <c r="F27">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G27">
         <v>1.79</v>
@@ -7206,16 +7206,16 @@
         <v>1.12</v>
       </c>
       <c r="N27">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O27">
         <v>1.55</v>
       </c>
       <c r="P27">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q27">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R27">
         <v>1.2</v>
@@ -7224,7 +7224,7 @@
         <v>5.4</v>
       </c>
       <c r="T27">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U27">
         <v>1.64</v>
@@ -7236,7 +7236,7 @@
         <v>2.26</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y27">
         <v>17</v>
@@ -7245,10 +7245,10 @@
         <v>60</v>
       </c>
       <c r="AA27">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB27">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AC27">
         <v>8.800000000000001</v>
@@ -7260,7 +7260,7 @@
         <v>160</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG27">
         <v>11.5</v>
@@ -7269,37 +7269,37 @@
         <v>36</v>
       </c>
       <c r="AI27">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL27">
         <v>70</v>
       </c>
       <c r="AM27">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN27">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO27">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AP27">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ27">
         <v>12.5</v>
       </c>
       <c r="AR27">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AS27">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT27">
         <v>5.4</v>
@@ -7308,22 +7308,22 @@
         <v>7.8</v>
       </c>
       <c r="AV27">
+        <v>7.2</v>
+      </c>
+      <c r="AW27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX27">
         <v>7.8</v>
-      </c>
-      <c r="AW27">
-        <v>9.4</v>
-      </c>
-      <c r="AX27">
-        <v>8</v>
       </c>
       <c r="AY27">
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BA27">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB27">
         <v>15.5</v>
@@ -7332,16 +7332,16 @@
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE27">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF27">
         <v>15.5</v>
       </c>
       <c r="BG27">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7424,22 +7424,22 @@
         <v>169</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="G28">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="I28">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="J28">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K28">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="Q28">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7666,16 +7666,16 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G29">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H29">
         <v>3.2</v>
       </c>
       <c r="I29">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J29">
         <v>3.55</v>
@@ -7699,7 +7699,7 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -7908,22 +7908,22 @@
         <v>171</v>
       </c>
       <c r="F30">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G30">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="H30">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I30">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J30">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K30">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q30">
         <v>2.14</v>
@@ -8156,13 +8156,13 @@
         <v>2.94</v>
       </c>
       <c r="H31">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I31">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J31">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K31">
         <v>3.15</v>
@@ -8395,19 +8395,19 @@
         <v>1.5</v>
       </c>
       <c r="G32">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H32">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I32">
         <v>870</v>
       </c>
       <c r="J32">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K32">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q32">
         <v>1.38</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="178">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Slovakian 2 Liga</t>
   </si>
   <si>
+    <t>Portuguese Segunda Liga</t>
+  </si>
+  <si>
     <t>Swedish Division 1</t>
   </si>
   <si>
@@ -277,12 +280,12 @@
     <t>Norwegian 1st Division</t>
   </si>
   <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
     <t>Slovenian 2 SNL</t>
   </si>
   <si>
-    <t>Uruguayan Primera Division</t>
-  </si>
-  <si>
     <t>Uruguayan Segunda Division</t>
   </si>
   <si>
@@ -376,6 +379,9 @@
     <t>Tegevajaro Miyazaki</t>
   </si>
   <si>
+    <t>Farense</t>
+  </si>
+  <si>
     <t>BK Olympic</t>
   </si>
   <si>
@@ -391,24 +397,27 @@
     <t>Bryne</t>
   </si>
   <si>
+    <t>Danubio</t>
+  </si>
+  <si>
     <t>NK Slovenska Bistrica</t>
   </si>
   <si>
-    <t>Danubio</t>
+    <t>NK Bilje</t>
   </si>
   <si>
     <t>Ilirija Extra-Lux</t>
   </si>
   <si>
-    <t>NK Bilje</t>
-  </si>
-  <si>
     <t>Sporting Gijon</t>
   </si>
   <si>
     <t>Umea FC</t>
   </si>
   <si>
+    <t>Centro Atletico Fenix</t>
+  </si>
+  <si>
     <t>Triglav</t>
   </si>
   <si>
@@ -418,9 +427,6 @@
     <t>Boston River</t>
   </si>
   <si>
-    <t>Centro Atletico Fenix</t>
-  </si>
-  <si>
     <t>Las Palmas</t>
   </si>
   <si>
@@ -469,6 +475,9 @@
     <t>Omiya</t>
   </si>
   <si>
+    <t>Chaves</t>
+  </si>
+  <si>
     <t>Trelleborgs</t>
   </si>
   <si>
@@ -484,24 +493,27 @@
     <t>Lyn</t>
   </si>
   <si>
+    <t>Cerro Largo FC</t>
+  </si>
+  <si>
     <t>Rudar</t>
   </si>
   <si>
-    <t>Cerro Largo FC</t>
+    <t>NK Jadran Dekani</t>
   </si>
   <si>
     <t>Beltinci</t>
   </si>
   <si>
-    <t>NK Jadran Dekani</t>
-  </si>
-  <si>
     <t>Celta Vigo B</t>
   </si>
   <si>
     <t>Hammarby TFF</t>
   </si>
   <si>
+    <t>Uruguay Montevideo FC</t>
+  </si>
+  <si>
     <t>Jesenice</t>
   </si>
   <si>
@@ -511,9 +523,6 @@
     <t>Juventud De Las Piedras</t>
   </si>
   <si>
-    <t>Uruguay Montevideo FC</t>
-  </si>
-  <si>
     <t>Valladolid</t>
   </si>
   <si>
@@ -538,7 +547,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 06:45:32</t>
+    <t>2026-10-02 09:02:20</t>
   </si>
 </sst>
 </file>
@@ -870,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1120,16 +1129,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F2">
         <v>4.2</v>
@@ -1354,7 +1363,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1362,16 +1371,16 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>2.26</v>
@@ -1596,7 +1605,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1604,22 +1613,22 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F4">
         <v>3.2</v>
       </c>
       <c r="G4">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="H4">
         <v>2.28</v>
@@ -1628,7 +1637,7 @@
         <v>2.64</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="K4">
         <v>3.45</v>
@@ -1646,13 +1655,13 @@
         <v>1.02</v>
       </c>
       <c r="P4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
         <v>3.95</v>
@@ -1664,7 +1673,7 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
         <v>1.34</v>
@@ -1679,7 +1688,7 @@
         <v>19</v>
       </c>
       <c r="AA4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
         <v>1000</v>
@@ -1691,7 +1700,7 @@
         <v>1000</v>
       </c>
       <c r="AE4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF4">
         <v>1000</v>
@@ -1724,7 +1733,7 @@
         <v>36</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ4">
         <v>1.45</v>
@@ -1733,10 +1742,10 @@
         <v>10</v>
       </c>
       <c r="AS4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU4">
         <v>1.41</v>
@@ -1754,25 +1763,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BA4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BB4">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BC4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BD4">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="BE4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BF4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BG4">
         <v>19</v>
@@ -1838,7 +1847,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1846,16 +1855,16 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F5">
         <v>1.1</v>
@@ -1906,10 +1915,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2080,7 +2089,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2088,16 +2097,16 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F6">
         <v>2.2</v>
@@ -2139,13 +2148,13 @@
         <v>1.29</v>
       </c>
       <c r="S6">
-        <v>2.28</v>
+        <v>3.45</v>
       </c>
       <c r="T6">
         <v>1.82</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
         <v>1.37</v>
@@ -2322,7 +2331,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2330,16 +2339,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>1.1</v>
@@ -2390,10 +2399,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2564,7 +2573,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2572,16 +2581,16 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F8">
         <v>1.1</v>
@@ -2632,10 +2641,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2806,7 +2815,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2814,28 +2823,28 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F9">
         <v>2.52</v>
       </c>
       <c r="G9">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H9">
         <v>2.56</v>
       </c>
       <c r="I9">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="J9">
         <v>3.55</v>
@@ -2844,211 +2853,211 @@
         <v>4.8</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P9">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q9">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3056,483 +3065,483 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
         <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F10">
-        <v>2.92</v>
+        <v>2.18</v>
       </c>
       <c r="G10">
-        <v>3.7</v>
+        <v>2.44</v>
       </c>
       <c r="H10">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="I10">
-        <v>2.46</v>
+        <v>3.95</v>
       </c>
       <c r="J10">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K10">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="Q10">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="CB10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F11">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="G11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H11">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="I11">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J11">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P11">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="Q11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3540,241 +3549,241 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
         <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F12">
         <v>2.64</v>
       </c>
       <c r="G12">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H12">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="I12">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3782,34 +3791,34 @@
         <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
         <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F13">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="G13">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="H13">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="I13">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="J13">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3824,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q13">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4016,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4024,40 +4033,40 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F14">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="G14">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="H14">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="I14">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="J14">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4066,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
         <v>1.53</v>
@@ -4258,7 +4267,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4266,52 +4275,52 @@
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F15">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="G15">
+        <v>2.06</v>
+      </c>
+      <c r="H15">
+        <v>3.65</v>
+      </c>
+      <c r="I15">
+        <v>4.4</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>5.2</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>2.58</v>
       </c>
-      <c r="H15">
-        <v>1.66</v>
-      </c>
-      <c r="I15">
-        <v>870</v>
-      </c>
-      <c r="J15">
-        <v>1.63</v>
-      </c>
-      <c r="K15">
-        <v>950</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>1.24</v>
-      </c>
       <c r="Q15">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4500,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4508,16 +4517,16 @@
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F16">
         <v>1.96</v>
@@ -4526,7 +4535,7 @@
         <v>2.2</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I16">
         <v>5.2</v>
@@ -4541,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4742,39 +4751,39 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
         <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F17">
         <v>1.1</v>
       </c>
       <c r="G17">
-        <v>600</v>
+        <v>2.58</v>
       </c>
       <c r="H17">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="I17">
         <v>870</v>
       </c>
       <c r="J17">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -4984,24 +4993,24 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F18">
         <v>1.1</v>
@@ -5226,48 +5235,48 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
         <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F19">
-        <v>1.58</v>
+        <v>1.1</v>
       </c>
       <c r="G19">
-        <v>1.66</v>
+        <v>600</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="I19">
-        <v>6.8</v>
+        <v>870</v>
       </c>
       <c r="J19">
-        <v>4.1</v>
+        <v>1.12</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5276,10 +5285,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5468,42 +5477,42 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
         <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F20">
-        <v>3.9</v>
+        <v>1.56</v>
       </c>
       <c r="G20">
-        <v>12</v>
+        <v>1.65</v>
       </c>
       <c r="H20">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="I20">
-        <v>1.94</v>
+        <v>7.2</v>
       </c>
       <c r="J20">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5521,7 +5530,7 @@
         <v>2.08</v>
       </c>
       <c r="Q20">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5710,48 +5719,48 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
         <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F21">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="G21">
-        <v>600</v>
+        <v>6.4</v>
       </c>
       <c r="H21">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="I21">
-        <v>870</v>
+        <v>1.7</v>
       </c>
       <c r="J21">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -5760,10 +5769,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="Q21">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5952,48 +5961,48 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F22">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G22">
-        <v>600</v>
+        <v>1.8</v>
       </c>
       <c r="H22">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="I22">
-        <v>870</v>
+        <v>48</v>
       </c>
       <c r="J22">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -6002,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q22">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6194,48 +6203,48 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F23">
-        <v>2.74</v>
+        <v>1.4</v>
       </c>
       <c r="G23">
-        <v>3.2</v>
+        <v>600</v>
       </c>
       <c r="H23">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="I23">
-        <v>3.05</v>
+        <v>870</v>
       </c>
       <c r="J23">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="K23">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -6244,10 +6253,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="Q23">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6436,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6444,40 +6453,40 @@
         <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F24">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="H24">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="I24">
-        <v>48</v>
+        <v>870</v>
       </c>
       <c r="J24">
-        <v>3.2</v>
+        <v>1.12</v>
       </c>
       <c r="K24">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -6486,10 +6495,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="Q24">
-        <v>2.04</v>
+        <v>1.02</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6678,48 +6687,48 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
         <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F25">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="G25">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="H25">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="I25">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="J25">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K25">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -6728,10 +6737,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q25">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6920,42 +6929,42 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F26">
-        <v>1.28</v>
+        <v>2.24</v>
       </c>
       <c r="G26">
-        <v>1.31</v>
+        <v>2.44</v>
       </c>
       <c r="H26">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="I26">
-        <v>15</v>
+        <v>3.55</v>
       </c>
       <c r="J26">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="K26">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6970,10 +6979,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q26">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7162,249 +7171,249 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
         <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F27">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="G27">
-        <v>1.79</v>
+        <v>1.3</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I27">
+        <v>16</v>
+      </c>
+      <c r="J27">
         <v>6.8</v>
       </c>
-      <c r="J27">
-        <v>3.5</v>
-      </c>
       <c r="K27">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="Q27">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="R27">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO27">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BG27">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7412,276 +7421,276 @@
         <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
         <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F28">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="G28">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="H28">
+        <v>5.8</v>
+      </c>
+      <c r="I28">
+        <v>6.8</v>
+      </c>
+      <c r="J28">
         <v>3.45</v>
       </c>
-      <c r="I28">
-        <v>3.9</v>
-      </c>
-      <c r="J28">
-        <v>3.1</v>
-      </c>
       <c r="K28">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P28">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q28">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F29">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="G29">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H29">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I29">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J29">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="K29">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7696,10 +7705,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q29">
-        <v>1.71</v>
+        <v>2.26</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -7888,48 +7897,48 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F30">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="G30">
-        <v>3.65</v>
+        <v>2.42</v>
       </c>
       <c r="H30">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="I30">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J30">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K30">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -7938,10 +7947,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="Q30">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8130,48 +8139,48 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
         <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F31">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G31">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="H31">
-        <v>2.96</v>
+        <v>2.28</v>
       </c>
       <c r="I31">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J31">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K31">
-        <v>3.15</v>
+        <v>900</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -8180,10 +8189,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q31">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8372,249 +8381,491 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>143</v>
+      </c>
+      <c r="E32" t="s">
+        <v>175</v>
+      </c>
+      <c r="F32">
+        <v>2.64</v>
+      </c>
+      <c r="G32">
+        <v>2.94</v>
+      </c>
+      <c r="H32">
+        <v>2.96</v>
+      </c>
+      <c r="I32">
+        <v>3.6</v>
+      </c>
+      <c r="J32">
+        <v>2.92</v>
+      </c>
+      <c r="K32">
+        <v>3.15</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>1.48</v>
+      </c>
+      <c r="Q32">
+        <v>2.6</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
         <v>93</v>
       </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32">
+      <c r="B33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
+        <v>144</v>
+      </c>
+      <c r="E33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F33">
         <v>1.5</v>
       </c>
-      <c r="G32">
+      <c r="G33">
         <v>1.89</v>
       </c>
-      <c r="H32">
+      <c r="H33">
         <v>4.3</v>
       </c>
-      <c r="I32">
+      <c r="I33">
         <v>870</v>
       </c>
-      <c r="J32">
+      <c r="J33">
         <v>3.8</v>
       </c>
-      <c r="K32">
+      <c r="K33">
         <v>10</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
         <v>2.4</v>
       </c>
-      <c r="Q32">
+      <c r="Q33">
         <v>1.38</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>0</v>
-      </c>
-      <c r="BC32">
-        <v>0</v>
-      </c>
-      <c r="BD32">
-        <v>0</v>
-      </c>
-      <c r="BE32">
-        <v>0</v>
-      </c>
-      <c r="BF32">
-        <v>0</v>
-      </c>
-      <c r="BG32">
-        <v>0</v>
-      </c>
-      <c r="BH32">
-        <v>0</v>
-      </c>
-      <c r="BI32">
-        <v>0</v>
-      </c>
-      <c r="BJ32">
-        <v>0</v>
-      </c>
-      <c r="BK32">
-        <v>0</v>
-      </c>
-      <c r="BL32">
-        <v>0</v>
-      </c>
-      <c r="BM32">
-        <v>0</v>
-      </c>
-      <c r="BN32">
-        <v>0</v>
-      </c>
-      <c r="BO32">
-        <v>0</v>
-      </c>
-      <c r="BP32">
-        <v>0</v>
-      </c>
-      <c r="BQ32">
-        <v>0</v>
-      </c>
-      <c r="BR32">
-        <v>0</v>
-      </c>
-      <c r="BS32">
-        <v>0</v>
-      </c>
-      <c r="BT32">
-        <v>0</v>
-      </c>
-      <c r="BU32">
-        <v>0</v>
-      </c>
-      <c r="BV32">
-        <v>0</v>
-      </c>
-      <c r="BW32">
-        <v>0</v>
-      </c>
-      <c r="BX32">
-        <v>0</v>
-      </c>
-      <c r="BY32">
-        <v>0</v>
-      </c>
-      <c r="BZ32">
-        <v>0</v>
-      </c>
-      <c r="CA32">
-        <v>0</v>
-      </c>
-      <c r="CB32" t="s">
-        <v>174</v>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>0</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="AV33">
+        <v>0</v>
+      </c>
+      <c r="AW33">
+        <v>0</v>
+      </c>
+      <c r="AX33">
+        <v>0</v>
+      </c>
+      <c r="AY33">
+        <v>0</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+      <c r="BA33">
+        <v>0</v>
+      </c>
+      <c r="BB33">
+        <v>0</v>
+      </c>
+      <c r="BC33">
+        <v>0</v>
+      </c>
+      <c r="BD33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>0</v>
+      </c>
+      <c r="BF33">
+        <v>0</v>
+      </c>
+      <c r="BG33">
+        <v>0</v>
+      </c>
+      <c r="BH33">
+        <v>0</v>
+      </c>
+      <c r="BI33">
+        <v>0</v>
+      </c>
+      <c r="BJ33">
+        <v>0</v>
+      </c>
+      <c r="BK33">
+        <v>0</v>
+      </c>
+      <c r="BL33">
+        <v>0</v>
+      </c>
+      <c r="BM33">
+        <v>0</v>
+      </c>
+      <c r="BN33">
+        <v>0</v>
+      </c>
+      <c r="BO33">
+        <v>0</v>
+      </c>
+      <c r="BP33">
+        <v>0</v>
+      </c>
+      <c r="BQ33">
+        <v>0</v>
+      </c>
+      <c r="BR33">
+        <v>0</v>
+      </c>
+      <c r="BS33">
+        <v>0</v>
+      </c>
+      <c r="BT33">
+        <v>0</v>
+      </c>
+      <c r="BU33">
+        <v>0</v>
+      </c>
+      <c r="BV33">
+        <v>0</v>
+      </c>
+      <c r="BW33">
+        <v>0</v>
+      </c>
+      <c r="BX33">
+        <v>0</v>
+      </c>
+      <c r="BY33">
+        <v>0</v>
+      </c>
+      <c r="BZ33">
+        <v>0</v>
+      </c>
+      <c r="CA33">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -547,7 +547,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 09:02:20</t>
+    <t>2026-10-02 11:19:20</t>
   </si>
 </sst>
 </file>
@@ -1156,13 +1156,13 @@
         <v>3.65</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
         <v>3.25</v>
@@ -1174,28 +1174,28 @@
         <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
         <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U2">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
         <v>2.04</v>
       </c>
       <c r="W2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Y2">
         <v>970</v>
@@ -1210,7 +1210,7 @@
         <v>1000</v>
       </c>
       <c r="AC2">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD2">
         <v>970</v>
@@ -1246,61 +1246,61 @@
         <v>1000</v>
       </c>
       <c r="AO2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AQ2">
-        <v>6</v>
+        <v>1.27</v>
       </c>
       <c r="AR2">
         <v>7.2</v>
       </c>
       <c r="AS2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>1.42</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>1.28</v>
       </c>
       <c r="AV2">
-        <v>7</v>
+        <v>1.31</v>
       </c>
       <c r="AW2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AX2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AY2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AZ2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BA2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BB2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BC2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BD2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BE2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BF2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BG2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1389,7 +1389,7 @@
         <v>2.58</v>
       </c>
       <c r="H3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I3">
         <v>3.3</v>
@@ -1398,7 +1398,7 @@
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1416,7 +1416,7 @@
         <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R3">
         <v>1.41</v>
@@ -1431,7 +1431,7 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
         <v>1.63</v>
@@ -1628,16 +1628,16 @@
         <v>3.2</v>
       </c>
       <c r="G4">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="H4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I4">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J4">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
         <v>3.45</v>
@@ -1658,22 +1658,22 @@
         <v>1.64</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
         <v>3.95</v>
       </c>
       <c r="T4">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="U4">
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
         <v>1.34</v>
@@ -1867,13 +1867,13 @@
         <v>148</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G5">
         <v>600</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I5">
         <v>870</v>
@@ -1897,7 +1897,7 @@
         <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q5">
         <v>1.35</v>
@@ -2109,22 +2109,22 @@
         <v>149</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G6">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.34</v>
@@ -2133,34 +2133,34 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q6">
         <v>2.02</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="T6">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2378,19 +2378,19 @@
         <v>1.07</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7">
         <v>1.07</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R7">
         <v>1.07</v>
       </c>
       <c r="S7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2617,13 +2617,13 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
         <v>1.18</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
         <v>1.18</v>
@@ -2632,7 +2632,7 @@
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2835,16 +2835,16 @@
         <v>152</v>
       </c>
       <c r="F9">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G9">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H9">
         <v>2.56</v>
       </c>
       <c r="I9">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J9">
         <v>3.55</v>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="P9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>1.77</v>
@@ -2877,7 +2877,7 @@
         <v>2.88</v>
       </c>
       <c r="T9">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U9">
         <v>2.14</v>
@@ -2958,7 +2958,7 @@
         <v>1.08</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
         <v>1.08</v>
@@ -3080,13 +3080,13 @@
         <v>2.18</v>
       </c>
       <c r="G10">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H10">
         <v>3.3</v>
       </c>
       <c r="I10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J10">
         <v>3.3</v>
@@ -3107,13 +3107,13 @@
         <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q10">
         <v>1.94</v>
       </c>
       <c r="R10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S10">
         <v>3.3</v>
@@ -3125,10 +3125,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3346,7 +3346,7 @@
         <v>2.9</v>
       </c>
       <c r="O11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P11">
         <v>2.4</v>
@@ -3561,13 +3561,13 @@
         <v>155</v>
       </c>
       <c r="F12">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="G12">
         <v>2.86</v>
       </c>
       <c r="H12">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="I12">
         <v>2.98</v>
@@ -3576,7 +3576,7 @@
         <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3588,7 +3588,7 @@
         <v>2.4</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12">
         <v>2.12</v>
@@ -3803,10 +3803,10 @@
         <v>156</v>
       </c>
       <c r="F13">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G13">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H13">
         <v>2.82</v>
@@ -3821,208 +3821,208 @@
         <v>3.65</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P13">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>177</v>
@@ -4048,31 +4048,31 @@
         <v>2.38</v>
       </c>
       <c r="G14">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H14">
         <v>2.62</v>
       </c>
       <c r="I14">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K14">
         <v>5.1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P14">
         <v>2.4</v>
@@ -4081,190 +4081,190 @@
         <v>1.53</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>177</v>
@@ -4287,226 +4287,226 @@
         <v>158</v>
       </c>
       <c r="F15">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G15">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H15">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>177</v>
@@ -4529,226 +4529,226 @@
         <v>159</v>
       </c>
       <c r="F16">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G16">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H16">
         <v>4.1</v>
       </c>
       <c r="I16">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K16">
         <v>3.5</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P16">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q16">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
         <v>177</v>
@@ -4771,34 +4771,34 @@
         <v>160</v>
       </c>
       <c r="F17">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G17">
         <v>2.58</v>
       </c>
       <c r="H17">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="I17">
         <v>870</v>
       </c>
       <c r="J17">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="K17">
         <v>950</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P17">
         <v>1.24</v>
@@ -4807,190 +4807,190 @@
         <v>1.02</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
         <v>177</v>
@@ -5031,16 +5031,16 @@
         <v>950</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P18">
         <v>1.24</v>
@@ -5049,190 +5049,190 @@
         <v>1.02</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
         <v>177</v>
@@ -5273,16 +5273,16 @@
         <v>950</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P19">
         <v>1.24</v>
@@ -5291,190 +5291,190 @@
         <v>1.02</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
         <v>177</v>
@@ -5497,22 +5497,22 @@
         <v>163</v>
       </c>
       <c r="F20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G20">
         <v>1.65</v>
       </c>
       <c r="H20">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I20">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5530,7 +5530,7 @@
         <v>2.08</v>
       </c>
       <c r="Q20">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -6223,19 +6223,19 @@
         <v>166</v>
       </c>
       <c r="F23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G23">
         <v>600</v>
       </c>
       <c r="H23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="I23">
         <v>870</v>
       </c>
       <c r="J23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q23">
         <v>1.03</v>
@@ -6707,16 +6707,16 @@
         <v>168</v>
       </c>
       <c r="F25">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G25">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H25">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="I25">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J25">
         <v>3.3</v>
@@ -6949,23 +6949,23 @@
         <v>169</v>
       </c>
       <c r="F26">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G26">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H26">
         <v>3.4</v>
       </c>
       <c r="I26">
+        <v>3.6</v>
+      </c>
+      <c r="J26">
+        <v>3.35</v>
+      </c>
+      <c r="K26">
         <v>3.55</v>
       </c>
-      <c r="J26">
-        <v>3.2</v>
-      </c>
-      <c r="K26">
-        <v>3.9</v>
-      </c>
       <c r="L26">
         <v>0</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="Q26">
         <v>2.08</v>
@@ -7191,22 +7191,22 @@
         <v>170</v>
       </c>
       <c r="F27">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="G27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J27">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K27">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7221,10 +7221,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="Q27">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7433,28 +7433,28 @@
         <v>171</v>
       </c>
       <c r="F28">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="G28">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="H28">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I28">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J28">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K28">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N28">
         <v>2.62</v>
@@ -7466,64 +7466,64 @@
         <v>1.56</v>
       </c>
       <c r="Q28">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R28">
         <v>1.2</v>
       </c>
       <c r="S28">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T28">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U28">
         <v>1.66</v>
       </c>
       <c r="V28">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W28">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="X28">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y28">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z28">
         <v>55</v>
       </c>
       <c r="AA28">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AB28">
         <v>6.2</v>
       </c>
       <c r="AC28">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD28">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE28">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF28">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AG28">
         <v>11.5</v>
       </c>
       <c r="AH28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI28">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ28">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AK28">
         <v>32</v>
@@ -7532,73 +7532,73 @@
         <v>75</v>
       </c>
       <c r="AM28">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN28">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO28">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AP28">
         <v>8</v>
       </c>
       <c r="AQ28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR28">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT28">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU28">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV28">
         <v>20</v>
       </c>
       <c r="AW28">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX28">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY28">
         <v>10</v>
       </c>
       <c r="AZ28">
+        <v>8</v>
+      </c>
+      <c r="BA28">
+        <v>9.6</v>
+      </c>
+      <c r="BB28">
+        <v>17</v>
+      </c>
+      <c r="BC28">
         <v>7.6</v>
       </c>
-      <c r="BA28">
+      <c r="BD28">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB28">
-        <v>15.5</v>
-      </c>
-      <c r="BC28">
-        <v>19</v>
-      </c>
-      <c r="BD28">
-        <v>8.6</v>
-      </c>
       <c r="BE28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF28">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BG28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
@@ -7616,7 +7616,7 @@
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BP28">
         <v>1000</v>
@@ -7920,10 +7920,10 @@
         <v>2.3</v>
       </c>
       <c r="G30">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H30">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I30">
         <v>3.3</v>
@@ -7947,10 +7947,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q30">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8174,7 +8174,7 @@
         <v>3.2</v>
       </c>
       <c r="K31">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8410,13 +8410,13 @@
         <v>2.96</v>
       </c>
       <c r="I32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J32">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K32">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -8431,10 +8431,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="Q32">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="R32">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="178">
   <si>
     <t>League</t>
   </si>
@@ -256,6 +256,9 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>Japanese J League 2</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
     <t>2026-10-04</t>
   </si>
   <si>
+    <t>01:20:00</t>
+  </si>
+  <si>
     <t>04:00:00</t>
   </si>
   <si>
@@ -355,6 +361,9 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>Real Cartagena</t>
+  </si>
+  <si>
     <t>Vanraure Hachinohe</t>
   </si>
   <si>
@@ -403,9 +412,6 @@
     <t>NK Slovenska Bistrica</t>
   </si>
   <si>
-    <t>NK Bilje</t>
-  </si>
-  <si>
     <t>Ilirija Extra-Lux</t>
   </si>
   <si>
@@ -415,18 +421,15 @@
     <t>Umea FC</t>
   </si>
   <si>
+    <t>Triglav</t>
+  </si>
+  <si>
+    <t>Boston River</t>
+  </si>
+  <si>
     <t>Centro Atletico Fenix</t>
   </si>
   <si>
-    <t>Triglav</t>
-  </si>
-  <si>
-    <t>Krka</t>
-  </si>
-  <si>
-    <t>Boston River</t>
-  </si>
-  <si>
     <t>Las Palmas</t>
   </si>
   <si>
@@ -451,6 +454,9 @@
     <t>FC Supra du Quebec</t>
   </si>
   <si>
+    <t>Boca Juniors de Cali</t>
+  </si>
+  <si>
     <t>Yokohama FC</t>
   </si>
   <si>
@@ -499,9 +505,6 @@
     <t>Rudar</t>
   </si>
   <si>
-    <t>NK Jadran Dekani</t>
-  </si>
-  <si>
     <t>Beltinci</t>
   </si>
   <si>
@@ -511,18 +514,15 @@
     <t>Hammarby TFF</t>
   </si>
   <si>
+    <t>Jesenice</t>
+  </si>
+  <si>
+    <t>Juventud De Las Piedras</t>
+  </si>
+  <si>
     <t>Uruguay Montevideo FC</t>
   </si>
   <si>
-    <t>Jesenice</t>
-  </si>
-  <si>
-    <t>Tabor Sezana</t>
-  </si>
-  <si>
-    <t>Juventud De Las Piedras</t>
-  </si>
-  <si>
     <t>Valladolid</t>
   </si>
   <si>
@@ -547,7 +547,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 11:19:20</t>
+    <t>2026-10-02 13:37:51</t>
   </si>
 </sst>
 </file>
@@ -879,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1129,79 +1129,79 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F2">
-        <v>4.2</v>
+        <v>1.39</v>
       </c>
       <c r="G2">
-        <v>5.9</v>
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>1.74</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>1.97</v>
+        <v>16</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="Q2">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>2.04</v>
+        <v>1.06</v>
       </c>
       <c r="W2">
-        <v>1.21</v>
+        <v>2.88</v>
       </c>
       <c r="X2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1210,10 +1210,10 @@
         <v>1000</v>
       </c>
       <c r="AC2">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
         <v>1000</v>
@@ -1249,58 +1249,58 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AR2">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="AU2">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AV2">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="AW2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="AY2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="BB2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="BC2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="BD2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1368,82 +1368,82 @@
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>4.2</v>
       </c>
       <c r="G3">
-        <v>2.58</v>
+        <v>5.9</v>
       </c>
       <c r="H3">
-        <v>2.78</v>
+        <v>1.75</v>
       </c>
       <c r="I3">
+        <v>1.96</v>
+      </c>
+      <c r="J3">
+        <v>3.65</v>
+      </c>
+      <c r="K3">
+        <v>4.9</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.03</v>
+      </c>
+      <c r="N3">
         <v>3.3</v>
       </c>
-      <c r="J3">
-        <v>3.8</v>
-      </c>
-      <c r="K3">
-        <v>5.1</v>
-      </c>
-      <c r="L3">
-        <v>1.01</v>
-      </c>
-      <c r="M3">
-        <v>1.01</v>
-      </c>
-      <c r="N3">
-        <v>4.1</v>
-      </c>
       <c r="O3">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="Q3">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>1.02</v>
+        <v>1.82</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="W3">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1452,10 +1452,10 @@
         <v>1000</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE3">
         <v>1000</v>
@@ -1488,61 +1488,61 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AR3">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AS3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AT3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AU3">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AV3">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AW3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AY3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AZ3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1610,82 +1610,82 @@
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="G4">
-        <v>3.9</v>
+        <v>2.58</v>
       </c>
       <c r="H4">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="I4">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
+        <v>1.24</v>
+      </c>
+      <c r="P4">
+        <v>2.12</v>
+      </c>
+      <c r="Q4">
+        <v>1.71</v>
+      </c>
+      <c r="R4">
+        <v>1.4</v>
+      </c>
+      <c r="S4">
+        <v>2.72</v>
+      </c>
+      <c r="T4">
+        <v>1.61</v>
+      </c>
+      <c r="U4">
         <v>1.02</v>
       </c>
-      <c r="P4">
-        <v>1.64</v>
-      </c>
-      <c r="Q4">
-        <v>2.18</v>
-      </c>
-      <c r="R4">
-        <v>1.18</v>
-      </c>
-      <c r="S4">
-        <v>3.95</v>
-      </c>
-      <c r="T4">
-        <v>1.89</v>
-      </c>
-      <c r="U4">
-        <v>1.01</v>
-      </c>
       <c r="V4">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="X4">
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1694,19 +1694,19 @@
         <v>1000</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
         <v>1000</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
         <v>1000</v>
       </c>
       <c r="AG4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
         <v>1000</v>
@@ -1715,13 +1715,13 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
         <v>1000</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -1730,61 +1730,61 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>1.45</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>1.62</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1855,79 +1855,79 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F5">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="G5">
-        <v>600</v>
+        <v>3.95</v>
       </c>
       <c r="H5">
-        <v>1.12</v>
+        <v>2.28</v>
       </c>
       <c r="I5">
-        <v>870</v>
+        <v>2.64</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.26</v>
+        <v>2.86</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="Q5">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V5">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="X5">
         <v>1000</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -1936,19 +1936,19 @@
         <v>1000</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>1000</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF5">
         <v>1000</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH5">
         <v>1000</v>
@@ -1957,13 +1957,13 @@
         <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK5">
         <v>1000</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM5">
         <v>1000</v>
@@ -1972,61 +1972,61 @@
         <v>1000</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2094,73 +2094,73 @@
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F6">
-        <v>2.22</v>
+        <v>1.12</v>
       </c>
       <c r="G6">
-        <v>2.44</v>
+        <v>600</v>
       </c>
       <c r="H6">
-        <v>3.2</v>
+        <v>1.12</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>870</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>1.12</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>1.26</v>
+      </c>
+      <c r="O6">
+        <v>1.33</v>
+      </c>
+      <c r="P6">
+        <v>1.26</v>
+      </c>
+      <c r="Q6">
+        <v>1.35</v>
+      </c>
+      <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
+        <v>2.6</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
         <v>1.04</v>
       </c>
-      <c r="N6">
-        <v>3.2</v>
-      </c>
-      <c r="O6">
-        <v>1.34</v>
-      </c>
-      <c r="P6">
-        <v>1.78</v>
-      </c>
-      <c r="Q6">
-        <v>2.02</v>
-      </c>
-      <c r="R6">
-        <v>1.28</v>
-      </c>
-      <c r="S6">
-        <v>2.3</v>
-      </c>
-      <c r="T6">
-        <v>1.77</v>
-      </c>
-      <c r="U6">
-        <v>1.97</v>
-      </c>
-      <c r="V6">
-        <v>1.38</v>
-      </c>
       <c r="W6">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2175,10 +2175,10 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
         <v>1000</v>
@@ -2217,58 +2217,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2336,73 +2336,73 @@
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>2.46</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>3.7</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>1.07</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2417,10 +2417,10 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7">
         <v>1000</v>
@@ -2459,58 +2459,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2578,19 +2578,19 @@
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F8">
         <v>1.1</v>
@@ -2617,22 +2617,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Q8">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S8">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2820,73 +2820,73 @@
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F9">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
-        <v>2.9</v>
+        <v>600</v>
       </c>
       <c r="H9">
-        <v>2.56</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
-        <v>2.96</v>
+        <v>870</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>1.12</v>
       </c>
       <c r="K9">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.25</v>
+      </c>
+      <c r="O9">
+        <v>1.18</v>
+      </c>
+      <c r="P9">
+        <v>1.25</v>
+      </c>
+      <c r="Q9">
+        <v>1.18</v>
+      </c>
+      <c r="R9">
+        <v>1.18</v>
+      </c>
+      <c r="S9">
+        <v>1.2</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
         <v>1.02</v>
       </c>
-      <c r="N9">
-        <v>4</v>
-      </c>
-      <c r="O9">
-        <v>1.25</v>
-      </c>
-      <c r="P9">
-        <v>2</v>
-      </c>
-      <c r="Q9">
-        <v>1.77</v>
-      </c>
-      <c r="R9">
-        <v>1.37</v>
-      </c>
-      <c r="S9">
-        <v>2.88</v>
-      </c>
-      <c r="T9">
-        <v>1.63</v>
-      </c>
-      <c r="U9">
-        <v>2.14</v>
-      </c>
-      <c r="V9">
-        <v>1.52</v>
-      </c>
       <c r="W9">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2904,7 +2904,7 @@
         <v>1000</v>
       </c>
       <c r="AC9">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
         <v>1000</v>
@@ -2943,64 +2943,64 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3062,73 +3062,73 @@
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F10">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="G10">
-        <v>2.46</v>
+        <v>2.94</v>
       </c>
       <c r="H10">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="I10">
+        <v>2.96</v>
+      </c>
+      <c r="J10">
+        <v>3.35</v>
+      </c>
+      <c r="K10">
+        <v>4.7</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.02</v>
+      </c>
+      <c r="N10">
         <v>4</v>
       </c>
-      <c r="J10">
-        <v>3.3</v>
-      </c>
-      <c r="K10">
-        <v>4.2</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>3.45</v>
-      </c>
       <c r="O10">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P10">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Q10">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="R10">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S10">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="W10">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3146,7 +3146,7 @@
         <v>1000</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD10">
         <v>1000</v>
@@ -3185,118 +3185,118 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH10">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>177</v>
@@ -3307,58 +3307,58 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F11">
-        <v>2.94</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
+        <v>2.44</v>
+      </c>
+      <c r="H11">
+        <v>3.3</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <v>3.3</v>
+      </c>
+      <c r="K11">
+        <v>4.2</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
         <v>3.45</v>
       </c>
-      <c r="H11">
-        <v>2.1</v>
-      </c>
-      <c r="I11">
-        <v>2.4</v>
-      </c>
-      <c r="J11">
-        <v>3.55</v>
-      </c>
-      <c r="K11">
-        <v>4.9</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>2.9</v>
-      </c>
       <c r="O11">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="P11">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="Q11">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="R11">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3367,10 +3367,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3481,64 +3481,64 @@
         <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="CB11" t="s">
         <v>177</v>
@@ -3546,37 +3546,37 @@
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F12">
-        <v>2.58</v>
+        <v>2.94</v>
       </c>
       <c r="G12">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="I12">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="J12">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K12">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3585,19 +3585,19 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="O12">
         <v>1.02</v>
       </c>
       <c r="P12">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="Q12">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="S12">
         <v>2.24</v>
@@ -3609,10 +3609,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="W12">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3791,178 +3791,178 @@
         <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F13">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="G13">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H13">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="I13">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q13">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="R13">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.24</v>
       </c>
       <c r="T13">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4033,178 +4033,178 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F14">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="G14">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="H14">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="I14">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J14">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N14">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="O14">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="P14">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q14">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="R14">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="S14">
-        <v>2.28</v>
+        <v>3.6</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4275,70 +4275,70 @@
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F15">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="G15">
-        <v>2.04</v>
+        <v>2.72</v>
       </c>
       <c r="H15">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="I15">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K15">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="O15">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="R15">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S15">
         <v>2.28</v>
       </c>
       <c r="T15">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4347,16 +4347,16 @@
         <v>1000</v>
       </c>
       <c r="Z15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
         <v>1000</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
         <v>1000</v>
@@ -4368,7 +4368,7 @@
         <v>1000</v>
       </c>
       <c r="AG15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
         <v>1000</v>
@@ -4389,7 +4389,7 @@
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
         <v>1000</v>
@@ -4398,7 +4398,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
         <v>1.03</v>
@@ -4407,46 +4407,46 @@
         <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
         <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
         <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4455,7 +4455,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
         <v>1.01</v>
@@ -4467,43 +4467,43 @@
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4517,235 +4517,235 @@
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F16">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="G16">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="H16">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I16">
+        <v>4.5</v>
+      </c>
+      <c r="J16">
+        <v>3.9</v>
+      </c>
+      <c r="K16">
+        <v>5.4</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.04</v>
+      </c>
+      <c r="N16">
+        <v>5.5</v>
+      </c>
+      <c r="O16">
+        <v>1.16</v>
+      </c>
+      <c r="P16">
+        <v>2.5</v>
+      </c>
+      <c r="Q16">
+        <v>1.49</v>
+      </c>
+      <c r="R16">
+        <v>1.6</v>
+      </c>
+      <c r="S16">
+        <v>2.28</v>
+      </c>
+      <c r="T16">
+        <v>1.54</v>
+      </c>
+      <c r="U16">
+        <v>2.46</v>
+      </c>
+      <c r="V16">
+        <v>1.28</v>
+      </c>
+      <c r="W16">
+        <v>1.95</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>42</v>
+      </c>
+      <c r="AA16">
+        <v>90</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>11</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>21</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>970</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.34</v>
+      </c>
+      <c r="AQ16">
+        <v>1.34</v>
+      </c>
+      <c r="AR16">
+        <v>1.3</v>
+      </c>
+      <c r="AS16">
+        <v>1.32</v>
+      </c>
+      <c r="AT16">
+        <v>1.34</v>
+      </c>
+      <c r="AU16">
+        <v>1.19</v>
+      </c>
+      <c r="AV16">
+        <v>1.34</v>
+      </c>
+      <c r="AW16">
+        <v>1.34</v>
+      </c>
+      <c r="AX16">
+        <v>1.34</v>
+      </c>
+      <c r="AY16">
+        <v>1.26</v>
+      </c>
+      <c r="AZ16">
+        <v>1.34</v>
+      </c>
+      <c r="BA16">
+        <v>1.34</v>
+      </c>
+      <c r="BB16">
+        <v>16</v>
+      </c>
+      <c r="BC16">
+        <v>1.34</v>
+      </c>
+      <c r="BD16">
+        <v>18.5</v>
+      </c>
+      <c r="BE16">
+        <v>1.34</v>
+      </c>
+      <c r="BF16">
+        <v>1.21</v>
+      </c>
+      <c r="BG16">
+        <v>19</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>12</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>6.8</v>
+      </c>
+      <c r="BO16">
+        <v>3.55</v>
+      </c>
+      <c r="BP16">
+        <v>17</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>29</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>10.5</v>
+      </c>
+      <c r="BU16">
         <v>5.1</v>
       </c>
-      <c r="J16">
-        <v>3.2</v>
-      </c>
-      <c r="K16">
-        <v>3.5</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.08</v>
-      </c>
-      <c r="N16">
-        <v>2.88</v>
-      </c>
-      <c r="O16">
-        <v>1.47</v>
-      </c>
-      <c r="P16">
-        <v>1.59</v>
-      </c>
-      <c r="Q16">
-        <v>2.3</v>
-      </c>
-      <c r="R16">
-        <v>1.2</v>
-      </c>
-      <c r="S16">
-        <v>4.4</v>
-      </c>
-      <c r="T16">
-        <v>1.99</v>
-      </c>
-      <c r="U16">
-        <v>1.73</v>
-      </c>
-      <c r="V16">
-        <v>1.25</v>
-      </c>
-      <c r="W16">
-        <v>1.82</v>
-      </c>
-      <c r="X16">
-        <v>11.5</v>
-      </c>
-      <c r="Y16">
-        <v>15</v>
-      </c>
-      <c r="Z16">
-        <v>46</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD16">
-        <v>24</v>
-      </c>
-      <c r="AE16">
-        <v>100</v>
-      </c>
-      <c r="AF16">
-        <v>14.5</v>
-      </c>
-      <c r="AG16">
-        <v>13.5</v>
-      </c>
-      <c r="AH16">
-        <v>29</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>36</v>
-      </c>
-      <c r="AK16">
-        <v>36</v>
-      </c>
-      <c r="AL16">
-        <v>75</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>30</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>7.2</v>
-      </c>
-      <c r="AQ16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR16">
-        <v>1.03</v>
-      </c>
-      <c r="AS16">
-        <v>1.03</v>
-      </c>
-      <c r="AT16">
-        <v>5.6</v>
-      </c>
-      <c r="AU16">
-        <v>5.9</v>
-      </c>
-      <c r="AV16">
-        <v>14</v>
-      </c>
-      <c r="AW16">
-        <v>1.03</v>
-      </c>
-      <c r="AX16">
-        <v>8.4</v>
-      </c>
-      <c r="AY16">
-        <v>8</v>
-      </c>
-      <c r="AZ16">
-        <v>14.5</v>
-      </c>
-      <c r="BA16">
-        <v>1.03</v>
-      </c>
-      <c r="BB16">
-        <v>16.5</v>
-      </c>
-      <c r="BC16">
-        <v>16.5</v>
-      </c>
-      <c r="BD16">
-        <v>1.03</v>
-      </c>
-      <c r="BE16">
-        <v>1.03</v>
-      </c>
-      <c r="BF16">
-        <v>15</v>
-      </c>
-      <c r="BG16">
-        <v>70</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.01</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.01</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.01</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.01</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.01</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.01</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.01</v>
-      </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
@@ -4759,178 +4759,178 @@
         <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F17">
-        <v>1.12</v>
+        <v>1.98</v>
       </c>
       <c r="G17">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="H17">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>870</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N17">
-        <v>1.24</v>
+        <v>2.72</v>
       </c>
       <c r="O17">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="P17">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q17">
-        <v>1.02</v>
+        <v>2.38</v>
       </c>
       <c r="R17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S17">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA17">
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI17">
         <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM17">
         <v>1000</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO17">
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4998,34 +4998,34 @@
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F18">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G18">
-        <v>600</v>
+        <v>2.58</v>
       </c>
       <c r="H18">
-        <v>1.1</v>
+        <v>2.14</v>
       </c>
       <c r="I18">
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5049,10 +5049,10 @@
         <v>1.02</v>
       </c>
       <c r="R18">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="S18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5064,7 +5064,7 @@
         <v>1.01</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5121,52 +5121,52 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5240,19 +5240,19 @@
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F19">
         <v>1.1</v>
@@ -5291,7 +5291,7 @@
         <v>1.02</v>
       </c>
       <c r="R19">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="S19">
         <v>1.02</v>
@@ -5363,52 +5363,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5482,241 +5482,241 @@
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F20">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G20">
         <v>1.65</v>
       </c>
       <c r="H20">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J20">
         <v>4.2</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q20">
         <v>1.78</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="CB20" t="s">
         <v>177</v>
@@ -5724,19 +5724,19 @@
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F21">
         <v>4.4</v>
@@ -5757,16 +5757,16 @@
         <v>5.3</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P21">
         <v>2.08</v>
@@ -5775,190 +5775,190 @@
         <v>1.56</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
         <v>177</v>
@@ -5969,238 +5969,238 @@
         <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F22">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="G22">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="H22">
-        <v>4.9</v>
+        <v>1.42</v>
       </c>
       <c r="I22">
-        <v>48</v>
+        <v>870</v>
       </c>
       <c r="J22">
-        <v>3.2</v>
+        <v>1.42</v>
       </c>
       <c r="K22">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P22">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q22">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
         <v>177</v>
@@ -6211,238 +6211,238 @@
         <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F23">
-        <v>1.42</v>
+        <v>2.76</v>
       </c>
       <c r="G23">
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>1.42</v>
+        <v>2.6</v>
       </c>
       <c r="I23">
-        <v>870</v>
+        <v>2.88</v>
       </c>
       <c r="J23">
-        <v>1.42</v>
+        <v>3.3</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P23">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="Q23">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
         <v>177</v>
@@ -6450,235 +6450,235 @@
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F24">
+        <v>1.5</v>
+      </c>
+      <c r="G24">
+        <v>1.8</v>
+      </c>
+      <c r="H24">
+        <v>4.9</v>
+      </c>
+      <c r="I24">
+        <v>10.5</v>
+      </c>
+      <c r="J24">
+        <v>3.2</v>
+      </c>
+      <c r="K24">
+        <v>7.8</v>
+      </c>
+      <c r="L24">
+        <v>1.38</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>2.96</v>
+      </c>
+      <c r="O24">
+        <v>1.01</v>
+      </c>
+      <c r="P24">
+        <v>1.05</v>
+      </c>
+      <c r="Q24">
+        <v>2.04</v>
+      </c>
+      <c r="R24">
+        <v>1.15</v>
+      </c>
+      <c r="S24">
+        <v>2.94</v>
+      </c>
+      <c r="T24">
+        <v>1.01</v>
+      </c>
+      <c r="U24">
+        <v>1.01</v>
+      </c>
+      <c r="V24">
         <v>1.1</v>
       </c>
-      <c r="G24">
-        <v>600</v>
-      </c>
-      <c r="H24">
-        <v>1.1</v>
-      </c>
-      <c r="I24">
-        <v>870</v>
-      </c>
-      <c r="J24">
-        <v>1.12</v>
-      </c>
-      <c r="K24">
-        <v>950</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>1.01</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>1.24</v>
-      </c>
-      <c r="Q24">
-        <v>1.02</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
       <c r="W24">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6692,34 +6692,34 @@
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F25">
-        <v>2.78</v>
+        <v>2.26</v>
       </c>
       <c r="G25">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="H25">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="I25">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="J25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K25">
         <v>3.6</v>
@@ -6728,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -6737,10 +6737,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q25">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6934,37 +6934,37 @@
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F26">
-        <v>2.26</v>
+        <v>1.25</v>
       </c>
       <c r="G26">
-        <v>2.42</v>
+        <v>1.28</v>
       </c>
       <c r="H26">
-        <v>3.4</v>
+        <v>12.5</v>
       </c>
       <c r="I26">
-        <v>3.6</v>
+        <v>16.5</v>
       </c>
       <c r="J26">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="K26">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6979,10 +6979,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="Q26">
-        <v>2.08</v>
+        <v>1.37</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7176,241 +7176,241 @@
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F27">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="G27">
-        <v>1.28</v>
+        <v>1.88</v>
       </c>
       <c r="H27">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="I27">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="J27">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
+        <v>3.55</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.13</v>
+      </c>
+      <c r="N27">
+        <v>2.62</v>
+      </c>
+      <c r="O27">
+        <v>1.56</v>
+      </c>
+      <c r="P27">
+        <v>1.56</v>
+      </c>
+      <c r="Q27">
+        <v>2.64</v>
+      </c>
+      <c r="R27">
+        <v>1.2</v>
+      </c>
+      <c r="S27">
+        <v>5.5</v>
+      </c>
+      <c r="T27">
+        <v>2.4</v>
+      </c>
+      <c r="U27">
+        <v>1.67</v>
+      </c>
+      <c r="V27">
+        <v>1.19</v>
+      </c>
+      <c r="W27">
+        <v>2.12</v>
+      </c>
+      <c r="X27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y27">
+        <v>14.5</v>
+      </c>
+      <c r="Z27">
+        <v>48</v>
+      </c>
+      <c r="AA27">
+        <v>230</v>
+      </c>
+      <c r="AB27">
+        <v>6.2</v>
+      </c>
+      <c r="AC27">
+        <v>8.4</v>
+      </c>
+      <c r="AD27">
+        <v>26</v>
+      </c>
+      <c r="AE27">
+        <v>140</v>
+      </c>
+      <c r="AF27">
+        <v>9.6</v>
+      </c>
+      <c r="AG27">
+        <v>11.5</v>
+      </c>
+      <c r="AH27">
+        <v>34</v>
+      </c>
+      <c r="AI27">
+        <v>150</v>
+      </c>
+      <c r="AJ27">
+        <v>22</v>
+      </c>
+      <c r="AK27">
+        <v>32</v>
+      </c>
+      <c r="AL27">
+        <v>75</v>
+      </c>
+      <c r="AM27">
+        <v>290</v>
+      </c>
+      <c r="AN27">
+        <v>23</v>
+      </c>
+      <c r="AO27">
+        <v>260</v>
+      </c>
+      <c r="AP27">
         <v>8</v>
       </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>3.2</v>
-      </c>
-      <c r="Q27">
-        <v>1.39</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27">
-        <v>0</v>
-      </c>
-      <c r="AI27">
-        <v>0</v>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>0</v>
-      </c>
-      <c r="AO27">
-        <v>0</v>
-      </c>
-      <c r="AP27">
-        <v>0</v>
-      </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
         <v>177</v>
@@ -7418,241 +7418,241 @@
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F28">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="G28">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="H28">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="I28">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J28">
+        <v>3.1</v>
+      </c>
+      <c r="K28">
         <v>3.4</v>
       </c>
-      <c r="K28">
-        <v>3.6</v>
-      </c>
       <c r="L28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q28">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="R28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL28">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AO28">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR28">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AU28">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW28">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AX28">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AY28">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BA28">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BB28">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BC28">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BD28">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BE28">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BF28">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BG28">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI28">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7660,37 +7660,37 @@
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F29">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="G29">
         <v>2.46</v>
       </c>
       <c r="H29">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I29">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J29">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K29">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7705,10 +7705,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="Q29">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -7902,43 +7902,43 @@
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F30">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="G30">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="H30">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="I30">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J30">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K30">
-        <v>3.8</v>
+        <v>48</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -7947,10 +7947,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="Q30">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8144,43 +8144,43 @@
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F31">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G31">
+        <v>2.94</v>
+      </c>
+      <c r="H31">
+        <v>2.96</v>
+      </c>
+      <c r="I31">
         <v>3.65</v>
       </c>
-      <c r="H31">
-        <v>2.28</v>
-      </c>
-      <c r="I31">
-        <v>2.9</v>
-      </c>
       <c r="J31">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="K31">
-        <v>48</v>
+        <v>3.55</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -8189,10 +8189,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q31">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8386,37 +8386,37 @@
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32">
-        <v>2.64</v>
+        <v>1.5</v>
       </c>
       <c r="G32">
-        <v>2.94</v>
+        <v>1.89</v>
       </c>
       <c r="H32">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="I32">
-        <v>3.65</v>
+        <v>870</v>
       </c>
       <c r="J32">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="K32">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -8431,10 +8431,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.56</v>
+        <v>2.4</v>
       </c>
       <c r="Q32">
-        <v>2.48</v>
+        <v>1.38</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8623,248 +8623,6 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" spans="1:80">
-      <c r="A33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>144</v>
-      </c>
-      <c r="E33" t="s">
-        <v>176</v>
-      </c>
-      <c r="F33">
-        <v>1.5</v>
-      </c>
-      <c r="G33">
-        <v>1.89</v>
-      </c>
-      <c r="H33">
-        <v>4.3</v>
-      </c>
-      <c r="I33">
-        <v>870</v>
-      </c>
-      <c r="J33">
-        <v>3.8</v>
-      </c>
-      <c r="K33">
-        <v>10</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>2.4</v>
-      </c>
-      <c r="Q33">
-        <v>1.38</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-      <c r="AC33">
-        <v>0</v>
-      </c>
-      <c r="AD33">
-        <v>0</v>
-      </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
-      <c r="AF33">
-        <v>0</v>
-      </c>
-      <c r="AG33">
-        <v>0</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AI33">
-        <v>0</v>
-      </c>
-      <c r="AJ33">
-        <v>0</v>
-      </c>
-      <c r="AK33">
-        <v>0</v>
-      </c>
-      <c r="AL33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>0</v>
-      </c>
-      <c r="AN33">
-        <v>0</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>0</v>
-      </c>
-      <c r="AQ33">
-        <v>0</v>
-      </c>
-      <c r="AR33">
-        <v>0</v>
-      </c>
-      <c r="AS33">
-        <v>0</v>
-      </c>
-      <c r="AT33">
-        <v>0</v>
-      </c>
-      <c r="AU33">
-        <v>0</v>
-      </c>
-      <c r="AV33">
-        <v>0</v>
-      </c>
-      <c r="AW33">
-        <v>0</v>
-      </c>
-      <c r="AX33">
-        <v>0</v>
-      </c>
-      <c r="AY33">
-        <v>0</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>0</v>
-      </c>
-      <c r="BC33">
-        <v>0</v>
-      </c>
-      <c r="BD33">
-        <v>0</v>
-      </c>
-      <c r="BE33">
-        <v>0</v>
-      </c>
-      <c r="BF33">
-        <v>0</v>
-      </c>
-      <c r="BG33">
-        <v>0</v>
-      </c>
-      <c r="BH33">
-        <v>0</v>
-      </c>
-      <c r="BI33">
-        <v>0</v>
-      </c>
-      <c r="BJ33">
-        <v>0</v>
-      </c>
-      <c r="BK33">
-        <v>0</v>
-      </c>
-      <c r="BL33">
-        <v>0</v>
-      </c>
-      <c r="BM33">
-        <v>0</v>
-      </c>
-      <c r="BN33">
-        <v>0</v>
-      </c>
-      <c r="BO33">
-        <v>0</v>
-      </c>
-      <c r="BP33">
-        <v>0</v>
-      </c>
-      <c r="BQ33">
-        <v>0</v>
-      </c>
-      <c r="BR33">
-        <v>0</v>
-      </c>
-      <c r="BS33">
-        <v>0</v>
-      </c>
-      <c r="BT33">
-        <v>0</v>
-      </c>
-      <c r="BU33">
-        <v>0</v>
-      </c>
-      <c r="BV33">
-        <v>0</v>
-      </c>
-      <c r="BW33">
-        <v>0</v>
-      </c>
-      <c r="BX33">
-        <v>0</v>
-      </c>
-      <c r="BY33">
-        <v>0</v>
-      </c>
-      <c r="BZ33">
-        <v>0</v>
-      </c>
-      <c r="CA33">
-        <v>0</v>
-      </c>
-      <c r="CB33" t="s">
         <v>177</v>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -547,7 +547,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 13:37:51</t>
+    <t>2026-10-02 15:56:54</t>
   </si>
 </sst>
 </file>
@@ -1147,7 +1147,7 @@
         <v>1.53</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>16</v>
@@ -1156,7 +1156,7 @@
         <v>4.5</v>
       </c>
       <c r="K2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1177,7 +1177,7 @@
         <v>1.72</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
         <v>2.84</v>
@@ -1867,79 +1867,79 @@
         <v>149</v>
       </c>
       <c r="F5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H5">
         <v>2.28</v>
       </c>
       <c r="I5">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J5">
         <v>3.1</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
         <v>2.86</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P5">
         <v>1.64</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U5">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
         <v>1.34</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z5">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE5">
         <v>40</v>
@@ -1948,7 +1948,7 @@
         <v>1000</v>
       </c>
       <c r="AG5">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
         <v>1000</v>
@@ -1975,55 +1975,55 @@
         <v>36</v>
       </c>
       <c r="AP5">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AQ5">
-        <v>1.45</v>
+        <v>7</v>
       </c>
       <c r="AR5">
-        <v>10</v>
+        <v>1.66</v>
       </c>
       <c r="AS5">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AT5">
-        <v>7.8</v>
+        <v>1.54</v>
       </c>
       <c r="AU5">
-        <v>1.41</v>
+        <v>5.5</v>
       </c>
       <c r="AV5">
-        <v>8.199999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="AW5">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AX5">
         <v>16</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>1.66</v>
       </c>
       <c r="AZ5">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BA5">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BB5">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BC5">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BD5">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="BE5">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BF5">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BG5">
         <v>19</v>
@@ -2133,7 +2133,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O6">
         <v>1.33</v>
@@ -2357,13 +2357,13 @@
         <v>2.46</v>
       </c>
       <c r="H7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I7">
         <v>3.7</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
         <v>4.1</v>
@@ -2384,25 +2384,25 @@
         <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R7">
         <v>1.28</v>
       </c>
       <c r="S7">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
         <v>1.77</v>
       </c>
       <c r="U7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
         <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2859,16 +2859,16 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O9">
         <v>1.18</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -3594,7 +3594,7 @@
         <v>2.4</v>
       </c>
       <c r="Q12">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
         <v>1.56</v>
@@ -4051,16 +4051,16 @@
         <v>2.84</v>
       </c>
       <c r="H14">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I14">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J14">
         <v>3.4</v>
       </c>
       <c r="K14">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14">
         <v>1.41</v>
@@ -4093,7 +4093,7 @@
         <v>2.16</v>
       </c>
       <c r="V14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
         <v>1.54</v>
@@ -4105,10 +4105,10 @@
         <v>11.5</v>
       </c>
       <c r="Z14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB14">
         <v>11.5</v>
@@ -4159,7 +4159,7 @@
         <v>10</v>
       </c>
       <c r="AR14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS14">
         <v>7.4</v>
@@ -4168,13 +4168,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV14">
         <v>11</v>
       </c>
       <c r="AW14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX14">
         <v>15</v>
@@ -4189,10 +4189,10 @@
         <v>7.6</v>
       </c>
       <c r="BB14">
+        <v>7.4</v>
+      </c>
+      <c r="BC14">
         <v>7.2</v>
-      </c>
-      <c r="BC14">
-        <v>7</v>
       </c>
       <c r="BD14">
         <v>7.6</v>
@@ -4296,7 +4296,7 @@
         <v>2.62</v>
       </c>
       <c r="I15">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
         <v>3.8</v>
@@ -4308,7 +4308,7 @@
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
         <v>4.4</v>
@@ -4538,13 +4538,13 @@
         <v>3.5</v>
       </c>
       <c r="I16">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J16">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4553,7 +4553,7 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O16">
         <v>1.16</v>
@@ -4562,7 +4562,7 @@
         <v>2.5</v>
       </c>
       <c r="Q16">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R16">
         <v>1.6</v>
@@ -4571,7 +4571,7 @@
         <v>2.28</v>
       </c>
       <c r="T16">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="U16">
         <v>2.46</v>
@@ -4580,7 +4580,7 @@
         <v>1.28</v>
       </c>
       <c r="W16">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4652,7 +4652,7 @@
         <v>1.34</v>
       </c>
       <c r="AU16">
-        <v>1.19</v>
+        <v>8.6</v>
       </c>
       <c r="AV16">
         <v>1.34</v>
@@ -4694,19 +4694,19 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BJ16">
         <v>12</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BN16">
         <v>6.8</v>
@@ -4718,13 +4718,13 @@
         <v>17</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BR16">
         <v>29</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BT16">
         <v>10.5</v>
@@ -4736,19 +4736,19 @@
         <v>38</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BX16">
         <v>44</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BZ16">
         <v>20</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="CB16" t="s">
         <v>177</v>
@@ -4774,7 +4774,7 @@
         <v>1.98</v>
       </c>
       <c r="G17">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -4786,7 +4786,7 @@
         <v>3.2</v>
       </c>
       <c r="K17">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4801,22 +4801,22 @@
         <v>1.47</v>
       </c>
       <c r="P17">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Q17">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
         <v>1.2</v>
       </c>
       <c r="S17">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T17">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="U17">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="V17">
         <v>1.25</v>
@@ -4849,10 +4849,10 @@
         <v>100</v>
       </c>
       <c r="AF17">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG17">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH17">
         <v>29</v>
@@ -4900,7 +4900,7 @@
         <v>14</v>
       </c>
       <c r="AW17">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="AX17">
         <v>8.800000000000001</v>
@@ -4912,7 +4912,7 @@
         <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>3.65</v>
+        <v>2.86</v>
       </c>
       <c r="BB17">
         <v>16.5</v>
@@ -4921,10 +4921,10 @@
         <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="BE17">
-        <v>3.65</v>
+        <v>2.86</v>
       </c>
       <c r="BF17">
         <v>15</v>
@@ -5019,13 +5019,13 @@
         <v>2.58</v>
       </c>
       <c r="H18">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="I18">
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5040,13 +5040,13 @@
         <v>1.24</v>
       </c>
       <c r="O18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P18">
         <v>1.24</v>
       </c>
       <c r="Q18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="R18">
         <v>1.18</v>
@@ -5061,7 +5061,7 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W18">
         <v>1.65</v>
@@ -5282,31 +5282,31 @@
         <v>1.24</v>
       </c>
       <c r="O19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P19">
         <v>1.24</v>
       </c>
       <c r="Q19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
+        <v>1.04</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
         <v>1.02</v>
       </c>
-      <c r="T19">
-        <v>1.01</v>
-      </c>
-      <c r="U19">
-        <v>1.01</v>
-      </c>
-      <c r="V19">
-        <v>1.01</v>
-      </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5518,7 +5518,7 @@
         <v>1.35</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
         <v>3.9</v>
@@ -5536,7 +5536,7 @@
         <v>1.39</v>
       </c>
       <c r="S20">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="T20">
         <v>1.89</v>
@@ -5766,13 +5766,13 @@
         <v>2.42</v>
       </c>
       <c r="O21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P21">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q21">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="R21">
         <v>1.42</v>
@@ -5981,19 +5981,19 @@
         <v>166</v>
       </c>
       <c r="F22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G22">
         <v>600</v>
       </c>
       <c r="H22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="I22">
         <v>870</v>
       </c>
       <c r="J22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="K22">
         <v>950</v>
@@ -6005,13 +6005,13 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P22">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q22">
         <v>1.03</v>
@@ -6020,7 +6020,7 @@
         <v>1.18</v>
       </c>
       <c r="S22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6029,7 +6029,7 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W22">
         <v>1.05</v>
@@ -6223,10 +6223,10 @@
         <v>167</v>
       </c>
       <c r="F23">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H23">
         <v>2.6</v>
@@ -6241,25 +6241,25 @@
         <v>3.6</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N23">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O23">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P23">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q23">
         <v>2.04</v>
       </c>
       <c r="R23">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S23">
         <v>3.55</v>
@@ -6274,7 +6274,7 @@
         <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6331,7 +6331,7 @@
         <v>34</v>
       </c>
       <c r="AP23">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AQ23">
         <v>7.8</v>
@@ -6340,10 +6340,10 @@
         <v>12.5</v>
       </c>
       <c r="AS23">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AT23">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU23">
         <v>6</v>
@@ -6364,22 +6364,22 @@
         <v>12.5</v>
       </c>
       <c r="BA23">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BB23">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BC23">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BD23">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BE23">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BF23">
-        <v>20</v>
+        <v>2.98</v>
       </c>
       <c r="BG23">
         <v>17.5</v>
@@ -6471,7 +6471,7 @@
         <v>1.8</v>
       </c>
       <c r="H24">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I24">
         <v>10.5</v>
@@ -6480,7 +6480,7 @@
         <v>3.2</v>
       </c>
       <c r="K24">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="L24">
         <v>1.38</v>
@@ -6489,19 +6489,19 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="O24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P24">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="Q24">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R24">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S24">
         <v>2.94</v>
@@ -6513,7 +6513,7 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W24">
         <v>2.24</v>
@@ -6710,223 +6710,223 @@
         <v>2.26</v>
       </c>
       <c r="G25">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H25">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I25">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J25">
         <v>3.35</v>
       </c>
       <c r="K25">
+        <v>3.55</v>
+      </c>
+      <c r="L25">
+        <v>1.44</v>
+      </c>
+      <c r="M25">
+        <v>1.08</v>
+      </c>
+      <c r="N25">
+        <v>3.25</v>
+      </c>
+      <c r="O25">
+        <v>1.35</v>
+      </c>
+      <c r="P25">
+        <v>1.8</v>
+      </c>
+      <c r="Q25">
+        <v>2.1</v>
+      </c>
+      <c r="R25">
+        <v>1.28</v>
+      </c>
+      <c r="S25">
+        <v>3.4</v>
+      </c>
+      <c r="T25">
+        <v>1.75</v>
+      </c>
+      <c r="U25">
+        <v>2</v>
+      </c>
+      <c r="V25">
+        <v>1.37</v>
+      </c>
+      <c r="W25">
+        <v>1.72</v>
+      </c>
+      <c r="X25">
+        <v>28</v>
+      </c>
+      <c r="Y25">
+        <v>27</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>90</v>
+      </c>
+      <c r="AB25">
+        <v>970</v>
+      </c>
+      <c r="AC25">
+        <v>11</v>
+      </c>
+      <c r="AD25">
+        <v>970</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>36</v>
+      </c>
+      <c r="AG25">
+        <v>22</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>8.6</v>
+      </c>
+      <c r="AQ25">
+        <v>8.6</v>
+      </c>
+      <c r="AR25">
+        <v>1.5</v>
+      </c>
+      <c r="AS25">
+        <v>1.47</v>
+      </c>
+      <c r="AT25">
+        <v>6.8</v>
+      </c>
+      <c r="AU25">
+        <v>5.7</v>
+      </c>
+      <c r="AV25">
+        <v>9.6</v>
+      </c>
+      <c r="AW25">
+        <v>1.5</v>
+      </c>
+      <c r="AX25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY25">
+        <v>8</v>
+      </c>
+      <c r="AZ25">
+        <v>11.5</v>
+      </c>
+      <c r="BA25">
+        <v>1.5</v>
+      </c>
+      <c r="BB25">
+        <v>1.5</v>
+      </c>
+      <c r="BC25">
+        <v>1.5</v>
+      </c>
+      <c r="BD25">
+        <v>1.5</v>
+      </c>
+      <c r="BE25">
+        <v>1.5</v>
+      </c>
+      <c r="BF25">
+        <v>15.5</v>
+      </c>
+      <c r="BG25">
+        <v>1.5</v>
+      </c>
+      <c r="BH25">
         <v>3.6</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>1.79</v>
-      </c>
-      <c r="Q25">
-        <v>2.08</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>0</v>
-      </c>
-      <c r="BC25">
-        <v>0</v>
-      </c>
-      <c r="BD25">
-        <v>0</v>
-      </c>
-      <c r="BE25">
-        <v>0</v>
-      </c>
-      <c r="BF25">
-        <v>0</v>
-      </c>
-      <c r="BG25">
-        <v>0</v>
-      </c>
-      <c r="BH25">
-        <v>0</v>
-      </c>
       <c r="BI25">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="CB25" t="s">
         <v>177</v>
@@ -6958,7 +6958,7 @@
         <v>12.5</v>
       </c>
       <c r="I26">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J26">
         <v>7.2</v>
@@ -6967,208 +6967,208 @@
         <v>8</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P26">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="Q26">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7191,7 +7191,7 @@
         <v>171</v>
       </c>
       <c r="F27">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G27">
         <v>1.88</v>
@@ -7209,7 +7209,7 @@
         <v>3.55</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M27">
         <v>1.13</v>
@@ -7362,7 +7362,7 @@
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BL27">
         <v>1000</v>
@@ -7463,7 +7463,7 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q28">
         <v>2.26</v>
@@ -7675,7 +7675,7 @@
         <v>173</v>
       </c>
       <c r="F29">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G29">
         <v>2.46</v>
@@ -8162,19 +8162,19 @@
         <v>2.64</v>
       </c>
       <c r="G31">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H31">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I31">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J31">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="K31">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L31">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -547,7 +547,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 15:56:54</t>
+    <t>2026-10-02 18:14:31</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1398,7 @@
         <v>3.65</v>
       </c>
       <c r="K3">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1428,7 +1428,7 @@
         <v>1.82</v>
       </c>
       <c r="U3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V3">
         <v>2.04</v>
@@ -1437,7 +1437,7 @@
         <v>1.21</v>
       </c>
       <c r="X3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
         <v>970</v>
@@ -1494,55 +1494,55 @@
         <v>1.4</v>
       </c>
       <c r="AQ3">
+        <v>1.26</v>
+      </c>
+      <c r="AR3">
         <v>1.3</v>
       </c>
-      <c r="AR3">
-        <v>1.35</v>
-      </c>
       <c r="AS3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AT3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AU3">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AV3">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AW3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AX3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AY3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AZ3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BA3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BB3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BC3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BD3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BE3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BF3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BG3">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1870,25 +1870,25 @@
         <v>3.25</v>
       </c>
       <c r="G5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>2.28</v>
       </c>
       <c r="I5">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J5">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
         <v>2.86</v>
@@ -1903,22 +1903,22 @@
         <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
         <v>1.91</v>
       </c>
       <c r="U5">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X5">
         <v>970</v>
@@ -1927,7 +1927,7 @@
         <v>970</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -1942,7 +1942,7 @@
         <v>24</v>
       </c>
       <c r="AE5">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
         <v>1000</v>
@@ -1957,13 +1957,13 @@
         <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
         <v>1000</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
         <v>1000</v>
@@ -1972,61 +1972,61 @@
         <v>1000</v>
       </c>
       <c r="AO5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>7</v>
+        <v>1.46</v>
       </c>
       <c r="AR5">
-        <v>1.66</v>
+        <v>9</v>
       </c>
       <c r="AS5">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AT5">
-        <v>1.54</v>
+        <v>7.6</v>
       </c>
       <c r="AU5">
         <v>5.5</v>
       </c>
       <c r="AV5">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AW5">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AX5">
-        <v>16</v>
+        <v>1.53</v>
       </c>
       <c r="AY5">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AZ5">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BA5">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BB5">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BC5">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BD5">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="BE5">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BF5">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BG5">
-        <v>19</v>
+        <v>1.53</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2133,13 +2133,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O6">
         <v>1.33</v>
       </c>
       <c r="P6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
         <v>1.35</v>
@@ -2351,7 +2351,7 @@
         <v>151</v>
       </c>
       <c r="F7">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G7">
         <v>2.46</v>
@@ -2360,13 +2360,13 @@
         <v>3.25</v>
       </c>
       <c r="I7">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J7">
         <v>3.5</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
         <v>1.34</v>
@@ -2375,19 +2375,19 @@
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
         <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
         <v>2.04</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
         <v>3.5</v>
@@ -2399,7 +2399,7 @@
         <v>1.98</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
         <v>1.69</v>
@@ -2859,16 +2859,16 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O9">
         <v>1.18</v>
       </c>
       <c r="P9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -3080,7 +3080,7 @@
         <v>2.52</v>
       </c>
       <c r="G10">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H10">
         <v>2.56</v>
@@ -3128,7 +3128,7 @@
         <v>1.52</v>
       </c>
       <c r="W10">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -4069,7 +4069,7 @@
         <v>1.07</v>
       </c>
       <c r="N14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O14">
         <v>1.33</v>
@@ -4108,7 +4108,7 @@
         <v>19.5</v>
       </c>
       <c r="AA14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB14">
         <v>11.5</v>
@@ -4120,7 +4120,7 @@
         <v>13</v>
       </c>
       <c r="AE14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF14">
         <v>22</v>
@@ -4132,7 +4132,7 @@
         <v>18.5</v>
       </c>
       <c r="AI14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ14">
         <v>46</v>
@@ -4162,7 +4162,7 @@
         <v>16</v>
       </c>
       <c r="AS14">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT14">
         <v>9.800000000000001</v>
@@ -4174,31 +4174,31 @@
         <v>11</v>
       </c>
       <c r="AW14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX14">
         <v>15</v>
       </c>
       <c r="AY14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14">
         <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB14">
+        <v>7.8</v>
+      </c>
+      <c r="BC14">
         <v>7.4</v>
       </c>
-      <c r="BC14">
-        <v>7.2</v>
-      </c>
       <c r="BD14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE14">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14">
         <v>19.5</v>
@@ -4296,10 +4296,10 @@
         <v>2.62</v>
       </c>
       <c r="I15">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4335,7 +4335,7 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
         <v>1.58</v>
@@ -4535,13 +4535,13 @@
         <v>2.06</v>
       </c>
       <c r="H16">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I16">
         <v>4.6</v>
       </c>
       <c r="J16">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
         <v>5.3</v>
@@ -4550,10 +4550,10 @@
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O16">
         <v>1.16</v>
@@ -4562,7 +4562,7 @@
         <v>2.5</v>
       </c>
       <c r="Q16">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="R16">
         <v>1.6</v>
@@ -4571,16 +4571,16 @@
         <v>2.28</v>
       </c>
       <c r="T16">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="U16">
         <v>2.46</v>
       </c>
       <c r="V16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W16">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4589,16 +4589,16 @@
         <v>1000</v>
       </c>
       <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
         <v>42</v>
       </c>
-      <c r="AA16">
-        <v>90</v>
-      </c>
-      <c r="AB16">
-        <v>1000</v>
-      </c>
       <c r="AC16">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD16">
         <v>1000</v>
@@ -4637,118 +4637,118 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AQ16">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AR16">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AS16">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AT16">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AU16">
-        <v>8.6</v>
+        <v>1.18</v>
       </c>
       <c r="AV16">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AW16">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AX16">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AY16">
+        <v>1.19</v>
+      </c>
+      <c r="AZ16">
         <v>1.26</v>
       </c>
-      <c r="AZ16">
-        <v>1.34</v>
-      </c>
       <c r="BA16">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="BB16">
-        <v>16</v>
+        <v>1.26</v>
       </c>
       <c r="BC16">
-        <v>1.34</v>
+        <v>10.5</v>
       </c>
       <c r="BD16">
-        <v>18.5</v>
+        <v>1.26</v>
       </c>
       <c r="BE16">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="BF16">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BG16">
-        <v>19</v>
+        <v>1.26</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
         <v>177</v>
@@ -4801,34 +4801,34 @@
         <v>1.47</v>
       </c>
       <c r="P17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q17">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S17">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T17">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="U17">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V17">
         <v>1.25</v>
       </c>
       <c r="W17">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X17">
         <v>970</v>
       </c>
       <c r="Y17">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z17">
         <v>46</v>
@@ -4837,19 +4837,19 @@
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC17">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD17">
         <v>24</v>
       </c>
       <c r="AE17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF17">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG17">
         <v>970</v>
@@ -4879,58 +4879,58 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>7.6</v>
+        <v>2.18</v>
       </c>
       <c r="AQ17">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR17">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AS17">
-        <v>2.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT17">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="AU17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV17">
-        <v>14</v>
+        <v>1.73</v>
       </c>
       <c r="AW17">
+        <v>1.7</v>
+      </c>
+      <c r="AX17">
         <v>2.78</v>
       </c>
-      <c r="AX17">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AY17">
-        <v>8</v>
+        <v>1.87</v>
       </c>
       <c r="AZ17">
-        <v>14.5</v>
+        <v>1.75</v>
       </c>
       <c r="BA17">
-        <v>2.86</v>
+        <v>1.73</v>
       </c>
       <c r="BB17">
-        <v>16.5</v>
+        <v>1.78</v>
       </c>
       <c r="BC17">
-        <v>16.5</v>
+        <v>1.78</v>
       </c>
       <c r="BD17">
-        <v>2.76</v>
+        <v>1.69</v>
       </c>
       <c r="BE17">
-        <v>2.86</v>
+        <v>1.73</v>
       </c>
       <c r="BF17">
-        <v>15</v>
+        <v>1.76</v>
       </c>
       <c r="BG17">
-        <v>2.86</v>
+        <v>1.73</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5025,7 +5025,7 @@
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5521,7 +5521,7 @@
         <v>1.05</v>
       </c>
       <c r="N20">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O20">
         <v>1.27</v>
@@ -5530,13 +5530,13 @@
         <v>2.1</v>
       </c>
       <c r="Q20">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R20">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S20">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T20">
         <v>1.89</v>
@@ -5659,13 +5659,13 @@
         <v>9.6</v>
       </c>
       <c r="BH20">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>3.15</v>
+        <v>1.28</v>
       </c>
       <c r="BJ20">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
         <v>7.8</v>
@@ -5674,49 +5674,49 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>4.3</v>
+        <v>1.88</v>
       </c>
       <c r="BN20">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>3.5</v>
+        <v>1.34</v>
       </c>
       <c r="BP20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>7.4</v>
+        <v>1.88</v>
       </c>
       <c r="BR20">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>3.9</v>
+        <v>1.88</v>
       </c>
       <c r="BT20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>7.4</v>
+        <v>1.88</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>4.1</v>
+        <v>1.88</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>4.1</v>
+        <v>1.88</v>
       </c>
       <c r="BZ20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>3.75</v>
+        <v>1.88</v>
       </c>
       <c r="CB20" t="s">
         <v>177</v>
@@ -5981,19 +5981,19 @@
         <v>166</v>
       </c>
       <c r="F22">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G22">
         <v>600</v>
       </c>
       <c r="H22">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="I22">
         <v>870</v>
       </c>
       <c r="J22">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="K22">
         <v>950</v>
@@ -6005,13 +6005,13 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O22">
         <v>1.02</v>
       </c>
       <c r="P22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q22">
         <v>1.03</v>
@@ -6223,7 +6223,7 @@
         <v>167</v>
       </c>
       <c r="F23">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G23">
         <v>3.1</v>
@@ -6232,7 +6232,7 @@
         <v>2.6</v>
       </c>
       <c r="I23">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="J23">
         <v>3.3</v>
@@ -6244,145 +6244,145 @@
         <v>1.34</v>
       </c>
       <c r="M23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O23">
         <v>1.34</v>
       </c>
       <c r="P23">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q23">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S23">
         <v>3.55</v>
       </c>
       <c r="T23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V23">
         <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X23">
         <v>1000</v>
       </c>
       <c r="Y23">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z23">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD23">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH23">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="AQ23">
-        <v>7.8</v>
+        <v>1.24</v>
       </c>
       <c r="AR23">
-        <v>12.5</v>
+        <v>1.32</v>
       </c>
       <c r="AS23">
-        <v>3</v>
+        <v>1.32</v>
       </c>
       <c r="AT23">
-        <v>8.800000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="AU23">
-        <v>6</v>
+        <v>1.17</v>
       </c>
       <c r="AV23">
-        <v>9.199999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="AW23">
-        <v>19</v>
+        <v>1.32</v>
       </c>
       <c r="AX23">
-        <v>14</v>
+        <v>1.32</v>
       </c>
       <c r="AY23">
-        <v>9.199999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="AZ23">
-        <v>12.5</v>
+        <v>1.32</v>
       </c>
       <c r="BA23">
-        <v>3.05</v>
+        <v>1.32</v>
       </c>
       <c r="BB23">
-        <v>3.05</v>
+        <v>1.32</v>
       </c>
       <c r="BC23">
-        <v>3</v>
+        <v>1.32</v>
       </c>
       <c r="BD23">
-        <v>3.05</v>
+        <v>1.32</v>
       </c>
       <c r="BE23">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="BF23">
-        <v>2.98</v>
+        <v>1.32</v>
       </c>
       <c r="BG23">
-        <v>17.5</v>
+        <v>1.32</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6468,7 +6468,7 @@
         <v>1.5</v>
       </c>
       <c r="G24">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="H24">
         <v>5.4</v>
@@ -6516,7 +6516,7 @@
         <v>1.11</v>
       </c>
       <c r="W24">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6710,19 +6710,19 @@
         <v>2.26</v>
       </c>
       <c r="G25">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H25">
         <v>3.4</v>
       </c>
       <c r="I25">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J25">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K25">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L25">
         <v>1.44</v>
@@ -6737,34 +6737,34 @@
         <v>1.35</v>
       </c>
       <c r="P25">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q25">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R25">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S25">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T25">
         <v>1.75</v>
       </c>
       <c r="U25">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V25">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X25">
         <v>28</v>
       </c>
       <c r="Y25">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Z25">
         <v>1000</v>
@@ -6773,7 +6773,7 @@
         <v>90</v>
       </c>
       <c r="AB25">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC25">
         <v>11</v>
@@ -6785,7 +6785,7 @@
         <v>1000</v>
       </c>
       <c r="AF25">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
         <v>22</v>
@@ -6809,7 +6809,7 @@
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO25">
         <v>1000</v>
@@ -6821,10 +6821,10 @@
         <v>8.6</v>
       </c>
       <c r="AR25">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AS25">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AT25">
         <v>6.8</v>
@@ -6836,7 +6836,7 @@
         <v>9.6</v>
       </c>
       <c r="AW25">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AX25">
         <v>9.199999999999999</v>
@@ -6848,85 +6848,85 @@
         <v>11.5</v>
       </c>
       <c r="BA25">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="BB25">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="BC25">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="BD25">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="BE25">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="BF25">
-        <v>15.5</v>
+        <v>1.62</v>
       </c>
       <c r="BG25">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="BH25">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
         <v>2.72</v>
       </c>
       <c r="BJ25">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>3.95</v>
+        <v>1.97</v>
       </c>
       <c r="BP25">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>13</v>
+        <v>2.94</v>
       </c>
       <c r="BR25">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>5.1</v>
+        <v>2.14</v>
       </c>
       <c r="BV25">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
         <v>177</v>
@@ -6958,7 +6958,7 @@
         <v>12.5</v>
       </c>
       <c r="I26">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="J26">
         <v>7.2</v>
@@ -6976,10 +6976,10 @@
         <v>6.2</v>
       </c>
       <c r="O26">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P26">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q26">
         <v>1.35</v>
@@ -6988,19 +6988,19 @@
         <v>1.8</v>
       </c>
       <c r="S26">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="T26">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U26">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V26">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W26">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7015,7 +7015,7 @@
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AC26">
         <v>1000</v>
@@ -7042,7 +7042,7 @@
         <v>970</v>
       </c>
       <c r="AK26">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL26">
         <v>1000</v>
@@ -7051,22 +7051,22 @@
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AO26">
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AQ26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AR26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AS26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AT26">
         <v>8.800000000000001</v>
@@ -7075,22 +7075,22 @@
         <v>10.5</v>
       </c>
       <c r="AV26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AW26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AX26">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AY26">
         <v>7.8</v>
       </c>
       <c r="AZ26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="BA26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="BB26">
         <v>7.4</v>
@@ -7099,40 +7099,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BD26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="BE26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="BF26">
         <v>3</v>
       </c>
       <c r="BG26">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BP26">
         <v>1000</v>
@@ -7144,31 +7144,31 @@
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7191,13 +7191,13 @@
         <v>171</v>
       </c>
       <c r="F27">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G27">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="H27">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I27">
         <v>6.2</v>
@@ -7206,7 +7206,7 @@
         <v>3.4</v>
       </c>
       <c r="K27">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
         <v>1.56</v>
@@ -7218,7 +7218,7 @@
         <v>2.62</v>
       </c>
       <c r="O27">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P27">
         <v>1.56</v>
@@ -7233,7 +7233,7 @@
         <v>5.5</v>
       </c>
       <c r="T27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U27">
         <v>1.67</v>
@@ -7242,7 +7242,7 @@
         <v>1.19</v>
       </c>
       <c r="W27">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X27">
         <v>8.800000000000001</v>
@@ -7281,7 +7281,7 @@
         <v>150</v>
       </c>
       <c r="AJ27">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK27">
         <v>32</v>
@@ -7293,7 +7293,7 @@
         <v>290</v>
       </c>
       <c r="AN27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO27">
         <v>260</v>
@@ -7305,10 +7305,10 @@
         <v>11.5</v>
       </c>
       <c r="AR27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT27">
         <v>5.6</v>
@@ -7320,7 +7320,7 @@
         <v>20</v>
       </c>
       <c r="AW27">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX27">
         <v>8.6</v>
@@ -7329,7 +7329,7 @@
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BA27">
         <v>9.800000000000001</v>
@@ -7341,16 +7341,16 @@
         <v>7.8</v>
       </c>
       <c r="BD27">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF27">
         <v>17</v>
       </c>
       <c r="BG27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7433,226 +7433,226 @@
         <v>172</v>
       </c>
       <c r="F28">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G28">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H28">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I28">
         <v>4.1</v>
       </c>
       <c r="J28">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K28">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P28">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q28">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7675,13 +7675,13 @@
         <v>173</v>
       </c>
       <c r="F29">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G29">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H29">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I29">
         <v>3.3</v>
@@ -7693,208 +7693,208 @@
         <v>3.8</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P29">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q29">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
         <v>177</v>
@@ -7917,7 +7917,7 @@
         <v>174</v>
       </c>
       <c r="F30">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G30">
         <v>3.65</v>
@@ -7932,19 +7932,19 @@
         <v>3.2</v>
       </c>
       <c r="K30">
-        <v>48</v>
+        <v>5.4</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P30">
         <v>1.52</v>
@@ -7953,190 +7953,190 @@
         <v>2.14</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="s">
         <v>177</v>
@@ -8159,226 +8159,226 @@
         <v>175</v>
       </c>
       <c r="F31">
+        <v>2.66</v>
+      </c>
+      <c r="G31">
+        <v>2.84</v>
+      </c>
+      <c r="H31">
+        <v>3.05</v>
+      </c>
+      <c r="I31">
+        <v>3.3</v>
+      </c>
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
+        <v>3.2</v>
+      </c>
+      <c r="L31">
+        <v>1.55</v>
+      </c>
+      <c r="M31">
+        <v>1.1</v>
+      </c>
+      <c r="N31">
         <v>2.64</v>
       </c>
-      <c r="G31">
-        <v>2.92</v>
-      </c>
-      <c r="H31">
-        <v>2.98</v>
-      </c>
-      <c r="I31">
-        <v>3.55</v>
-      </c>
-      <c r="J31">
-        <v>2.98</v>
-      </c>
-      <c r="K31">
-        <v>3.25</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P31">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q31">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BG31">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BV31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="s">
         <v>177</v>
@@ -8404,31 +8404,31 @@
         <v>1.5</v>
       </c>
       <c r="G32">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="H32">
         <v>4.3</v>
       </c>
       <c r="I32">
-        <v>870</v>
+        <v>9.4</v>
       </c>
       <c r="J32">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P32">
         <v>2.4</v>
@@ -8437,190 +8437,190 @@
         <v>1.38</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
         <v>177</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="182">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Colombian Primera B</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Japanese J League 2</t>
   </si>
   <si>
@@ -277,18 +280,18 @@
     <t>Spanish Segunda Division</t>
   </si>
   <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
     <t>Dutch Eerste Divisie</t>
   </si>
   <si>
-    <t>Norwegian 1st Division</t>
+    <t>Slovenian 2 SNL</t>
   </si>
   <si>
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
-    <t>Slovenian 2 SNL</t>
-  </si>
-  <si>
     <t>Uruguayan Segunda Division</t>
   </si>
   <si>
@@ -307,6 +310,9 @@
     <t>01:20:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>04:00:00</t>
   </si>
   <si>
@@ -364,6 +370,9 @@
     <t>Real Cartagena</t>
   </si>
   <si>
+    <t>Belize</t>
+  </si>
+  <si>
     <t>Vanraure Hachinohe</t>
   </si>
   <si>
@@ -400,18 +409,18 @@
     <t>Sociedad B</t>
   </si>
   <si>
+    <t>Bryne</t>
+  </si>
+  <si>
     <t>VVV Venlo</t>
   </si>
   <si>
-    <t>Bryne</t>
+    <t>NK Slovenska Bistrica</t>
   </si>
   <si>
     <t>Danubio</t>
   </si>
   <si>
-    <t>NK Slovenska Bistrica</t>
-  </si>
-  <si>
     <t>Ilirija Extra-Lux</t>
   </si>
   <si>
@@ -421,15 +430,15 @@
     <t>Umea FC</t>
   </si>
   <si>
+    <t>Centro Atletico Fenix</t>
+  </si>
+  <si>
     <t>Triglav</t>
   </si>
   <si>
     <t>Boston River</t>
   </si>
   <si>
-    <t>Centro Atletico Fenix</t>
-  </si>
-  <si>
     <t>Las Palmas</t>
   </si>
   <si>
@@ -457,6 +466,9 @@
     <t>Boca Juniors de Cali</t>
   </si>
   <si>
+    <t>French Guyana</t>
+  </si>
+  <si>
     <t>Yokohama FC</t>
   </si>
   <si>
@@ -493,18 +505,18 @@
     <t>Granada</t>
   </si>
   <si>
+    <t>Lyn</t>
+  </si>
+  <si>
     <t>Roda JC</t>
   </si>
   <si>
-    <t>Lyn</t>
+    <t>Rudar</t>
   </si>
   <si>
     <t>Cerro Largo FC</t>
   </si>
   <si>
-    <t>Rudar</t>
-  </si>
-  <si>
     <t>Beltinci</t>
   </si>
   <si>
@@ -514,15 +526,15 @@
     <t>Hammarby TFF</t>
   </si>
   <si>
+    <t>Uruguay Montevideo FC</t>
+  </si>
+  <si>
     <t>Jesenice</t>
   </si>
   <si>
     <t>Juventud De Las Piedras</t>
   </si>
   <si>
-    <t>Uruguay Montevideo FC</t>
-  </si>
-  <si>
     <t>Valladolid</t>
   </si>
   <si>
@@ -547,7 +559,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 18:14:31</t>
+    <t>2026-10-02 20:31:41</t>
   </si>
 </sst>
 </file>
@@ -879,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1129,16 +1141,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F2">
         <v>1.39</v>
@@ -1177,7 +1189,7 @@
         <v>1.72</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
         <v>2.84</v>
@@ -1363,7 +1375,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1371,79 +1383,79 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F3">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="G3">
-        <v>5.9</v>
+        <v>110</v>
       </c>
       <c r="H3">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="I3">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>1.59</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="Q3">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>1.77</v>
       </c>
       <c r="T3">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
         <v>1000</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1452,10 +1464,10 @@
         <v>1000</v>
       </c>
       <c r="AC3">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
         <v>1000</v>
@@ -1488,61 +1500,61 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU3">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AV3">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE3">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1605,186 +1617,186 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F4">
-        <v>2.26</v>
+        <v>4.2</v>
       </c>
       <c r="G4">
-        <v>2.58</v>
+        <v>5.9</v>
       </c>
       <c r="H4">
-        <v>2.78</v>
+        <v>1.75</v>
       </c>
       <c r="I4">
+        <v>1.96</v>
+      </c>
+      <c r="J4">
+        <v>3.65</v>
+      </c>
+      <c r="K4">
+        <v>4.8</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.03</v>
+      </c>
+      <c r="N4">
         <v>3.3</v>
       </c>
-      <c r="J4">
-        <v>3.8</v>
-      </c>
-      <c r="K4">
-        <v>5.1</v>
-      </c>
-      <c r="L4">
-        <v>1.01</v>
-      </c>
-      <c r="M4">
-        <v>1.01</v>
-      </c>
-      <c r="N4">
-        <v>4.1</v>
-      </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="R4">
+        <v>1.27</v>
+      </c>
+      <c r="S4">
+        <v>3.4</v>
+      </c>
+      <c r="T4">
+        <v>1.82</v>
+      </c>
+      <c r="U4">
+        <v>1.89</v>
+      </c>
+      <c r="V4">
+        <v>2.04</v>
+      </c>
+      <c r="W4">
+        <v>1.21</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>970</v>
+      </c>
+      <c r="Z4">
+        <v>970</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>970</v>
+      </c>
+      <c r="AD4">
+        <v>970</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>50</v>
+      </c>
+      <c r="AP4">
         <v>1.4</v>
       </c>
-      <c r="S4">
-        <v>2.72</v>
-      </c>
-      <c r="T4">
-        <v>1.61</v>
-      </c>
-      <c r="U4">
-        <v>1.02</v>
-      </c>
-      <c r="V4">
-        <v>1.43</v>
-      </c>
-      <c r="W4">
-        <v>1.63</v>
-      </c>
-      <c r="X4">
-        <v>1000</v>
-      </c>
-      <c r="Y4">
-        <v>1000</v>
-      </c>
-      <c r="Z4">
-        <v>1000</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>1000</v>
-      </c>
-      <c r="AC4">
-        <v>1000</v>
-      </c>
-      <c r="AD4">
-        <v>1000</v>
-      </c>
-      <c r="AE4">
-        <v>1000</v>
-      </c>
-      <c r="AF4">
-        <v>1000</v>
-      </c>
-      <c r="AG4">
-        <v>1000</v>
-      </c>
-      <c r="AH4">
-        <v>1000</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>1000</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>1.03</v>
-      </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1847,99 +1859,99 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F5">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="H5">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="I5">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="U5">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
+        <v>1.43</v>
+      </c>
+      <c r="W5">
         <v>1.63</v>
       </c>
-      <c r="W5">
-        <v>1.33</v>
-      </c>
       <c r="X5">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
         <v>1000</v>
@@ -1975,58 +1987,58 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2089,7 +2101,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2097,91 +2109,91 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F6">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>3.95</v>
       </c>
       <c r="H6">
-        <v>1.12</v>
+        <v>2.28</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>2.58</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>1.28</v>
+        <v>2.86</v>
       </c>
       <c r="O6">
+        <v>1.42</v>
+      </c>
+      <c r="P6">
+        <v>1.64</v>
+      </c>
+      <c r="Q6">
+        <v>2.2</v>
+      </c>
+      <c r="R6">
+        <v>1.23</v>
+      </c>
+      <c r="S6">
+        <v>3.95</v>
+      </c>
+      <c r="T6">
+        <v>1.84</v>
+      </c>
+      <c r="U6">
+        <v>1.84</v>
+      </c>
+      <c r="V6">
+        <v>1.63</v>
+      </c>
+      <c r="W6">
         <v>1.33</v>
       </c>
-      <c r="P6">
-        <v>1.25</v>
-      </c>
-      <c r="Q6">
-        <v>1.35</v>
-      </c>
-      <c r="R6">
-        <v>1.18</v>
-      </c>
-      <c r="S6">
-        <v>2.6</v>
-      </c>
-      <c r="T6">
-        <v>1.01</v>
-      </c>
-      <c r="U6">
-        <v>1.01</v>
-      </c>
-      <c r="V6">
-        <v>1.04</v>
-      </c>
-      <c r="W6">
-        <v>1.04</v>
-      </c>
       <c r="X6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE6">
         <v>1000</v>
@@ -2217,58 +2229,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2331,78 +2343,78 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F7">
-        <v>2.24</v>
+        <v>1.12</v>
       </c>
       <c r="G7">
-        <v>2.46</v>
+        <v>600</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>870</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L7">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.28</v>
+      </c>
+      <c r="O7">
+        <v>1.33</v>
+      </c>
+      <c r="P7">
+        <v>1.25</v>
+      </c>
+      <c r="Q7">
+        <v>1.35</v>
+      </c>
+      <c r="R7">
+        <v>1.18</v>
+      </c>
+      <c r="S7">
+        <v>2.6</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
         <v>1.04</v>
       </c>
-      <c r="N7">
-        <v>3.35</v>
-      </c>
-      <c r="O7">
-        <v>1.34</v>
-      </c>
-      <c r="P7">
-        <v>1.86</v>
-      </c>
-      <c r="Q7">
-        <v>2.04</v>
-      </c>
-      <c r="R7">
-        <v>1.32</v>
-      </c>
-      <c r="S7">
-        <v>3.5</v>
-      </c>
-      <c r="T7">
-        <v>1.77</v>
-      </c>
-      <c r="U7">
-        <v>1.98</v>
-      </c>
-      <c r="V7">
-        <v>1.39</v>
-      </c>
       <c r="W7">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2417,10 +2429,10 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
         <v>1000</v>
@@ -2459,58 +2471,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2573,78 +2585,78 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>2.46</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>3.55</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="R8">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="S8">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2659,10 +2671,10 @@
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2701,58 +2713,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2815,24 +2827,24 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F9">
         <v>1.1</v>
@@ -2859,22 +2871,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="Q9">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S9">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -3057,78 +3069,78 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F10">
-        <v>2.52</v>
+        <v>1.1</v>
       </c>
       <c r="G10">
-        <v>2.9</v>
+        <v>600</v>
       </c>
       <c r="H10">
-        <v>2.56</v>
+        <v>1.1</v>
       </c>
       <c r="I10">
-        <v>2.96</v>
+        <v>870</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.3</v>
+      </c>
+      <c r="O10">
+        <v>1.18</v>
+      </c>
+      <c r="P10">
+        <v>1.3</v>
+      </c>
+      <c r="Q10">
+        <v>1.18</v>
+      </c>
+      <c r="R10">
+        <v>1.18</v>
+      </c>
+      <c r="S10">
+        <v>1.2</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
         <v>1.02</v>
       </c>
-      <c r="N10">
-        <v>4</v>
-      </c>
-      <c r="O10">
-        <v>1.27</v>
-      </c>
-      <c r="P10">
-        <v>1.94</v>
-      </c>
-      <c r="Q10">
-        <v>1.77</v>
-      </c>
-      <c r="R10">
-        <v>1.37</v>
-      </c>
-      <c r="S10">
-        <v>2.92</v>
-      </c>
-      <c r="T10">
-        <v>1.62</v>
-      </c>
-      <c r="U10">
-        <v>2.16</v>
-      </c>
-      <c r="V10">
-        <v>1.52</v>
-      </c>
       <c r="W10">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3146,7 +3158,7 @@
         <v>1000</v>
       </c>
       <c r="AC10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
         <v>1000</v>
@@ -3185,64 +3197,64 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
@@ -3299,78 +3311,78 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F11">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="G11">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="H11">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="I11">
+        <v>2.96</v>
+      </c>
+      <c r="J11">
+        <v>3.35</v>
+      </c>
+      <c r="K11">
+        <v>4.8</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.02</v>
+      </c>
+      <c r="N11">
         <v>4</v>
       </c>
-      <c r="J11">
-        <v>3.3</v>
-      </c>
-      <c r="K11">
-        <v>4.2</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>3.45</v>
-      </c>
       <c r="O11">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P11">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="Q11">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S11">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3388,7 +3400,7 @@
         <v>1000</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD11">
         <v>1000</v>
@@ -3427,121 +3439,121 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH11">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3549,58 +3561,58 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F12">
-        <v>2.94</v>
+        <v>2.18</v>
       </c>
       <c r="G12">
+        <v>2.46</v>
+      </c>
+      <c r="H12">
+        <v>3.3</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
+      </c>
+      <c r="J12">
+        <v>3.3</v>
+      </c>
+      <c r="K12">
+        <v>4.2</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
         <v>3.45</v>
       </c>
-      <c r="H12">
-        <v>2.1</v>
-      </c>
-      <c r="I12">
-        <v>2.4</v>
-      </c>
-      <c r="J12">
-        <v>3.55</v>
-      </c>
-      <c r="K12">
-        <v>4.9</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>2.88</v>
-      </c>
       <c r="O12">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Q12">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="R12">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3609,10 +3621,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3723,102 +3735,102 @@
         <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="CB12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="G13">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="H13">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="J13">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3827,19 +3839,19 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="O13">
         <v>1.02</v>
       </c>
       <c r="P13">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R13">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="S13">
         <v>2.24</v>
@@ -3851,10 +3863,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="W13">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4025,7 +4037,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4033,178 +4045,178 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F14">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="G14">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H14">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="I14">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L14">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="P14">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q14">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="R14">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S14">
-        <v>3.6</v>
+        <v>2.24</v>
       </c>
       <c r="T14">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
+        <v>1.5</v>
+      </c>
+      <c r="W14">
         <v>1.53</v>
       </c>
-      <c r="W14">
-        <v>1.54</v>
-      </c>
       <c r="X14">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4267,7 +4279,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4275,178 +4287,178 @@
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F15">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="G15">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="H15">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="I15">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="O15">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q15">
+        <v>2.02</v>
+      </c>
+      <c r="R15">
+        <v>1.33</v>
+      </c>
+      <c r="S15">
+        <v>3.6</v>
+      </c>
+      <c r="T15">
+        <v>1.8</v>
+      </c>
+      <c r="U15">
+        <v>2.16</v>
+      </c>
+      <c r="V15">
         <v>1.53</v>
       </c>
-      <c r="R15">
-        <v>1.58</v>
-      </c>
-      <c r="S15">
-        <v>2.28</v>
-      </c>
-      <c r="T15">
-        <v>1.01</v>
-      </c>
-      <c r="U15">
-        <v>1.01</v>
-      </c>
-      <c r="V15">
-        <v>1.49</v>
-      </c>
       <c r="W15">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4509,7 +4521,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4517,16 +4529,16 @@
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F16">
         <v>1.88</v>
@@ -4538,22 +4550,22 @@
         <v>3.6</v>
       </c>
       <c r="I16">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J16">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
         <v>5.3</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M16">
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O16">
         <v>1.16</v>
@@ -4562,7 +4574,7 @@
         <v>2.5</v>
       </c>
       <c r="Q16">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R16">
         <v>1.6</v>
@@ -4580,7 +4592,7 @@
         <v>1.27</v>
       </c>
       <c r="W16">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4751,7 +4763,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4759,178 +4771,178 @@
         <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F17">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="G17">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="I17">
+        <v>3.1</v>
+      </c>
+      <c r="J17">
+        <v>3.8</v>
+      </c>
+      <c r="K17">
+        <v>4.2</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.04</v>
+      </c>
+      <c r="N17">
         <v>5</v>
       </c>
-      <c r="J17">
-        <v>3.2</v>
-      </c>
-      <c r="K17">
-        <v>3.45</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.11</v>
-      </c>
-      <c r="N17">
-        <v>2.72</v>
-      </c>
       <c r="O17">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="P17">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="Q17">
-        <v>2.44</v>
+        <v>1.55</v>
       </c>
       <c r="R17">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="S17">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="T17">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="U17">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="V17">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="X17">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AD17">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
         <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
         <v>1000</v>
       </c>
       <c r="AN17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>2.18</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>1.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>1.87</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>1.78</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.78</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>1.69</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
-        <v>1.76</v>
+        <v>9</v>
       </c>
       <c r="BG17">
-        <v>1.73</v>
+        <v>10</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4993,7 +5005,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5001,16 +5013,16 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F18">
         <v>1.12</v>
@@ -5025,7 +5037,7 @@
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5061,7 +5073,7 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W18">
         <v>1.65</v>
@@ -5235,186 +5247,186 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19">
+        <v>1.98</v>
+      </c>
+      <c r="G19">
+        <v>2.2</v>
+      </c>
+      <c r="H19">
+        <v>3.95</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>3.1</v>
+      </c>
+      <c r="K19">
+        <v>3.5</v>
+      </c>
+      <c r="L19">
+        <v>1.46</v>
+      </c>
+      <c r="M19">
+        <v>1.11</v>
+      </c>
+      <c r="N19">
+        <v>2.94</v>
+      </c>
+      <c r="O19">
+        <v>1.45</v>
+      </c>
+      <c r="P19">
+        <v>1.6</v>
+      </c>
+      <c r="Q19">
+        <v>2.24</v>
+      </c>
+      <c r="R19">
+        <v>1.21</v>
+      </c>
+      <c r="S19">
+        <v>4.1</v>
+      </c>
+      <c r="T19">
+        <v>2.02</v>
+      </c>
+      <c r="U19">
+        <v>1.75</v>
+      </c>
+      <c r="V19">
+        <v>1.25</v>
+      </c>
+      <c r="W19">
+        <v>1.83</v>
+      </c>
+      <c r="X19">
+        <v>970</v>
+      </c>
+      <c r="Y19">
+        <v>970</v>
+      </c>
+      <c r="Z19">
+        <v>46</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>970</v>
+      </c>
+      <c r="AC19">
+        <v>970</v>
+      </c>
+      <c r="AD19">
+        <v>24</v>
+      </c>
+      <c r="AE19">
         <v>95</v>
       </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>163</v>
-      </c>
-      <c r="F19">
-        <v>1.1</v>
-      </c>
-      <c r="G19">
-        <v>600</v>
-      </c>
-      <c r="H19">
-        <v>1.1</v>
-      </c>
-      <c r="I19">
-        <v>870</v>
-      </c>
-      <c r="J19">
-        <v>1.12</v>
-      </c>
-      <c r="K19">
-        <v>950</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>1.24</v>
-      </c>
-      <c r="O19">
-        <v>1.02</v>
-      </c>
-      <c r="P19">
-        <v>1.24</v>
-      </c>
-      <c r="Q19">
-        <v>1.03</v>
-      </c>
-      <c r="R19">
-        <v>1.18</v>
-      </c>
-      <c r="S19">
-        <v>1.04</v>
-      </c>
-      <c r="T19">
-        <v>1.01</v>
-      </c>
-      <c r="U19">
-        <v>1.01</v>
-      </c>
-      <c r="V19">
-        <v>1.02</v>
-      </c>
-      <c r="W19">
-        <v>1.02</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI19">
         <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM19">
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO19">
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5477,526 +5489,526 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F20">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="G20">
-        <v>1.65</v>
+        <v>600</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="I20">
-        <v>6.8</v>
+        <v>870</v>
       </c>
       <c r="J20">
-        <v>4.2</v>
+        <v>1.12</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L20">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="O20">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="P20">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q20">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="R20">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="S20">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="T20">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="W20">
-        <v>2.52</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F21">
-        <v>4.4</v>
+        <v>1.59</v>
       </c>
       <c r="G21">
-        <v>6.4</v>
+        <v>1.65</v>
       </c>
       <c r="H21">
-        <v>1.64</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K21">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N21">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="O21">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="P21">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q21">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="R21">
         <v>1.42</v>
       </c>
       <c r="S21">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V21">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="W21">
-        <v>1.19</v>
+        <v>2.52</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="CB21" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F22">
-        <v>1.46</v>
+        <v>3.8</v>
       </c>
       <c r="G22">
-        <v>600</v>
+        <v>6.8</v>
       </c>
       <c r="H22">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="I22">
-        <v>870</v>
+        <v>1.7</v>
       </c>
       <c r="J22">
-        <v>1.46</v>
+        <v>4.1</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6005,22 +6017,22 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.53</v>
+        <v>2.42</v>
       </c>
       <c r="O22">
         <v>1.02</v>
       </c>
       <c r="P22">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="Q22">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="R22">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S22">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6029,10 +6041,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.02</v>
+        <v>2.42</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6203,84 +6215,84 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F23">
-        <v>2.76</v>
+        <v>1.5</v>
       </c>
       <c r="G23">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="H23">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="I23">
+        <v>10.5</v>
+      </c>
+      <c r="J23">
+        <v>3.2</v>
+      </c>
+      <c r="K23">
+        <v>6.8</v>
+      </c>
+      <c r="L23">
+        <v>1.38</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>2.46</v>
+      </c>
+      <c r="O23">
+        <v>1.02</v>
+      </c>
+      <c r="P23">
+        <v>1.54</v>
+      </c>
+      <c r="Q23">
+        <v>2.12</v>
+      </c>
+      <c r="R23">
+        <v>1.16</v>
+      </c>
+      <c r="S23">
         <v>2.94</v>
       </c>
-      <c r="J23">
-        <v>3.3</v>
-      </c>
-      <c r="K23">
-        <v>3.6</v>
-      </c>
-      <c r="L23">
-        <v>1.34</v>
-      </c>
-      <c r="M23">
-        <v>1.08</v>
-      </c>
-      <c r="N23">
-        <v>3.4</v>
-      </c>
-      <c r="O23">
-        <v>1.34</v>
-      </c>
-      <c r="P23">
-        <v>1.87</v>
-      </c>
-      <c r="Q23">
-        <v>2</v>
-      </c>
-      <c r="R23">
-        <v>1.32</v>
-      </c>
-      <c r="S23">
-        <v>3.55</v>
-      </c>
       <c r="T23">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="W23">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="X23">
         <v>1000</v>
       </c>
       <c r="Y23">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
         <v>1000</v>
@@ -6289,13 +6301,13 @@
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
         <v>1000</v>
@@ -6304,7 +6316,7 @@
         <v>1000</v>
       </c>
       <c r="AG23">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
         <v>1000</v>
@@ -6331,58 +6343,58 @@
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AR23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AS23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AU23">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AV23">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AW23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AX23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AY23">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BA23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BD23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BE23">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BF23">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6439,72 +6451,72 @@
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F24">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="G24">
-        <v>1.95</v>
+        <v>600</v>
       </c>
       <c r="H24">
-        <v>5.4</v>
+        <v>1.46</v>
       </c>
       <c r="I24">
-        <v>10.5</v>
+        <v>870</v>
       </c>
       <c r="J24">
-        <v>3.2</v>
+        <v>1.46</v>
       </c>
       <c r="K24">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L24">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>2.46</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
         <v>1.02</v>
       </c>
       <c r="P24">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q24">
-        <v>2.12</v>
+        <v>1.03</v>
       </c>
       <c r="R24">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S24">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6513,10 +6525,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W24">
-        <v>2.06</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6681,102 +6693,102 @@
         <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F25">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="G25">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="H25">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="I25">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="J25">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="M25">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O25">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P25">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q25">
+        <v>1.94</v>
+      </c>
+      <c r="R25">
+        <v>1.31</v>
+      </c>
+      <c r="S25">
+        <v>3.35</v>
+      </c>
+      <c r="T25">
+        <v>1.73</v>
+      </c>
+      <c r="U25">
         <v>2.06</v>
       </c>
-      <c r="R25">
-        <v>1.27</v>
-      </c>
-      <c r="S25">
-        <v>3.6</v>
-      </c>
-      <c r="T25">
-        <v>1.75</v>
-      </c>
-      <c r="U25">
-        <v>1.95</v>
-      </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="X25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y25">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z25">
         <v>1000</v>
       </c>
       <c r="AA25">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC25">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD25">
         <v>970</v>
@@ -6788,7 +6800,7 @@
         <v>1000</v>
       </c>
       <c r="AG25">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AH25">
         <v>1000</v>
@@ -6809,76 +6821,76 @@
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>8.6</v>
+        <v>1.32</v>
       </c>
       <c r="AQ25">
-        <v>8.6</v>
+        <v>1.3</v>
       </c>
       <c r="AR25">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AS25">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AT25">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="AU25">
-        <v>5.7</v>
+        <v>1.22</v>
       </c>
       <c r="AV25">
-        <v>9.6</v>
+        <v>1.33</v>
       </c>
       <c r="AW25">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AX25">
-        <v>9.199999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="AY25">
-        <v>8</v>
+        <v>1.34</v>
       </c>
       <c r="AZ25">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA25">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="BB25">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="BC25">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="BD25">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="BE25">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="BF25">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="BG25">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
         <v>1000</v>
@@ -6890,13 +6902,13 @@
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
         <v>1000</v>
@@ -6908,7 +6920,7 @@
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
         <v>1000</v>
@@ -6929,198 +6941,198 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F26">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="G26">
-        <v>1.28</v>
+        <v>2.42</v>
       </c>
       <c r="H26">
-        <v>12.5</v>
+        <v>3.25</v>
       </c>
       <c r="I26">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="J26">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="K26">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="L26">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="M26">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="O26">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="P26">
-        <v>2.96</v>
+        <v>1.75</v>
       </c>
       <c r="Q26">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="R26">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="S26">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
         <v>1.8</v>
       </c>
       <c r="U26">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V26">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>4.6</v>
+        <v>1.71</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z26">
         <v>1000</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB26">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE26">
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG26">
+        <v>22</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
         <v>23</v>
       </c>
-      <c r="AH26">
-        <v>1000</v>
-      </c>
-      <c r="AI26">
-        <v>1000</v>
-      </c>
-      <c r="AJ26">
-        <v>970</v>
-      </c>
-      <c r="AK26">
-        <v>34</v>
-      </c>
-      <c r="AL26">
-        <v>1000</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>3.85</v>
-      </c>
       <c r="AO26">
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>2.06</v>
+        <v>8.6</v>
       </c>
       <c r="AQ26">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="AR26">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AS26">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AT26">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU26">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV26">
-        <v>2.06</v>
+        <v>9.6</v>
       </c>
       <c r="AW26">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AX26">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY26">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ26">
-        <v>2.06</v>
+        <v>11.5</v>
       </c>
       <c r="BA26">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="BB26">
-        <v>7.4</v>
+        <v>1.99</v>
       </c>
       <c r="BC26">
-        <v>8.800000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="BD26">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="BE26">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="BF26">
-        <v>3</v>
+        <v>15.5</v>
       </c>
       <c r="BG26">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.51</v>
+        <v>2.72</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="BL26">
         <v>1000</v>
@@ -7132,25 +7144,25 @@
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.37</v>
+        <v>1.97</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.6</v>
+        <v>2.94</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="BV26">
         <v>1000</v>
@@ -7171,198 +7183,198 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F27">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="G27">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="H27">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="I27">
+        <v>14.5</v>
+      </c>
+      <c r="J27">
+        <v>7.2</v>
+      </c>
+      <c r="K27">
+        <v>8</v>
+      </c>
+      <c r="L27">
+        <v>1.21</v>
+      </c>
+      <c r="M27">
+        <v>1.02</v>
+      </c>
+      <c r="N27">
         <v>6.2</v>
       </c>
-      <c r="J27">
-        <v>3.4</v>
-      </c>
-      <c r="K27">
-        <v>3.6</v>
-      </c>
-      <c r="L27">
-        <v>1.56</v>
-      </c>
-      <c r="M27">
-        <v>1.13</v>
-      </c>
-      <c r="N27">
-        <v>2.62</v>
-      </c>
       <c r="O27">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="P27">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="Q27">
-        <v>2.64</v>
+        <v>1.35</v>
       </c>
       <c r="R27">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="S27">
-        <v>5.5</v>
+        <v>1.98</v>
       </c>
       <c r="T27">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="U27">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="W27">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="X27">
+        <v>1000</v>
+      </c>
+      <c r="Y27">
+        <v>1000</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>36</v>
+      </c>
+      <c r="AC27">
+        <v>1000</v>
+      </c>
+      <c r="AD27">
+        <v>1000</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>970</v>
+      </c>
+      <c r="AG27">
+        <v>23</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>970</v>
+      </c>
+      <c r="AK27">
+        <v>34</v>
+      </c>
+      <c r="AL27">
+        <v>1000</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>3.85</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>1.89</v>
+      </c>
+      <c r="AQ27">
+        <v>1.89</v>
+      </c>
+      <c r="AR27">
+        <v>1.89</v>
+      </c>
+      <c r="AS27">
+        <v>1.89</v>
+      </c>
+      <c r="AT27">
         <v>8.800000000000001</v>
       </c>
-      <c r="Y27">
-        <v>14.5</v>
-      </c>
-      <c r="Z27">
-        <v>48</v>
-      </c>
-      <c r="AA27">
-        <v>230</v>
-      </c>
-      <c r="AB27">
-        <v>6.2</v>
-      </c>
-      <c r="AC27">
-        <v>8.4</v>
-      </c>
-      <c r="AD27">
-        <v>26</v>
-      </c>
-      <c r="AE27">
-        <v>140</v>
-      </c>
-      <c r="AF27">
-        <v>9.6</v>
-      </c>
-      <c r="AG27">
-        <v>11.5</v>
-      </c>
-      <c r="AH27">
-        <v>34</v>
-      </c>
-      <c r="AI27">
-        <v>150</v>
-      </c>
-      <c r="AJ27">
-        <v>24</v>
-      </c>
-      <c r="AK27">
-        <v>32</v>
-      </c>
-      <c r="AL27">
-        <v>75</v>
-      </c>
-      <c r="AM27">
-        <v>290</v>
-      </c>
-      <c r="AN27">
-        <v>22</v>
-      </c>
-      <c r="AO27">
-        <v>260</v>
-      </c>
-      <c r="AP27">
-        <v>8</v>
-      </c>
-      <c r="AQ27">
-        <v>11.5</v>
-      </c>
-      <c r="AR27">
-        <v>8.6</v>
-      </c>
-      <c r="AS27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT27">
-        <v>5.6</v>
-      </c>
       <c r="AU27">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV27">
-        <v>20</v>
+        <v>1.89</v>
       </c>
       <c r="AW27">
-        <v>9.6</v>
+        <v>1.89</v>
       </c>
       <c r="AX27">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AZ27">
-        <v>8</v>
+        <v>1.89</v>
       </c>
       <c r="BA27">
-        <v>9.800000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="BB27">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="BC27">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD27">
-        <v>9.199999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="BE27">
-        <v>9.800000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="BF27">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="BG27">
-        <v>9.800000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="BL27">
         <v>1000</v>
@@ -7374,25 +7386,25 @@
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BV27">
         <v>1000</v>
@@ -7413,7 +7425,7 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7421,190 +7433,190 @@
         <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F28">
+        <v>1.76</v>
+      </c>
+      <c r="G28">
+        <v>1.81</v>
+      </c>
+      <c r="H28">
+        <v>5.9</v>
+      </c>
+      <c r="I28">
+        <v>6.8</v>
+      </c>
+      <c r="J28">
+        <v>3.5</v>
+      </c>
+      <c r="K28">
+        <v>3.7</v>
+      </c>
+      <c r="L28">
+        <v>1.56</v>
+      </c>
+      <c r="M28">
+        <v>1.12</v>
+      </c>
+      <c r="N28">
+        <v>2.66</v>
+      </c>
+      <c r="O28">
+        <v>1.56</v>
+      </c>
+      <c r="P28">
+        <v>1.58</v>
+      </c>
+      <c r="Q28">
+        <v>2.6</v>
+      </c>
+      <c r="R28">
+        <v>1.2</v>
+      </c>
+      <c r="S28">
+        <v>5.3</v>
+      </c>
+      <c r="T28">
+        <v>2.42</v>
+      </c>
+      <c r="U28">
+        <v>1.67</v>
+      </c>
+      <c r="V28">
+        <v>1.17</v>
+      </c>
+      <c r="W28">
         <v>2.22</v>
       </c>
-      <c r="G28">
-        <v>2.44</v>
-      </c>
-      <c r="H28">
-        <v>3.55</v>
-      </c>
-      <c r="I28">
-        <v>4.1</v>
-      </c>
-      <c r="J28">
-        <v>3</v>
-      </c>
-      <c r="K28">
-        <v>3.45</v>
-      </c>
-      <c r="L28">
-        <v>1.01</v>
-      </c>
-      <c r="M28">
-        <v>1.11</v>
-      </c>
-      <c r="N28">
-        <v>2.96</v>
-      </c>
-      <c r="O28">
-        <v>1.45</v>
-      </c>
-      <c r="P28">
-        <v>1.65</v>
-      </c>
-      <c r="Q28">
-        <v>2.3</v>
-      </c>
-      <c r="R28">
-        <v>1.25</v>
-      </c>
-      <c r="S28">
-        <v>4.4</v>
-      </c>
-      <c r="T28">
-        <v>1.94</v>
-      </c>
-      <c r="U28">
-        <v>1.88</v>
-      </c>
-      <c r="V28">
-        <v>1.33</v>
-      </c>
-      <c r="W28">
-        <v>1.69</v>
-      </c>
       <c r="X28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y28">
+        <v>15</v>
+      </c>
+      <c r="Z28">
+        <v>60</v>
+      </c>
+      <c r="AA28">
+        <v>270</v>
+      </c>
+      <c r="AB28">
+        <v>6.2</v>
+      </c>
+      <c r="AC28">
+        <v>9</v>
+      </c>
+      <c r="AD28">
+        <v>27</v>
+      </c>
+      <c r="AE28">
+        <v>160</v>
+      </c>
+      <c r="AF28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG28">
+        <v>11.5</v>
+      </c>
+      <c r="AH28">
+        <v>34</v>
+      </c>
+      <c r="AI28">
+        <v>160</v>
+      </c>
+      <c r="AJ28">
+        <v>19</v>
+      </c>
+      <c r="AK28">
+        <v>26</v>
+      </c>
+      <c r="AL28">
+        <v>70</v>
+      </c>
+      <c r="AM28">
+        <v>310</v>
+      </c>
+      <c r="AN28">
+        <v>18.5</v>
+      </c>
+      <c r="AO28">
+        <v>260</v>
+      </c>
+      <c r="AP28">
+        <v>7.8</v>
+      </c>
+      <c r="AQ28">
+        <v>11.5</v>
+      </c>
+      <c r="AR28">
         <v>10.5</v>
       </c>
-      <c r="Y28">
+      <c r="AS28">
         <v>12</v>
       </c>
-      <c r="Z28">
-        <v>27</v>
-      </c>
-      <c r="AA28">
-        <v>100</v>
-      </c>
-      <c r="AB28">
-        <v>8.6</v>
-      </c>
-      <c r="AC28">
-        <v>7.8</v>
-      </c>
-      <c r="AD28">
-        <v>17</v>
-      </c>
-      <c r="AE28">
-        <v>60</v>
-      </c>
-      <c r="AF28">
-        <v>14.5</v>
-      </c>
-      <c r="AG28">
-        <v>12</v>
-      </c>
-      <c r="AH28">
-        <v>22</v>
-      </c>
-      <c r="AI28">
-        <v>80</v>
-      </c>
-      <c r="AJ28">
-        <v>34</v>
-      </c>
-      <c r="AK28">
-        <v>32</v>
-      </c>
-      <c r="AL28">
-        <v>55</v>
-      </c>
-      <c r="AM28">
-        <v>170</v>
-      </c>
-      <c r="AN28">
-        <v>28</v>
-      </c>
-      <c r="AO28">
-        <v>80</v>
-      </c>
-      <c r="AP28">
-        <v>8.6</v>
-      </c>
-      <c r="AQ28">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR28">
-        <v>22</v>
-      </c>
-      <c r="AS28">
-        <v>8.6</v>
-      </c>
       <c r="AT28">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AU28">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AV28">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AW28">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AX28">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AY28">
         <v>10</v>
       </c>
       <c r="AZ28">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA28">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB28">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BC28">
         <v>21</v>
       </c>
       <c r="BD28">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BE28">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BF28">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BG28">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7616,7 +7628,7 @@
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BP28">
         <v>1000</v>
@@ -7655,198 +7667,198 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F29">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="G29">
         <v>2.44</v>
       </c>
       <c r="H29">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I29">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J29">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="K29">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L29">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="O29">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="P29">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="Q29">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="R29">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S29">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="T29">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="U29">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
         <v>1.69</v>
       </c>
       <c r="X29">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="Y29">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z29">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA29">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AB29">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC29">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD29">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE29">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AF29">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG29">
         <v>12</v>
       </c>
       <c r="AH29">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AI29">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AJ29">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK29">
         <v>32</v>
       </c>
       <c r="AL29">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM29">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AN29">
+        <v>28</v>
+      </c>
+      <c r="AO29">
+        <v>80</v>
+      </c>
+      <c r="AP29">
+        <v>8.6</v>
+      </c>
+      <c r="AQ29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR29">
         <v>22</v>
-      </c>
-      <c r="AO29">
-        <v>40</v>
-      </c>
-      <c r="AP29">
-        <v>13.5</v>
-      </c>
-      <c r="AQ29">
-        <v>12</v>
-      </c>
-      <c r="AR29">
-        <v>6.8</v>
       </c>
       <c r="AS29">
         <v>8.6</v>
       </c>
       <c r="AT29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU29">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV29">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW29">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX29">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AY29">
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA29">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB29">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BC29">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BD29">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE29">
         <v>8.800000000000001</v>
       </c>
       <c r="BF29">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BG29">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH29">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
         <v>1000</v>
@@ -7855,16 +7867,16 @@
         <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
         <v>1000</v>
@@ -7873,10 +7885,10 @@
         <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
         <v>1000</v>
@@ -7897,198 +7909,198 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F30">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="G30">
-        <v>3.65</v>
+        <v>2.44</v>
       </c>
       <c r="H30">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="I30">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J30">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K30">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N30">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="O30">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="P30">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="Q30">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="R30">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="S30">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP30">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ30">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR30">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS30">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT30">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU30">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV30">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW30">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX30">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY30">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA30">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB30">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BC30">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BD30">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE30">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH30">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BI30">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8097,16 +8109,16 @@
         <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR30">
         <v>1000</v>
@@ -8118,7 +8130,7 @@
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV30">
         <v>1000</v>
@@ -8139,198 +8151,198 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F31">
         <v>2.66</v>
       </c>
       <c r="G31">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="H31">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="I31">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K31">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="L31">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N31">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="O31">
         <v>1.44</v>
       </c>
       <c r="P31">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="Q31">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="R31">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S31">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="T31">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U31">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="X31">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC31">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD31">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE31">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF31">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH31">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI31">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK31">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM31">
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO31">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP31">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR31">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS31">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AT31">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU31">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV31">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW31">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX31">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY31">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA31">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB31">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC31">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BD31">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BE31">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF31">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BG31">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI31">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
         <v>1000</v>
@@ -8342,7 +8354,7 @@
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP31">
         <v>1000</v>
@@ -8360,7 +8372,7 @@
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8381,249 +8393,491 @@
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32">
+        <v>2.62</v>
+      </c>
+      <c r="G32">
+        <v>2.9</v>
+      </c>
+      <c r="H32">
+        <v>2.96</v>
+      </c>
+      <c r="I32">
+        <v>3.35</v>
+      </c>
+      <c r="J32">
+        <v>3</v>
+      </c>
+      <c r="K32">
+        <v>3.6</v>
+      </c>
+      <c r="L32">
+        <v>1.55</v>
+      </c>
+      <c r="M32">
+        <v>1.12</v>
+      </c>
+      <c r="N32">
+        <v>2.68</v>
+      </c>
+      <c r="O32">
+        <v>1.46</v>
+      </c>
+      <c r="P32">
+        <v>1.51</v>
+      </c>
+      <c r="Q32">
+        <v>2.56</v>
+      </c>
+      <c r="R32">
+        <v>1.21</v>
+      </c>
+      <c r="S32">
+        <v>4.7</v>
+      </c>
+      <c r="T32">
+        <v>2</v>
+      </c>
+      <c r="U32">
+        <v>1.74</v>
+      </c>
+      <c r="V32">
+        <v>1.42</v>
+      </c>
+      <c r="W32">
+        <v>1.52</v>
+      </c>
+      <c r="X32">
+        <v>13.5</v>
+      </c>
+      <c r="Y32">
+        <v>11.5</v>
+      </c>
+      <c r="Z32">
+        <v>25</v>
+      </c>
+      <c r="AA32">
+        <v>80</v>
+      </c>
+      <c r="AB32">
+        <v>10</v>
+      </c>
+      <c r="AC32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD32">
+        <v>19</v>
+      </c>
+      <c r="AE32">
+        <v>60</v>
+      </c>
+      <c r="AF32">
+        <v>22</v>
+      </c>
+      <c r="AG32">
+        <v>15.5</v>
+      </c>
+      <c r="AH32">
+        <v>26</v>
+      </c>
+      <c r="AI32">
+        <v>90</v>
+      </c>
+      <c r="AJ32">
+        <v>60</v>
+      </c>
+      <c r="AK32">
+        <v>50</v>
+      </c>
+      <c r="AL32">
+        <v>80</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>50</v>
+      </c>
+      <c r="AO32">
+        <v>75</v>
+      </c>
+      <c r="AP32">
+        <v>6.4</v>
+      </c>
+      <c r="AQ32">
+        <v>8</v>
+      </c>
+      <c r="AR32">
+        <v>14.5</v>
+      </c>
+      <c r="AS32">
+        <v>3.95</v>
+      </c>
+      <c r="AT32">
+        <v>7.2</v>
+      </c>
+      <c r="AU32">
+        <v>5.5</v>
+      </c>
+      <c r="AV32">
+        <v>10.5</v>
+      </c>
+      <c r="AW32">
+        <v>3.9</v>
+      </c>
+      <c r="AX32">
+        <v>12.5</v>
+      </c>
+      <c r="AY32">
+        <v>10.5</v>
+      </c>
+      <c r="AZ32">
+        <v>15.5</v>
+      </c>
+      <c r="BA32">
+        <v>4</v>
+      </c>
+      <c r="BB32">
+        <v>3.9</v>
+      </c>
+      <c r="BC32">
+        <v>25</v>
+      </c>
+      <c r="BD32">
+        <v>3.95</v>
+      </c>
+      <c r="BE32">
+        <v>4.1</v>
+      </c>
+      <c r="BF32">
+        <v>3.85</v>
+      </c>
+      <c r="BG32">
+        <v>3.95</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>2.24</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.12</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.12</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.85</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.12</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.12</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.14</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.12</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.12</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.12</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
         <v>95</v>
       </c>
-      <c r="C32" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" t="s">
-        <v>176</v>
-      </c>
-      <c r="F32">
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33">
         <v>1.5</v>
       </c>
-      <c r="G32">
+      <c r="G33">
         <v>1.82</v>
       </c>
-      <c r="H32">
+      <c r="H33">
         <v>4.3</v>
       </c>
-      <c r="I32">
+      <c r="I33">
         <v>9.4</v>
       </c>
-      <c r="J32">
+      <c r="J33">
         <v>4.1</v>
       </c>
-      <c r="K32">
+      <c r="K33">
         <v>10</v>
       </c>
-      <c r="L32">
-        <v>1.01</v>
-      </c>
-      <c r="M32">
-        <v>1.01</v>
-      </c>
-      <c r="N32">
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.01</v>
+      </c>
+      <c r="N33">
         <v>2.4</v>
       </c>
-      <c r="O32">
+      <c r="O33">
         <v>1.12</v>
       </c>
-      <c r="P32">
+      <c r="P33">
         <v>2.4</v>
       </c>
-      <c r="Q32">
+      <c r="Q33">
         <v>1.38</v>
       </c>
-      <c r="R32">
+      <c r="R33">
         <v>1.57</v>
       </c>
-      <c r="S32">
+      <c r="S33">
         <v>2</v>
       </c>
-      <c r="T32">
-        <v>1.01</v>
-      </c>
-      <c r="U32">
-        <v>1.01</v>
-      </c>
-      <c r="V32">
-        <v>1.11</v>
-      </c>
-      <c r="W32">
-        <v>2.2</v>
-      </c>
-      <c r="X32">
-        <v>1000</v>
-      </c>
-      <c r="Y32">
-        <v>1000</v>
-      </c>
-      <c r="Z32">
-        <v>1000</v>
-      </c>
-      <c r="AA32">
-        <v>1000</v>
-      </c>
-      <c r="AB32">
-        <v>1000</v>
-      </c>
-      <c r="AC32">
-        <v>1000</v>
-      </c>
-      <c r="AD32">
-        <v>1000</v>
-      </c>
-      <c r="AE32">
-        <v>1000</v>
-      </c>
-      <c r="AF32">
-        <v>1000</v>
-      </c>
-      <c r="AG32">
-        <v>1000</v>
-      </c>
-      <c r="AH32">
-        <v>1000</v>
-      </c>
-      <c r="AI32">
-        <v>1000</v>
-      </c>
-      <c r="AJ32">
-        <v>1000</v>
-      </c>
-      <c r="AK32">
-        <v>1000</v>
-      </c>
-      <c r="AL32">
-        <v>1000</v>
-      </c>
-      <c r="AM32">
-        <v>1000</v>
-      </c>
-      <c r="AN32">
-        <v>1000</v>
-      </c>
-      <c r="AO32">
-        <v>1000</v>
-      </c>
-      <c r="AP32">
-        <v>1.01</v>
-      </c>
-      <c r="AQ32">
-        <v>1.01</v>
-      </c>
-      <c r="AR32">
-        <v>1.01</v>
-      </c>
-      <c r="AS32">
-        <v>1.01</v>
-      </c>
-      <c r="AT32">
-        <v>1.01</v>
-      </c>
-      <c r="AU32">
-        <v>1.01</v>
-      </c>
-      <c r="AV32">
-        <v>1.01</v>
-      </c>
-      <c r="AW32">
-        <v>1.01</v>
-      </c>
-      <c r="AX32">
-        <v>1.01</v>
-      </c>
-      <c r="AY32">
-        <v>1.01</v>
-      </c>
-      <c r="AZ32">
-        <v>1.01</v>
-      </c>
-      <c r="BA32">
-        <v>1.01</v>
-      </c>
-      <c r="BB32">
-        <v>1.01</v>
-      </c>
-      <c r="BC32">
-        <v>1.01</v>
-      </c>
-      <c r="BD32">
-        <v>1.01</v>
-      </c>
-      <c r="BE32">
-        <v>1.01</v>
-      </c>
-      <c r="BF32">
-        <v>1.01</v>
-      </c>
-      <c r="BG32">
-        <v>1.01</v>
-      </c>
-      <c r="BH32">
-        <v>1000</v>
-      </c>
-      <c r="BI32">
-        <v>1.01</v>
-      </c>
-      <c r="BJ32">
-        <v>1000</v>
-      </c>
-      <c r="BK32">
-        <v>1.01</v>
-      </c>
-      <c r="BL32">
-        <v>1000</v>
-      </c>
-      <c r="BM32">
-        <v>1.01</v>
-      </c>
-      <c r="BN32">
-        <v>1000</v>
-      </c>
-      <c r="BO32">
-        <v>1.01</v>
-      </c>
-      <c r="BP32">
-        <v>1000</v>
-      </c>
-      <c r="BQ32">
-        <v>1.01</v>
-      </c>
-      <c r="BR32">
-        <v>1000</v>
-      </c>
-      <c r="BS32">
-        <v>1.01</v>
-      </c>
-      <c r="BT32">
-        <v>1000</v>
-      </c>
-      <c r="BU32">
-        <v>1.01</v>
-      </c>
-      <c r="BV32">
-        <v>1000</v>
-      </c>
-      <c r="BW32">
-        <v>1.01</v>
-      </c>
-      <c r="BX32">
-        <v>1000</v>
-      </c>
-      <c r="BY32">
-        <v>1.01</v>
-      </c>
-      <c r="BZ32">
-        <v>1000</v>
-      </c>
-      <c r="CA32">
-        <v>1.01</v>
-      </c>
-      <c r="CB32" t="s">
-        <v>177</v>
+      <c r="T33">
+        <v>1.01</v>
+      </c>
+      <c r="U33">
+        <v>1.01</v>
+      </c>
+      <c r="V33">
+        <v>1.12</v>
+      </c>
+      <c r="W33">
+        <v>2.22</v>
+      </c>
+      <c r="X33">
+        <v>1000</v>
+      </c>
+      <c r="Y33">
+        <v>1000</v>
+      </c>
+      <c r="Z33">
+        <v>1000</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>1000</v>
+      </c>
+      <c r="AC33">
+        <v>1000</v>
+      </c>
+      <c r="AD33">
+        <v>1000</v>
+      </c>
+      <c r="AE33">
+        <v>1000</v>
+      </c>
+      <c r="AF33">
+        <v>1000</v>
+      </c>
+      <c r="AG33">
+        <v>1000</v>
+      </c>
+      <c r="AH33">
+        <v>1000</v>
+      </c>
+      <c r="AI33">
+        <v>1000</v>
+      </c>
+      <c r="AJ33">
+        <v>1000</v>
+      </c>
+      <c r="AK33">
+        <v>1000</v>
+      </c>
+      <c r="AL33">
+        <v>1000</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>1000</v>
+      </c>
+      <c r="AO33">
+        <v>1000</v>
+      </c>
+      <c r="AP33">
+        <v>1.03</v>
+      </c>
+      <c r="AQ33">
+        <v>1.03</v>
+      </c>
+      <c r="AR33">
+        <v>1.03</v>
+      </c>
+      <c r="AS33">
+        <v>1.03</v>
+      </c>
+      <c r="AT33">
+        <v>1.03</v>
+      </c>
+      <c r="AU33">
+        <v>1.03</v>
+      </c>
+      <c r="AV33">
+        <v>1.03</v>
+      </c>
+      <c r="AW33">
+        <v>1.03</v>
+      </c>
+      <c r="AX33">
+        <v>1.03</v>
+      </c>
+      <c r="AY33">
+        <v>1.03</v>
+      </c>
+      <c r="AZ33">
+        <v>1.03</v>
+      </c>
+      <c r="BA33">
+        <v>1.03</v>
+      </c>
+      <c r="BB33">
+        <v>1.03</v>
+      </c>
+      <c r="BC33">
+        <v>1.03</v>
+      </c>
+      <c r="BD33">
+        <v>1.03</v>
+      </c>
+      <c r="BE33">
+        <v>1.03</v>
+      </c>
+      <c r="BF33">
+        <v>1.01</v>
+      </c>
+      <c r="BG33">
+        <v>1.01</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.01</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.01</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.01</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.01</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.01</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.01</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.01</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.01</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -559,7 +559,7 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>2026-10-02 20:31:41</t>
+    <t>2026-10-02 22:47:54</t>
   </si>
 </sst>
 </file>
@@ -1153,58 +1153,58 @@
         <v>149</v>
       </c>
       <c r="F2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G2">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P2">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q2">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="S2">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W2">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1231,7 +1231,7 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
         <v>1000</v>
@@ -1255,7 +1255,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>1.03</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1395,7 +1395,7 @@
         <v>150</v>
       </c>
       <c r="F3">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="G3">
         <v>110</v>
@@ -1425,16 +1425,16 @@
         <v>1.01</v>
       </c>
       <c r="P3">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Q3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>1.77</v>
+        <v>1.02</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1446,7 +1446,7 @@
         <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1652,7 +1652,7 @@
         <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1664,7 +1664,7 @@
         <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
         <v>1.8</v>
@@ -2142,7 +2142,7 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
         <v>2.86</v>
@@ -2172,7 +2172,7 @@
         <v>1.63</v>
       </c>
       <c r="W6">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X6">
         <v>970</v>
@@ -2241,7 +2241,7 @@
         <v>1.56</v>
       </c>
       <c r="AT6">
-        <v>7.6</v>
+        <v>1.45</v>
       </c>
       <c r="AU6">
         <v>5.5</v>
@@ -2608,7 +2608,7 @@
         <v>2.22</v>
       </c>
       <c r="G8">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H8">
         <v>3.25</v>
@@ -2656,7 +2656,7 @@
         <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -3113,16 +3113,16 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O10">
         <v>1.18</v>
       </c>
       <c r="P10">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q10">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="R10">
         <v>1.18</v>
@@ -3334,7 +3334,7 @@
         <v>2.5</v>
       </c>
       <c r="G11">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H11">
         <v>2.54</v>
@@ -3367,7 +3367,7 @@
         <v>1.78</v>
       </c>
       <c r="R11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S11">
         <v>2.92</v>
@@ -4057,22 +4057,22 @@
         <v>161</v>
       </c>
       <c r="F14">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="G14">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="H14">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="J14">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4105,10 +4105,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4323,10 +4323,10 @@
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O15">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P15">
         <v>1.91</v>
@@ -4335,13 +4335,13 @@
         <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S15">
         <v>3.6</v>
       </c>
       <c r="T15">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U15">
         <v>2.16</v>
@@ -4350,7 +4350,7 @@
         <v>1.53</v>
       </c>
       <c r="W15">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X15">
         <v>14.5</v>
@@ -4386,7 +4386,7 @@
         <v>18.5</v>
       </c>
       <c r="AI15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ15">
         <v>46</v>
@@ -4416,7 +4416,7 @@
         <v>16</v>
       </c>
       <c r="AS15">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15">
         <v>9.800000000000001</v>
@@ -4428,7 +4428,7 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX15">
         <v>15</v>
@@ -4440,16 +4440,16 @@
         <v>15.5</v>
       </c>
       <c r="BA15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC15">
         <v>7.8</v>
       </c>
-      <c r="BB15">
-        <v>7.8</v>
-      </c>
-      <c r="BC15">
-        <v>7.4</v>
-      </c>
       <c r="BD15">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE15">
         <v>8.800000000000001</v>
@@ -4464,61 +4464,61 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="CB15" t="s">
         <v>181</v>
@@ -4544,10 +4544,10 @@
         <v>1.88</v>
       </c>
       <c r="G16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I16">
         <v>4.5</v>
@@ -4556,7 +4556,7 @@
         <v>3.9</v>
       </c>
       <c r="K16">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L16">
         <v>1.25</v>
@@ -4565,13 +4565,13 @@
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O16">
         <v>1.16</v>
       </c>
       <c r="P16">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q16">
         <v>1.52</v>
@@ -4580,7 +4580,7 @@
         <v>1.6</v>
       </c>
       <c r="S16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T16">
         <v>1.48</v>
@@ -4589,10 +4589,10 @@
         <v>2.46</v>
       </c>
       <c r="V16">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W16">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4664,7 +4664,7 @@
         <v>1.23</v>
       </c>
       <c r="AU16">
-        <v>1.18</v>
+        <v>7</v>
       </c>
       <c r="AV16">
         <v>1.26</v>
@@ -4688,7 +4688,7 @@
         <v>1.26</v>
       </c>
       <c r="BC16">
-        <v>10.5</v>
+        <v>1.26</v>
       </c>
       <c r="BD16">
         <v>1.26</v>
@@ -4697,7 +4697,7 @@
         <v>1.26</v>
       </c>
       <c r="BF16">
-        <v>1.15</v>
+        <v>6.2</v>
       </c>
       <c r="BG16">
         <v>1.26</v>
@@ -4706,25 +4706,25 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BP16">
         <v>1000</v>
@@ -4742,7 +4742,7 @@
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BV16">
         <v>1000</v>
@@ -4754,7 +4754,7 @@
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
@@ -4786,10 +4786,10 @@
         <v>2.4</v>
       </c>
       <c r="G17">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H17">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I17">
         <v>3.1</v>
@@ -4798,7 +4798,7 @@
         <v>3.8</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4807,25 +4807,25 @@
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O17">
         <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q17">
         <v>1.55</v>
       </c>
       <c r="R17">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="S17">
         <v>2.3</v>
       </c>
       <c r="T17">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="U17">
         <v>2.58</v>
@@ -4834,7 +4834,7 @@
         <v>1.48</v>
       </c>
       <c r="W17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4855,7 +4855,7 @@
         <v>15</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE17">
         <v>1000</v>
@@ -4864,7 +4864,7 @@
         <v>1000</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH17">
         <v>1000</v>
@@ -5031,13 +5031,13 @@
         <v>2.58</v>
       </c>
       <c r="H18">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="I18">
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5273,7 +5273,7 @@
         <v>2.2</v>
       </c>
       <c r="H19">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -5282,16 +5282,16 @@
         <v>3.1</v>
       </c>
       <c r="K19">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M19">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N19">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
         <v>1.45</v>
@@ -5303,7 +5303,7 @@
         <v>2.24</v>
       </c>
       <c r="R19">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S19">
         <v>4.1</v>
@@ -5375,64 +5375,64 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AQ19">
-        <v>8</v>
+        <v>2.24</v>
       </c>
       <c r="AR19">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="AS19">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="AT19">
         <v>2.42</v>
       </c>
       <c r="AU19">
-        <v>6</v>
+        <v>2.48</v>
       </c>
       <c r="AV19">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="AW19">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="AX19">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AY19">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="AZ19">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="BA19">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="BB19">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="BC19">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="BD19">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="BE19">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="BF19">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="BG19">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
@@ -5450,7 +5450,7 @@
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP19">
         <v>1000</v>
@@ -5769,7 +5769,7 @@
         <v>4.5</v>
       </c>
       <c r="L21">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M21">
         <v>1.05</v>
@@ -5913,64 +5913,64 @@
         <v>9.6</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI21">
-        <v>1.28</v>
+        <v>3.4</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>11</v>
+      </c>
+      <c r="BN21">
+        <v>4.2</v>
+      </c>
+      <c r="BO21">
+        <v>3.75</v>
+      </c>
+      <c r="BP21">
+        <v>10.5</v>
+      </c>
+      <c r="BQ21">
         <v>7.8</v>
       </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.88</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.34</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.88</v>
-      </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS21">
-        <v>1.88</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU21">
-        <v>1.88</v>
+        <v>7.8</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW21">
-        <v>1.88</v>
+        <v>10</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY21">
-        <v>1.88</v>
+        <v>10</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA21">
-        <v>1.88</v>
+        <v>7.6</v>
       </c>
       <c r="CB21" t="s">
         <v>181</v>
@@ -6477,19 +6477,19 @@
         <v>171</v>
       </c>
       <c r="F24">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G24">
         <v>600</v>
       </c>
       <c r="H24">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="I24">
         <v>870</v>
       </c>
       <c r="J24">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6501,13 +6501,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O24">
         <v>1.02</v>
       </c>
       <c r="P24">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q24">
         <v>1.03</v>
@@ -6722,16 +6722,16 @@
         <v>2.76</v>
       </c>
       <c r="G25">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H25">
         <v>2.6</v>
       </c>
       <c r="I25">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K25">
         <v>3.65</v>
@@ -6743,13 +6743,13 @@
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O25">
         <v>1.33</v>
       </c>
       <c r="P25">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q25">
         <v>1.94</v>
@@ -6761,124 +6761,124 @@
         <v>3.35</v>
       </c>
       <c r="T25">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W25">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X25">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="Y25">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB25">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC25">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD25">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG25">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP25">
-        <v>1.32</v>
+        <v>12</v>
       </c>
       <c r="AQ25">
-        <v>1.3</v>
+        <v>9.6</v>
       </c>
       <c r="AR25">
-        <v>1.39</v>
+        <v>15</v>
       </c>
       <c r="AS25">
-        <v>1.39</v>
+        <v>7.6</v>
       </c>
       <c r="AT25">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="AU25">
-        <v>1.22</v>
+        <v>7</v>
       </c>
       <c r="AV25">
-        <v>1.33</v>
+        <v>10.5</v>
       </c>
       <c r="AW25">
-        <v>1.39</v>
+        <v>7</v>
       </c>
       <c r="AX25">
-        <v>1.39</v>
+        <v>16.5</v>
       </c>
       <c r="AY25">
-        <v>1.34</v>
+        <v>11</v>
       </c>
       <c r="AZ25">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BA25">
-        <v>1.39</v>
+        <v>7.8</v>
       </c>
       <c r="BB25">
-        <v>1.39</v>
+        <v>7.8</v>
       </c>
       <c r="BC25">
-        <v>1.39</v>
+        <v>7.2</v>
       </c>
       <c r="BD25">
-        <v>1.39</v>
+        <v>7.6</v>
       </c>
       <c r="BE25">
-        <v>1.39</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25">
-        <v>1.39</v>
+        <v>7</v>
       </c>
       <c r="BG25">
-        <v>1.39</v>
+        <v>19.5</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6961,13 +6961,13 @@
         <v>173</v>
       </c>
       <c r="F26">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G26">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H26">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I26">
         <v>3.6</v>
@@ -7000,13 +7000,13 @@
         <v>1.27</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T26">
         <v>1.8</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V26">
         <v>1.38</v>
@@ -7027,7 +7027,7 @@
         <v>90</v>
       </c>
       <c r="AB26">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC26">
         <v>11</v>
@@ -7039,7 +7039,7 @@
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="AG26">
         <v>22</v>
@@ -7075,13 +7075,13 @@
         <v>8.4</v>
       </c>
       <c r="AR26">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="AS26">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AT26">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AU26">
         <v>5.7</v>
@@ -7090,7 +7090,7 @@
         <v>9.6</v>
       </c>
       <c r="AW26">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="AX26">
         <v>9.199999999999999</v>
@@ -7102,25 +7102,25 @@
         <v>11.5</v>
       </c>
       <c r="BA26">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="BB26">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="BC26">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="BD26">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="BE26">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="BF26">
         <v>15.5</v>
       </c>
       <c r="BG26">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7138,49 +7138,49 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="CB26" t="s">
         <v>181</v>
@@ -7242,127 +7242,127 @@
         <v>1.81</v>
       </c>
       <c r="S27">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="T27">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U27">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="V27">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W27">
         <v>4.6</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB27">
+        <v>13.5</v>
+      </c>
+      <c r="AC27">
+        <v>18.5</v>
+      </c>
+      <c r="AD27">
+        <v>55</v>
+      </c>
+      <c r="AE27">
+        <v>200</v>
+      </c>
+      <c r="AF27">
+        <v>10</v>
+      </c>
+      <c r="AG27">
+        <v>11.5</v>
+      </c>
+      <c r="AH27">
         <v>36</v>
       </c>
-      <c r="AC27">
-        <v>1000</v>
-      </c>
-      <c r="AD27">
-        <v>1000</v>
-      </c>
-      <c r="AE27">
-        <v>1000</v>
-      </c>
-      <c r="AF27">
-        <v>970</v>
-      </c>
-      <c r="AG27">
-        <v>23</v>
-      </c>
-      <c r="AH27">
-        <v>1000</v>
-      </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ27">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AK27">
+        <v>13</v>
+      </c>
+      <c r="AL27">
         <v>34</v>
       </c>
-      <c r="AL27">
-        <v>1000</v>
-      </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN27">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP27">
-        <v>1.89</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="AR27">
-        <v>1.89</v>
+        <v>11.5</v>
       </c>
       <c r="AS27">
-        <v>1.89</v>
+        <v>11</v>
       </c>
       <c r="AT27">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AU27">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AV27">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="AW27">
-        <v>1.89</v>
+        <v>11.5</v>
       </c>
       <c r="AX27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY27">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>1.89</v>
+        <v>9</v>
       </c>
       <c r="BA27">
-        <v>1.89</v>
+        <v>11</v>
       </c>
       <c r="BB27">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC27">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BD27">
-        <v>1.89</v>
+        <v>9</v>
       </c>
       <c r="BE27">
-        <v>1.89</v>
+        <v>11</v>
       </c>
       <c r="BF27">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BG27">
-        <v>1.89</v>
+        <v>11.5</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7469,10 +7469,10 @@
         <v>1.12</v>
       </c>
       <c r="N28">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O28">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P28">
         <v>1.58</v>
@@ -7484,7 +7484,7 @@
         <v>1.2</v>
       </c>
       <c r="S28">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T28">
         <v>2.42</v>
@@ -7547,7 +7547,7 @@
         <v>310</v>
       </c>
       <c r="AN28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO28">
         <v>260</v>
@@ -7559,7 +7559,7 @@
         <v>11.5</v>
       </c>
       <c r="AR28">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS28">
         <v>12</v>
@@ -7586,7 +7586,7 @@
         <v>10</v>
       </c>
       <c r="BA28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB28">
         <v>16</v>
@@ -7598,13 +7598,13 @@
         <v>11</v>
       </c>
       <c r="BE28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF28">
         <v>16</v>
       </c>
       <c r="BG28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7690,7 +7690,7 @@
         <v>2.22</v>
       </c>
       <c r="G29">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H29">
         <v>3.55</v>
@@ -7705,7 +7705,7 @@
         <v>3.45</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M29">
         <v>1.11</v>
@@ -7720,7 +7720,7 @@
         <v>1.65</v>
       </c>
       <c r="Q29">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R29">
         <v>1.25</v>
@@ -7738,7 +7738,7 @@
         <v>1.33</v>
       </c>
       <c r="W29">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X29">
         <v>10.5</v>
@@ -7804,7 +7804,7 @@
         <v>22</v>
       </c>
       <c r="AS29">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT29">
         <v>7</v>
@@ -7831,7 +7831,7 @@
         <v>8.4</v>
       </c>
       <c r="BB29">
-        <v>24</v>
+        <v>7.4</v>
       </c>
       <c r="BC29">
         <v>21</v>
@@ -7849,64 +7849,64 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="CB29" t="s">
         <v>181</v>
@@ -7932,16 +7932,16 @@
         <v>2.34</v>
       </c>
       <c r="G30">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="H30">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I30">
         <v>3.3</v>
       </c>
       <c r="J30">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
         <v>3.8</v>
@@ -7950,37 +7950,37 @@
         <v>1.35</v>
       </c>
       <c r="M30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P30">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="Q30">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="R30">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S30">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T30">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U30">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="V30">
         <v>1.43</v>
       </c>
       <c r="W30">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="X30">
         <v>16</v>
@@ -8031,7 +8031,7 @@
         <v>100</v>
       </c>
       <c r="AN30">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AO30">
         <v>40</v>
@@ -8043,10 +8043,10 @@
         <v>12</v>
       </c>
       <c r="AR30">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS30">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT30">
         <v>10</v>
@@ -8058,7 +8058,7 @@
         <v>12</v>
       </c>
       <c r="AW30">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX30">
         <v>14</v>
@@ -8070,25 +8070,25 @@
         <v>14.5</v>
       </c>
       <c r="BA30">
+        <v>8.4</v>
+      </c>
+      <c r="BB30">
         <v>8</v>
       </c>
-      <c r="BB30">
+      <c r="BC30">
         <v>7.6</v>
       </c>
-      <c r="BC30">
-        <v>7.4</v>
-      </c>
       <c r="BD30">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE30">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF30">
         <v>15.5</v>
       </c>
       <c r="BG30">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH30">
         <v>4.3</v>
@@ -8458,10 +8458,10 @@
         <v>2</v>
       </c>
       <c r="U32">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
         <v>1.52</v>
@@ -8476,7 +8476,7 @@
         <v>25</v>
       </c>
       <c r="AA32">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -8485,31 +8485,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD32">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AE32">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="AG32">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH32">
         <v>26</v>
       </c>
       <c r="AI32">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
         <v>60</v>
       </c>
       <c r="AK32">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
         <v>1000</v>
@@ -8518,7 +8518,7 @@
         <v>50</v>
       </c>
       <c r="AO32">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
         <v>6.4</v>
@@ -8527,10 +8527,10 @@
         <v>8</v>
       </c>
       <c r="AR32">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS32">
-        <v>3.95</v>
+        <v>2.52</v>
       </c>
       <c r="AT32">
         <v>7.2</v>
@@ -8542,7 +8542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW32">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="AX32">
         <v>12.5</v>
@@ -8554,25 +8554,25 @@
         <v>15.5</v>
       </c>
       <c r="BA32">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="BB32">
-        <v>3.9</v>
+        <v>2.42</v>
       </c>
       <c r="BC32">
         <v>25</v>
       </c>
       <c r="BD32">
-        <v>3.95</v>
+        <v>2.52</v>
       </c>
       <c r="BE32">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="BF32">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="BG32">
-        <v>3.95</v>
+        <v>2.52</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8655,22 +8655,22 @@
         <v>180</v>
       </c>
       <c r="F33">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G33">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="H33">
+        <v>2.6</v>
+      </c>
+      <c r="I33">
+        <v>6.8</v>
+      </c>
+      <c r="J33">
         <v>4.3</v>
       </c>
-      <c r="I33">
-        <v>9.4</v>
-      </c>
-      <c r="J33">
-        <v>4.1</v>
-      </c>
       <c r="K33">
-        <v>10</v>
+        <v>950</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8679,19 +8679,19 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P33">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q33">
         <v>1.38</v>
       </c>
       <c r="R33">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S33">
         <v>2</v>
@@ -8703,10 +8703,10 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W33">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="X33">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="208">
   <si>
     <t>League</t>
   </si>
@@ -280,18 +280,21 @@
     <t>Spanish Segunda Division</t>
   </si>
   <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
-    <t>Dutch Eerste Divisie</t>
-  </si>
-  <si>
     <t>Slovenian 2 SNL</t>
   </si>
   <si>
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
+    <t>Georgian Umaglesi Liga</t>
+  </si>
+  <si>
     <t>Uruguayan Segunda Division</t>
   </si>
   <si>
@@ -304,6 +307,9 @@
     <t>Canadian Premier League</t>
   </si>
   <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
     <t>2026-10-04</t>
   </si>
   <si>
@@ -367,6 +373,24 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>21:05:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:15:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:10:00</t>
+  </si>
+  <si>
     <t>Real Cartagena</t>
   </si>
   <si>
@@ -394,12 +418,12 @@
     <t>Kagoshima Utd</t>
   </si>
   <si>
+    <t>Farense</t>
+  </si>
+  <si>
     <t>Tegevajaro Miyazaki</t>
   </si>
   <si>
-    <t>Farense</t>
-  </si>
-  <si>
     <t>BK Olympic</t>
   </si>
   <si>
@@ -409,12 +433,12 @@
     <t>Sociedad B</t>
   </si>
   <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
     <t>Bryne</t>
   </si>
   <si>
-    <t>VVV Venlo</t>
-  </si>
-  <si>
     <t>NK Slovenska Bistrica</t>
   </si>
   <si>
@@ -430,15 +454,18 @@
     <t>Umea FC</t>
   </si>
   <si>
+    <t>FC Iberia 1999</t>
+  </si>
+  <si>
+    <t>Triglav</t>
+  </si>
+  <si>
+    <t>Boston River</t>
+  </si>
+  <si>
     <t>Centro Atletico Fenix</t>
   </si>
   <si>
-    <t>Triglav</t>
-  </si>
-  <si>
-    <t>Boston River</t>
-  </si>
-  <si>
     <t>Las Palmas</t>
   </si>
   <si>
@@ -457,10 +484,34 @@
     <t>Cerro</t>
   </si>
   <si>
+    <t>FC Supra du Quebec</t>
+  </si>
+  <si>
     <t>Talleres</t>
   </si>
   <si>
-    <t>FC Supra du Quebec</t>
+    <t>Tigres FC Zipaquira</t>
+  </si>
+  <si>
+    <t>Internacional de Bogotá</t>
+  </si>
+  <si>
+    <t>Cucuta Deportivo</t>
+  </si>
+  <si>
+    <t>Trinidad &amp; Tobago</t>
+  </si>
+  <si>
+    <t>La Luz FC</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Racing Club (Uru)</t>
+  </si>
+  <si>
+    <t>Atletico Bucaramanga</t>
   </si>
   <si>
     <t>Boca Juniors de Cali</t>
@@ -490,12 +541,12 @@
     <t>Fukushima Utd</t>
   </si>
   <si>
+    <t>Chaves</t>
+  </si>
+  <si>
     <t>Omiya</t>
   </si>
   <si>
-    <t>Chaves</t>
-  </si>
-  <si>
     <t>Trelleborgs</t>
   </si>
   <si>
@@ -505,12 +556,12 @@
     <t>Granada</t>
   </si>
   <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Roda JC</t>
-  </si>
-  <si>
     <t>Rudar</t>
   </si>
   <si>
@@ -526,15 +577,18 @@
     <t>Hammarby TFF</t>
   </si>
   <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Jesenice</t>
+  </si>
+  <si>
+    <t>Juventud De Las Piedras</t>
+  </si>
+  <si>
     <t>Uruguay Montevideo FC</t>
   </si>
   <si>
-    <t>Jesenice</t>
-  </si>
-  <si>
-    <t>Juventud De Las Piedras</t>
-  </si>
-  <si>
     <t>Valladolid</t>
   </si>
   <si>
@@ -553,13 +607,37 @@
     <t>Wanderers (Uru)</t>
   </si>
   <si>
+    <t>Pacific</t>
+  </si>
+  <si>
     <t>Belgrano</t>
   </si>
   <si>
-    <t>Pacific</t>
-  </si>
-  <si>
-    <t>2026-10-02 22:47:54</t>
+    <t>Internacional de Palmira</t>
+  </si>
+  <si>
+    <t>Once Caldas</t>
+  </si>
+  <si>
+    <t>Deportivo Pereira</t>
+  </si>
+  <si>
+    <t>Curacao</t>
+  </si>
+  <si>
+    <t>River Plate (Uru)</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Penarol</t>
+  </si>
+  <si>
+    <t>Junior FC Barranquilla</t>
+  </si>
+  <si>
+    <t>2026-10-03 01:04:06</t>
   </si>
 </sst>
 </file>
@@ -891,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1141,34 +1219,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="F2">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="G2">
         <v>1.47</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>9.4</v>
+        <v>110</v>
       </c>
       <c r="J2">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1177,7 +1255,7 @@
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O2">
         <v>1.24</v>
@@ -1186,13 +1264,13 @@
         <v>2.16</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="T2">
         <v>2.04</v>
@@ -1201,10 +1279,10 @@
         <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1219,7 +1297,7 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC2">
         <v>1000</v>
@@ -1231,7 +1309,7 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>1000</v>
@@ -1291,7 +1369,7 @@
         <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
         <v>1.03</v>
@@ -1375,7 +1453,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1383,31 +1461,31 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="F3">
         <v>1.28</v>
       </c>
       <c r="G3">
+        <v>3.65</v>
+      </c>
+      <c r="H3">
+        <v>1.12</v>
+      </c>
+      <c r="I3">
         <v>110</v>
       </c>
-      <c r="H3">
-        <v>1.71</v>
-      </c>
-      <c r="I3">
-        <v>1000</v>
-      </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
         <v>110</v>
@@ -1416,13 +1494,13 @@
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>1.59</v>
       </c>
       <c r="O3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="P3">
         <v>1.48</v>
@@ -1434,19 +1512,19 @@
         <v>1.18</v>
       </c>
       <c r="S3">
+        <v>2.06</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
         <v>1.02</v>
       </c>
-      <c r="T3">
-        <v>1.01</v>
-      </c>
-      <c r="U3">
-        <v>1.01</v>
-      </c>
-      <c r="V3">
-        <v>1.01</v>
-      </c>
       <c r="W3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1461,13 +1539,13 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE3">
         <v>1000</v>
@@ -1506,7 +1584,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR3">
         <v>1.03</v>
@@ -1530,7 +1608,7 @@
         <v>1.03</v>
       </c>
       <c r="AY3">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3">
         <v>1.03</v>
@@ -1617,7 +1695,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1625,22 +1703,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="F4">
         <v>4.2</v>
       </c>
       <c r="G4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>1.75</v>
@@ -1652,7 +1730,7 @@
         <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1745,58 +1823,58 @@
         <v>50</v>
       </c>
       <c r="AP4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AQ4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AR4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AS4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AT4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AU4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AV4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AW4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AX4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AY4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AZ4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BA4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BB4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BC4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BD4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BE4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BG4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1859,7 +1937,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1867,16 +1945,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F5">
         <v>2.26</v>
@@ -2101,7 +2179,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2109,16 +2187,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="F6">
         <v>3.25</v>
@@ -2157,7 +2235,7 @@
         <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S6">
         <v>3.95</v>
@@ -2343,7 +2421,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2351,16 +2429,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="F7">
         <v>1.12</v>
@@ -2585,7 +2663,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2593,22 +2671,22 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="F8">
         <v>2.22</v>
       </c>
       <c r="G8">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H8">
         <v>3.25</v>
@@ -2656,7 +2734,7 @@
         <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2827,7 +2905,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2835,31 +2913,31 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>1.43</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="I9">
         <v>870</v>
       </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2871,22 +2949,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
         <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="R9">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="S9">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2898,7 +2976,7 @@
         <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3069,7 +3147,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3077,16 +3155,16 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -3311,78 +3389,78 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
-        <v>2.92</v>
+        <v>2.46</v>
       </c>
       <c r="H11">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="I11">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K11">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="O11">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P11">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Q11">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="R11">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="T11">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3400,7 +3478,7 @@
         <v>1000</v>
       </c>
       <c r="AC11">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
         <v>1000</v>
@@ -3439,192 +3517,192 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI11">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="CB11" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="F12">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="G12">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="H12">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="I12">
+        <v>2.96</v>
+      </c>
+      <c r="J12">
+        <v>3.35</v>
+      </c>
+      <c r="K12">
+        <v>4.8</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.02</v>
+      </c>
+      <c r="N12">
         <v>4</v>
       </c>
-      <c r="J12">
-        <v>3.3</v>
-      </c>
-      <c r="K12">
-        <v>4.2</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>3.45</v>
-      </c>
       <c r="O12">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P12">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Q12">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="R12">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S12">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3642,7 +3720,7 @@
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3681,121 +3759,121 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH12">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3803,16 +3881,16 @@
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="F13">
         <v>2.94</v>
@@ -3977,16 +4055,16 @@
         <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3995,49 +4073,49 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB13" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4045,34 +4123,34 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="F14">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="G14">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="H14">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="I14">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4105,10 +4183,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4279,7 +4357,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4287,22 +4365,22 @@
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="F15">
         <v>2.66</v>
       </c>
       <c r="G15">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H15">
         <v>2.78</v>
@@ -4332,7 +4410,7 @@
         <v>1.91</v>
       </c>
       <c r="Q15">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R15">
         <v>1.35</v>
@@ -4521,7 +4599,7 @@
         <v>1.06</v>
       </c>
       <c r="CB15" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4529,70 +4607,70 @@
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="F16">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="G16">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="H16">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="I16">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J16">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L16">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O16">
         <v>1.16</v>
       </c>
       <c r="P16">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R16">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S16">
         <v>2.3</v>
       </c>
       <c r="T16">
+        <v>1.47</v>
+      </c>
+      <c r="U16">
+        <v>2.58</v>
+      </c>
+      <c r="V16">
         <v>1.48</v>
       </c>
-      <c r="U16">
-        <v>2.46</v>
-      </c>
-      <c r="V16">
-        <v>1.28</v>
-      </c>
       <c r="W16">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4607,13 +4685,13 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE16">
         <v>1000</v>
@@ -4622,7 +4700,7 @@
         <v>1000</v>
       </c>
       <c r="AG16">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AH16">
         <v>1000</v>
@@ -4643,88 +4721,88 @@
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BG16">
-        <v>1.26</v>
+        <v>10</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
         <v>1000</v>
@@ -4742,7 +4820,7 @@
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
         <v>1000</v>
@@ -4754,7 +4832,7 @@
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
@@ -4763,7 +4841,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4771,70 +4849,70 @@
         <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="F17">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="G17">
-        <v>2.66</v>
+        <v>2.06</v>
       </c>
       <c r="H17">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="I17">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J17">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
         <v>4.9</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O17">
         <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q17">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S17">
         <v>2.3</v>
       </c>
       <c r="T17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U17">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="W17">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4849,13 +4927,13 @@
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AC17">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AD17">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
         <v>1000</v>
@@ -4864,7 +4942,7 @@
         <v>1000</v>
       </c>
       <c r="AG17">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AH17">
         <v>1000</v>
@@ -4885,76 +4963,76 @@
         <v>1000</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO17">
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BF17">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BG17">
-        <v>10</v>
+        <v>1.26</v>
       </c>
       <c r="BH17">
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BL17">
         <v>1000</v>
@@ -4966,7 +5044,7 @@
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BP17">
         <v>1000</v>
@@ -4984,7 +5062,7 @@
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BV17">
         <v>1000</v>
@@ -5005,7 +5083,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5013,16 +5091,16 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E18" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="F18">
         <v>1.12</v>
@@ -5247,7 +5325,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5255,16 +5333,16 @@
         <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="F19">
         <v>1.98</v>
@@ -5276,7 +5354,7 @@
         <v>3.85</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J19">
         <v>3.1</v>
@@ -5315,7 +5393,7 @@
         <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W19">
         <v>1.83</v>
@@ -5378,7 +5456,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ19">
-        <v>2.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19">
         <v>2.14</v>
@@ -5438,58 +5516,58 @@
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="CB19" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5497,16 +5575,16 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="F20">
         <v>1.1</v>
@@ -5731,7 +5809,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5739,16 +5817,16 @@
         <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="F21">
         <v>1.59</v>
@@ -5784,7 +5862,7 @@
         <v>2.1</v>
       </c>
       <c r="Q21">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R21">
         <v>1.42</v>
@@ -5793,13 +5871,13 @@
         <v>3.05</v>
       </c>
       <c r="T21">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U21">
         <v>2</v>
       </c>
       <c r="V21">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W21">
         <v>2.52</v>
@@ -5865,10 +5943,10 @@
         <v>18</v>
       </c>
       <c r="AR21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT21">
         <v>8</v>
@@ -5880,7 +5958,7 @@
         <v>20</v>
       </c>
       <c r="AW21">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX21">
         <v>8.800000000000001</v>
@@ -5892,7 +5970,7 @@
         <v>18</v>
       </c>
       <c r="BA21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB21">
         <v>13.5</v>
@@ -5901,16 +5979,16 @@
         <v>14.5</v>
       </c>
       <c r="BD21">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF21">
         <v>7.4</v>
       </c>
       <c r="BG21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH21">
         <v>3.75</v>
@@ -5928,7 +6006,7 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN21">
         <v>4.2</v>
@@ -5946,10 +6024,10 @@
         <v>26</v>
       </c>
       <c r="BS21">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU21">
         <v>7.8</v>
@@ -5958,22 +6036,22 @@
         <v>60</v>
       </c>
       <c r="BW21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX21">
         <v>60</v>
       </c>
       <c r="BY21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ21">
         <v>18.5</v>
       </c>
       <c r="CA21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB21" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5981,16 +6059,16 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="F22">
         <v>3.8</v>
@@ -6029,10 +6107,10 @@
         <v>1.51</v>
       </c>
       <c r="R22">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S22">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6215,7 +6293,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6223,58 +6301,58 @@
         <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="F23">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="G23">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="H23">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="I23">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J23">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="K23">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L23">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="O23">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P23">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q23">
-        <v>2.12</v>
+        <v>1.37</v>
       </c>
       <c r="R23">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
-        <v>2.94</v>
+        <v>1.37</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6283,10 +6361,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W23">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6451,13 +6529,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6465,16 +6543,16 @@
         <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F24">
         <v>1.47</v>
@@ -6483,13 +6561,13 @@
         <v>600</v>
       </c>
       <c r="H24">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I24">
         <v>870</v>
       </c>
       <c r="J24">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6699,7 +6777,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6707,34 +6785,34 @@
         <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E25" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="F25">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H25">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I25">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J25">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K25">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L25">
         <v>1.34</v>
@@ -6743,16 +6821,16 @@
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O25">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P25">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q25">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R25">
         <v>1.31</v>
@@ -6761,25 +6839,25 @@
         <v>3.35</v>
       </c>
       <c r="T25">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="U25">
         <v>2.12</v>
       </c>
       <c r="V25">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y25">
         <v>11.5</v>
       </c>
       <c r="Z25">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA25">
         <v>46</v>
@@ -6806,7 +6884,7 @@
         <v>18</v>
       </c>
       <c r="AI25">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ25">
         <v>50</v>
@@ -6821,22 +6899,22 @@
         <v>110</v>
       </c>
       <c r="AN25">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO25">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AP25">
         <v>12</v>
       </c>
       <c r="AQ25">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR25">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS25">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25">
         <v>10</v>
@@ -6848,7 +6926,7 @@
         <v>10.5</v>
       </c>
       <c r="AW25">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX25">
         <v>16.5</v>
@@ -6860,22 +6938,22 @@
         <v>15</v>
       </c>
       <c r="BA25">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC25">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD25">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE25">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG25">
         <v>19.5</v>
@@ -6941,108 +7019,108 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="F26">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G26">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H26">
+        <v>5.4</v>
+      </c>
+      <c r="I26">
+        <v>10.5</v>
+      </c>
+      <c r="J26">
         <v>3.2</v>
       </c>
-      <c r="I26">
-        <v>3.6</v>
-      </c>
-      <c r="J26">
-        <v>3.4</v>
-      </c>
       <c r="K26">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="L26">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="O26">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P26">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="Q26">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R26">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="S26">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="T26">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="W26">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="X26">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
         <v>1000</v>
       </c>
       <c r="AA26">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
         <v>1000</v>
@@ -7063,127 +7141,127 @@
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR26">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="AS26">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU26">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV26">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW26">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY26">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA26">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="BB26">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="BC26">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="BD26">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="BE26">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="BF26">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA26">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7191,432 +7269,432 @@
         <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="F27">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="G27">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="H27">
-        <v>12.5</v>
+        <v>3.4</v>
       </c>
       <c r="I27">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="J27">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
+        <v>3.6</v>
+      </c>
+      <c r="L27">
+        <v>1.44</v>
+      </c>
+      <c r="M27">
+        <v>1.08</v>
+      </c>
+      <c r="N27">
+        <v>3.25</v>
+      </c>
+      <c r="O27">
+        <v>1.36</v>
+      </c>
+      <c r="P27">
+        <v>1.76</v>
+      </c>
+      <c r="Q27">
+        <v>2.06</v>
+      </c>
+      <c r="R27">
+        <v>1.27</v>
+      </c>
+      <c r="S27">
+        <v>3.65</v>
+      </c>
+      <c r="T27">
+        <v>1.8</v>
+      </c>
+      <c r="U27">
+        <v>1.95</v>
+      </c>
+      <c r="V27">
+        <v>1.38</v>
+      </c>
+      <c r="W27">
+        <v>1.72</v>
+      </c>
+      <c r="X27">
+        <v>28</v>
+      </c>
+      <c r="Y27">
+        <v>13</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>90</v>
+      </c>
+      <c r="AB27">
+        <v>970</v>
+      </c>
+      <c r="AC27">
+        <v>11</v>
+      </c>
+      <c r="AD27">
+        <v>970</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>36</v>
+      </c>
+      <c r="AG27">
+        <v>22</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>1000</v>
+      </c>
+      <c r="AK27">
+        <v>1000</v>
+      </c>
+      <c r="AL27">
+        <v>1000</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>23</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>8.6</v>
+      </c>
+      <c r="AQ27">
+        <v>8.4</v>
+      </c>
+      <c r="AR27">
+        <v>1.71</v>
+      </c>
+      <c r="AS27">
+        <v>1.68</v>
+      </c>
+      <c r="AT27">
+        <v>6.8</v>
+      </c>
+      <c r="AU27">
+        <v>5.7</v>
+      </c>
+      <c r="AV27">
+        <v>9.6</v>
+      </c>
+      <c r="AW27">
+        <v>1.71</v>
+      </c>
+      <c r="AX27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY27">
         <v>8</v>
       </c>
-      <c r="L27">
-        <v>1.21</v>
-      </c>
-      <c r="M27">
-        <v>1.02</v>
-      </c>
-      <c r="N27">
-        <v>6.2</v>
-      </c>
-      <c r="O27">
-        <v>1.11</v>
-      </c>
-      <c r="P27">
-        <v>2.96</v>
-      </c>
-      <c r="Q27">
-        <v>1.35</v>
-      </c>
-      <c r="R27">
-        <v>1.81</v>
-      </c>
-      <c r="S27">
-        <v>1.96</v>
-      </c>
-      <c r="T27">
-        <v>1.85</v>
-      </c>
-      <c r="U27">
-        <v>2.06</v>
-      </c>
-      <c r="V27">
-        <v>1.07</v>
-      </c>
-      <c r="W27">
-        <v>4.6</v>
-      </c>
-      <c r="X27">
-        <v>50</v>
-      </c>
-      <c r="Y27">
-        <v>65</v>
-      </c>
-      <c r="Z27">
-        <v>160</v>
-      </c>
-      <c r="AA27">
-        <v>500</v>
-      </c>
-      <c r="AB27">
-        <v>13.5</v>
-      </c>
-      <c r="AC27">
-        <v>18.5</v>
-      </c>
-      <c r="AD27">
-        <v>55</v>
-      </c>
-      <c r="AE27">
-        <v>200</v>
-      </c>
-      <c r="AF27">
-        <v>10</v>
-      </c>
-      <c r="AG27">
+      <c r="AZ27">
         <v>11.5</v>
       </c>
-      <c r="AH27">
-        <v>36</v>
-      </c>
-      <c r="AI27">
-        <v>140</v>
-      </c>
-      <c r="AJ27">
-        <v>11</v>
-      </c>
-      <c r="AK27">
-        <v>13</v>
-      </c>
-      <c r="AL27">
-        <v>34</v>
-      </c>
-      <c r="AM27">
-        <v>140</v>
-      </c>
-      <c r="AN27">
-        <v>3.45</v>
-      </c>
-      <c r="AO27">
-        <v>190</v>
-      </c>
-      <c r="AP27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ27">
-        <v>10</v>
-      </c>
-      <c r="AR27">
-        <v>11.5</v>
-      </c>
-      <c r="AS27">
-        <v>11</v>
-      </c>
-      <c r="AT27">
-        <v>11.5</v>
-      </c>
-      <c r="AU27">
+      <c r="BA27">
+        <v>1.71</v>
+      </c>
+      <c r="BB27">
+        <v>1.71</v>
+      </c>
+      <c r="BC27">
+        <v>1.71</v>
+      </c>
+      <c r="BD27">
+        <v>1.71</v>
+      </c>
+      <c r="BE27">
+        <v>1.71</v>
+      </c>
+      <c r="BF27">
         <v>15.5</v>
       </c>
-      <c r="AV27">
-        <v>10</v>
-      </c>
-      <c r="AW27">
-        <v>11.5</v>
-      </c>
-      <c r="AX27">
-        <v>9</v>
-      </c>
-      <c r="AY27">
-        <v>10</v>
-      </c>
-      <c r="AZ27">
-        <v>9</v>
-      </c>
-      <c r="BA27">
-        <v>11</v>
-      </c>
-      <c r="BB27">
-        <v>9.6</v>
-      </c>
-      <c r="BC27">
-        <v>11.5</v>
-      </c>
-      <c r="BD27">
-        <v>9</v>
-      </c>
-      <c r="BE27">
-        <v>11</v>
-      </c>
-      <c r="BF27">
-        <v>3.2</v>
-      </c>
       <c r="BG27">
-        <v>11.5</v>
+        <v>1.71</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.51</v>
+        <v>2.72</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.37</v>
+        <v>4</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.6</v>
+        <v>2.76</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="CB27" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E28" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="F28">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="G28">
+        <v>1.28</v>
+      </c>
+      <c r="H28">
+        <v>12.5</v>
+      </c>
+      <c r="I28">
+        <v>14.5</v>
+      </c>
+      <c r="J28">
+        <v>7.2</v>
+      </c>
+      <c r="K28">
+        <v>8</v>
+      </c>
+      <c r="L28">
+        <v>1.21</v>
+      </c>
+      <c r="M28">
+        <v>1.02</v>
+      </c>
+      <c r="N28">
+        <v>6.2</v>
+      </c>
+      <c r="O28">
+        <v>1.11</v>
+      </c>
+      <c r="P28">
+        <v>2.96</v>
+      </c>
+      <c r="Q28">
+        <v>1.35</v>
+      </c>
+      <c r="R28">
         <v>1.81</v>
       </c>
-      <c r="H28">
-        <v>5.9</v>
-      </c>
-      <c r="I28">
-        <v>6.8</v>
-      </c>
-      <c r="J28">
-        <v>3.5</v>
-      </c>
-      <c r="K28">
-        <v>3.7</v>
-      </c>
-      <c r="L28">
-        <v>1.56</v>
-      </c>
-      <c r="M28">
-        <v>1.12</v>
-      </c>
-      <c r="N28">
-        <v>2.68</v>
-      </c>
-      <c r="O28">
-        <v>1.55</v>
-      </c>
-      <c r="P28">
-        <v>1.58</v>
-      </c>
-      <c r="Q28">
-        <v>2.6</v>
-      </c>
-      <c r="R28">
-        <v>1.2</v>
-      </c>
       <c r="S28">
-        <v>5.4</v>
+        <v>1.96</v>
       </c>
       <c r="T28">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="U28">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="V28">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="W28">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="X28">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="Y28">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="Z28">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AA28">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AB28">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="AD28">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AE28">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AF28">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>11.5</v>
       </c>
       <c r="AH28">
+        <v>36</v>
+      </c>
+      <c r="AI28">
+        <v>140</v>
+      </c>
+      <c r="AJ28">
+        <v>11</v>
+      </c>
+      <c r="AK28">
+        <v>13</v>
+      </c>
+      <c r="AL28">
         <v>34</v>
       </c>
-      <c r="AI28">
-        <v>160</v>
-      </c>
-      <c r="AJ28">
-        <v>19</v>
-      </c>
-      <c r="AK28">
-        <v>26</v>
-      </c>
-      <c r="AL28">
-        <v>70</v>
-      </c>
       <c r="AM28">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="AN28">
-        <v>18</v>
+        <v>3.45</v>
       </c>
       <c r="AO28">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="AP28">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ28">
+        <v>10</v>
+      </c>
+      <c r="AR28">
         <v>11.5</v>
       </c>
-      <c r="AR28">
+      <c r="AS28">
         <v>11</v>
       </c>
-      <c r="AS28">
-        <v>12</v>
-      </c>
       <c r="AT28">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU28">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="AV28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AW28">
         <v>11.5</v>
       </c>
       <c r="AX28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY28">
         <v>10</v>
       </c>
       <c r="AZ28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB28">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="BC28">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BD28">
+        <v>9</v>
+      </c>
+      <c r="BE28">
         <v>11</v>
       </c>
-      <c r="BE28">
-        <v>12.5</v>
-      </c>
       <c r="BF28">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="BG28">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>2.36</v>
+        <v>1.96</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7628,25 +7706,25 @@
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7667,7 +7745,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7675,674 +7753,674 @@
         <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E29" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="F29">
+        <v>1.75</v>
+      </c>
+      <c r="G29">
+        <v>1.81</v>
+      </c>
+      <c r="H29">
+        <v>5.9</v>
+      </c>
+      <c r="I29">
+        <v>6.8</v>
+      </c>
+      <c r="J29">
+        <v>3.5</v>
+      </c>
+      <c r="K29">
+        <v>3.7</v>
+      </c>
+      <c r="L29">
+        <v>1.56</v>
+      </c>
+      <c r="M29">
+        <v>1.12</v>
+      </c>
+      <c r="N29">
+        <v>2.68</v>
+      </c>
+      <c r="O29">
+        <v>1.55</v>
+      </c>
+      <c r="P29">
+        <v>1.58</v>
+      </c>
+      <c r="Q29">
+        <v>2.6</v>
+      </c>
+      <c r="R29">
+        <v>1.2</v>
+      </c>
+      <c r="S29">
+        <v>5.3</v>
+      </c>
+      <c r="T29">
+        <v>2.42</v>
+      </c>
+      <c r="U29">
+        <v>1.67</v>
+      </c>
+      <c r="V29">
+        <v>1.17</v>
+      </c>
+      <c r="W29">
         <v>2.22</v>
       </c>
-      <c r="G29">
-        <v>2.46</v>
-      </c>
-      <c r="H29">
-        <v>3.55</v>
-      </c>
-      <c r="I29">
-        <v>4.1</v>
-      </c>
-      <c r="J29">
-        <v>3</v>
-      </c>
-      <c r="K29">
-        <v>3.45</v>
-      </c>
-      <c r="L29">
-        <v>1.48</v>
-      </c>
-      <c r="M29">
-        <v>1.11</v>
-      </c>
-      <c r="N29">
-        <v>2.96</v>
-      </c>
-      <c r="O29">
-        <v>1.45</v>
-      </c>
-      <c r="P29">
-        <v>1.65</v>
-      </c>
-      <c r="Q29">
-        <v>2.28</v>
-      </c>
-      <c r="R29">
-        <v>1.25</v>
-      </c>
-      <c r="S29">
-        <v>4.4</v>
-      </c>
-      <c r="T29">
-        <v>1.94</v>
-      </c>
-      <c r="U29">
-        <v>1.88</v>
-      </c>
-      <c r="V29">
-        <v>1.33</v>
-      </c>
-      <c r="W29">
-        <v>1.68</v>
-      </c>
       <c r="X29">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y29">
+        <v>15</v>
+      </c>
+      <c r="Z29">
+        <v>60</v>
+      </c>
+      <c r="AA29">
+        <v>270</v>
+      </c>
+      <c r="AB29">
+        <v>6.2</v>
+      </c>
+      <c r="AC29">
+        <v>9</v>
+      </c>
+      <c r="AD29">
+        <v>27</v>
+      </c>
+      <c r="AE29">
+        <v>160</v>
+      </c>
+      <c r="AF29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG29">
+        <v>11.5</v>
+      </c>
+      <c r="AH29">
+        <v>34</v>
+      </c>
+      <c r="AI29">
+        <v>160</v>
+      </c>
+      <c r="AJ29">
+        <v>19</v>
+      </c>
+      <c r="AK29">
+        <v>26</v>
+      </c>
+      <c r="AL29">
+        <v>70</v>
+      </c>
+      <c r="AM29">
+        <v>310</v>
+      </c>
+      <c r="AN29">
+        <v>18</v>
+      </c>
+      <c r="AO29">
+        <v>260</v>
+      </c>
+      <c r="AP29">
+        <v>7.8</v>
+      </c>
+      <c r="AQ29">
+        <v>11.5</v>
+      </c>
+      <c r="AR29">
+        <v>11</v>
+      </c>
+      <c r="AS29">
         <v>12</v>
       </c>
-      <c r="Z29">
-        <v>27</v>
-      </c>
-      <c r="AA29">
-        <v>100</v>
-      </c>
-      <c r="AB29">
-        <v>8.6</v>
-      </c>
-      <c r="AC29">
-        <v>7.8</v>
-      </c>
-      <c r="AD29">
-        <v>17</v>
-      </c>
-      <c r="AE29">
-        <v>60</v>
-      </c>
-      <c r="AF29">
-        <v>14.5</v>
-      </c>
-      <c r="AG29">
-        <v>12</v>
-      </c>
-      <c r="AH29">
-        <v>22</v>
-      </c>
-      <c r="AI29">
-        <v>80</v>
-      </c>
-      <c r="AJ29">
-        <v>34</v>
-      </c>
-      <c r="AK29">
-        <v>32</v>
-      </c>
-      <c r="AL29">
-        <v>55</v>
-      </c>
-      <c r="AM29">
-        <v>170</v>
-      </c>
-      <c r="AN29">
-        <v>28</v>
-      </c>
-      <c r="AO29">
-        <v>80</v>
-      </c>
-      <c r="AP29">
-        <v>8.6</v>
-      </c>
-      <c r="AQ29">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR29">
-        <v>22</v>
-      </c>
-      <c r="AS29">
-        <v>8.4</v>
-      </c>
       <c r="AT29">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AU29">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AV29">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AW29">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AX29">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AY29">
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA29">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BB29">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BC29">
         <v>21</v>
       </c>
       <c r="BD29">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BE29">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BF29">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BG29">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BH29">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.4</v>
+        <v>1.29</v>
       </c>
       <c r="BJ29">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>7.6</v>
+        <v>2.36</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>4.3</v>
+        <v>1.56</v>
       </c>
       <c r="BP29">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="F30">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="G30">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="H30">
+        <v>3.55</v>
+      </c>
+      <c r="I30">
+        <v>4.1</v>
+      </c>
+      <c r="J30">
         <v>3</v>
       </c>
-      <c r="I30">
-        <v>3.3</v>
-      </c>
-      <c r="J30">
-        <v>3.25</v>
-      </c>
       <c r="K30">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L30">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="M30">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N30">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="O30">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="P30">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="Q30">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S30">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T30">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="U30">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="V30">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X30">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="Y30">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA30">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AB30">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC30">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD30">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE30">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AF30">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG30">
         <v>12</v>
       </c>
       <c r="AH30">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AI30">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AJ30">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK30">
         <v>32</v>
       </c>
       <c r="AL30">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM30">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AN30">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="AO30">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AP30">
+        <v>8.6</v>
+      </c>
+      <c r="AQ30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR30">
+        <v>22</v>
+      </c>
+      <c r="AS30">
+        <v>8.4</v>
+      </c>
+      <c r="AT30">
+        <v>7</v>
+      </c>
+      <c r="AU30">
+        <v>6.4</v>
+      </c>
+      <c r="AV30">
         <v>13.5</v>
-      </c>
-      <c r="AQ30">
-        <v>12</v>
-      </c>
-      <c r="AR30">
-        <v>7.2</v>
-      </c>
-      <c r="AS30">
-        <v>9</v>
-      </c>
-      <c r="AT30">
-        <v>10</v>
-      </c>
-      <c r="AU30">
-        <v>7.4</v>
-      </c>
-      <c r="AV30">
-        <v>12</v>
       </c>
       <c r="AW30">
         <v>8.199999999999999</v>
       </c>
       <c r="AX30">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AY30">
         <v>10</v>
       </c>
       <c r="AZ30">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA30">
         <v>8.4</v>
       </c>
       <c r="BB30">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BC30">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BD30">
         <v>8.199999999999999</v>
       </c>
       <c r="BE30">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BG30">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH30">
+        <v>3.05</v>
+      </c>
+      <c r="BI30">
+        <v>2.4</v>
+      </c>
+      <c r="BJ30">
+        <v>11</v>
+      </c>
+      <c r="BK30">
+        <v>7.6</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>21</v>
+      </c>
+      <c r="BN30">
+        <v>5.1</v>
+      </c>
+      <c r="BO30">
         <v>4.3</v>
       </c>
-      <c r="BI30">
-        <v>2.94</v>
-      </c>
-      <c r="BJ30">
-        <v>1000</v>
-      </c>
-      <c r="BK30">
-        <v>5.9</v>
-      </c>
-      <c r="BL30">
-        <v>1000</v>
-      </c>
-      <c r="BM30">
-        <v>1.01</v>
-      </c>
-      <c r="BN30">
+      <c r="BP30">
+        <v>19</v>
+      </c>
+      <c r="BQ30">
+        <v>13</v>
+      </c>
+      <c r="BR30">
+        <v>38</v>
+      </c>
+      <c r="BS30">
+        <v>26</v>
+      </c>
+      <c r="BT30">
         <v>7.2</v>
       </c>
-      <c r="BO30">
-        <v>3.75</v>
-      </c>
-      <c r="BP30">
-        <v>1000</v>
-      </c>
-      <c r="BQ30">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR30">
-        <v>1000</v>
-      </c>
-      <c r="BS30">
-        <v>1.01</v>
-      </c>
-      <c r="BT30">
-        <v>1000</v>
-      </c>
       <c r="BU30">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="CB30" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="F31">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="G31">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="H31">
-        <v>2.28</v>
+        <v>2.98</v>
       </c>
       <c r="I31">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J31">
         <v>3.2</v>
       </c>
       <c r="K31">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M31">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N31">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="O31">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="P31">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="Q31">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="R31">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="S31">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="T31">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB31">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC31">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN31">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP31">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ31">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR31">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS31">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AT31">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU31">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV31">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW31">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX31">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY31">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ31">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA31">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB31">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC31">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BD31">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BF31">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BI31">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL31">
         <v>1000</v>
@@ -8351,16 +8429,16 @@
         <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP31">
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR31">
         <v>1000</v>
@@ -8372,7 +8450,7 @@
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8393,117 +8471,117 @@
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E32" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="F32">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G32">
+        <v>3.65</v>
+      </c>
+      <c r="H32">
+        <v>2.28</v>
+      </c>
+      <c r="I32">
         <v>2.9</v>
       </c>
-      <c r="H32">
-        <v>2.96</v>
-      </c>
-      <c r="I32">
-        <v>3.35</v>
-      </c>
       <c r="J32">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K32">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="L32">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="N32">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="O32">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P32">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q32">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="R32">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="T32">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W32">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="X32">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
         <v>1000</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
         <v>1000</v>
       </c>
       <c r="AF32">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
         <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
         <v>1000</v>
@@ -8515,153 +8593,153 @@
         <v>1000</v>
       </c>
       <c r="AN32">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR32">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS32">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AT32">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU32">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV32">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW32">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AX32">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY32">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA32">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="BB32">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="BC32">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BD32">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="BE32">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="BF32">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI32">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="F33">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="G33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H33">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="I33">
         <v>6.8</v>
@@ -8706,7 +8784,7 @@
         <v>1.17</v>
       </c>
       <c r="W33">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -8877,7 +8955,2185 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>181</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34">
+        <v>2.66</v>
+      </c>
+      <c r="G34">
+        <v>3.1</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>3.35</v>
+      </c>
+      <c r="J34">
+        <v>2.8</v>
+      </c>
+      <c r="K34">
+        <v>3.45</v>
+      </c>
+      <c r="L34">
+        <v>1.55</v>
+      </c>
+      <c r="M34">
+        <v>1.12</v>
+      </c>
+      <c r="N34">
+        <v>2.56</v>
+      </c>
+      <c r="O34">
+        <v>1.45</v>
+      </c>
+      <c r="P34">
+        <v>1.56</v>
+      </c>
+      <c r="Q34">
+        <v>2.56</v>
+      </c>
+      <c r="R34">
+        <v>1.21</v>
+      </c>
+      <c r="S34">
+        <v>4.7</v>
+      </c>
+      <c r="T34">
+        <v>2</v>
+      </c>
+      <c r="U34">
+        <v>1.78</v>
+      </c>
+      <c r="V34">
+        <v>1.42</v>
+      </c>
+      <c r="W34">
+        <v>1.48</v>
+      </c>
+      <c r="X34">
+        <v>13.5</v>
+      </c>
+      <c r="Y34">
+        <v>11.5</v>
+      </c>
+      <c r="Z34">
+        <v>25</v>
+      </c>
+      <c r="AA34">
+        <v>80</v>
+      </c>
+      <c r="AB34">
+        <v>10</v>
+      </c>
+      <c r="AC34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD34">
+        <v>55</v>
+      </c>
+      <c r="AE34">
+        <v>65</v>
+      </c>
+      <c r="AF34">
+        <v>23</v>
+      </c>
+      <c r="AG34">
+        <v>15</v>
+      </c>
+      <c r="AH34">
+        <v>26</v>
+      </c>
+      <c r="AI34">
+        <v>95</v>
+      </c>
+      <c r="AJ34">
+        <v>60</v>
+      </c>
+      <c r="AK34">
+        <v>55</v>
+      </c>
+      <c r="AL34">
+        <v>85</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>50</v>
+      </c>
+      <c r="AO34">
+        <v>80</v>
+      </c>
+      <c r="AP34">
+        <v>6.4</v>
+      </c>
+      <c r="AQ34">
+        <v>8</v>
+      </c>
+      <c r="AR34">
+        <v>14</v>
+      </c>
+      <c r="AS34">
+        <v>3.4</v>
+      </c>
+      <c r="AT34">
+        <v>7.2</v>
+      </c>
+      <c r="AU34">
+        <v>5.5</v>
+      </c>
+      <c r="AV34">
+        <v>10.5</v>
+      </c>
+      <c r="AW34">
+        <v>3.35</v>
+      </c>
+      <c r="AX34">
+        <v>12.5</v>
+      </c>
+      <c r="AY34">
+        <v>10.5</v>
+      </c>
+      <c r="AZ34">
+        <v>15.5</v>
+      </c>
+      <c r="BA34">
+        <v>3.45</v>
+      </c>
+      <c r="BB34">
+        <v>3.35</v>
+      </c>
+      <c r="BC34">
+        <v>25</v>
+      </c>
+      <c r="BD34">
+        <v>3.4</v>
+      </c>
+      <c r="BE34">
+        <v>3.55</v>
+      </c>
+      <c r="BF34">
+        <v>3.3</v>
+      </c>
+      <c r="BG34">
+        <v>3.4</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>2.24</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.12</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.12</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.85</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.12</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.12</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.14</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.12</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.12</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.12</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" t="s">
+        <v>158</v>
+      </c>
+      <c r="E35" t="s">
+        <v>199</v>
+      </c>
+      <c r="F35">
+        <v>2.8</v>
+      </c>
+      <c r="G35">
+        <v>3.4</v>
+      </c>
+      <c r="H35">
+        <v>2.7</v>
+      </c>
+      <c r="I35">
+        <v>3.25</v>
+      </c>
+      <c r="J35">
+        <v>2.78</v>
+      </c>
+      <c r="K35">
+        <v>3.7</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>2.44</v>
+      </c>
+      <c r="O35">
+        <v>1.54</v>
+      </c>
+      <c r="P35">
+        <v>1.44</v>
+      </c>
+      <c r="Q35">
+        <v>2.6</v>
+      </c>
+      <c r="R35">
+        <v>1.13</v>
+      </c>
+      <c r="S35">
+        <v>2.6</v>
+      </c>
+      <c r="T35">
+        <v>1.01</v>
+      </c>
+      <c r="U35">
+        <v>1.01</v>
+      </c>
+      <c r="V35">
+        <v>1.45</v>
+      </c>
+      <c r="W35">
+        <v>1.42</v>
+      </c>
+      <c r="X35">
+        <v>1000</v>
+      </c>
+      <c r="Y35">
+        <v>1000</v>
+      </c>
+      <c r="Z35">
+        <v>1000</v>
+      </c>
+      <c r="AA35">
+        <v>1000</v>
+      </c>
+      <c r="AB35">
+        <v>1000</v>
+      </c>
+      <c r="AC35">
+        <v>1000</v>
+      </c>
+      <c r="AD35">
+        <v>1000</v>
+      </c>
+      <c r="AE35">
+        <v>1000</v>
+      </c>
+      <c r="AF35">
+        <v>1000</v>
+      </c>
+      <c r="AG35">
+        <v>1000</v>
+      </c>
+      <c r="AH35">
+        <v>1000</v>
+      </c>
+      <c r="AI35">
+        <v>1000</v>
+      </c>
+      <c r="AJ35">
+        <v>1000</v>
+      </c>
+      <c r="AK35">
+        <v>1000</v>
+      </c>
+      <c r="AL35">
+        <v>1000</v>
+      </c>
+      <c r="AM35">
+        <v>1000</v>
+      </c>
+      <c r="AN35">
+        <v>1000</v>
+      </c>
+      <c r="AO35">
+        <v>1000</v>
+      </c>
+      <c r="AP35">
+        <v>1.03</v>
+      </c>
+      <c r="AQ35">
+        <v>1.03</v>
+      </c>
+      <c r="AR35">
+        <v>1.03</v>
+      </c>
+      <c r="AS35">
+        <v>1.03</v>
+      </c>
+      <c r="AT35">
+        <v>1.03</v>
+      </c>
+      <c r="AU35">
+        <v>1.03</v>
+      </c>
+      <c r="AV35">
+        <v>1.03</v>
+      </c>
+      <c r="AW35">
+        <v>1.03</v>
+      </c>
+      <c r="AX35">
+        <v>1.03</v>
+      </c>
+      <c r="AY35">
+        <v>1.03</v>
+      </c>
+      <c r="AZ35">
+        <v>1.03</v>
+      </c>
+      <c r="BA35">
+        <v>1.03</v>
+      </c>
+      <c r="BB35">
+        <v>1.03</v>
+      </c>
+      <c r="BC35">
+        <v>1.03</v>
+      </c>
+      <c r="BD35">
+        <v>1.03</v>
+      </c>
+      <c r="BE35">
+        <v>1.03</v>
+      </c>
+      <c r="BF35">
+        <v>1.01</v>
+      </c>
+      <c r="BG35">
+        <v>1.01</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.01</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.01</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.01</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.01</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.01</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" t="s">
+        <v>200</v>
+      </c>
+      <c r="F36">
+        <v>2.92</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>2.72</v>
+      </c>
+      <c r="I36">
+        <v>2.82</v>
+      </c>
+      <c r="J36">
+        <v>3.3</v>
+      </c>
+      <c r="K36">
+        <v>3.35</v>
+      </c>
+      <c r="L36">
+        <v>1.44</v>
+      </c>
+      <c r="M36">
+        <v>1.08</v>
+      </c>
+      <c r="N36">
+        <v>3.35</v>
+      </c>
+      <c r="O36">
+        <v>1.37</v>
+      </c>
+      <c r="P36">
+        <v>1.78</v>
+      </c>
+      <c r="Q36">
+        <v>2.08</v>
+      </c>
+      <c r="R36">
+        <v>1.3</v>
+      </c>
+      <c r="S36">
+        <v>3.95</v>
+      </c>
+      <c r="T36">
+        <v>1.81</v>
+      </c>
+      <c r="U36">
+        <v>2.08</v>
+      </c>
+      <c r="V36">
+        <v>1.55</v>
+      </c>
+      <c r="W36">
+        <v>1.5</v>
+      </c>
+      <c r="X36">
+        <v>13</v>
+      </c>
+      <c r="Y36">
+        <v>11</v>
+      </c>
+      <c r="Z36">
+        <v>18</v>
+      </c>
+      <c r="AA36">
+        <v>44</v>
+      </c>
+      <c r="AB36">
+        <v>11.5</v>
+      </c>
+      <c r="AC36">
+        <v>7.4</v>
+      </c>
+      <c r="AD36">
+        <v>12.5</v>
+      </c>
+      <c r="AE36">
+        <v>36</v>
+      </c>
+      <c r="AF36">
+        <v>19.5</v>
+      </c>
+      <c r="AG36">
+        <v>15.5</v>
+      </c>
+      <c r="AH36">
+        <v>18.5</v>
+      </c>
+      <c r="AI36">
+        <v>50</v>
+      </c>
+      <c r="AJ36">
+        <v>50</v>
+      </c>
+      <c r="AK36">
+        <v>38</v>
+      </c>
+      <c r="AL36">
+        <v>55</v>
+      </c>
+      <c r="AM36">
+        <v>110</v>
+      </c>
+      <c r="AN36">
+        <v>36</v>
+      </c>
+      <c r="AO36">
+        <v>32</v>
+      </c>
+      <c r="AP36">
+        <v>11.5</v>
+      </c>
+      <c r="AQ36">
+        <v>9.6</v>
+      </c>
+      <c r="AR36">
+        <v>15.5</v>
+      </c>
+      <c r="AS36">
+        <v>36</v>
+      </c>
+      <c r="AT36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU36">
+        <v>6.6</v>
+      </c>
+      <c r="AV36">
+        <v>11</v>
+      </c>
+      <c r="AW36">
+        <v>27</v>
+      </c>
+      <c r="AX36">
+        <v>16.5</v>
+      </c>
+      <c r="AY36">
+        <v>11.5</v>
+      </c>
+      <c r="AZ36">
+        <v>15.5</v>
+      </c>
+      <c r="BA36">
+        <v>38</v>
+      </c>
+      <c r="BB36">
+        <v>40</v>
+      </c>
+      <c r="BC36">
+        <v>30</v>
+      </c>
+      <c r="BD36">
+        <v>34</v>
+      </c>
+      <c r="BE36">
+        <v>10.5</v>
+      </c>
+      <c r="BF36">
+        <v>27</v>
+      </c>
+      <c r="BG36">
+        <v>24</v>
+      </c>
+      <c r="BH36">
+        <v>3.7</v>
+      </c>
+      <c r="BI36">
+        <v>2.58</v>
+      </c>
+      <c r="BJ36">
+        <v>10</v>
+      </c>
+      <c r="BK36">
+        <v>4.3</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>7.4</v>
+      </c>
+      <c r="BN36">
+        <v>6.2</v>
+      </c>
+      <c r="BO36">
+        <v>5.1</v>
+      </c>
+      <c r="BP36">
+        <v>25</v>
+      </c>
+      <c r="BQ36">
+        <v>5.9</v>
+      </c>
+      <c r="BR36">
+        <v>42</v>
+      </c>
+      <c r="BS36">
+        <v>6.4</v>
+      </c>
+      <c r="BT36">
+        <v>5.9</v>
+      </c>
+      <c r="BU36">
+        <v>4.9</v>
+      </c>
+      <c r="BV36">
+        <v>23</v>
+      </c>
+      <c r="BW36">
+        <v>5.8</v>
+      </c>
+      <c r="BX36">
+        <v>40</v>
+      </c>
+      <c r="BY36">
+        <v>6.4</v>
+      </c>
+      <c r="BZ36">
+        <v>36</v>
+      </c>
+      <c r="CA36">
+        <v>6.2</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F37">
+        <v>1.76</v>
+      </c>
+      <c r="G37">
+        <v>1.91</v>
+      </c>
+      <c r="H37">
+        <v>4.8</v>
+      </c>
+      <c r="I37">
+        <v>5.7</v>
+      </c>
+      <c r="J37">
+        <v>3.6</v>
+      </c>
+      <c r="K37">
+        <v>3.95</v>
+      </c>
+      <c r="L37">
+        <v>1.01</v>
+      </c>
+      <c r="M37">
+        <v>1.07</v>
+      </c>
+      <c r="N37">
+        <v>3.5</v>
+      </c>
+      <c r="O37">
+        <v>1.34</v>
+      </c>
+      <c r="P37">
+        <v>1.86</v>
+      </c>
+      <c r="Q37">
+        <v>1.99</v>
+      </c>
+      <c r="R37">
+        <v>1.33</v>
+      </c>
+      <c r="S37">
+        <v>3.5</v>
+      </c>
+      <c r="T37">
+        <v>1.87</v>
+      </c>
+      <c r="U37">
+        <v>1.96</v>
+      </c>
+      <c r="V37">
+        <v>1.21</v>
+      </c>
+      <c r="W37">
+        <v>2.08</v>
+      </c>
+      <c r="X37">
+        <v>17</v>
+      </c>
+      <c r="Y37">
+        <v>21</v>
+      </c>
+      <c r="Z37">
+        <v>48</v>
+      </c>
+      <c r="AA37">
+        <v>160</v>
+      </c>
+      <c r="AB37">
+        <v>10</v>
+      </c>
+      <c r="AC37">
+        <v>10.5</v>
+      </c>
+      <c r="AD37">
+        <v>25</v>
+      </c>
+      <c r="AE37">
+        <v>90</v>
+      </c>
+      <c r="AF37">
+        <v>13.5</v>
+      </c>
+      <c r="AG37">
+        <v>12.5</v>
+      </c>
+      <c r="AH37">
+        <v>25</v>
+      </c>
+      <c r="AI37">
+        <v>95</v>
+      </c>
+      <c r="AJ37">
+        <v>24</v>
+      </c>
+      <c r="AK37">
+        <v>25</v>
+      </c>
+      <c r="AL37">
+        <v>48</v>
+      </c>
+      <c r="AM37">
+        <v>150</v>
+      </c>
+      <c r="AN37">
+        <v>16</v>
+      </c>
+      <c r="AO37">
+        <v>110</v>
+      </c>
+      <c r="AP37">
+        <v>11.5</v>
+      </c>
+      <c r="AQ37">
+        <v>14</v>
+      </c>
+      <c r="AR37">
+        <v>4.1</v>
+      </c>
+      <c r="AS37">
+        <v>4.4</v>
+      </c>
+      <c r="AT37">
+        <v>7</v>
+      </c>
+      <c r="AU37">
+        <v>7.4</v>
+      </c>
+      <c r="AV37">
+        <v>17</v>
+      </c>
+      <c r="AW37">
+        <v>4.3</v>
+      </c>
+      <c r="AX37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY37">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ37">
+        <v>17</v>
+      </c>
+      <c r="BA37">
+        <v>4.3</v>
+      </c>
+      <c r="BB37">
+        <v>16.5</v>
+      </c>
+      <c r="BC37">
+        <v>17</v>
+      </c>
+      <c r="BD37">
+        <v>4.1</v>
+      </c>
+      <c r="BE37">
+        <v>4.4</v>
+      </c>
+      <c r="BF37">
+        <v>11</v>
+      </c>
+      <c r="BG37">
+        <v>4.3</v>
+      </c>
+      <c r="BH37">
+        <v>1000</v>
+      </c>
+      <c r="BI37">
+        <v>1.01</v>
+      </c>
+      <c r="BJ37">
+        <v>1000</v>
+      </c>
+      <c r="BK37">
+        <v>1.01</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>1.01</v>
+      </c>
+      <c r="BN37">
+        <v>1000</v>
+      </c>
+      <c r="BO37">
+        <v>1.01</v>
+      </c>
+      <c r="BP37">
+        <v>1000</v>
+      </c>
+      <c r="BQ37">
+        <v>1.01</v>
+      </c>
+      <c r="BR37">
+        <v>1000</v>
+      </c>
+      <c r="BS37">
+        <v>1.01</v>
+      </c>
+      <c r="BT37">
+        <v>1000</v>
+      </c>
+      <c r="BU37">
+        <v>1.01</v>
+      </c>
+      <c r="BV37">
+        <v>1000</v>
+      </c>
+      <c r="BW37">
+        <v>1.01</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
+        <v>1.01</v>
+      </c>
+      <c r="BZ37">
+        <v>1000</v>
+      </c>
+      <c r="CA37">
+        <v>1.01</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" t="s">
+        <v>202</v>
+      </c>
+      <c r="F38">
+        <v>5.8</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+      <c r="H38">
+        <v>1.44</v>
+      </c>
+      <c r="I38">
+        <v>1.53</v>
+      </c>
+      <c r="J38">
+        <v>4.7</v>
+      </c>
+      <c r="K38">
+        <v>5.7</v>
+      </c>
+      <c r="L38">
+        <v>1.01</v>
+      </c>
+      <c r="M38">
+        <v>1.01</v>
+      </c>
+      <c r="N38">
+        <v>2.24</v>
+      </c>
+      <c r="O38">
+        <v>1.19</v>
+      </c>
+      <c r="P38">
+        <v>2.24</v>
+      </c>
+      <c r="Q38">
+        <v>1.48</v>
+      </c>
+      <c r="R38">
+        <v>1.5</v>
+      </c>
+      <c r="S38">
+        <v>2.24</v>
+      </c>
+      <c r="T38">
+        <v>1.01</v>
+      </c>
+      <c r="U38">
+        <v>1.01</v>
+      </c>
+      <c r="V38">
+        <v>2.88</v>
+      </c>
+      <c r="W38">
+        <v>1.12</v>
+      </c>
+      <c r="X38">
+        <v>30</v>
+      </c>
+      <c r="Y38">
+        <v>13</v>
+      </c>
+      <c r="Z38">
+        <v>12.5</v>
+      </c>
+      <c r="AA38">
+        <v>16</v>
+      </c>
+      <c r="AB38">
+        <v>38</v>
+      </c>
+      <c r="AC38">
+        <v>14.5</v>
+      </c>
+      <c r="AD38">
+        <v>12.5</v>
+      </c>
+      <c r="AE38">
+        <v>18</v>
+      </c>
+      <c r="AF38">
+        <v>85</v>
+      </c>
+      <c r="AG38">
+        <v>36</v>
+      </c>
+      <c r="AH38">
+        <v>27</v>
+      </c>
+      <c r="AI38">
+        <v>38</v>
+      </c>
+      <c r="AJ38">
+        <v>260</v>
+      </c>
+      <c r="AK38">
+        <v>120</v>
+      </c>
+      <c r="AL38">
+        <v>100</v>
+      </c>
+      <c r="AM38">
+        <v>130</v>
+      </c>
+      <c r="AN38">
+        <v>130</v>
+      </c>
+      <c r="AO38">
+        <v>6.8</v>
+      </c>
+      <c r="AP38">
+        <v>3.8</v>
+      </c>
+      <c r="AQ38">
+        <v>3.25</v>
+      </c>
+      <c r="AR38">
+        <v>3.2</v>
+      </c>
+      <c r="AS38">
+        <v>3.4</v>
+      </c>
+      <c r="AT38">
+        <v>3.9</v>
+      </c>
+      <c r="AU38">
+        <v>3.35</v>
+      </c>
+      <c r="AV38">
+        <v>3.2</v>
+      </c>
+      <c r="AW38">
+        <v>3.5</v>
+      </c>
+      <c r="AX38">
+        <v>4.1</v>
+      </c>
+      <c r="AY38">
+        <v>3.85</v>
+      </c>
+      <c r="AZ38">
+        <v>3.75</v>
+      </c>
+      <c r="BA38">
+        <v>3.9</v>
+      </c>
+      <c r="BB38">
+        <v>4.2</v>
+      </c>
+      <c r="BC38">
+        <v>4.2</v>
+      </c>
+      <c r="BD38">
+        <v>4.1</v>
+      </c>
+      <c r="BE38">
+        <v>4.2</v>
+      </c>
+      <c r="BF38">
+        <v>4.2</v>
+      </c>
+      <c r="BG38">
+        <v>2.64</v>
+      </c>
+      <c r="BH38">
+        <v>1000</v>
+      </c>
+      <c r="BI38">
+        <v>1.01</v>
+      </c>
+      <c r="BJ38">
+        <v>1000</v>
+      </c>
+      <c r="BK38">
+        <v>1.01</v>
+      </c>
+      <c r="BL38">
+        <v>1000</v>
+      </c>
+      <c r="BM38">
+        <v>1.01</v>
+      </c>
+      <c r="BN38">
+        <v>1000</v>
+      </c>
+      <c r="BO38">
+        <v>1.01</v>
+      </c>
+      <c r="BP38">
+        <v>1000</v>
+      </c>
+      <c r="BQ38">
+        <v>1.01</v>
+      </c>
+      <c r="BR38">
+        <v>1000</v>
+      </c>
+      <c r="BS38">
+        <v>1.01</v>
+      </c>
+      <c r="BT38">
+        <v>1000</v>
+      </c>
+      <c r="BU38">
+        <v>1.01</v>
+      </c>
+      <c r="BV38">
+        <v>1000</v>
+      </c>
+      <c r="BW38">
+        <v>1.01</v>
+      </c>
+      <c r="BX38">
+        <v>1000</v>
+      </c>
+      <c r="BY38">
+        <v>1.01</v>
+      </c>
+      <c r="BZ38">
+        <v>1000</v>
+      </c>
+      <c r="CA38">
+        <v>1.01</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" t="s">
+        <v>162</v>
+      </c>
+      <c r="E39" t="s">
+        <v>203</v>
+      </c>
+      <c r="F39">
+        <v>2.64</v>
+      </c>
+      <c r="G39">
+        <v>3.25</v>
+      </c>
+      <c r="H39">
+        <v>2.62</v>
+      </c>
+      <c r="I39">
+        <v>3.25</v>
+      </c>
+      <c r="J39">
+        <v>2.92</v>
+      </c>
+      <c r="K39">
+        <v>4.2</v>
+      </c>
+      <c r="L39">
+        <v>1.41</v>
+      </c>
+      <c r="M39">
+        <v>1.01</v>
+      </c>
+      <c r="N39">
+        <v>2.8</v>
+      </c>
+      <c r="O39">
+        <v>1.38</v>
+      </c>
+      <c r="P39">
+        <v>1.58</v>
+      </c>
+      <c r="Q39">
+        <v>2.26</v>
+      </c>
+      <c r="R39">
+        <v>1.18</v>
+      </c>
+      <c r="S39">
+        <v>3.4</v>
+      </c>
+      <c r="T39">
+        <v>1.01</v>
+      </c>
+      <c r="U39">
+        <v>1.01</v>
+      </c>
+      <c r="V39">
+        <v>1.45</v>
+      </c>
+      <c r="W39">
+        <v>1.44</v>
+      </c>
+      <c r="X39">
+        <v>1000</v>
+      </c>
+      <c r="Y39">
+        <v>1000</v>
+      </c>
+      <c r="Z39">
+        <v>1000</v>
+      </c>
+      <c r="AA39">
+        <v>1000</v>
+      </c>
+      <c r="AB39">
+        <v>1000</v>
+      </c>
+      <c r="AC39">
+        <v>1000</v>
+      </c>
+      <c r="AD39">
+        <v>1000</v>
+      </c>
+      <c r="AE39">
+        <v>1000</v>
+      </c>
+      <c r="AF39">
+        <v>1000</v>
+      </c>
+      <c r="AG39">
+        <v>1000</v>
+      </c>
+      <c r="AH39">
+        <v>1000</v>
+      </c>
+      <c r="AI39">
+        <v>1000</v>
+      </c>
+      <c r="AJ39">
+        <v>1000</v>
+      </c>
+      <c r="AK39">
+        <v>1000</v>
+      </c>
+      <c r="AL39">
+        <v>1000</v>
+      </c>
+      <c r="AM39">
+        <v>1000</v>
+      </c>
+      <c r="AN39">
+        <v>1000</v>
+      </c>
+      <c r="AO39">
+        <v>1000</v>
+      </c>
+      <c r="AP39">
+        <v>1.03</v>
+      </c>
+      <c r="AQ39">
+        <v>1.03</v>
+      </c>
+      <c r="AR39">
+        <v>1.03</v>
+      </c>
+      <c r="AS39">
+        <v>1.03</v>
+      </c>
+      <c r="AT39">
+        <v>1.03</v>
+      </c>
+      <c r="AU39">
+        <v>1.03</v>
+      </c>
+      <c r="AV39">
+        <v>1.03</v>
+      </c>
+      <c r="AW39">
+        <v>1.03</v>
+      </c>
+      <c r="AX39">
+        <v>1.03</v>
+      </c>
+      <c r="AY39">
+        <v>1.03</v>
+      </c>
+      <c r="AZ39">
+        <v>1.03</v>
+      </c>
+      <c r="BA39">
+        <v>1.03</v>
+      </c>
+      <c r="BB39">
+        <v>1.03</v>
+      </c>
+      <c r="BC39">
+        <v>1.03</v>
+      </c>
+      <c r="BD39">
+        <v>1.03</v>
+      </c>
+      <c r="BE39">
+        <v>1.03</v>
+      </c>
+      <c r="BF39">
+        <v>1.01</v>
+      </c>
+      <c r="BG39">
+        <v>1.01</v>
+      </c>
+      <c r="BH39">
+        <v>1000</v>
+      </c>
+      <c r="BI39">
+        <v>1.01</v>
+      </c>
+      <c r="BJ39">
+        <v>1000</v>
+      </c>
+      <c r="BK39">
+        <v>1.01</v>
+      </c>
+      <c r="BL39">
+        <v>1000</v>
+      </c>
+      <c r="BM39">
+        <v>1.01</v>
+      </c>
+      <c r="BN39">
+        <v>1000</v>
+      </c>
+      <c r="BO39">
+        <v>1.01</v>
+      </c>
+      <c r="BP39">
+        <v>1000</v>
+      </c>
+      <c r="BQ39">
+        <v>1.01</v>
+      </c>
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
+        <v>1.01</v>
+      </c>
+      <c r="BT39">
+        <v>1000</v>
+      </c>
+      <c r="BU39">
+        <v>1.01</v>
+      </c>
+      <c r="BV39">
+        <v>1000</v>
+      </c>
+      <c r="BW39">
+        <v>1.01</v>
+      </c>
+      <c r="BX39">
+        <v>1000</v>
+      </c>
+      <c r="BY39">
+        <v>1.01</v>
+      </c>
+      <c r="BZ39">
+        <v>1000</v>
+      </c>
+      <c r="CA39">
+        <v>1.01</v>
+      </c>
+      <c r="CB39" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="40" spans="1:80">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" t="s">
+        <v>163</v>
+      </c>
+      <c r="E40" t="s">
+        <v>204</v>
+      </c>
+      <c r="F40">
+        <v>1.87</v>
+      </c>
+      <c r="G40">
+        <v>1.96</v>
+      </c>
+      <c r="H40">
+        <v>5.2</v>
+      </c>
+      <c r="I40">
+        <v>5.7</v>
+      </c>
+      <c r="J40">
+        <v>3.3</v>
+      </c>
+      <c r="K40">
+        <v>3.55</v>
+      </c>
+      <c r="L40">
+        <v>1.55</v>
+      </c>
+      <c r="M40">
+        <v>1.11</v>
+      </c>
+      <c r="N40">
+        <v>2.62</v>
+      </c>
+      <c r="O40">
+        <v>1.53</v>
+      </c>
+      <c r="P40">
+        <v>1.53</v>
+      </c>
+      <c r="Q40">
+        <v>2.56</v>
+      </c>
+      <c r="R40">
+        <v>1.2</v>
+      </c>
+      <c r="S40">
+        <v>5.3</v>
+      </c>
+      <c r="T40">
+        <v>2.26</v>
+      </c>
+      <c r="U40">
+        <v>1.7</v>
+      </c>
+      <c r="V40">
+        <v>1.21</v>
+      </c>
+      <c r="W40">
+        <v>2.04</v>
+      </c>
+      <c r="X40">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y40">
+        <v>13.5</v>
+      </c>
+      <c r="Z40">
+        <v>50</v>
+      </c>
+      <c r="AA40">
+        <v>220</v>
+      </c>
+      <c r="AB40">
+        <v>6.4</v>
+      </c>
+      <c r="AC40">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD40">
+        <v>26</v>
+      </c>
+      <c r="AE40">
+        <v>130</v>
+      </c>
+      <c r="AF40">
+        <v>10.5</v>
+      </c>
+      <c r="AG40">
+        <v>11.5</v>
+      </c>
+      <c r="AH40">
+        <v>32</v>
+      </c>
+      <c r="AI40">
+        <v>140</v>
+      </c>
+      <c r="AJ40">
+        <v>27</v>
+      </c>
+      <c r="AK40">
+        <v>30</v>
+      </c>
+      <c r="AL40">
+        <v>75</v>
+      </c>
+      <c r="AM40">
+        <v>270</v>
+      </c>
+      <c r="AN40">
+        <v>23</v>
+      </c>
+      <c r="AO40">
+        <v>220</v>
+      </c>
+      <c r="AP40">
+        <v>7.8</v>
+      </c>
+      <c r="AQ40">
+        <v>11.5</v>
+      </c>
+      <c r="AR40">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS40">
+        <v>10.5</v>
+      </c>
+      <c r="AT40">
+        <v>5.7</v>
+      </c>
+      <c r="AU40">
+        <v>7.2</v>
+      </c>
+      <c r="AV40">
+        <v>8</v>
+      </c>
+      <c r="AW40">
+        <v>10</v>
+      </c>
+      <c r="AX40">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY40">
+        <v>10</v>
+      </c>
+      <c r="AZ40">
+        <v>8.4</v>
+      </c>
+      <c r="BA40">
+        <v>10.5</v>
+      </c>
+      <c r="BB40">
+        <v>20</v>
+      </c>
+      <c r="BC40">
+        <v>8.4</v>
+      </c>
+      <c r="BD40">
+        <v>10</v>
+      </c>
+      <c r="BE40">
+        <v>10.5</v>
+      </c>
+      <c r="BF40">
+        <v>18</v>
+      </c>
+      <c r="BG40">
+        <v>10.5</v>
+      </c>
+      <c r="BH40">
+        <v>1000</v>
+      </c>
+      <c r="BI40">
+        <v>1.25</v>
+      </c>
+      <c r="BJ40">
+        <v>1000</v>
+      </c>
+      <c r="BK40">
+        <v>1.25</v>
+      </c>
+      <c r="BL40">
+        <v>1000</v>
+      </c>
+      <c r="BM40">
+        <v>1.25</v>
+      </c>
+      <c r="BN40">
+        <v>1000</v>
+      </c>
+      <c r="BO40">
+        <v>1.55</v>
+      </c>
+      <c r="BP40">
+        <v>1000</v>
+      </c>
+      <c r="BQ40">
+        <v>1.25</v>
+      </c>
+      <c r="BR40">
+        <v>1000</v>
+      </c>
+      <c r="BS40">
+        <v>1.25</v>
+      </c>
+      <c r="BT40">
+        <v>1000</v>
+      </c>
+      <c r="BU40">
+        <v>1.25</v>
+      </c>
+      <c r="BV40">
+        <v>1000</v>
+      </c>
+      <c r="BW40">
+        <v>1.25</v>
+      </c>
+      <c r="BX40">
+        <v>1000</v>
+      </c>
+      <c r="BY40">
+        <v>1.25</v>
+      </c>
+      <c r="BZ40">
+        <v>1000</v>
+      </c>
+      <c r="CA40">
+        <v>1.25</v>
+      </c>
+      <c r="CB40" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="1:80">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" t="s">
+        <v>164</v>
+      </c>
+      <c r="E41" t="s">
+        <v>205</v>
+      </c>
+      <c r="F41">
+        <v>4.1</v>
+      </c>
+      <c r="G41">
+        <v>4.5</v>
+      </c>
+      <c r="H41">
+        <v>2.16</v>
+      </c>
+      <c r="I41">
+        <v>2.28</v>
+      </c>
+      <c r="J41">
+        <v>3.05</v>
+      </c>
+      <c r="K41">
+        <v>3.25</v>
+      </c>
+      <c r="L41">
+        <v>1.01</v>
+      </c>
+      <c r="M41">
+        <v>1.12</v>
+      </c>
+      <c r="N41">
+        <v>2.56</v>
+      </c>
+      <c r="O41">
+        <v>1.48</v>
+      </c>
+      <c r="P41">
+        <v>1.53</v>
+      </c>
+      <c r="Q41">
+        <v>2.48</v>
+      </c>
+      <c r="R41">
+        <v>1.18</v>
+      </c>
+      <c r="S41">
+        <v>5.3</v>
+      </c>
+      <c r="T41">
+        <v>2.1</v>
+      </c>
+      <c r="U41">
+        <v>1.79</v>
+      </c>
+      <c r="V41">
+        <v>1.78</v>
+      </c>
+      <c r="W41">
+        <v>1.28</v>
+      </c>
+      <c r="X41">
+        <v>11</v>
+      </c>
+      <c r="Y41">
+        <v>7.2</v>
+      </c>
+      <c r="Z41">
+        <v>15</v>
+      </c>
+      <c r="AA41">
+        <v>30</v>
+      </c>
+      <c r="AB41">
+        <v>12</v>
+      </c>
+      <c r="AC41">
+        <v>7.4</v>
+      </c>
+      <c r="AD41">
+        <v>13.5</v>
+      </c>
+      <c r="AE41">
+        <v>30</v>
+      </c>
+      <c r="AF41">
+        <v>30</v>
+      </c>
+      <c r="AG41">
+        <v>18.5</v>
+      </c>
+      <c r="AH41">
+        <v>24</v>
+      </c>
+      <c r="AI41">
+        <v>60</v>
+      </c>
+      <c r="AJ41">
+        <v>110</v>
+      </c>
+      <c r="AK41">
+        <v>75</v>
+      </c>
+      <c r="AL41">
+        <v>90</v>
+      </c>
+      <c r="AM41">
+        <v>180</v>
+      </c>
+      <c r="AN41">
+        <v>110</v>
+      </c>
+      <c r="AO41">
+        <v>36</v>
+      </c>
+      <c r="AP41">
+        <v>8</v>
+      </c>
+      <c r="AQ41">
+        <v>6.2</v>
+      </c>
+      <c r="AR41">
+        <v>10.5</v>
+      </c>
+      <c r="AS41">
+        <v>23</v>
+      </c>
+      <c r="AT41">
+        <v>10</v>
+      </c>
+      <c r="AU41">
+        <v>6.4</v>
+      </c>
+      <c r="AV41">
+        <v>10.5</v>
+      </c>
+      <c r="AW41">
+        <v>25</v>
+      </c>
+      <c r="AX41">
+        <v>25</v>
+      </c>
+      <c r="AY41">
+        <v>16</v>
+      </c>
+      <c r="AZ41">
+        <v>21</v>
+      </c>
+      <c r="BA41">
+        <v>50</v>
+      </c>
+      <c r="BB41">
+        <v>11.5</v>
+      </c>
+      <c r="BC41">
+        <v>55</v>
+      </c>
+      <c r="BD41">
+        <v>11</v>
+      </c>
+      <c r="BE41">
+        <v>11</v>
+      </c>
+      <c r="BF41">
+        <v>11.5</v>
+      </c>
+      <c r="BG41">
+        <v>21</v>
+      </c>
+      <c r="BH41">
+        <v>1000</v>
+      </c>
+      <c r="BI41">
+        <v>1.01</v>
+      </c>
+      <c r="BJ41">
+        <v>1000</v>
+      </c>
+      <c r="BK41">
+        <v>1.01</v>
+      </c>
+      <c r="BL41">
+        <v>1000</v>
+      </c>
+      <c r="BM41">
+        <v>1.01</v>
+      </c>
+      <c r="BN41">
+        <v>1000</v>
+      </c>
+      <c r="BO41">
+        <v>1.01</v>
+      </c>
+      <c r="BP41">
+        <v>1000</v>
+      </c>
+      <c r="BQ41">
+        <v>1.01</v>
+      </c>
+      <c r="BR41">
+        <v>1000</v>
+      </c>
+      <c r="BS41">
+        <v>1.01</v>
+      </c>
+      <c r="BT41">
+        <v>1000</v>
+      </c>
+      <c r="BU41">
+        <v>1.01</v>
+      </c>
+      <c r="BV41">
+        <v>1000</v>
+      </c>
+      <c r="BW41">
+        <v>1.01</v>
+      </c>
+      <c r="BX41">
+        <v>1000</v>
+      </c>
+      <c r="BY41">
+        <v>1.01</v>
+      </c>
+      <c r="BZ41">
+        <v>1000</v>
+      </c>
+      <c r="CA41">
+        <v>1.01</v>
+      </c>
+      <c r="CB41" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="42" spans="1:80">
+      <c r="A42" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" t="s">
+        <v>165</v>
+      </c>
+      <c r="E42" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42">
+        <v>1.92</v>
+      </c>
+      <c r="G42">
+        <v>2.08</v>
+      </c>
+      <c r="H42">
+        <v>3.9</v>
+      </c>
+      <c r="I42">
+        <v>4.9</v>
+      </c>
+      <c r="J42">
+        <v>3.5</v>
+      </c>
+      <c r="K42">
+        <v>3.8</v>
+      </c>
+      <c r="L42">
+        <v>1.01</v>
+      </c>
+      <c r="M42">
+        <v>1.04</v>
+      </c>
+      <c r="N42">
+        <v>3.15</v>
+      </c>
+      <c r="O42">
+        <v>1.35</v>
+      </c>
+      <c r="P42">
+        <v>1.77</v>
+      </c>
+      <c r="Q42">
+        <v>2.04</v>
+      </c>
+      <c r="R42">
+        <v>1.26</v>
+      </c>
+      <c r="S42">
+        <v>3.55</v>
+      </c>
+      <c r="T42">
+        <v>1.81</v>
+      </c>
+      <c r="U42">
+        <v>1.9</v>
+      </c>
+      <c r="V42">
+        <v>1.26</v>
+      </c>
+      <c r="W42">
+        <v>1.94</v>
+      </c>
+      <c r="X42">
+        <v>1000</v>
+      </c>
+      <c r="Y42">
+        <v>1000</v>
+      </c>
+      <c r="Z42">
+        <v>1000</v>
+      </c>
+      <c r="AA42">
+        <v>1000</v>
+      </c>
+      <c r="AB42">
+        <v>13</v>
+      </c>
+      <c r="AC42">
+        <v>11.5</v>
+      </c>
+      <c r="AD42">
+        <v>1000</v>
+      </c>
+      <c r="AE42">
+        <v>1000</v>
+      </c>
+      <c r="AF42">
+        <v>1000</v>
+      </c>
+      <c r="AG42">
+        <v>1000</v>
+      </c>
+      <c r="AH42">
+        <v>1000</v>
+      </c>
+      <c r="AI42">
+        <v>1000</v>
+      </c>
+      <c r="AJ42">
+        <v>1000</v>
+      </c>
+      <c r="AK42">
+        <v>1000</v>
+      </c>
+      <c r="AL42">
+        <v>1000</v>
+      </c>
+      <c r="AM42">
+        <v>1000</v>
+      </c>
+      <c r="AN42">
+        <v>1000</v>
+      </c>
+      <c r="AO42">
+        <v>1000</v>
+      </c>
+      <c r="AP42">
+        <v>1.19</v>
+      </c>
+      <c r="AQ42">
+        <v>1.19</v>
+      </c>
+      <c r="AR42">
+        <v>1.19</v>
+      </c>
+      <c r="AS42">
+        <v>1.19</v>
+      </c>
+      <c r="AT42">
+        <v>1.09</v>
+      </c>
+      <c r="AU42">
+        <v>1.08</v>
+      </c>
+      <c r="AV42">
+        <v>1.19</v>
+      </c>
+      <c r="AW42">
+        <v>1.19</v>
+      </c>
+      <c r="AX42">
+        <v>1.19</v>
+      </c>
+      <c r="AY42">
+        <v>1.19</v>
+      </c>
+      <c r="AZ42">
+        <v>1.19</v>
+      </c>
+      <c r="BA42">
+        <v>1.19</v>
+      </c>
+      <c r="BB42">
+        <v>1.19</v>
+      </c>
+      <c r="BC42">
+        <v>1.19</v>
+      </c>
+      <c r="BD42">
+        <v>1.19</v>
+      </c>
+      <c r="BE42">
+        <v>1.19</v>
+      </c>
+      <c r="BF42">
+        <v>1.19</v>
+      </c>
+      <c r="BG42">
+        <v>1.19</v>
+      </c>
+      <c r="BH42">
+        <v>1000</v>
+      </c>
+      <c r="BI42">
+        <v>1.01</v>
+      </c>
+      <c r="BJ42">
+        <v>1000</v>
+      </c>
+      <c r="BK42">
+        <v>1.01</v>
+      </c>
+      <c r="BL42">
+        <v>1000</v>
+      </c>
+      <c r="BM42">
+        <v>1.01</v>
+      </c>
+      <c r="BN42">
+        <v>1000</v>
+      </c>
+      <c r="BO42">
+        <v>1.01</v>
+      </c>
+      <c r="BP42">
+        <v>1000</v>
+      </c>
+      <c r="BQ42">
+        <v>1.01</v>
+      </c>
+      <c r="BR42">
+        <v>1000</v>
+      </c>
+      <c r="BS42">
+        <v>1.01</v>
+      </c>
+      <c r="BT42">
+        <v>1000</v>
+      </c>
+      <c r="BU42">
+        <v>1.01</v>
+      </c>
+      <c r="BV42">
+        <v>1000</v>
+      </c>
+      <c r="BW42">
+        <v>1.01</v>
+      </c>
+      <c r="BX42">
+        <v>1000</v>
+      </c>
+      <c r="BY42">
+        <v>1.01</v>
+      </c>
+      <c r="BZ42">
+        <v>1000</v>
+      </c>
+      <c r="CA42">
+        <v>1.01</v>
+      </c>
+      <c r="CB42" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -637,7 +637,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-10-03 01:04:06</t>
+    <t>2026-10-03 03:19:53</t>
   </si>
 </sst>
 </file>
@@ -1231,55 +1231,55 @@
         <v>166</v>
       </c>
       <c r="F2">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H2">
         <v>8</v>
       </c>
       <c r="I2">
-        <v>110</v>
+        <v>10.5</v>
       </c>
       <c r="J2">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K2">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
         <v>2.16</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="R2">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S2">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W2">
         <v>3.1</v>
@@ -1297,7 +1297,7 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC2">
         <v>1000</v>
@@ -1369,7 +1369,7 @@
         <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
         <v>1.03</v>
@@ -1384,7 +1384,7 @@
         <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BF2">
         <v>5.2</v>
@@ -1473,64 +1473,64 @@
         <v>167</v>
       </c>
       <c r="F3">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>1.12</v>
+        <v>2.42</v>
       </c>
       <c r="I3">
-        <v>110</v>
+        <v>2.72</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K3">
-        <v>110</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>1.59</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
-        <v>1.06</v>
+        <v>1.45</v>
       </c>
       <c r="P3">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
+        <v>2.28</v>
+      </c>
+      <c r="R3">
+        <v>1.21</v>
+      </c>
+      <c r="S3">
+        <v>3.2</v>
+      </c>
+      <c r="T3">
+        <v>1.9</v>
+      </c>
+      <c r="U3">
         <v>1.78</v>
       </c>
-      <c r="R3">
-        <v>1.18</v>
-      </c>
-      <c r="S3">
-        <v>2.06</v>
-      </c>
-      <c r="T3">
-        <v>1.01</v>
-      </c>
-      <c r="U3">
-        <v>1.01</v>
-      </c>
       <c r="V3">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X3">
         <v>1000</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
         <v>1000</v>
@@ -1539,7 +1539,7 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC3">
         <v>13</v>
@@ -1554,7 +1554,7 @@
         <v>1000</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH3">
         <v>1000</v>
@@ -1581,58 +1581,58 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AQ3">
         <v>5.7</v>
       </c>
       <c r="AR3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AS3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AT3">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AU3">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AV3">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AW3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AY3">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1718,10 +1718,10 @@
         <v>4.2</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H4">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="I4">
         <v>1.96</v>
@@ -1730,25 +1730,25 @@
         <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
         <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="R4">
         <v>1.27</v>
@@ -1760,7 +1760,7 @@
         <v>1.82</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V4">
         <v>2.04</v>
@@ -1772,19 +1772,19 @@
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC4">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
         <v>970</v>
@@ -1793,13 +1793,13 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI4">
         <v>1000</v>
@@ -1823,58 +1823,58 @@
         <v>50</v>
       </c>
       <c r="AP4">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AQ4">
-        <v>1.27</v>
+        <v>6.2</v>
       </c>
       <c r="AR4">
-        <v>1.31</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4">
-        <v>1.42</v>
+        <v>14</v>
       </c>
       <c r="AT4">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="AU4">
-        <v>1.27</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>1.31</v>
+        <v>8</v>
       </c>
       <c r="AW4">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AX4">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AY4">
-        <v>1.42</v>
+        <v>14</v>
       </c>
       <c r="AZ4">
-        <v>1.42</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>1.42</v>
+        <v>23</v>
       </c>
       <c r="BB4">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="BC4">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="BD4">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="BE4">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="BF4">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="BG4">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1957,61 +1957,61 @@
         <v>169</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="G5">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="H5">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="I5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J5">
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
         <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S5">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="T5">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y5">
         <v>1000</v>
@@ -2023,10 +2023,10 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD5">
         <v>1000</v>
@@ -2035,13 +2035,13 @@
         <v>1000</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG5">
         <v>1000</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI5">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>1.03</v>
@@ -2104,7 +2104,7 @@
         <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD5">
         <v>1.03</v>
@@ -2113,7 +2113,7 @@
         <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
         <v>1.01</v>
@@ -2202,16 +2202,16 @@
         <v>3.25</v>
       </c>
       <c r="G6">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="H6">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I6">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J6">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
         <v>3.45</v>
@@ -2229,16 +2229,16 @@
         <v>1.42</v>
       </c>
       <c r="P6">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S6">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T6">
         <v>1.84</v>
@@ -2247,10 +2247,10 @@
         <v>1.84</v>
       </c>
       <c r="V6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W6">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X6">
         <v>970</v>
@@ -2259,7 +2259,7 @@
         <v>970</v>
       </c>
       <c r="Z6">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -2307,58 +2307,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AQ6">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AR6">
-        <v>9</v>
+        <v>1.47</v>
       </c>
       <c r="AS6">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AT6">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AU6">
         <v>5.5</v>
       </c>
       <c r="AV6">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AW6">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AX6">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AY6">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AZ6">
-        <v>1.53</v>
+        <v>18</v>
       </c>
       <c r="BA6">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BB6">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BC6">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BD6">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BE6">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BF6">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BG6">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2370,55 +2370,55 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="CB6" t="s">
         <v>207</v>
@@ -2441,58 +2441,58 @@
         <v>171</v>
       </c>
       <c r="F7">
-        <v>1.12</v>
+        <v>3.7</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>1.12</v>
+        <v>1.89</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>2.14</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>1.28</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P7">
+        <v>1.88</v>
+      </c>
+      <c r="Q7">
+        <v>1.84</v>
+      </c>
+      <c r="R7">
+        <v>1.32</v>
+      </c>
+      <c r="S7">
+        <v>2.88</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>1.89</v>
+      </c>
+      <c r="W7">
         <v>1.25</v>
-      </c>
-      <c r="Q7">
-        <v>1.35</v>
-      </c>
-      <c r="R7">
-        <v>1.18</v>
-      </c>
-      <c r="S7">
-        <v>2.6</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>1.04</v>
-      </c>
-      <c r="W7">
-        <v>1.04</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2683,22 +2683,22 @@
         <v>172</v>
       </c>
       <c r="F8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G8">
         <v>2.46</v>
       </c>
       <c r="H8">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J8">
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
         <v>1.34</v>
@@ -2707,31 +2707,31 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
         <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
       </c>
       <c r="R8">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S8">
         <v>3.5</v>
       </c>
       <c r="T8">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="U8">
         <v>2.02</v>
       </c>
       <c r="V8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
         <v>1.69</v>
@@ -2740,10 +2740,10 @@
         <v>1000</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2752,7 +2752,7 @@
         <v>970</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2767,7 +2767,7 @@
         <v>1000</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI8">
         <v>1000</v>
@@ -2791,58 +2791,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AS8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AT8">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="AU8">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AV8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AW8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AX8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AY8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AZ8">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="BA8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="BB8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="BC8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="BD8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="BE8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="BF8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="BG8">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2925,19 +2925,19 @@
         <v>173</v>
       </c>
       <c r="F9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="G9">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H9">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I9">
         <v>870</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2973,10 +2973,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3200,7 +3200,7 @@
         <v>1.32</v>
       </c>
       <c r="Q10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R10">
         <v>1.18</v>
@@ -3917,7 +3917,7 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O13">
         <v>1.02</v>
@@ -3929,10 +3929,10 @@
         <v>1.5</v>
       </c>
       <c r="R13">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S13">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4135,13 +4135,13 @@
         <v>178</v>
       </c>
       <c r="F14">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G14">
         <v>2.88</v>
       </c>
       <c r="H14">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I14">
         <v>3</v>
@@ -4150,7 +4150,7 @@
         <v>3.15</v>
       </c>
       <c r="K14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4377,16 +4377,16 @@
         <v>179</v>
       </c>
       <c r="F15">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G15">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H15">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I15">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J15">
         <v>3.4</v>
@@ -4404,16 +4404,16 @@
         <v>3.65</v>
       </c>
       <c r="O15">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P15">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q15">
         <v>1.99</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
         <v>3.6</v>
@@ -4425,7 +4425,7 @@
         <v>2.16</v>
       </c>
       <c r="V15">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W15">
         <v>1.55</v>
@@ -4479,7 +4479,7 @@
         <v>120</v>
       </c>
       <c r="AN15">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO15">
         <v>32</v>
@@ -4506,7 +4506,7 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX15">
         <v>15</v>
@@ -4515,22 +4515,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA15">
         <v>8.199999999999999</v>
       </c>
       <c r="BB15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC15">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF15">
         <v>19.5</v>
@@ -4661,7 +4661,7 @@
         <v>2.3</v>
       </c>
       <c r="T16">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="U16">
         <v>2.58</v>
@@ -4867,16 +4867,16 @@
         <v>2.06</v>
       </c>
       <c r="H17">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K17">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L17">
         <v>1.25</v>
@@ -5345,16 +5345,16 @@
         <v>183</v>
       </c>
       <c r="F19">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="G19">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="H19">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I19">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J19">
         <v>3.1</v>
@@ -5375,7 +5375,7 @@
         <v>1.45</v>
       </c>
       <c r="P19">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q19">
         <v>2.24</v>
@@ -5384,7 +5384,7 @@
         <v>1.19</v>
       </c>
       <c r="S19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T19">
         <v>2.02</v>
@@ -5393,10 +5393,10 @@
         <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W19">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="X19">
         <v>970</v>
@@ -5844,7 +5844,7 @@
         <v>4.2</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L21">
         <v>1.37</v>
@@ -5889,10 +5889,10 @@
         <v>23</v>
       </c>
       <c r="Z21">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA21">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB21">
         <v>9.199999999999999</v>
@@ -6074,7 +6074,7 @@
         <v>3.8</v>
       </c>
       <c r="G22">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H22">
         <v>1.55</v>
@@ -6083,7 +6083,7 @@
         <v>1.7</v>
       </c>
       <c r="J22">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K22">
         <v>11</v>
@@ -6110,7 +6110,7 @@
         <v>1.37</v>
       </c>
       <c r="S22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6340,19 +6340,19 @@
         <v>1.24</v>
       </c>
       <c r="O23">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P23">
         <v>1.24</v>
       </c>
       <c r="Q23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R23">
         <v>1.18</v>
       </c>
       <c r="S23">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6579,13 +6579,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O24">
         <v>1.02</v>
       </c>
       <c r="P24">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q24">
         <v>1.03</v>
@@ -6800,7 +6800,7 @@
         <v>2.72</v>
       </c>
       <c r="G25">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H25">
         <v>2.56</v>
@@ -6815,19 +6815,19 @@
         <v>4.1</v>
       </c>
       <c r="L25">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M25">
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O25">
         <v>1.32</v>
       </c>
       <c r="P25">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Q25">
         <v>1.91</v>
@@ -6857,7 +6857,7 @@
         <v>11.5</v>
       </c>
       <c r="Z25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA25">
         <v>46</v>
@@ -6890,7 +6890,7 @@
         <v>50</v>
       </c>
       <c r="AK25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL25">
         <v>48</v>
@@ -6899,7 +6899,7 @@
         <v>110</v>
       </c>
       <c r="AN25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO25">
         <v>26</v>
@@ -6908,13 +6908,13 @@
         <v>12</v>
       </c>
       <c r="AQ25">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR25">
         <v>15.5</v>
       </c>
       <c r="AS25">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT25">
         <v>10</v>
@@ -6923,10 +6923,10 @@
         <v>7</v>
       </c>
       <c r="AV25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW25">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX25">
         <v>16.5</v>
@@ -6938,22 +6938,22 @@
         <v>15</v>
       </c>
       <c r="BA25">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC25">
         <v>8.4</v>
       </c>
-      <c r="BC25">
-        <v>7.6</v>
-      </c>
       <c r="BD25">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE25">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG25">
         <v>19.5</v>
@@ -6962,61 +6962,61 @@
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="CB25" t="s">
         <v>207</v>
@@ -7281,13 +7281,13 @@
         <v>191</v>
       </c>
       <c r="F27">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I27">
         <v>3.6</v>
@@ -7296,10 +7296,10 @@
         <v>3.4</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M27">
         <v>1.08</v>
@@ -7308,10 +7308,10 @@
         <v>3.25</v>
       </c>
       <c r="O27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P27">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q27">
         <v>2.06</v>
@@ -7326,10 +7326,10 @@
         <v>1.8</v>
       </c>
       <c r="U27">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W27">
         <v>1.72</v>
@@ -7344,10 +7344,10 @@
         <v>1000</v>
       </c>
       <c r="AA27">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB27">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC27">
         <v>11</v>
@@ -7356,7 +7356,7 @@
         <v>970</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF27">
         <v>36</v>
@@ -7374,7 +7374,7 @@
         <v>1000</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL27">
         <v>1000</v>
@@ -7383,10 +7383,10 @@
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP27">
         <v>8.6</v>
@@ -7395,13 +7395,13 @@
         <v>8.4</v>
       </c>
       <c r="AR27">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="AS27">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AT27">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AU27">
         <v>5.7</v>
@@ -7410,7 +7410,7 @@
         <v>9.6</v>
       </c>
       <c r="AW27">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AX27">
         <v>9.199999999999999</v>
@@ -7422,25 +7422,25 @@
         <v>11.5</v>
       </c>
       <c r="BA27">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="BB27">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="BC27">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="BD27">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="BE27">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="BF27">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BG27">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7458,7 +7458,7 @@
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>2.76</v>
+        <v>1.06</v>
       </c>
       <c r="BN27">
         <v>1000</v>
@@ -7470,13 +7470,13 @@
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>2.76</v>
+        <v>1.06</v>
       </c>
       <c r="BT27">
         <v>1000</v>
@@ -7488,19 +7488,19 @@
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>2.76</v>
+        <v>1.06</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>2.76</v>
+        <v>1.06</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>2.76</v>
+        <v>1.06</v>
       </c>
       <c r="CB27" t="s">
         <v>207</v>
@@ -7526,7 +7526,7 @@
         <v>1.25</v>
       </c>
       <c r="G28">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H28">
         <v>12.5</v>
@@ -7559,22 +7559,22 @@
         <v>1.35</v>
       </c>
       <c r="R28">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="S28">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T28">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U28">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X28">
         <v>50</v>
@@ -7625,22 +7625,22 @@
         <v>140</v>
       </c>
       <c r="AN28">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AO28">
         <v>190</v>
       </c>
       <c r="AP28">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR28">
+        <v>12</v>
+      </c>
+      <c r="AS28">
         <v>11.5</v>
-      </c>
-      <c r="AS28">
-        <v>11</v>
       </c>
       <c r="AT28">
         <v>11.5</v>
@@ -7649,10 +7649,10 @@
         <v>15.5</v>
       </c>
       <c r="AV28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX28">
         <v>9</v>
@@ -7661,10 +7661,10 @@
         <v>10</v>
       </c>
       <c r="AZ28">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BA28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB28">
         <v>9.6</v>
@@ -7673,16 +7673,16 @@
         <v>11.5</v>
       </c>
       <c r="BD28">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF28">
         <v>3.2</v>
       </c>
       <c r="BG28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7765,7 +7765,7 @@
         <v>193</v>
       </c>
       <c r="F29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G29">
         <v>1.81</v>
@@ -7774,7 +7774,7 @@
         <v>5.9</v>
       </c>
       <c r="I29">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J29">
         <v>3.5</v>
@@ -7795,7 +7795,7 @@
         <v>1.55</v>
       </c>
       <c r="P29">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q29">
         <v>2.6</v>
@@ -7807,13 +7807,13 @@
         <v>5.3</v>
       </c>
       <c r="T29">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U29">
         <v>1.67</v>
       </c>
       <c r="V29">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W29">
         <v>2.22</v>
@@ -7825,22 +7825,22 @@
         <v>15</v>
       </c>
       <c r="Z29">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA29">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
         <v>6.2</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29">
         <v>27</v>
       </c>
       <c r="AE29">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
         <v>8.800000000000001</v>
@@ -7852,7 +7852,7 @@
         <v>34</v>
       </c>
       <c r="AI29">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
         <v>19</v>
@@ -7861,7 +7861,7 @@
         <v>26</v>
       </c>
       <c r="AL29">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
         <v>310</v>
@@ -7870,7 +7870,7 @@
         <v>18</v>
       </c>
       <c r="AO29">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
         <v>7.8</v>
@@ -7879,10 +7879,10 @@
         <v>11.5</v>
       </c>
       <c r="AR29">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AS29">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="AT29">
         <v>5.5</v>
@@ -7894,7 +7894,7 @@
         <v>20</v>
       </c>
       <c r="AW29">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AX29">
         <v>8</v>
@@ -7903,10 +7903,10 @@
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BA29">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BB29">
         <v>16</v>
@@ -7915,16 +7915,16 @@
         <v>21</v>
       </c>
       <c r="BD29">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="BE29">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BF29">
         <v>16</v>
       </c>
       <c r="BG29">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7954,7 +7954,7 @@
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BR29">
         <v>1000</v>
@@ -8007,19 +8007,19 @@
         <v>194</v>
       </c>
       <c r="F30">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G30">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H30">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K30">
         <v>3.45</v>
@@ -8031,16 +8031,16 @@
         <v>1.11</v>
       </c>
       <c r="N30">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O30">
         <v>1.45</v>
       </c>
       <c r="P30">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q30">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R30">
         <v>1.25</v>
@@ -8058,7 +8058,7 @@
         <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X30">
         <v>10.5</v>
@@ -8076,7 +8076,7 @@
         <v>8.6</v>
       </c>
       <c r="AC30">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD30">
         <v>17</v>
@@ -8091,7 +8091,7 @@
         <v>12</v>
       </c>
       <c r="AH30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI30">
         <v>80</v>
@@ -8100,7 +8100,7 @@
         <v>34</v>
       </c>
       <c r="AK30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL30">
         <v>55</v>
@@ -8109,25 +8109,25 @@
         <v>170</v>
       </c>
       <c r="AN30">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO30">
         <v>80</v>
       </c>
       <c r="AP30">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR30">
         <v>22</v>
       </c>
       <c r="AS30">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT30">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU30">
         <v>6.4</v>
@@ -8136,7 +8136,7 @@
         <v>13.5</v>
       </c>
       <c r="AW30">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
@@ -8148,37 +8148,37 @@
         <v>17</v>
       </c>
       <c r="BA30">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB30">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC30">
         <v>21</v>
       </c>
       <c r="BD30">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE30">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF30">
         <v>19</v>
       </c>
       <c r="BG30">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH30">
         <v>3.05</v>
       </c>
       <c r="BI30">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ30">
         <v>11</v>
       </c>
       <c r="BK30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8205,10 +8205,10 @@
         <v>26</v>
       </c>
       <c r="BT30">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU30">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV30">
         <v>36</v>
@@ -8223,7 +8223,7 @@
         <v>36</v>
       </c>
       <c r="BZ30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA30">
         <v>26</v>
@@ -8264,7 +8264,7 @@
         <v>3.2</v>
       </c>
       <c r="K31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L31">
         <v>1.35</v>
@@ -8300,7 +8300,7 @@
         <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X31">
         <v>16</v>
@@ -8312,7 +8312,7 @@
         <v>25</v>
       </c>
       <c r="AA31">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB31">
         <v>11.5</v>
@@ -8342,7 +8342,7 @@
         <v>40</v>
       </c>
       <c r="AK31">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL31">
         <v>46</v>
@@ -8363,10 +8363,10 @@
         <v>12</v>
       </c>
       <c r="AR31">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS31">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT31">
         <v>10</v>
@@ -8378,7 +8378,7 @@
         <v>12</v>
       </c>
       <c r="AW31">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX31">
         <v>14</v>
@@ -8390,25 +8390,25 @@
         <v>14.5</v>
       </c>
       <c r="BA31">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB31">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD31">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE31">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF31">
         <v>15.5</v>
       </c>
       <c r="BG31">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH31">
         <v>4.3</v>
@@ -8539,10 +8539,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8662,55 +8662,55 @@
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="CB32" t="s">
         <v>207</v>
@@ -8733,19 +8733,19 @@
         <v>197</v>
       </c>
       <c r="F33">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="G33">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H33">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="I33">
         <v>6.8</v>
       </c>
       <c r="J33">
-        <v>4.3</v>
+        <v>2.56</v>
       </c>
       <c r="K33">
         <v>950</v>
@@ -8757,19 +8757,19 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="O33">
         <v>1.13</v>
       </c>
       <c r="P33">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="Q33">
         <v>1.38</v>
       </c>
       <c r="R33">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="S33">
         <v>2</v>
@@ -8781,10 +8781,10 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="W33">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -8978,10 +8978,10 @@
         <v>2.66</v>
       </c>
       <c r="G34">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I34">
         <v>3.35</v>
@@ -8990,7 +8990,7 @@
         <v>2.8</v>
       </c>
       <c r="K34">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L34">
         <v>1.55</v>
@@ -8999,13 +8999,13 @@
         <v>1.12</v>
       </c>
       <c r="N34">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="O34">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P34">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="Q34">
         <v>2.56</v>
@@ -9026,7 +9026,7 @@
         <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X34">
         <v>13.5</v>
@@ -9056,7 +9056,7 @@
         <v>23</v>
       </c>
       <c r="AG34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH34">
         <v>26</v>
@@ -9092,7 +9092,7 @@
         <v>14</v>
       </c>
       <c r="AS34">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AT34">
         <v>7.2</v>
@@ -9104,7 +9104,7 @@
         <v>10.5</v>
       </c>
       <c r="AW34">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AX34">
         <v>12.5</v>
@@ -9119,22 +9119,22 @@
         <v>3.45</v>
       </c>
       <c r="BB34">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BC34">
         <v>25</v>
       </c>
       <c r="BD34">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BE34">
         <v>3.55</v>
       </c>
       <c r="BF34">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG34">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9462,34 +9462,34 @@
         <v>2.92</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H36">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I36">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J36">
         <v>3.3</v>
       </c>
       <c r="K36">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L36">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M36">
         <v>1.08</v>
       </c>
       <c r="N36">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O36">
         <v>1.37</v>
       </c>
       <c r="P36">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q36">
         <v>2.08</v>
@@ -9510,10 +9510,10 @@
         <v>1.55</v>
       </c>
       <c r="W36">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X36">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y36">
         <v>11</v>
@@ -9531,10 +9531,10 @@
         <v>7.4</v>
       </c>
       <c r="AD36">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE36">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF36">
         <v>19.5</v>
@@ -9546,7 +9546,7 @@
         <v>18.5</v>
       </c>
       <c r="AI36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ36">
         <v>50</v>
@@ -9555,7 +9555,7 @@
         <v>38</v>
       </c>
       <c r="AL36">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM36">
         <v>110</v>
@@ -9564,7 +9564,7 @@
         <v>36</v>
       </c>
       <c r="AO36">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP36">
         <v>11.5</v>
@@ -9579,7 +9579,7 @@
         <v>36</v>
       </c>
       <c r="AT36">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU36">
         <v>6.6</v>
@@ -9600,10 +9600,10 @@
         <v>15.5</v>
       </c>
       <c r="BA36">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB36">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC36">
         <v>30</v>
@@ -9612,7 +9612,7 @@
         <v>34</v>
       </c>
       <c r="BE36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF36">
         <v>27</v>
@@ -9624,61 +9624,61 @@
         <v>3.7</v>
       </c>
       <c r="BI36">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ36">
         <v>10</v>
       </c>
       <c r="BK36">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN36">
         <v>6.2</v>
       </c>
       <c r="BO36">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP36">
         <v>25</v>
       </c>
       <c r="BQ36">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR36">
         <v>42</v>
       </c>
       <c r="BS36">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT36">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU36">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV36">
         <v>23</v>
       </c>
       <c r="BW36">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX36">
         <v>40</v>
       </c>
       <c r="BY36">
+        <v>6.6</v>
+      </c>
+      <c r="BZ36">
+        <v>1000</v>
+      </c>
+      <c r="CA36">
         <v>6.4</v>
-      </c>
-      <c r="BZ36">
-        <v>36</v>
-      </c>
-      <c r="CA36">
-        <v>6.2</v>
       </c>
       <c r="CB36" t="s">
         <v>207</v>
@@ -9701,22 +9701,22 @@
         <v>201</v>
       </c>
       <c r="F37">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G37">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H37">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I37">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J37">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K37">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9725,34 +9725,34 @@
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O37">
         <v>1.34</v>
       </c>
       <c r="P37">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q37">
         <v>1.99</v>
       </c>
       <c r="R37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S37">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T37">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U37">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W37">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X37">
         <v>17</v>
@@ -9761,13 +9761,13 @@
         <v>21</v>
       </c>
       <c r="Z37">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA37">
         <v>160</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC37">
         <v>10.5</v>
@@ -9779,7 +9779,7 @@
         <v>90</v>
       </c>
       <c r="AF37">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG37">
         <v>12.5</v>
@@ -9794,73 +9794,73 @@
         <v>24</v>
       </c>
       <c r="AK37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL37">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM37">
         <v>150</v>
       </c>
       <c r="AN37">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO37">
         <v>110</v>
       </c>
       <c r="AP37">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR37">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS37">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT37">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU37">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV37">
+        <v>17.5</v>
+      </c>
+      <c r="AW37">
+        <v>4.5</v>
+      </c>
+      <c r="AX37">
+        <v>9.6</v>
+      </c>
+      <c r="AY37">
+        <v>9</v>
+      </c>
+      <c r="AZ37">
+        <v>17.5</v>
+      </c>
+      <c r="BA37">
+        <v>4.5</v>
+      </c>
+      <c r="BB37">
         <v>17</v>
       </c>
-      <c r="AW37">
+      <c r="BC37">
+        <v>17.5</v>
+      </c>
+      <c r="BD37">
         <v>4.3</v>
       </c>
-      <c r="AX37">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY37">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ37">
-        <v>17</v>
-      </c>
-      <c r="BA37">
-        <v>4.3</v>
-      </c>
-      <c r="BB37">
-        <v>16.5</v>
-      </c>
-      <c r="BC37">
-        <v>17</v>
-      </c>
-      <c r="BD37">
-        <v>4.1</v>
-      </c>
       <c r="BE37">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF37">
         <v>11</v>
       </c>
       <c r="BG37">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9943,10 +9943,10 @@
         <v>202</v>
       </c>
       <c r="F38">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="G38">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="H38">
         <v>1.44</v>
@@ -9967,37 +9967,37 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="O38">
         <v>1.19</v>
       </c>
       <c r="P38">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q38">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="R38">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="S38">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T38">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U38">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V38">
         <v>2.88</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y38">
         <v>13</v>
@@ -10006,7 +10006,7 @@
         <v>12.5</v>
       </c>
       <c r="AA38">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB38">
         <v>38</v>
@@ -10018,7 +10018,7 @@
         <v>12.5</v>
       </c>
       <c r="AE38">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AF38">
         <v>85</v>
@@ -10051,58 +10051,58 @@
         <v>6.8</v>
       </c>
       <c r="AP38">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AQ38">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AR38">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AS38">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AT38">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AU38">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AV38">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AW38">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AX38">
+        <v>4.5</v>
+      </c>
+      <c r="AY38">
+        <v>4.2</v>
+      </c>
+      <c r="AZ38">
         <v>4.1</v>
       </c>
-      <c r="AY38">
-        <v>3.85</v>
-      </c>
-      <c r="AZ38">
-        <v>3.75</v>
-      </c>
       <c r="BA38">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BB38">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC38">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD38">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE38">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF38">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BG38">
-        <v>2.64</v>
+        <v>4.7</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10442,7 +10442,7 @@
         <v>3.3</v>
       </c>
       <c r="K40">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L40">
         <v>1.55</v>
@@ -10454,13 +10454,13 @@
         <v>2.62</v>
       </c>
       <c r="O40">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P40">
         <v>1.53</v>
       </c>
       <c r="Q40">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R40">
         <v>1.2</v>
@@ -10529,7 +10529,7 @@
         <v>270</v>
       </c>
       <c r="AN40">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO40">
         <v>220</v>
@@ -10696,19 +10696,19 @@
         <v>2.56</v>
       </c>
       <c r="O41">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P41">
         <v>1.53</v>
       </c>
       <c r="Q41">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R41">
         <v>1.18</v>
       </c>
       <c r="S41">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="T41">
         <v>2.1</v>
@@ -10732,7 +10732,7 @@
         <v>15</v>
       </c>
       <c r="AA41">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB41">
         <v>12</v>
@@ -10744,7 +10744,7 @@
         <v>13.5</v>
       </c>
       <c r="AE41">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AF41">
         <v>30</v>
@@ -10759,19 +10759,19 @@
         <v>60</v>
       </c>
       <c r="AJ41">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AK41">
         <v>75</v>
       </c>
       <c r="AL41">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AM41">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AN41">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AO41">
         <v>36</v>
@@ -10780,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="AQ41">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR41">
         <v>10.5</v>
@@ -10819,10 +10819,10 @@
         <v>55</v>
       </c>
       <c r="BD41">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE41">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF41">
         <v>11.5</v>
@@ -10911,7 +10911,7 @@
         <v>206</v>
       </c>
       <c r="F42">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="G42">
         <v>2.08</v>
@@ -10920,7 +10920,7 @@
         <v>3.9</v>
       </c>
       <c r="I42">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J42">
         <v>3.5</v>
@@ -10935,7 +10935,7 @@
         <v>1.04</v>
       </c>
       <c r="N42">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O42">
         <v>1.35</v>
@@ -10944,19 +10944,19 @@
         <v>1.77</v>
       </c>
       <c r="Q42">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S42">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T42">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U42">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V42">
         <v>1.26</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -637,7 +637,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-10-03 03:19:53</t>
+    <t>2026-10-03 05:36:12</t>
   </si>
 </sst>
 </file>
@@ -1234,16 +1234,16 @@
         <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K2">
         <v>5.2</v>
@@ -1255,19 +1255,19 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q2">
         <v>1.79</v>
       </c>
       <c r="R2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S2">
         <v>3</v>
@@ -1276,7 +1276,7 @@
         <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
         <v>1.12</v>
@@ -1384,7 +1384,7 @@
         <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
         <v>5.2</v>
@@ -1473,166 +1473,166 @@
         <v>167</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G3">
+        <v>3.55</v>
+      </c>
+      <c r="H3">
+        <v>2.4</v>
+      </c>
+      <c r="I3">
+        <v>2.64</v>
+      </c>
+      <c r="J3">
+        <v>3.05</v>
+      </c>
+      <c r="K3">
         <v>3.4</v>
-      </c>
-      <c r="H3">
-        <v>2.42</v>
-      </c>
-      <c r="I3">
-        <v>2.72</v>
-      </c>
-      <c r="J3">
-        <v>2.98</v>
-      </c>
-      <c r="K3">
-        <v>3.9</v>
       </c>
       <c r="L3">
         <v>1.48</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="V3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y3">
+        <v>8.6</v>
+      </c>
+      <c r="Z3">
+        <v>18.5</v>
+      </c>
+      <c r="AA3">
+        <v>46</v>
+      </c>
+      <c r="AB3">
+        <v>11</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>12.5</v>
+      </c>
+      <c r="AE3">
+        <v>40</v>
+      </c>
+      <c r="AF3">
+        <v>28</v>
+      </c>
+      <c r="AG3">
+        <v>15.5</v>
+      </c>
+      <c r="AH3">
+        <v>25</v>
+      </c>
+      <c r="AI3">
+        <v>65</v>
+      </c>
+      <c r="AJ3">
+        <v>85</v>
+      </c>
+      <c r="AK3">
+        <v>60</v>
+      </c>
+      <c r="AL3">
+        <v>85</v>
+      </c>
+      <c r="AM3">
+        <v>180</v>
+      </c>
+      <c r="AN3">
+        <v>75</v>
+      </c>
+      <c r="AO3">
+        <v>40</v>
+      </c>
+      <c r="AP3">
+        <v>8.6</v>
+      </c>
+      <c r="AQ3">
+        <v>7.2</v>
+      </c>
+      <c r="AR3">
+        <v>13</v>
+      </c>
+      <c r="AS3">
+        <v>5.7</v>
+      </c>
+      <c r="AT3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
         <v>10.5</v>
       </c>
-      <c r="Z3">
-        <v>1000</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
+      <c r="AW3">
+        <v>11</v>
+      </c>
+      <c r="AX3">
+        <v>19.5</v>
+      </c>
+      <c r="AY3">
         <v>13</v>
       </c>
-      <c r="AC3">
-        <v>13</v>
-      </c>
-      <c r="AD3">
-        <v>29</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>1000</v>
-      </c>
-      <c r="AG3">
-        <v>29</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>1.46</v>
-      </c>
-      <c r="AQ3">
-        <v>5.7</v>
-      </c>
-      <c r="AR3">
-        <v>1.46</v>
-      </c>
-      <c r="AS3">
-        <v>1.46</v>
-      </c>
-      <c r="AT3">
-        <v>1.31</v>
-      </c>
-      <c r="AU3">
-        <v>4.8</v>
-      </c>
-      <c r="AV3">
-        <v>1.39</v>
-      </c>
-      <c r="AW3">
-        <v>1.46</v>
-      </c>
-      <c r="AX3">
-        <v>1.46</v>
-      </c>
-      <c r="AY3">
-        <v>9.4</v>
-      </c>
       <c r="AZ3">
-        <v>1.46</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>1.46</v>
+        <v>5.9</v>
       </c>
       <c r="BB3">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="BC3">
-        <v>1.46</v>
+        <v>5.9</v>
       </c>
       <c r="BD3">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="BE3">
-        <v>1.46</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="BG3">
-        <v>1.46</v>
+        <v>5.6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1742,7 +1742,7 @@
         <v>3.7</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P4">
         <v>1.79</v>
@@ -1841,7 +1841,7 @@
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AW4">
         <v>2.1</v>
@@ -1850,7 +1850,7 @@
         <v>2</v>
       </c>
       <c r="AY4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
         <v>14</v>
@@ -1963,7 +1963,7 @@
         <v>2.48</v>
       </c>
       <c r="H5">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I5">
         <v>3.1</v>
@@ -1972,37 +1972,37 @@
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.32</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="O5">
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S5">
         <v>2.86</v>
       </c>
       <c r="T5">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
         <v>1.47</v>
@@ -2011,91 +2011,91 @@
         <v>1.67</v>
       </c>
       <c r="X5">
+        <v>19</v>
+      </c>
+      <c r="Y5">
+        <v>15</v>
+      </c>
+      <c r="Z5">
         <v>26</v>
       </c>
-      <c r="Y5">
-        <v>1000</v>
-      </c>
-      <c r="Z5">
-        <v>1000</v>
-      </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB5">
         <v>13</v>
       </c>
       <c r="AC5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF5">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS5">
         <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW5">
         <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
         <v>1.03</v>
@@ -2104,7 +2104,7 @@
         <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
         <v>1.03</v>
@@ -2113,10 +2113,10 @@
         <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2199,19 +2199,19 @@
         <v>170</v>
       </c>
       <c r="F6">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H6">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I6">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K6">
         <v>3.45</v>
@@ -2232,22 +2232,22 @@
         <v>1.67</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
         <v>1.22</v>
       </c>
       <c r="S6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T6">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W6">
         <v>1.37</v>
@@ -2262,13 +2262,13 @@
         <v>1000</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
         <v>24</v>
@@ -2307,58 +2307,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AQ6">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AR6">
+        <v>1.58</v>
+      </c>
+      <c r="AS6">
+        <v>1.51</v>
+      </c>
+      <c r="AT6">
         <v>1.47</v>
-      </c>
-      <c r="AS6">
-        <v>1.45</v>
-      </c>
-      <c r="AT6">
-        <v>1.38</v>
       </c>
       <c r="AU6">
         <v>5.5</v>
       </c>
       <c r="AV6">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AW6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AX6">
-        <v>1.45</v>
+        <v>15.5</v>
       </c>
       <c r="AY6">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>1.55</v>
       </c>
       <c r="BA6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="BB6">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="BC6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="BD6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="BE6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="BF6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="BG6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2441,25 +2441,25 @@
         <v>171</v>
       </c>
       <c r="F7">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>600</v>
       </c>
       <c r="H7">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="I7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
         <v>1.03</v>
@@ -2471,10 +2471,10 @@
         <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="R7">
         <v>1.32</v>
@@ -2489,10 +2489,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W7">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2683,16 +2683,16 @@
         <v>172</v>
       </c>
       <c r="F8">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G8">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H8">
         <v>3.15</v>
       </c>
       <c r="I8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J8">
         <v>3.5</v>
@@ -2710,37 +2710,37 @@
         <v>3.5</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q8">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="R8">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S8">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T8">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="U8">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X8">
         <v>1000</v>
       </c>
       <c r="Y8">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
         <v>27</v>
@@ -2752,7 +2752,7 @@
         <v>970</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2764,7 +2764,7 @@
         <v>1000</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH8">
         <v>27</v>
@@ -2794,7 +2794,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
         <v>1.42</v>
@@ -2803,7 +2803,7 @@
         <v>1.5</v>
       </c>
       <c r="AT8">
-        <v>1.37</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8">
         <v>1.27</v>
@@ -2818,7 +2818,7 @@
         <v>1.5</v>
       </c>
       <c r="AY8">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AZ8">
         <v>1.42</v>
@@ -2937,7 +2937,7 @@
         <v>870</v>
       </c>
       <c r="J9">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -3167,13 +3167,13 @@
         <v>174</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G10">
         <v>600</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I10">
         <v>870</v>
@@ -3215,10 +3215,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3917,10 +3917,10 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
         <v>2.4</v>
@@ -3932,7 +3932,7 @@
         <v>1.54</v>
       </c>
       <c r="S13">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4135,13 +4135,13 @@
         <v>178</v>
       </c>
       <c r="F14">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G14">
         <v>2.88</v>
       </c>
       <c r="H14">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I14">
         <v>3</v>
@@ -4150,7 +4150,7 @@
         <v>3.15</v>
       </c>
       <c r="K14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4377,13 +4377,13 @@
         <v>179</v>
       </c>
       <c r="F15">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G15">
         <v>2.82</v>
       </c>
       <c r="H15">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I15">
         <v>2.9</v>
@@ -4410,10 +4410,10 @@
         <v>1.9</v>
       </c>
       <c r="Q15">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S15">
         <v>3.6</v>
@@ -4437,7 +4437,7 @@
         <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA15">
         <v>50</v>
@@ -4452,7 +4452,7 @@
         <v>13</v>
       </c>
       <c r="AE15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF15">
         <v>22</v>
@@ -4494,7 +4494,7 @@
         <v>16</v>
       </c>
       <c r="AS15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT15">
         <v>9.800000000000001</v>
@@ -4506,7 +4506,7 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX15">
         <v>15</v>
@@ -4515,10 +4515,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB15">
         <v>8.4</v>
@@ -4867,16 +4867,16 @@
         <v>2.06</v>
       </c>
       <c r="H17">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I17">
         <v>4.5</v>
       </c>
       <c r="J17">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K17">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L17">
         <v>1.25</v>
@@ -5106,7 +5106,7 @@
         <v>1.12</v>
       </c>
       <c r="G18">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H18">
         <v>2.14</v>
@@ -5354,7 +5354,7 @@
         <v>3.8</v>
       </c>
       <c r="I19">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>3.1</v>
@@ -5393,7 +5393,7 @@
         <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W19">
         <v>1.75</v>
@@ -5832,7 +5832,7 @@
         <v>1.59</v>
       </c>
       <c r="G21">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -5880,7 +5880,7 @@
         <v>1.18</v>
       </c>
       <c r="W21">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="X21">
         <v>18.5</v>
@@ -6071,7 +6071,7 @@
         <v>186</v>
       </c>
       <c r="F22">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -6083,10 +6083,10 @@
         <v>1.7</v>
       </c>
       <c r="J22">
-        <v>3.6</v>
+        <v>1.12</v>
       </c>
       <c r="K22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6098,7 +6098,7 @@
         <v>2.42</v>
       </c>
       <c r="O22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P22">
         <v>2.06</v>
@@ -6227,7 +6227,7 @@
         <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG22">
         <v>1.01</v>
@@ -6316,13 +6316,13 @@
         <v>1.1</v>
       </c>
       <c r="G23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H23">
         <v>1.1</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J23">
         <v>1.1</v>
@@ -6337,16 +6337,16 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O23">
         <v>1.34</v>
       </c>
       <c r="P23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q23">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="R23">
         <v>1.18</v>
@@ -6361,10 +6361,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6561,13 +6561,13 @@
         <v>600</v>
       </c>
       <c r="H24">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="I24">
         <v>870</v>
       </c>
       <c r="J24">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6579,13 +6579,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="O24">
         <v>1.02</v>
       </c>
       <c r="P24">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q24">
         <v>1.03</v>
@@ -6899,7 +6899,7 @@
         <v>110</v>
       </c>
       <c r="AN25">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO25">
         <v>26</v>
@@ -6962,61 +6962,61 @@
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.14</v>
+        <v>1.67</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="CB25" t="s">
         <v>207</v>
@@ -7281,13 +7281,13 @@
         <v>191</v>
       </c>
       <c r="F27">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G27">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H27">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I27">
         <v>3.6</v>
@@ -7296,7 +7296,7 @@
         <v>3.4</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L27">
         <v>1.4</v>
@@ -7311,7 +7311,7 @@
         <v>1.35</v>
       </c>
       <c r="P27">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q27">
         <v>2.06</v>
@@ -7320,19 +7320,19 @@
         <v>1.27</v>
       </c>
       <c r="S27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T27">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U27">
         <v>2.02</v>
       </c>
       <c r="V27">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X27">
         <v>28</v>
@@ -7341,7 +7341,7 @@
         <v>13</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA27">
         <v>85</v>
@@ -7383,7 +7383,7 @@
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO27">
         <v>55</v>
@@ -7395,10 +7395,10 @@
         <v>8.4</v>
       </c>
       <c r="AR27">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="AS27">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="AT27">
         <v>8</v>
@@ -7410,7 +7410,7 @@
         <v>9.6</v>
       </c>
       <c r="AW27">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="AX27">
         <v>9.199999999999999</v>
@@ -7422,25 +7422,25 @@
         <v>11.5</v>
       </c>
       <c r="BA27">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="BB27">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="BC27">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="BD27">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="BE27">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="BF27">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="BG27">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7538,7 +7538,7 @@
         <v>7.2</v>
       </c>
       <c r="K28">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L28">
         <v>1.21</v>
@@ -7547,19 +7547,19 @@
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="O28">
         <v>1.11</v>
       </c>
       <c r="P28">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="R28">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S28">
         <v>1.98</v>
@@ -7568,7 +7568,7 @@
         <v>1.86</v>
       </c>
       <c r="U28">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V28">
         <v>1.07</v>
@@ -7580,10 +7580,10 @@
         <v>50</v>
       </c>
       <c r="Y28">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z28">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
         <v>500</v>
@@ -7592,13 +7592,13 @@
         <v>13.5</v>
       </c>
       <c r="AC28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD28">
         <v>55</v>
       </c>
       <c r="AE28">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
         <v>10</v>
@@ -7610,7 +7610,7 @@
         <v>36</v>
       </c>
       <c r="AI28">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
         <v>11</v>
@@ -7622,25 +7622,25 @@
         <v>34</v>
       </c>
       <c r="AM28">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
         <v>3.4</v>
       </c>
       <c r="AO28">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AQ28">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AR28">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AS28">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AT28">
         <v>11.5</v>
@@ -7649,10 +7649,10 @@
         <v>15.5</v>
       </c>
       <c r="AV28">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="AW28">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AX28">
         <v>9</v>
@@ -7661,28 +7661,28 @@
         <v>10</v>
       </c>
       <c r="AZ28">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="BA28">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BB28">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC28">
         <v>11.5</v>
       </c>
       <c r="BD28">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE28">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BF28">
         <v>3.2</v>
       </c>
       <c r="BG28">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7700,7 +7700,7 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BN28">
         <v>1000</v>
@@ -7730,19 +7730,19 @@
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="CB28" t="s">
         <v>207</v>
@@ -7765,7 +7765,7 @@
         <v>193</v>
       </c>
       <c r="F29">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G29">
         <v>1.81</v>
@@ -7777,10 +7777,10 @@
         <v>6.6</v>
       </c>
       <c r="J29">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K29">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L29">
         <v>1.56</v>
@@ -7789,7 +7789,7 @@
         <v>1.12</v>
       </c>
       <c r="N29">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O29">
         <v>1.55</v>
@@ -7804,7 +7804,7 @@
         <v>1.2</v>
       </c>
       <c r="S29">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T29">
         <v>2.44</v>
@@ -7876,10 +7876,10 @@
         <v>7.8</v>
       </c>
       <c r="AQ29">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS29">
         <v>46</v>
@@ -7888,7 +7888,7 @@
         <v>5.5</v>
       </c>
       <c r="AU29">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV29">
         <v>20</v>
@@ -7903,7 +7903,7 @@
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA29">
         <v>44</v>
@@ -8007,22 +8007,22 @@
         <v>194</v>
       </c>
       <c r="F30">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G30">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H30">
         <v>3.65</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J30">
         <v>3.1</v>
       </c>
       <c r="K30">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L30">
         <v>1.48</v>
@@ -8031,28 +8031,28 @@
         <v>1.11</v>
       </c>
       <c r="N30">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>1.45</v>
       </c>
       <c r="P30">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
       </c>
       <c r="R30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S30">
         <v>4.4</v>
       </c>
       <c r="T30">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U30">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="V30">
         <v>1.33</v>
@@ -8136,7 +8136,7 @@
         <v>13.5</v>
       </c>
       <c r="AW30">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
@@ -8145,7 +8145,7 @@
         <v>10</v>
       </c>
       <c r="AZ30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
         <v>8.800000000000001</v>
@@ -8157,7 +8157,7 @@
         <v>21</v>
       </c>
       <c r="BD30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE30">
         <v>9.6</v>
@@ -8166,7 +8166,7 @@
         <v>19</v>
       </c>
       <c r="BG30">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH30">
         <v>3.05</v>
@@ -8252,19 +8252,19 @@
         <v>2.32</v>
       </c>
       <c r="G31">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H31">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I31">
         <v>3.3</v>
       </c>
       <c r="J31">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K31">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L31">
         <v>1.35</v>
@@ -8273,7 +8273,7 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O31">
         <v>1.29</v>
@@ -8291,7 +8291,7 @@
         <v>3</v>
       </c>
       <c r="T31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U31">
         <v>2.16</v>
@@ -8300,7 +8300,7 @@
         <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X31">
         <v>16</v>
@@ -8351,7 +8351,7 @@
         <v>100</v>
       </c>
       <c r="AN31">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO31">
         <v>40</v>
@@ -8363,10 +8363,10 @@
         <v>12</v>
       </c>
       <c r="AR31">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS31">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT31">
         <v>10</v>
@@ -8378,7 +8378,7 @@
         <v>12</v>
       </c>
       <c r="AW31">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX31">
         <v>14</v>
@@ -8390,25 +8390,25 @@
         <v>14.5</v>
       </c>
       <c r="BA31">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB31">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC31">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD31">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE31">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF31">
         <v>15.5</v>
       </c>
       <c r="BG31">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31">
         <v>4.3</v>
@@ -8739,7 +8739,7 @@
         <v>2.16</v>
       </c>
       <c r="H33">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="I33">
         <v>6.8</v>
@@ -8763,13 +8763,13 @@
         <v>1.13</v>
       </c>
       <c r="P33">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="Q33">
         <v>1.38</v>
       </c>
       <c r="R33">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S33">
         <v>2</v>
@@ -8784,7 +8784,7 @@
         <v>1.23</v>
       </c>
       <c r="W33">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -8975,10 +8975,10 @@
         <v>198</v>
       </c>
       <c r="F34">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="G34">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="H34">
         <v>3.05</v>
@@ -8987,31 +8987,31 @@
         <v>3.35</v>
       </c>
       <c r="J34">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K34">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L34">
         <v>1.55</v>
       </c>
       <c r="M34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N34">
         <v>2.68</v>
       </c>
       <c r="O34">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="P34">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q34">
         <v>2.56</v>
       </c>
       <c r="R34">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S34">
         <v>4.7</v>
@@ -9020,19 +9020,19 @@
         <v>2</v>
       </c>
       <c r="U34">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V34">
         <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X34">
         <v>13.5</v>
       </c>
       <c r="Y34">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Z34">
         <v>25</v>
@@ -9041,10 +9041,10 @@
         <v>80</v>
       </c>
       <c r="AB34">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AC34">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD34">
         <v>55</v>
@@ -9056,7 +9056,7 @@
         <v>23</v>
       </c>
       <c r="AG34">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="AH34">
         <v>26</v>
@@ -9086,55 +9086,55 @@
         <v>6.4</v>
       </c>
       <c r="AQ34">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AR34">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AS34">
-        <v>3.45</v>
+        <v>2.46</v>
       </c>
       <c r="AT34">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU34">
         <v>5.5</v>
       </c>
       <c r="AV34">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="AW34">
-        <v>3.4</v>
+        <v>2.46</v>
       </c>
       <c r="AX34">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AY34">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ34">
-        <v>15.5</v>
+        <v>2.32</v>
       </c>
       <c r="BA34">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="BB34">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="BC34">
-        <v>25</v>
+        <v>2.44</v>
       </c>
       <c r="BD34">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="BE34">
-        <v>3.55</v>
+        <v>2.28</v>
       </c>
       <c r="BF34">
-        <v>3.35</v>
+        <v>1.87</v>
       </c>
       <c r="BG34">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9146,55 +9146,55 @@
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.12</v>
+        <v>2.64</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.14</v>
+        <v>1.99</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="CB34" t="s">
         <v>207</v>
@@ -9489,19 +9489,19 @@
         <v>1.37</v>
       </c>
       <c r="P36">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q36">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
         <v>1.3</v>
       </c>
       <c r="S36">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="T36">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U36">
         <v>2.08</v>
@@ -9540,13 +9540,13 @@
         <v>19.5</v>
       </c>
       <c r="AG36">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH36">
         <v>18.5</v>
       </c>
       <c r="AI36">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ36">
         <v>50</v>
@@ -9564,7 +9564,7 @@
         <v>36</v>
       </c>
       <c r="AO36">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP36">
         <v>11.5</v>
@@ -9579,7 +9579,7 @@
         <v>36</v>
       </c>
       <c r="AT36">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU36">
         <v>6.6</v>
@@ -9591,7 +9591,7 @@
         <v>27</v>
       </c>
       <c r="AX36">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY36">
         <v>11.5</v>
@@ -9737,7 +9737,7 @@
         <v>1.99</v>
       </c>
       <c r="R37">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S37">
         <v>3.55</v>
@@ -9767,7 +9767,7 @@
         <v>160</v>
       </c>
       <c r="AB37">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC37">
         <v>10.5</v>
@@ -9815,10 +9815,10 @@
         <v>15</v>
       </c>
       <c r="AR37">
+        <v>4.1</v>
+      </c>
+      <c r="AS37">
         <v>4.4</v>
-      </c>
-      <c r="AS37">
-        <v>4.6</v>
       </c>
       <c r="AT37">
         <v>7.4</v>
@@ -9830,7 +9830,7 @@
         <v>17.5</v>
       </c>
       <c r="AW37">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX37">
         <v>9.6</v>
@@ -9842,7 +9842,7 @@
         <v>17.5</v>
       </c>
       <c r="BA37">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB37">
         <v>17</v>
@@ -9851,16 +9851,16 @@
         <v>17.5</v>
       </c>
       <c r="BD37">
+        <v>4.1</v>
+      </c>
+      <c r="BE37">
         <v>4.3</v>
-      </c>
-      <c r="BE37">
-        <v>4.6</v>
       </c>
       <c r="BF37">
         <v>11</v>
       </c>
       <c r="BG37">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9943,19 +9943,19 @@
         <v>202</v>
       </c>
       <c r="F38">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>8.6</v>
       </c>
       <c r="H38">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I38">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="J38">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K38">
         <v>5.7</v>
@@ -9967,13 +9967,13 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>4.7</v>
+        <v>2.44</v>
       </c>
       <c r="O38">
         <v>1.19</v>
       </c>
       <c r="P38">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
         <v>1.56</v>
@@ -9982,7 +9982,7 @@
         <v>1.56</v>
       </c>
       <c r="S38">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T38">
         <v>1.63</v>
@@ -9991,7 +9991,7 @@
         <v>1.83</v>
       </c>
       <c r="V38">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="W38">
         <v>1.13</v>
@@ -10003,10 +10003,10 @@
         <v>13</v>
       </c>
       <c r="Z38">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA38">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AB38">
         <v>38</v>
@@ -10048,58 +10048,58 @@
         <v>130</v>
       </c>
       <c r="AO38">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AP38">
+        <v>4.7</v>
+      </c>
+      <c r="AQ38">
         <v>4</v>
       </c>
-      <c r="AQ38">
-        <v>3.5</v>
-      </c>
       <c r="AR38">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AS38">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AT38">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AU38">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AV38">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AW38">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AX38">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY38">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AZ38">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BA38">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BB38">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC38">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD38">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE38">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF38">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG38">
         <v>4.7</v>
@@ -10451,16 +10451,16 @@
         <v>1.11</v>
       </c>
       <c r="N40">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O40">
         <v>1.54</v>
       </c>
       <c r="P40">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q40">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R40">
         <v>1.2</v>
@@ -10529,7 +10529,7 @@
         <v>270</v>
       </c>
       <c r="AN40">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO40">
         <v>220</v>
@@ -10729,7 +10729,7 @@
         <v>7.2</v>
       </c>
       <c r="Z41">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA41">
         <v>32</v>
@@ -10801,7 +10801,7 @@
         <v>25</v>
       </c>
       <c r="AX41">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY41">
         <v>16</v>
@@ -10813,19 +10813,19 @@
         <v>50</v>
       </c>
       <c r="BB41">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC41">
         <v>55</v>
       </c>
       <c r="BD41">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BE41">
         <v>11.5</v>
       </c>
       <c r="BF41">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG41">
         <v>21</v>
@@ -10911,16 +10911,16 @@
         <v>206</v>
       </c>
       <c r="F42">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="G42">
         <v>2.08</v>
       </c>
       <c r="H42">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J42">
         <v>3.5</v>
@@ -10929,7 +10929,7 @@
         <v>3.8</v>
       </c>
       <c r="L42">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M42">
         <v>1.04</v>
@@ -10944,7 +10944,7 @@
         <v>1.77</v>
       </c>
       <c r="Q42">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R42">
         <v>1.28</v>
@@ -10956,13 +10956,13 @@
         <v>1.83</v>
       </c>
       <c r="U42">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V42">
         <v>1.26</v>
       </c>
       <c r="W42">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X42">
         <v>1000</v>
@@ -11073,64 +11073,64 @@
         <v>1.19</v>
       </c>
       <c r="BH42">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI42">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ42">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK42">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN42">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO42">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP42">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ42">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR42">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS42">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT42">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU42">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV42">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW42">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BX42">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY42">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ42">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA42">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB42" t="s">
         <v>207</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -637,7 +637,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-10-03 05:36:12</t>
+    <t>2026-10-03 07:52:35</t>
   </si>
 </sst>
 </file>
@@ -1237,16 +1237,16 @@
         <v>1.47</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="J2">
         <v>4.9</v>
       </c>
       <c r="K2">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1255,13 +1255,13 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q2">
         <v>1.79</v>
@@ -1273,13 +1273,13 @@
         <v>3</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="V2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W2">
         <v>3.1</v>
@@ -1297,10 +1297,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1315,7 +1315,7 @@
         <v>1000</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -1369,7 +1369,7 @@
         <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
         <v>1.03</v>
@@ -1482,37 +1482,37 @@
         <v>2.4</v>
       </c>
       <c r="I3">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
         <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O3">
         <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
         <v>1.96</v>
@@ -1521,7 +1521,7 @@
         <v>1.88</v>
       </c>
       <c r="V3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
         <v>1.4</v>
@@ -1715,19 +1715,19 @@
         <v>168</v>
       </c>
       <c r="F4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>4.3</v>
@@ -1745,13 +1745,13 @@
         <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
         <v>1.98</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
         <v>3.4</v>
@@ -1766,13 +1766,13 @@
         <v>2.04</v>
       </c>
       <c r="W4">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X4">
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
         <v>14.5</v>
@@ -1793,13 +1793,13 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AH4">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AI4">
         <v>1000</v>
@@ -1823,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AP4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AQ4">
         <v>6.2</v>
@@ -1835,46 +1835,46 @@
         <v>14</v>
       </c>
       <c r="AT4">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>7.2</v>
       </c>
       <c r="AW4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AX4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AY4">
         <v>11</v>
       </c>
       <c r="AZ4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA4">
         <v>23</v>
       </c>
       <c r="BB4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="BC4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="BD4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="BE4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="BF4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="BG4">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -2199,7 +2199,7 @@
         <v>170</v>
       </c>
       <c r="F6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G6">
         <v>3.7</v>
@@ -2208,157 +2208,157 @@
         <v>2.36</v>
       </c>
       <c r="I6">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J6">
         <v>3.2</v>
       </c>
       <c r="K6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R6">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
         <v>4.3</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="V6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W6">
         <v>1.37</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y6">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA6">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AB6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AC6">
+        <v>7.6</v>
+      </c>
+      <c r="AD6">
+        <v>14.5</v>
+      </c>
+      <c r="AE6">
+        <v>38</v>
+      </c>
+      <c r="AF6">
+        <v>29</v>
+      </c>
+      <c r="AG6">
+        <v>18.5</v>
+      </c>
+      <c r="AH6">
+        <v>20</v>
+      </c>
+      <c r="AI6">
+        <v>60</v>
+      </c>
+      <c r="AJ6">
+        <v>85</v>
+      </c>
+      <c r="AK6">
+        <v>60</v>
+      </c>
+      <c r="AL6">
+        <v>75</v>
+      </c>
+      <c r="AM6">
+        <v>160</v>
+      </c>
+      <c r="AN6">
+        <v>70</v>
+      </c>
+      <c r="AO6">
+        <v>34</v>
+      </c>
+      <c r="AP6">
+        <v>9.6</v>
+      </c>
+      <c r="AQ6">
+        <v>7.6</v>
+      </c>
+      <c r="AR6">
+        <v>13</v>
+      </c>
+      <c r="AS6">
+        <v>5.1</v>
+      </c>
+      <c r="AT6">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD6">
-        <v>24</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.47</v>
-      </c>
-      <c r="AQ6">
-        <v>1.43</v>
-      </c>
-      <c r="AR6">
-        <v>1.58</v>
-      </c>
-      <c r="AS6">
-        <v>1.51</v>
-      </c>
-      <c r="AT6">
-        <v>1.47</v>
-      </c>
       <c r="AU6">
+        <v>6.6</v>
+      </c>
+      <c r="AV6">
+        <v>10</v>
+      </c>
+      <c r="AW6">
+        <v>21</v>
+      </c>
+      <c r="AX6">
+        <v>20</v>
+      </c>
+      <c r="AY6">
+        <v>13</v>
+      </c>
+      <c r="AZ6">
+        <v>17</v>
+      </c>
+      <c r="BA6">
         <v>5.5</v>
       </c>
-      <c r="AV6">
-        <v>1.48</v>
-      </c>
-      <c r="AW6">
-        <v>1.55</v>
-      </c>
-      <c r="AX6">
-        <v>15.5</v>
-      </c>
-      <c r="AY6">
-        <v>1.58</v>
-      </c>
-      <c r="AZ6">
-        <v>1.55</v>
-      </c>
-      <c r="BA6">
-        <v>1.55</v>
-      </c>
       <c r="BB6">
-        <v>1.65</v>
+        <v>5.6</v>
       </c>
       <c r="BC6">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="BD6">
-        <v>1.55</v>
+        <v>5.6</v>
       </c>
       <c r="BE6">
-        <v>1.55</v>
+        <v>5.8</v>
       </c>
       <c r="BF6">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="BG6">
-        <v>1.55</v>
+        <v>20</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2370,55 +2370,55 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>207</v>
@@ -2444,19 +2444,19 @@
         <v>3.6</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>4.6</v>
       </c>
       <c r="H7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J7">
         <v>1.12</v>
       </c>
       <c r="K7">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.34</v>
@@ -2465,22 +2465,22 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O7">
         <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q7">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S7">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2489,10 +2489,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W7">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2683,10 +2683,10 @@
         <v>172</v>
       </c>
       <c r="F8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G8">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H8">
         <v>3.15</v>
@@ -2698,7 +2698,7 @@
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.34</v>
@@ -2931,7 +2931,7 @@
         <v>1.45</v>
       </c>
       <c r="H9">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
         <v>870</v>
@@ -3167,58 +3167,58 @@
         <v>174</v>
       </c>
       <c r="F10">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="G10">
-        <v>600</v>
+        <v>1.43</v>
       </c>
       <c r="H10">
-        <v>1.12</v>
+        <v>5.9</v>
       </c>
       <c r="I10">
         <v>870</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>4.5</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>460</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.32</v>
+        <v>2.52</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P10">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q10">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="S10">
-        <v>1.2</v>
+        <v>2.14</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AO10">
         <v>1000</v>
@@ -3323,7 +3323,7 @@
         <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG10">
         <v>1.01</v>
@@ -3350,7 +3350,7 @@
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP10">
         <v>1000</v>
@@ -3409,64 +3409,64 @@
         <v>175</v>
       </c>
       <c r="F11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P11">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q11">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z11">
         <v>1000</v>
@@ -3475,10 +3475,10 @@
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD11">
         <v>1000</v>
@@ -3487,10 +3487,10 @@
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH11">
         <v>1000</v>
@@ -3529,10 +3529,10 @@
         <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV11">
         <v>1.03</v>
@@ -3544,7 +3544,7 @@
         <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ11">
         <v>1.03</v>
@@ -3565,7 +3565,7 @@
         <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG11">
         <v>1.01</v>
@@ -3580,7 +3580,7 @@
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3592,7 +3592,7 @@
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="BP11">
         <v>1000</v>
@@ -3651,58 +3651,58 @@
         <v>176</v>
       </c>
       <c r="F12">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="G12">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H12">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="I12">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P12">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R12">
         <v>1.37</v>
       </c>
       <c r="S12">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T12">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U12">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W12">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3735,7 +3735,7 @@
         <v>1000</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI12">
         <v>1000</v>
@@ -3759,58 +3759,58 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AS12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AT12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AW12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AX12">
-        <v>1.08</v>
+        <v>13.5</v>
       </c>
       <c r="AY12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AZ12">
         <v>1.08</v>
       </c>
       <c r="BA12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BB12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BC12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BD12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BE12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BF12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3896,19 +3896,19 @@
         <v>2.94</v>
       </c>
       <c r="G13">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H13">
         <v>2.1</v>
       </c>
       <c r="I13">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="J13">
         <v>3.55</v>
       </c>
       <c r="K13">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3917,10 +3917,10 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P13">
         <v>2.4</v>
@@ -3929,76 +3929,76 @@
         <v>1.5</v>
       </c>
       <c r="R13">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S13">
         <v>2.24</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V13">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W13">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP13">
         <v>1.03</v>
@@ -4049,10 +4049,10 @@
         <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH13">
         <v>5</v>
@@ -4147,7 +4147,7 @@
         <v>3</v>
       </c>
       <c r="J14">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K14">
         <v>3.6</v>
@@ -4189,58 +4189,58 @@
         <v>1.53</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP14">
         <v>1.03</v>
@@ -4291,10 +4291,10 @@
         <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4377,13 +4377,13 @@
         <v>179</v>
       </c>
       <c r="F15">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G15">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H15">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I15">
         <v>2.9</v>
@@ -4392,7 +4392,7 @@
         <v>3.4</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L15">
         <v>1.41</v>
@@ -4401,22 +4401,22 @@
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O15">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P15">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q15">
         <v>2</v>
       </c>
       <c r="R15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T15">
         <v>1.79</v>
@@ -4437,16 +4437,16 @@
         <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA15">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AB15">
         <v>11.5</v>
       </c>
       <c r="AC15">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15">
         <v>13</v>
@@ -4455,19 +4455,19 @@
         <v>34</v>
       </c>
       <c r="AF15">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AG15">
         <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI15">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK15">
         <v>38</v>
@@ -4476,10 +4476,10 @@
         <v>55</v>
       </c>
       <c r="AM15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO15">
         <v>32</v>
@@ -4494,7 +4494,7 @@
         <v>16</v>
       </c>
       <c r="AS15">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AT15">
         <v>9.800000000000001</v>
@@ -4506,31 +4506,31 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AX15">
+        <v>16</v>
+      </c>
+      <c r="AY15">
+        <v>11</v>
+      </c>
+      <c r="AZ15">
         <v>15</v>
       </c>
-      <c r="AY15">
-        <v>10.5</v>
-      </c>
-      <c r="AZ15">
-        <v>15.5</v>
-      </c>
       <c r="BA15">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BB15">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BC15">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="BD15">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="BE15">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BF15">
         <v>19.5</v>
@@ -4622,16 +4622,16 @@
         <v>2.4</v>
       </c>
       <c r="G16">
+        <v>2.48</v>
+      </c>
+      <c r="H16">
         <v>2.66</v>
       </c>
-      <c r="H16">
-        <v>2.64</v>
-      </c>
       <c r="I16">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J16">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
         <v>4.9</v>
@@ -4643,7 +4643,7 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O16">
         <v>1.16</v>
@@ -4667,10 +4667,10 @@
         <v>2.58</v>
       </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4721,7 +4721,7 @@
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4739,7 +4739,7 @@
         <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU16">
         <v>1.03</v>
@@ -4778,7 +4778,7 @@
         <v>9</v>
       </c>
       <c r="BG16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4870,13 +4870,13 @@
         <v>3.65</v>
       </c>
       <c r="I17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L17">
         <v>1.25</v>
@@ -4903,10 +4903,10 @@
         <v>2.3</v>
       </c>
       <c r="T17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U17">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
         <v>1.28</v>
@@ -5109,13 +5109,13 @@
         <v>2.52</v>
       </c>
       <c r="H18">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I18">
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5151,10 +5151,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W18">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5348,7 +5348,7 @@
         <v>2.06</v>
       </c>
       <c r="G19">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H19">
         <v>3.8</v>
@@ -5357,7 +5357,7 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K19">
         <v>4</v>
@@ -5369,13 +5369,13 @@
         <v>1.07</v>
       </c>
       <c r="N19">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O19">
         <v>1.45</v>
       </c>
       <c r="P19">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q19">
         <v>2.24</v>
@@ -5387,7 +5387,7 @@
         <v>4.2</v>
       </c>
       <c r="T19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U19">
         <v>1.75</v>
@@ -5396,7 +5396,7 @@
         <v>1.26</v>
       </c>
       <c r="W19">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X19">
         <v>970</v>
@@ -5453,58 +5453,58 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AQ19">
         <v>8.199999999999999</v>
       </c>
       <c r="AR19">
+        <v>2.04</v>
+      </c>
+      <c r="AS19">
         <v>2.14</v>
       </c>
-      <c r="AS19">
+      <c r="AT19">
+        <v>2.38</v>
+      </c>
+      <c r="AU19">
+        <v>2.36</v>
+      </c>
+      <c r="AV19">
+        <v>2.14</v>
+      </c>
+      <c r="AW19">
+        <v>2.08</v>
+      </c>
+      <c r="AX19">
         <v>2.24</v>
       </c>
-      <c r="AT19">
-        <v>2.42</v>
-      </c>
-      <c r="AU19">
-        <v>2.48</v>
-      </c>
-      <c r="AV19">
-        <v>2.24</v>
-      </c>
-      <c r="AW19">
-        <v>2.18</v>
-      </c>
-      <c r="AX19">
-        <v>2.36</v>
-      </c>
       <c r="AY19">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AZ19">
+        <v>1.99</v>
+      </c>
+      <c r="BA19">
+        <v>2.14</v>
+      </c>
+      <c r="BB19">
+        <v>2.02</v>
+      </c>
+      <c r="BC19">
+        <v>2.02</v>
+      </c>
+      <c r="BD19">
         <v>2.08</v>
       </c>
-      <c r="BA19">
-        <v>2.24</v>
-      </c>
-      <c r="BB19">
-        <v>2.1</v>
-      </c>
-      <c r="BC19">
-        <v>2.1</v>
-      </c>
-      <c r="BD19">
-        <v>2.18</v>
-      </c>
       <c r="BE19">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BF19">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BG19">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5832,7 +5832,7 @@
         <v>1.59</v>
       </c>
       <c r="G21">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -5844,7 +5844,7 @@
         <v>4.2</v>
       </c>
       <c r="K21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
         <v>1.37</v>
@@ -5865,13 +5865,13 @@
         <v>1.77</v>
       </c>
       <c r="R21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S21">
         <v>3.05</v>
       </c>
       <c r="T21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U21">
         <v>2</v>
@@ -5880,7 +5880,7 @@
         <v>1.18</v>
       </c>
       <c r="W21">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X21">
         <v>18.5</v>
@@ -6071,46 +6071,46 @@
         <v>186</v>
       </c>
       <c r="F22">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="G22">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="H22">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="I22">
         <v>1.7</v>
       </c>
       <c r="J22">
-        <v>1.12</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
         <v>2.42</v>
       </c>
       <c r="O22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q22">
         <v>1.51</v>
       </c>
       <c r="R22">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S22">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6128,55 +6128,55 @@
         <v>1000</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ22">
         <v>1000</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP22">
         <v>1.03</v>
@@ -6230,7 +6230,7 @@
         <v>9</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6316,7 +6316,7 @@
         <v>1.1</v>
       </c>
       <c r="G23">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="H23">
         <v>1.1</v>
@@ -6328,7 +6328,7 @@
         <v>1.1</v>
       </c>
       <c r="K23">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6361,10 +6361,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6603,10 +6603,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6926,7 +6926,7 @@
         <v>11</v>
       </c>
       <c r="AW25">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX25">
         <v>16.5</v>
@@ -6938,7 +6938,7 @@
         <v>15</v>
       </c>
       <c r="BA25">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB25">
         <v>8.800000000000001</v>
@@ -6947,7 +6947,7 @@
         <v>8.4</v>
       </c>
       <c r="BD25">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE25">
         <v>9.800000000000001</v>
@@ -7042,7 +7042,7 @@
         <v>1.5</v>
       </c>
       <c r="G26">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H26">
         <v>5.4</v>
@@ -7090,7 +7090,7 @@
         <v>1.11</v>
       </c>
       <c r="W26">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7284,19 +7284,19 @@
         <v>2.26</v>
       </c>
       <c r="G27">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H27">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I27">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J27">
         <v>3.4</v>
       </c>
       <c r="K27">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="L27">
         <v>1.4</v>
@@ -7305,16 +7305,16 @@
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O27">
         <v>1.35</v>
       </c>
       <c r="P27">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q27">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R27">
         <v>1.27</v>
@@ -7323,16 +7323,16 @@
         <v>3.6</v>
       </c>
       <c r="T27">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="U27">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X27">
         <v>28</v>
@@ -7341,7 +7341,7 @@
         <v>13</v>
       </c>
       <c r="Z27">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
         <v>85</v>
@@ -7374,7 +7374,7 @@
         <v>1000</v>
       </c>
       <c r="AK27">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
         <v>1000</v>
@@ -7395,13 +7395,13 @@
         <v>8.4</v>
       </c>
       <c r="AR27">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AS27">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AT27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU27">
         <v>5.7</v>
@@ -7410,7 +7410,7 @@
         <v>9.6</v>
       </c>
       <c r="AW27">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="AX27">
         <v>9.199999999999999</v>
@@ -7422,25 +7422,25 @@
         <v>11.5</v>
       </c>
       <c r="BA27">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="BB27">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="BC27">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="BD27">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="BE27">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="BF27">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="BG27">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7523,16 +7523,16 @@
         <v>192</v>
       </c>
       <c r="F28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G28">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H28">
         <v>12.5</v>
       </c>
       <c r="I28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J28">
         <v>7.2</v>
@@ -7547,25 +7547,25 @@
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P28">
         <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="R28">
         <v>1.89</v>
       </c>
       <c r="S28">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T28">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U28">
         <v>2.08</v>
@@ -7574,7 +7574,7 @@
         <v>1.07</v>
       </c>
       <c r="W28">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="X28">
         <v>50</v>
@@ -7586,7 +7586,7 @@
         <v>1000</v>
       </c>
       <c r="AA28">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AB28">
         <v>13.5</v>
@@ -7601,7 +7601,7 @@
         <v>1000</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG28">
         <v>11.5</v>
@@ -7783,7 +7783,7 @@
         <v>3.65</v>
       </c>
       <c r="L29">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M29">
         <v>1.12</v>
@@ -8007,7 +8007,7 @@
         <v>194</v>
       </c>
       <c r="F30">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G30">
         <v>2.4</v>
@@ -8022,7 +8022,7 @@
         <v>3.1</v>
       </c>
       <c r="K30">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L30">
         <v>1.48</v>
@@ -8037,13 +8037,13 @@
         <v>1.45</v>
       </c>
       <c r="P30">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q30">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R30">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S30">
         <v>4.4</v>
@@ -8073,7 +8073,7 @@
         <v>100</v>
       </c>
       <c r="AB30">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC30">
         <v>7.6</v>
@@ -8121,10 +8121,10 @@
         <v>10</v>
       </c>
       <c r="AR30">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS30">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT30">
         <v>7.4</v>
@@ -8136,7 +8136,7 @@
         <v>13.5</v>
       </c>
       <c r="AW30">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
@@ -8148,10 +8148,10 @@
         <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB30">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC30">
         <v>21</v>
@@ -8160,13 +8160,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE30">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF30">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG30">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH30">
         <v>3.05</v>
@@ -8249,22 +8249,22 @@
         <v>195</v>
       </c>
       <c r="F31">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G31">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I31">
         <v>3.3</v>
       </c>
       <c r="J31">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K31">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L31">
         <v>1.35</v>
@@ -8279,28 +8279,28 @@
         <v>1.29</v>
       </c>
       <c r="P31">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
       </c>
       <c r="R31">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T31">
         <v>1.68</v>
       </c>
       <c r="U31">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
         <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X31">
         <v>16</v>
@@ -8327,7 +8327,7 @@
         <v>44</v>
       </c>
       <c r="AF31">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG31">
         <v>12</v>
@@ -8345,13 +8345,13 @@
         <v>27</v>
       </c>
       <c r="AL31">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM31">
         <v>100</v>
       </c>
       <c r="AN31">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO31">
         <v>40</v>
@@ -8363,10 +8363,10 @@
         <v>12</v>
       </c>
       <c r="AR31">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS31">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT31">
         <v>10</v>
@@ -8378,7 +8378,7 @@
         <v>12</v>
       </c>
       <c r="AW31">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX31">
         <v>14</v>
@@ -8390,25 +8390,25 @@
         <v>14.5</v>
       </c>
       <c r="BA31">
+        <v>9</v>
+      </c>
+      <c r="BB31">
         <v>8.6</v>
       </c>
-      <c r="BB31">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD31">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE31">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF31">
         <v>15.5</v>
       </c>
       <c r="BG31">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH31">
         <v>4.3</v>
@@ -8736,16 +8736,16 @@
         <v>1.66</v>
       </c>
       <c r="G33">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H33">
         <v>2.3</v>
       </c>
       <c r="I33">
-        <v>6.8</v>
+        <v>870</v>
       </c>
       <c r="J33">
-        <v>2.56</v>
+        <v>1.12</v>
       </c>
       <c r="K33">
         <v>950</v>
@@ -8769,10 +8769,10 @@
         <v>1.38</v>
       </c>
       <c r="R33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S33">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T33">
         <v>1.01</v>
@@ -8987,10 +8987,10 @@
         <v>3.35</v>
       </c>
       <c r="J34">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K34">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L34">
         <v>1.55</v>
@@ -8999,13 +8999,13 @@
         <v>1.11</v>
       </c>
       <c r="N34">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="O34">
         <v>1.51</v>
       </c>
       <c r="P34">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="Q34">
         <v>2.56</v>
@@ -9020,7 +9020,7 @@
         <v>2</v>
       </c>
       <c r="U34">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V34">
         <v>1.42</v>
@@ -9053,7 +9053,7 @@
         <v>65</v>
       </c>
       <c r="AF34">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AG34">
         <v>36</v>
@@ -9128,13 +9128,13 @@
         <v>2.48</v>
       </c>
       <c r="BE34">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="BF34">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BG34">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9486,10 +9486,10 @@
         <v>3.4</v>
       </c>
       <c r="O36">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P36">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q36">
         <v>2.1</v>
@@ -9498,7 +9498,7 @@
         <v>1.3</v>
       </c>
       <c r="S36">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T36">
         <v>1.82</v>
@@ -9510,7 +9510,7 @@
         <v>1.55</v>
       </c>
       <c r="W36">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X36">
         <v>12.5</v>
@@ -9704,19 +9704,19 @@
         <v>1.78</v>
       </c>
       <c r="G37">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H37">
         <v>4.9</v>
       </c>
       <c r="I37">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J37">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9725,22 +9725,22 @@
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O37">
         <v>1.34</v>
       </c>
       <c r="P37">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q37">
         <v>1.99</v>
       </c>
       <c r="R37">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S37">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
         <v>1.9</v>
@@ -9770,7 +9770,7 @@
         <v>10</v>
       </c>
       <c r="AC37">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD37">
         <v>25</v>
@@ -9782,7 +9782,7 @@
         <v>13</v>
       </c>
       <c r="AG37">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH37">
         <v>25</v>
@@ -9809,16 +9809,16 @@
         <v>110</v>
       </c>
       <c r="AP37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ37">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR37">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS37">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT37">
         <v>7.4</v>
@@ -9830,7 +9830,7 @@
         <v>17.5</v>
       </c>
       <c r="AW37">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX37">
         <v>9.6</v>
@@ -9842,7 +9842,7 @@
         <v>17.5</v>
       </c>
       <c r="BA37">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB37">
         <v>17</v>
@@ -9851,16 +9851,16 @@
         <v>17.5</v>
       </c>
       <c r="BD37">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE37">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF37">
         <v>11</v>
       </c>
       <c r="BG37">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9943,22 +9943,22 @@
         <v>202</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G38">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H38">
         <v>1.43</v>
       </c>
       <c r="I38">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J38">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K38">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -9967,13 +9967,13 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="O38">
         <v>1.19</v>
       </c>
       <c r="P38">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q38">
         <v>1.56</v>
@@ -9985,13 +9985,13 @@
         <v>2.32</v>
       </c>
       <c r="T38">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="U38">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="V38">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W38">
         <v>1.13</v>
@@ -10000,10 +10000,10 @@
         <v>26</v>
       </c>
       <c r="Y38">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z38">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AA38">
         <v>13.5</v>
@@ -10051,55 +10051,55 @@
         <v>5.7</v>
       </c>
       <c r="AP38">
+        <v>5.4</v>
+      </c>
+      <c r="AQ38">
+        <v>4.2</v>
+      </c>
+      <c r="AR38">
+        <v>4.1</v>
+      </c>
+      <c r="AS38">
+        <v>4.5</v>
+      </c>
+      <c r="AT38">
+        <v>5.8</v>
+      </c>
+      <c r="AU38">
+        <v>4.6</v>
+      </c>
+      <c r="AV38">
+        <v>4.4</v>
+      </c>
+      <c r="AW38">
         <v>4.7</v>
       </c>
-      <c r="AQ38">
-        <v>4</v>
-      </c>
-      <c r="AR38">
-        <v>3.9</v>
-      </c>
-      <c r="AS38">
-        <v>4</v>
-      </c>
-      <c r="AT38">
-        <v>5</v>
-      </c>
-      <c r="AU38">
-        <v>4.1</v>
-      </c>
-      <c r="AV38">
-        <v>3.95</v>
-      </c>
-      <c r="AW38">
-        <v>4.2</v>
-      </c>
       <c r="AX38">
+        <v>6.2</v>
+      </c>
+      <c r="AY38">
+        <v>5.7</v>
+      </c>
+      <c r="AZ38">
         <v>5.4</v>
       </c>
-      <c r="AY38">
-        <v>5</v>
-      </c>
-      <c r="AZ38">
-        <v>4.7</v>
-      </c>
       <c r="BA38">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB38">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC38">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD38">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE38">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF38">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG38">
         <v>4.7</v>
@@ -10427,16 +10427,16 @@
         <v>204</v>
       </c>
       <c r="F40">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G40">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H40">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I40">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J40">
         <v>3.3</v>
@@ -10448,19 +10448,19 @@
         <v>1.55</v>
       </c>
       <c r="M40">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N40">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O40">
         <v>1.54</v>
       </c>
       <c r="P40">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q40">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R40">
         <v>1.2</v>
@@ -10469,19 +10469,19 @@
         <v>5.3</v>
       </c>
       <c r="T40">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U40">
         <v>1.7</v>
       </c>
       <c r="V40">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W40">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X40">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y40">
         <v>13.5</v>
@@ -10490,7 +10490,7 @@
         <v>50</v>
       </c>
       <c r="AA40">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB40">
         <v>6.4</v>
@@ -10502,7 +10502,7 @@
         <v>26</v>
       </c>
       <c r="AE40">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF40">
         <v>10.5</v>
@@ -10511,10 +10511,10 @@
         <v>11.5</v>
       </c>
       <c r="AH40">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AI40">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ40">
         <v>27</v>
@@ -10526,13 +10526,13 @@
         <v>75</v>
       </c>
       <c r="AM40">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN40">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO40">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP40">
         <v>7.8</v>
@@ -10541,22 +10541,22 @@
         <v>11.5</v>
       </c>
       <c r="AR40">
-        <v>9.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="AS40">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AT40">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU40">
         <v>7.2</v>
       </c>
       <c r="AV40">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AW40">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AX40">
         <v>8.800000000000001</v>
@@ -10565,64 +10565,64 @@
         <v>10</v>
       </c>
       <c r="AZ40">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BA40">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BB40">
         <v>20</v>
       </c>
       <c r="BC40">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BD40">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BE40">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BF40">
         <v>18</v>
       </c>
       <c r="BG40">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BH40">
         <v>1000</v>
       </c>
       <c r="BI40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
       </c>
       <c r="BK40">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BN40">
         <v>1000</v>
       </c>
       <c r="BO40">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="BP40">
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BT40">
         <v>1000</v>
@@ -10634,19 +10634,19 @@
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="CB40" t="s">
         <v>207</v>
@@ -10678,16 +10678,16 @@
         <v>2.16</v>
       </c>
       <c r="I41">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J41">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K41">
         <v>3.25</v>
       </c>
       <c r="L41">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M41">
         <v>1.12</v>
@@ -10696,19 +10696,19 @@
         <v>2.56</v>
       </c>
       <c r="O41">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P41">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q41">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R41">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S41">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T41">
         <v>2.1</v>
@@ -10717,10 +10717,10 @@
         <v>1.79</v>
       </c>
       <c r="V41">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W41">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X41">
         <v>11</v>
@@ -10732,7 +10732,7 @@
         <v>12</v>
       </c>
       <c r="AA41">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB41">
         <v>12</v>
@@ -10741,13 +10741,13 @@
         <v>7.4</v>
       </c>
       <c r="AD41">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE41">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF41">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG41">
         <v>18.5</v>
@@ -10756,25 +10756,25 @@
         <v>24</v>
       </c>
       <c r="AI41">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ41">
         <v>130</v>
       </c>
       <c r="AK41">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL41">
         <v>110</v>
       </c>
       <c r="AM41">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN41">
         <v>130</v>
       </c>
       <c r="AO41">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP41">
         <v>8</v>
@@ -10813,28 +10813,28 @@
         <v>50</v>
       </c>
       <c r="BB41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC41">
         <v>55</v>
       </c>
       <c r="BD41">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="BE41">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BF41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG41">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BH41">
         <v>1000</v>
       </c>
       <c r="BI41">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ41">
         <v>1000</v>
@@ -10870,7 +10870,7 @@
         <v>1000</v>
       </c>
       <c r="BU41">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV41">
         <v>1000</v>
@@ -10911,22 +10911,22 @@
         <v>206</v>
       </c>
       <c r="F42">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G42">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H42">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I42">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="K42">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L42">
         <v>1.43</v>
@@ -10935,7 +10935,7 @@
         <v>1.04</v>
       </c>
       <c r="N42">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O42">
         <v>1.35</v>
@@ -10944,7 +10944,7 @@
         <v>1.77</v>
       </c>
       <c r="Q42">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R42">
         <v>1.28</v>
@@ -10953,16 +10953,16 @@
         <v>3.3</v>
       </c>
       <c r="T42">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="U42">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V42">
         <v>1.26</v>
       </c>
       <c r="W42">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="X42">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="212">
   <si>
     <t>League</t>
   </si>
@@ -424,12 +424,12 @@
     <t>Tegevajaro Miyazaki</t>
   </si>
   <si>
+    <t>Vasalunds IF</t>
+  </si>
+  <si>
     <t>BK Olympic</t>
   </si>
   <si>
-    <t>Vasalunds IF</t>
-  </si>
-  <si>
     <t>Sociedad B</t>
   </si>
   <si>
@@ -475,21 +475,24 @@
     <t>CA Huracan</t>
   </si>
   <si>
+    <t>Cerro</t>
+  </si>
+  <si>
+    <t>Girona</t>
+  </si>
+  <si>
+    <t>Guyana</t>
+  </si>
+  <si>
     <t>Deportivo Pasto</t>
   </si>
   <si>
-    <t>Girona</t>
-  </si>
-  <si>
-    <t>Cerro</t>
+    <t>Talleres</t>
   </si>
   <si>
     <t>FC Supra du Quebec</t>
   </si>
   <si>
-    <t>Talleres</t>
-  </si>
-  <si>
     <t>Tigres FC Zipaquira</t>
   </si>
   <si>
@@ -499,10 +502,13 @@
     <t>Cucuta Deportivo</t>
   </si>
   <si>
+    <t>La Luz FC</t>
+  </si>
+  <si>
     <t>Trinidad &amp; Tobago</t>
   </si>
   <si>
-    <t>La Luz FC</t>
+    <t>Puerto Rico</t>
   </si>
   <si>
     <t>Argentinos Juniors</t>
@@ -547,12 +553,12 @@
     <t>Omiya</t>
   </si>
   <si>
+    <t>FC Arlanda</t>
+  </si>
+  <si>
     <t>Trelleborgs</t>
   </si>
   <si>
-    <t>FC Arlanda</t>
-  </si>
-  <si>
     <t>Granada</t>
   </si>
   <si>
@@ -598,21 +604,24 @@
     <t>Aldosivi</t>
   </si>
   <si>
+    <t>Wanderers (Uru)</t>
+  </si>
+  <si>
+    <t>Mallorca</t>
+  </si>
+  <si>
+    <t>Dominica</t>
+  </si>
+  <si>
     <t>Fortaleza FC</t>
   </si>
   <si>
-    <t>Mallorca</t>
-  </si>
-  <si>
-    <t>Wanderers (Uru)</t>
+    <t>Belgrano</t>
   </si>
   <si>
     <t>Pacific</t>
   </si>
   <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
     <t>Internacional de Palmira</t>
   </si>
   <si>
@@ -622,10 +631,13 @@
     <t>Deportivo Pereira</t>
   </si>
   <si>
+    <t>River Plate (Uru)</t>
+  </si>
+  <si>
     <t>Curacao</t>
   </si>
   <si>
-    <t>River Plate (Uru)</t>
+    <t>Cayman Islands</t>
   </si>
   <si>
     <t>Tigre</t>
@@ -637,7 +649,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-10-03 07:52:35</t>
+    <t>2026-10-03 10:09:05</t>
   </si>
 </sst>
 </file>
@@ -969,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB42"/>
+  <dimension ref="A1:CB44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1228,25 +1240,25 @@
         <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F2">
         <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1261,85 +1273,85 @@
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q2">
         <v>1.79</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S2">
         <v>3</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
         <v>1.11</v>
       </c>
       <c r="W2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AC2">
         <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP2">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2">
         <v>1.03</v>
@@ -1351,10 +1363,10 @@
         <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU2">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AV2">
         <v>1.03</v>
@@ -1363,22 +1375,22 @@
         <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY2">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
         <v>1.03</v>
       </c>
       <c r="BB2">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BC2">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD2">
         <v>1.03</v>
@@ -1387,10 +1399,10 @@
         <v>1.03</v>
       </c>
       <c r="BF2">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>150</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1453,7 +1465,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1470,7 +1482,7 @@
         <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F3">
         <v>3.25</v>
@@ -1479,7 +1491,7 @@
         <v>3.55</v>
       </c>
       <c r="H3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I3">
         <v>2.6</v>
@@ -1488,13 +1500,13 @@
         <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
         <v>1.52</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
         <v>2.94</v>
@@ -1518,10 +1530,10 @@
         <v>1.96</v>
       </c>
       <c r="U3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W3">
         <v>1.4</v>
@@ -1533,7 +1545,7 @@
         <v>8.6</v>
       </c>
       <c r="Z3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA3">
         <v>46</v>
@@ -1695,7 +1707,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1712,25 +1724,25 @@
         <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="H4">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="I4">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1751,40 +1763,40 @@
         <v>1.98</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
         <v>3.4</v>
       </c>
       <c r="T4">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U4">
         <v>1.94</v>
       </c>
       <c r="V4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="W4">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X4">
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
         <v>19.5</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
         <v>970</v>
@@ -1793,13 +1805,13 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AG4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI4">
         <v>1000</v>
@@ -1823,19 +1835,19 @@
         <v>50</v>
       </c>
       <c r="AP4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
-        <v>6.2</v>
+        <v>1.66</v>
       </c>
       <c r="AR4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS4">
         <v>14</v>
       </c>
       <c r="AT4">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AU4">
         <v>6.6</v>
@@ -1844,10 +1856,10 @@
         <v>7.2</v>
       </c>
       <c r="AW4">
-        <v>2.04</v>
+        <v>14</v>
       </c>
       <c r="AX4">
-        <v>1.98</v>
+        <v>19.5</v>
       </c>
       <c r="AY4">
         <v>11</v>
@@ -1859,22 +1871,22 @@
         <v>23</v>
       </c>
       <c r="BB4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BC4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BD4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BE4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BF4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BG4">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1937,7 +1949,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1954,28 +1966,28 @@
         <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F5">
         <v>2.36</v>
       </c>
       <c r="G5">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H5">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J5">
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1993,10 +2005,10 @@
         <v>1.75</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S5">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T5">
         <v>1.65</v>
@@ -2005,7 +2017,7 @@
         <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
         <v>1.67</v>
@@ -2020,7 +2032,7 @@
         <v>26</v>
       </c>
       <c r="AA5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB5">
         <v>13</v>
@@ -2053,7 +2065,7 @@
         <v>28</v>
       </c>
       <c r="AL5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM5">
         <v>85</v>
@@ -2095,7 +2107,7 @@
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA5">
         <v>1.03</v>
@@ -2179,7 +2191,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2196,7 +2208,7 @@
         <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F6">
         <v>3.4</v>
@@ -2205,16 +2217,16 @@
         <v>3.7</v>
       </c>
       <c r="H6">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I6">
         <v>2.5</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2223,22 +2235,22 @@
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q6">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R6">
         <v>1.26</v>
       </c>
       <c r="S6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
         <v>1.93</v>
@@ -2247,7 +2259,7 @@
         <v>1.96</v>
       </c>
       <c r="V6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W6">
         <v>1.37</v>
@@ -2265,7 +2277,7 @@
         <v>36</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
@@ -2316,7 +2328,7 @@
         <v>13</v>
       </c>
       <c r="AS6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT6">
         <v>9.800000000000001</v>
@@ -2337,25 +2349,25 @@
         <v>13</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB6">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD6">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE6">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF6">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG6">
         <v>20</v>
@@ -2421,7 +2433,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2438,25 +2450,25 @@
         <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F7">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="G7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H7">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>3.65</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
         <v>1.34</v>
@@ -2465,22 +2477,22 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
         <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
         <v>1.84</v>
       </c>
       <c r="R7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>2.06</v>
+        <v>1.02</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2489,10 +2501,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="W7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2663,7 +2675,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2680,25 +2692,25 @@
         <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="G8">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I8">
+        <v>3.5</v>
+      </c>
+      <c r="J8">
         <v>3.55</v>
       </c>
-      <c r="J8">
-        <v>3.5</v>
-      </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
         <v>1.34</v>
@@ -2707,7 +2719,7 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O8">
         <v>1.31</v>
@@ -2722,19 +2734,19 @@
         <v>1.32</v>
       </c>
       <c r="S8">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="T8">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="U8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2743,7 +2755,7 @@
         <v>1000</v>
       </c>
       <c r="Z8">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2764,10 +2776,10 @@
         <v>1000</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
         <v>1000</v>
@@ -2791,58 +2803,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AR8">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AS8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AT8">
-        <v>8.800000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="AU8">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AV8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AW8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AX8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AY8">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AZ8">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="BA8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="BB8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="BC8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="BD8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="BE8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="BF8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="BG8">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2905,7 +2917,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2922,7 +2934,7 @@
         <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F9">
         <v>1.22</v>
@@ -2931,7 +2943,7 @@
         <v>1.45</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I9">
         <v>870</v>
@@ -3147,7 +3159,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3164,25 +3176,25 @@
         <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F10">
         <v>1.34</v>
       </c>
       <c r="G10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H10">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I10">
         <v>870</v>
       </c>
       <c r="J10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="L10">
         <v>1.22</v>
@@ -3389,7 +3401,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3406,28 +3418,28 @@
         <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F11">
         <v>2.2</v>
       </c>
       <c r="G11">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M11">
         <v>1.03</v>
@@ -3445,7 +3457,7 @@
         <v>1.96</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
         <v>3.35</v>
@@ -3460,10 +3472,10 @@
         <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y11">
         <v>32</v>
@@ -3487,7 +3499,7 @@
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AG11">
         <v>21</v>
@@ -3571,22 +3583,22 @@
         <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.68</v>
+        <v>1.17</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="BN11">
         <v>1000</v>
@@ -3598,40 +3610,40 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="CB11" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3648,25 +3660,25 @@
         <v>135</v>
       </c>
       <c r="E12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F12">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="G12">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H12">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="I12">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="J12">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3678,31 +3690,31 @@
         <v>3.7</v>
       </c>
       <c r="O12">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P12">
         <v>2.04</v>
       </c>
       <c r="Q12">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R12">
         <v>1.37</v>
       </c>
       <c r="S12">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T12">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U12">
         <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3783,7 +3795,7 @@
         <v>1.13</v>
       </c>
       <c r="AX12">
-        <v>13.5</v>
+        <v>1.13</v>
       </c>
       <c r="AY12">
         <v>1.13</v>
@@ -3795,7 +3807,7 @@
         <v>1.13</v>
       </c>
       <c r="BB12">
-        <v>1.13</v>
+        <v>25</v>
       </c>
       <c r="BC12">
         <v>1.13</v>
@@ -3873,7 +3885,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3890,115 +3902,115 @@
         <v>136</v>
       </c>
       <c r="E13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F13">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="G13">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="H13">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>3.2</v>
+      </c>
+      <c r="K13">
+        <v>3.6</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
         <v>2.4</v>
       </c>
-      <c r="J13">
-        <v>3.55</v>
-      </c>
-      <c r="K13">
-        <v>4.9</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>4</v>
-      </c>
       <c r="O13">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q13">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R13">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="S13">
         <v>2.24</v>
       </c>
       <c r="T13">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X13">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Y13">
+        <v>18.5</v>
+      </c>
+      <c r="Z13">
+        <v>26</v>
+      </c>
+      <c r="AA13">
+        <v>50</v>
+      </c>
+      <c r="AB13">
+        <v>18.5</v>
+      </c>
+      <c r="AC13">
+        <v>11</v>
+      </c>
+      <c r="AD13">
+        <v>16</v>
+      </c>
+      <c r="AE13">
+        <v>34</v>
+      </c>
+      <c r="AF13">
+        <v>22</v>
+      </c>
+      <c r="AG13">
+        <v>15.5</v>
+      </c>
+      <c r="AH13">
+        <v>15.5</v>
+      </c>
+      <c r="AI13">
+        <v>42</v>
+      </c>
+      <c r="AJ13">
+        <v>55</v>
+      </c>
+      <c r="AK13">
+        <v>32</v>
+      </c>
+      <c r="AL13">
+        <v>46</v>
+      </c>
+      <c r="AM13">
+        <v>70</v>
+      </c>
+      <c r="AN13">
         <v>17.5</v>
       </c>
-      <c r="Z13">
-        <v>21</v>
-      </c>
-      <c r="AA13">
-        <v>34</v>
-      </c>
-      <c r="AB13">
-        <v>22</v>
-      </c>
-      <c r="AC13">
-        <v>11.5</v>
-      </c>
-      <c r="AD13">
-        <v>13.5</v>
-      </c>
-      <c r="AE13">
-        <v>24</v>
-      </c>
-      <c r="AF13">
-        <v>32</v>
-      </c>
-      <c r="AG13">
-        <v>17</v>
-      </c>
-      <c r="AH13">
-        <v>17.5</v>
-      </c>
-      <c r="AI13">
-        <v>32</v>
-      </c>
-      <c r="AJ13">
-        <v>60</v>
-      </c>
-      <c r="AK13">
-        <v>36</v>
-      </c>
-      <c r="AL13">
-        <v>40</v>
-      </c>
-      <c r="AM13">
-        <v>65</v>
-      </c>
-      <c r="AN13">
-        <v>23</v>
-      </c>
       <c r="AO13">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AP13">
         <v>1.03</v>
@@ -4049,22 +4061,22 @@
         <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG13">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH13">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -4073,49 +4085,49 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4132,25 +4144,25 @@
         <v>137</v>
       </c>
       <c r="E14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F14">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="G14">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="H14">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="J14">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4159,205 +4171,205 @@
         <v>1.01</v>
       </c>
       <c r="N14">
+        <v>2.92</v>
+      </c>
+      <c r="O14">
+        <v>1.11</v>
+      </c>
+      <c r="P14">
         <v>2.4</v>
       </c>
-      <c r="O14">
-        <v>1.02</v>
-      </c>
-      <c r="P14">
-        <v>2.12</v>
-      </c>
       <c r="Q14">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R14">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="S14">
         <v>2.24</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="W14">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="X14">
+        <v>30</v>
+      </c>
+      <c r="Y14">
+        <v>17.5</v>
+      </c>
+      <c r="Z14">
+        <v>21</v>
+      </c>
+      <c r="AA14">
+        <v>34</v>
+      </c>
+      <c r="AB14">
         <v>22</v>
       </c>
-      <c r="Y14">
-        <v>18.5</v>
-      </c>
-      <c r="Z14">
+      <c r="AC14">
+        <v>11.5</v>
+      </c>
+      <c r="AD14">
+        <v>13.5</v>
+      </c>
+      <c r="AE14">
+        <v>24</v>
+      </c>
+      <c r="AF14">
+        <v>32</v>
+      </c>
+      <c r="AG14">
+        <v>17</v>
+      </c>
+      <c r="AH14">
+        <v>17.5</v>
+      </c>
+      <c r="AI14">
+        <v>32</v>
+      </c>
+      <c r="AJ14">
+        <v>60</v>
+      </c>
+      <c r="AK14">
+        <v>36</v>
+      </c>
+      <c r="AL14">
+        <v>40</v>
+      </c>
+      <c r="AM14">
+        <v>65</v>
+      </c>
+      <c r="AN14">
+        <v>23</v>
+      </c>
+      <c r="AO14">
+        <v>13</v>
+      </c>
+      <c r="AP14">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14">
+        <v>1.03</v>
+      </c>
+      <c r="AR14">
+        <v>1.03</v>
+      </c>
+      <c r="AS14">
+        <v>1.03</v>
+      </c>
+      <c r="AT14">
+        <v>1.03</v>
+      </c>
+      <c r="AU14">
+        <v>1.03</v>
+      </c>
+      <c r="AV14">
+        <v>1.03</v>
+      </c>
+      <c r="AW14">
+        <v>1.03</v>
+      </c>
+      <c r="AX14">
+        <v>1.03</v>
+      </c>
+      <c r="AY14">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14">
+        <v>1.03</v>
+      </c>
+      <c r="BA14">
+        <v>1.03</v>
+      </c>
+      <c r="BB14">
+        <v>1.03</v>
+      </c>
+      <c r="BC14">
+        <v>1.03</v>
+      </c>
+      <c r="BD14">
+        <v>1.03</v>
+      </c>
+      <c r="BE14">
+        <v>1.03</v>
+      </c>
+      <c r="BF14">
+        <v>15</v>
+      </c>
+      <c r="BG14">
+        <v>8.4</v>
+      </c>
+      <c r="BH14">
+        <v>5</v>
+      </c>
+      <c r="BI14">
+        <v>3.6</v>
+      </c>
+      <c r="BJ14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK14">
+        <v>6.6</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>7.8</v>
+      </c>
+      <c r="BO14">
+        <v>5.4</v>
+      </c>
+      <c r="BP14">
+        <v>25</v>
+      </c>
+      <c r="BQ14">
+        <v>16.5</v>
+      </c>
+      <c r="BR14">
+        <v>32</v>
+      </c>
+      <c r="BS14">
+        <v>20</v>
+      </c>
+      <c r="BT14">
+        <v>6.4</v>
+      </c>
+      <c r="BU14">
+        <v>4.4</v>
+      </c>
+      <c r="BV14">
+        <v>17</v>
+      </c>
+      <c r="BW14">
+        <v>11</v>
+      </c>
+      <c r="BX14">
         <v>26</v>
       </c>
-      <c r="AA14">
-        <v>50</v>
-      </c>
-      <c r="AB14">
-        <v>18.5</v>
-      </c>
-      <c r="AC14">
-        <v>11</v>
-      </c>
-      <c r="AD14">
-        <v>16</v>
-      </c>
-      <c r="AE14">
-        <v>34</v>
-      </c>
-      <c r="AF14">
-        <v>22</v>
-      </c>
-      <c r="AG14">
-        <v>15.5</v>
-      </c>
-      <c r="AH14">
-        <v>15.5</v>
-      </c>
-      <c r="AI14">
-        <v>42</v>
-      </c>
-      <c r="AJ14">
-        <v>55</v>
-      </c>
-      <c r="AK14">
-        <v>32</v>
-      </c>
-      <c r="AL14">
-        <v>46</v>
-      </c>
-      <c r="AM14">
-        <v>70</v>
-      </c>
-      <c r="AN14">
+      <c r="BY14">
+        <v>17</v>
+      </c>
+      <c r="BZ14">
         <v>17.5</v>
       </c>
-      <c r="AO14">
-        <v>18.5</v>
-      </c>
-      <c r="AP14">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14">
-        <v>1.03</v>
-      </c>
-      <c r="AR14">
-        <v>1.03</v>
-      </c>
-      <c r="AS14">
-        <v>1.03</v>
-      </c>
-      <c r="AT14">
-        <v>1.03</v>
-      </c>
-      <c r="AU14">
-        <v>1.03</v>
-      </c>
-      <c r="AV14">
-        <v>1.03</v>
-      </c>
-      <c r="AW14">
-        <v>1.03</v>
-      </c>
-      <c r="AX14">
-        <v>1.03</v>
-      </c>
-      <c r="AY14">
-        <v>1.03</v>
-      </c>
-      <c r="AZ14">
-        <v>1.03</v>
-      </c>
-      <c r="BA14">
-        <v>1.03</v>
-      </c>
-      <c r="BB14">
-        <v>1.03</v>
-      </c>
-      <c r="BC14">
-        <v>1.03</v>
-      </c>
-      <c r="BD14">
-        <v>1.03</v>
-      </c>
-      <c r="BE14">
-        <v>1.03</v>
-      </c>
-      <c r="BF14">
-        <v>12</v>
-      </c>
-      <c r="BG14">
-        <v>12.5</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.01</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.01</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.01</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.01</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.01</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.01</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>1.01</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>1.01</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>1.01</v>
-      </c>
-      <c r="BZ14">
-        <v>1000</v>
-      </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4374,16 +4386,16 @@
         <v>138</v>
       </c>
       <c r="E15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F15">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G15">
+        <v>2.78</v>
+      </c>
+      <c r="H15">
         <v>2.8</v>
-      </c>
-      <c r="H15">
-        <v>2.76</v>
       </c>
       <c r="I15">
         <v>2.9</v>
@@ -4392,7 +4404,7 @@
         <v>3.4</v>
       </c>
       <c r="K15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L15">
         <v>1.41</v>
@@ -4404,10 +4416,10 @@
         <v>3.7</v>
       </c>
       <c r="O15">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q15">
         <v>2</v>
@@ -4416,19 +4428,19 @@
         <v>1.35</v>
       </c>
       <c r="S15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T15">
         <v>1.79</v>
       </c>
       <c r="U15">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
         <v>1.52</v>
       </c>
       <c r="W15">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X15">
         <v>14.5</v>
@@ -4446,13 +4458,13 @@
         <v>11.5</v>
       </c>
       <c r="AC15">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD15">
         <v>13</v>
       </c>
       <c r="AE15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF15">
         <v>18.5</v>
@@ -4467,7 +4479,7 @@
         <v>150</v>
       </c>
       <c r="AJ15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK15">
         <v>38</v>
@@ -4479,10 +4491,10 @@
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP15">
         <v>12.5</v>
@@ -4491,7 +4503,7 @@
         <v>10</v>
       </c>
       <c r="AR15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS15">
         <v>25</v>
@@ -4524,7 +4536,7 @@
         <v>24</v>
       </c>
       <c r="BC15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD15">
         <v>25</v>
@@ -4599,7 +4611,7 @@
         <v>1.06</v>
       </c>
       <c r="CB15" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4616,25 +4628,25 @@
         <v>139</v>
       </c>
       <c r="E16" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F16">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G16">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="H16">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="J16">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4643,35 +4655,35 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>1.16</v>
       </c>
       <c r="P16">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Q16">
         <v>1.55</v>
       </c>
       <c r="R16">
+        <v>1.6</v>
+      </c>
+      <c r="S16">
+        <v>2.48</v>
+      </c>
+      <c r="T16">
+        <v>1.55</v>
+      </c>
+      <c r="U16">
+        <v>2.46</v>
+      </c>
+      <c r="V16">
+        <v>1.53</v>
+      </c>
+      <c r="W16">
         <v>1.59</v>
       </c>
-      <c r="S16">
-        <v>2.3</v>
-      </c>
-      <c r="T16">
-        <v>1.45</v>
-      </c>
-      <c r="U16">
-        <v>2.58</v>
-      </c>
-      <c r="V16">
-        <v>1.51</v>
-      </c>
-      <c r="W16">
-        <v>1.67</v>
-      </c>
       <c r="X16">
         <v>1000</v>
       </c>
@@ -4679,7 +4691,7 @@
         <v>1000</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA16">
         <v>1000</v>
@@ -4688,7 +4700,7 @@
         <v>1000</v>
       </c>
       <c r="AC16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD16">
         <v>28</v>
@@ -4721,7 +4733,7 @@
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4733,16 +4745,16 @@
         <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AS16">
         <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV16">
         <v>1.03</v>
@@ -4778,7 +4790,7 @@
         <v>9</v>
       </c>
       <c r="BG16">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4841,7 +4853,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4858,13 +4870,13 @@
         <v>140</v>
       </c>
       <c r="E17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F17">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G17">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H17">
         <v>3.65</v>
@@ -4876,7 +4888,7 @@
         <v>3.6</v>
       </c>
       <c r="K17">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>1.25</v>
@@ -4885,31 +4897,31 @@
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O17">
         <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R17">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S17">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V17">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
         <v>1.94</v>
@@ -4927,7 +4939,7 @@
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AC17">
         <v>970</v>
@@ -4969,58 +4981,58 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AQ17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AR17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AS17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AT17">
         <v>1.23</v>
       </c>
       <c r="AU17">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AW17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AX17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AY17">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AZ17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BA17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BB17">
-        <v>1.26</v>
+        <v>18.5</v>
       </c>
       <c r="BC17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BD17">
-        <v>1.26</v>
+        <v>20</v>
       </c>
       <c r="BE17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BF17">
         <v>6.2</v>
       </c>
       <c r="BG17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5083,7 +5095,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5100,13 +5112,13 @@
         <v>141</v>
       </c>
       <c r="E18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F18">
         <v>1.12</v>
       </c>
       <c r="G18">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H18">
         <v>2.16</v>
@@ -5115,7 +5127,7 @@
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5325,7 +5337,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5342,19 +5354,19 @@
         <v>142</v>
       </c>
       <c r="E19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F19">
         <v>2.06</v>
       </c>
       <c r="G19">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H19">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J19">
         <v>3.2</v>
@@ -5369,16 +5381,16 @@
         <v>1.07</v>
       </c>
       <c r="N19">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O19">
         <v>1.45</v>
       </c>
       <c r="P19">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Q19">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R19">
         <v>1.19</v>
@@ -5387,16 +5399,16 @@
         <v>4.2</v>
       </c>
       <c r="T19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U19">
+        <v>1.76</v>
+      </c>
+      <c r="V19">
+        <v>1.28</v>
+      </c>
+      <c r="W19">
         <v>1.75</v>
-      </c>
-      <c r="V19">
-        <v>1.26</v>
-      </c>
-      <c r="W19">
-        <v>1.76</v>
       </c>
       <c r="X19">
         <v>970</v>
@@ -5414,10 +5426,10 @@
         <v>970</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE19">
         <v>95</v>
@@ -5453,64 +5465,64 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AQ19">
         <v>8.199999999999999</v>
       </c>
       <c r="AR19">
-        <v>2.04</v>
+        <v>17.5</v>
       </c>
       <c r="AS19">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AT19">
+        <v>5.7</v>
+      </c>
+      <c r="AU19">
+        <v>5.7</v>
+      </c>
+      <c r="AV19">
+        <v>12.5</v>
+      </c>
+      <c r="AW19">
+        <v>2.54</v>
+      </c>
+      <c r="AX19">
+        <v>7.8</v>
+      </c>
+      <c r="AY19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ19">
+        <v>2.56</v>
+      </c>
+      <c r="BA19">
+        <v>2.6</v>
+      </c>
+      <c r="BB19">
+        <v>17</v>
+      </c>
+      <c r="BC19">
+        <v>17</v>
+      </c>
+      <c r="BD19">
+        <v>2.52</v>
+      </c>
+      <c r="BE19">
+        <v>2.6</v>
+      </c>
+      <c r="BF19">
+        <v>2.4</v>
+      </c>
+      <c r="BG19">
         <v>2.38</v>
       </c>
-      <c r="AU19">
-        <v>2.36</v>
-      </c>
-      <c r="AV19">
-        <v>2.14</v>
-      </c>
-      <c r="AW19">
-        <v>2.08</v>
-      </c>
-      <c r="AX19">
-        <v>2.24</v>
-      </c>
-      <c r="AY19">
-        <v>2.14</v>
-      </c>
-      <c r="AZ19">
-        <v>1.99</v>
-      </c>
-      <c r="BA19">
-        <v>2.14</v>
-      </c>
-      <c r="BB19">
-        <v>2.02</v>
-      </c>
-      <c r="BC19">
-        <v>2.02</v>
-      </c>
-      <c r="BD19">
-        <v>2.08</v>
-      </c>
-      <c r="BE19">
-        <v>2.14</v>
-      </c>
-      <c r="BF19">
-        <v>2</v>
-      </c>
-      <c r="BG19">
-        <v>2.14</v>
-      </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI19">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
@@ -5567,7 +5579,7 @@
         <v>1.5</v>
       </c>
       <c r="CB19" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5584,7 +5596,7 @@
         <v>143</v>
       </c>
       <c r="E20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F20">
         <v>1.1</v>
@@ -5809,7 +5821,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5826,13 +5838,13 @@
         <v>144</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F21">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -5844,7 +5856,7 @@
         <v>4.2</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L21">
         <v>1.37</v>
@@ -5871,16 +5883,16 @@
         <v>3.05</v>
       </c>
       <c r="T21">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U21">
         <v>2</v>
       </c>
       <c r="V21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W21">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X21">
         <v>18.5</v>
@@ -6051,7 +6063,7 @@
         <v>7.8</v>
       </c>
       <c r="CB21" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6068,7 +6080,7 @@
         <v>145</v>
       </c>
       <c r="E22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F22">
         <v>4.4</v>
@@ -6089,79 +6101,79 @@
         <v>5.3</v>
       </c>
       <c r="L22">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N22">
         <v>2.42</v>
       </c>
       <c r="O22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="P22">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R22">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S22">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="W22">
         <v>1.19</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y22">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z22">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA22">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AB22">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AC22">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD22">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE22">
+        <v>17.5</v>
+      </c>
+      <c r="AF22">
+        <v>46</v>
+      </c>
+      <c r="AG22">
         <v>22</v>
       </c>
-      <c r="AF22">
-        <v>55</v>
-      </c>
-      <c r="AG22">
-        <v>28</v>
-      </c>
       <c r="AH22">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AI22">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK22">
         <v>80</v>
@@ -6170,13 +6182,13 @@
         <v>75</v>
       </c>
       <c r="AM22">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN22">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AO22">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AP22">
         <v>1.03</v>
@@ -6293,7 +6305,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6310,7 +6322,7 @@
         <v>146</v>
       </c>
       <c r="E23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F23">
         <v>1.1</v>
@@ -6352,7 +6364,7 @@
         <v>1.18</v>
       </c>
       <c r="S23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6535,7 +6547,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6552,7 +6564,7 @@
         <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F24">
         <v>1.47</v>
@@ -6561,13 +6573,13 @@
         <v>600</v>
       </c>
       <c r="H24">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="I24">
         <v>870</v>
       </c>
       <c r="J24">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6579,13 +6591,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O24">
         <v>1.02</v>
       </c>
       <c r="P24">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q24">
         <v>1.03</v>
@@ -6777,7 +6789,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6794,7 +6806,7 @@
         <v>148</v>
       </c>
       <c r="E25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F25">
         <v>2.72</v>
@@ -6821,7 +6833,7 @@
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O25">
         <v>1.32</v>
@@ -6839,10 +6851,10 @@
         <v>3.35</v>
       </c>
       <c r="T25">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U25">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V25">
         <v>1.5</v>
@@ -6890,7 +6902,7 @@
         <v>50</v>
       </c>
       <c r="AK25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL25">
         <v>48</v>
@@ -7019,7 +7031,7 @@
         <v>1.32</v>
       </c>
       <c r="CB25" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7036,7 +7048,7 @@
         <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F26">
         <v>1.5</v>
@@ -7045,7 +7057,7 @@
         <v>1.88</v>
       </c>
       <c r="H26">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I26">
         <v>10.5</v>
@@ -7054,7 +7066,7 @@
         <v>3.2</v>
       </c>
       <c r="K26">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L26">
         <v>1.38</v>
@@ -7063,7 +7075,7 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O26">
         <v>1.02</v>
@@ -7072,10 +7084,10 @@
         <v>1.54</v>
       </c>
       <c r="Q26">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S26">
         <v>2.94</v>
@@ -7261,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7278,7 +7290,7 @@
         <v>150</v>
       </c>
       <c r="E27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F27">
         <v>2.26</v>
@@ -7287,7 +7299,7 @@
         <v>2.36</v>
       </c>
       <c r="H27">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I27">
         <v>3.65</v>
@@ -7305,7 +7317,7 @@
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O27">
         <v>1.35</v>
@@ -7314,19 +7326,19 @@
         <v>1.81</v>
       </c>
       <c r="Q27">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R27">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S27">
         <v>3.6</v>
       </c>
       <c r="T27">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="U27">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="V27">
         <v>1.37</v>
@@ -7335,13 +7347,13 @@
         <v>1.73</v>
       </c>
       <c r="X27">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y27">
         <v>13</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA27">
         <v>85</v>
@@ -7350,16 +7362,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD27">
         <v>970</v>
       </c>
       <c r="AE27">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF27">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="AG27">
         <v>22</v>
@@ -7374,7 +7386,7 @@
         <v>1000</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL27">
         <v>1000</v>
@@ -7383,7 +7395,7 @@
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
         <v>55</v>
@@ -7392,55 +7404,55 @@
         <v>8.6</v>
       </c>
       <c r="AQ27">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR27">
-        <v>2.16</v>
+        <v>20</v>
       </c>
       <c r="AS27">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AT27">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU27">
         <v>5.7</v>
       </c>
       <c r="AV27">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW27">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AX27">
         <v>9.199999999999999</v>
       </c>
       <c r="AY27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
         <v>11.5</v>
       </c>
       <c r="BA27">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BB27">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BC27">
         <v>2.16</v>
       </c>
       <c r="BD27">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BE27">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BF27">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG27">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7503,7 +7515,7 @@
         <v>1.06</v>
       </c>
       <c r="CB27" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7520,7 +7532,7 @@
         <v>151</v>
       </c>
       <c r="E28" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F28">
         <v>1.26</v>
@@ -7553,25 +7565,25 @@
         <v>1.12</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R28">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S28">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="T28">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U28">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W28">
         <v>4.6</v>
@@ -7580,7 +7592,7 @@
         <v>50</v>
       </c>
       <c r="Y28">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="Z28">
         <v>1000</v>
@@ -7649,7 +7661,7 @@
         <v>15.5</v>
       </c>
       <c r="AV28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW28">
         <v>44</v>
@@ -7664,7 +7676,7 @@
         <v>19</v>
       </c>
       <c r="BA28">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB28">
         <v>9.800000000000001</v>
@@ -7679,7 +7691,7 @@
         <v>40</v>
       </c>
       <c r="BF28">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG28">
         <v>44</v>
@@ -7745,7 +7757,7 @@
         <v>1.96</v>
       </c>
       <c r="CB28" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7762,7 +7774,7 @@
         <v>152</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F29">
         <v>1.79</v>
@@ -7783,7 +7795,7 @@
         <v>3.65</v>
       </c>
       <c r="L29">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M29">
         <v>1.12</v>
@@ -7795,7 +7807,7 @@
         <v>1.55</v>
       </c>
       <c r="P29">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q29">
         <v>2.6</v>
@@ -7987,12 +7999,12 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
         <v>98</v>
@@ -8004,232 +8016,232 @@
         <v>153</v>
       </c>
       <c r="E30" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F30">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="G30">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="H30">
-        <v>3.65</v>
+        <v>2.28</v>
       </c>
       <c r="I30">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="J30">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K30">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="L30">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="O30">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P30">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="Q30">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="R30">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="S30">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T30">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="X30">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR30">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS30">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT30">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU30">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV30">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW30">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AX30">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY30">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA30">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BB30">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC30">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD30">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BE30">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BF30">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BI30">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="BJ30">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>7.8</v>
+        <v>1.42</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>21</v>
+        <v>1.42</v>
       </c>
       <c r="BN30">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>4.3</v>
+        <v>1.42</v>
       </c>
       <c r="BP30">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>13</v>
+        <v>1.42</v>
       </c>
       <c r="BR30">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>26</v>
+        <v>1.42</v>
       </c>
       <c r="BT30">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>5.2</v>
+        <v>1.42</v>
       </c>
       <c r="BV30">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>24</v>
+        <v>1.42</v>
       </c>
       <c r="BX30">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>36</v>
+        <v>1.42</v>
       </c>
       <c r="BZ30">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>26</v>
+        <v>1.42</v>
       </c>
       <c r="CB30" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8246,25 +8258,25 @@
         <v>154</v>
       </c>
       <c r="E31" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F31">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G31">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H31">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I31">
         <v>3.3</v>
       </c>
       <c r="J31">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K31">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L31">
         <v>1.35</v>
@@ -8285,7 +8297,7 @@
         <v>1.8</v>
       </c>
       <c r="R31">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S31">
         <v>3.2</v>
@@ -8300,7 +8312,7 @@
         <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X31">
         <v>16</v>
@@ -8309,10 +8321,10 @@
         <v>13.5</v>
       </c>
       <c r="Z31">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA31">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB31">
         <v>11.5</v>
@@ -8324,7 +8336,7 @@
         <v>14</v>
       </c>
       <c r="AE31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF31">
         <v>16.5</v>
@@ -8333,19 +8345,19 @@
         <v>12</v>
       </c>
       <c r="AH31">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI31">
         <v>55</v>
       </c>
       <c r="AJ31">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK31">
         <v>27</v>
       </c>
       <c r="AL31">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM31">
         <v>100</v>
@@ -8354,7 +8366,7 @@
         <v>19</v>
       </c>
       <c r="AO31">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP31">
         <v>13.5</v>
@@ -8363,10 +8375,10 @@
         <v>12</v>
       </c>
       <c r="AR31">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS31">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT31">
         <v>10</v>
@@ -8378,7 +8390,7 @@
         <v>12</v>
       </c>
       <c r="AW31">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX31">
         <v>14</v>
@@ -8390,25 +8402,25 @@
         <v>14.5</v>
       </c>
       <c r="BA31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB31">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC31">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD31">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE31">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF31">
         <v>15.5</v>
       </c>
       <c r="BG31">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH31">
         <v>4.3</v>
@@ -8447,7 +8459,7 @@
         <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU31">
         <v>4.4</v>
@@ -8471,12 +8483,12 @@
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
@@ -8488,49 +8500,49 @@
         <v>155</v>
       </c>
       <c r="E32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F32">
-        <v>2.66</v>
+        <v>1.1</v>
       </c>
       <c r="G32">
-        <v>3.65</v>
+        <v>1.32</v>
       </c>
       <c r="H32">
-        <v>2.28</v>
+        <v>10.5</v>
       </c>
       <c r="I32">
-        <v>2.9</v>
+        <v>120</v>
       </c>
       <c r="J32">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>5.4</v>
+        <v>110</v>
       </c>
       <c r="L32">
         <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="O32">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="P32">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="Q32">
-        <v>2.14</v>
+        <v>1.2</v>
       </c>
       <c r="R32">
-        <v>1.17</v>
+        <v>1.87</v>
       </c>
       <c r="S32">
-        <v>3.9</v>
+        <v>1.58</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8539,10 +8551,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="W32">
-        <v>1.38</v>
+        <v>4.2</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8599,52 +8611,52 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
         <v>1.01</v>
@@ -8653,309 +8665,309 @@
         <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
         <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
         <v>156</v>
       </c>
       <c r="E33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F33">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="G33">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="H33">
+        <v>3.65</v>
+      </c>
+      <c r="I33">
+        <v>3.95</v>
+      </c>
+      <c r="J33">
+        <v>3.1</v>
+      </c>
+      <c r="K33">
+        <v>3.4</v>
+      </c>
+      <c r="L33">
+        <v>1.48</v>
+      </c>
+      <c r="M33">
+        <v>1.11</v>
+      </c>
+      <c r="N33">
+        <v>2.98</v>
+      </c>
+      <c r="O33">
+        <v>1.45</v>
+      </c>
+      <c r="P33">
+        <v>1.67</v>
+      </c>
+      <c r="Q33">
         <v>2.3</v>
       </c>
-      <c r="I33">
-        <v>870</v>
-      </c>
-      <c r="J33">
-        <v>1.12</v>
-      </c>
-      <c r="K33">
-        <v>950</v>
-      </c>
-      <c r="L33">
-        <v>1.01</v>
-      </c>
-      <c r="M33">
-        <v>1.01</v>
-      </c>
-      <c r="N33">
-        <v>3</v>
-      </c>
-      <c r="O33">
-        <v>1.13</v>
-      </c>
-      <c r="P33">
-        <v>2.62</v>
-      </c>
-      <c r="Q33">
-        <v>1.38</v>
-      </c>
       <c r="R33">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="S33">
-        <v>2.02</v>
+        <v>4.5</v>
       </c>
       <c r="T33">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U33">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V33">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="W33">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="X33">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y33">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z33">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB33">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC33">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD33">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE33">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF33">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG33">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH33">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI33">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ33">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK33">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL33">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM33">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO33">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP33">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ33">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR33">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS33">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AT33">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU33">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV33">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW33">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX33">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY33">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ33">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA33">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BB33">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC33">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD33">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BE33">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG33">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH33">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ33">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP33">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BR33">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BX33">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="CB33" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8972,25 +8984,25 @@
         <v>157</v>
       </c>
       <c r="E34" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F34">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G34">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H34">
         <v>3.05</v>
       </c>
       <c r="I34">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J34">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L34">
         <v>1.55</v>
@@ -8999,31 +9011,31 @@
         <v>1.11</v>
       </c>
       <c r="N34">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="O34">
         <v>1.51</v>
       </c>
       <c r="P34">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q34">
         <v>2.56</v>
       </c>
       <c r="R34">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S34">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U34">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
         <v>1.54</v>
@@ -9032,37 +9044,37 @@
         <v>13.5</v>
       </c>
       <c r="Y34">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="Z34">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AA34">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB34">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AD34">
-        <v>55</v>
+        <v>16.5</v>
       </c>
       <c r="AE34">
         <v>65</v>
       </c>
       <c r="AF34">
-        <v>55</v>
+        <v>16.5</v>
       </c>
       <c r="AG34">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="AH34">
         <v>26</v>
       </c>
       <c r="AI34">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ34">
         <v>60</v>
@@ -9071,7 +9083,7 @@
         <v>55</v>
       </c>
       <c r="AL34">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM34">
         <v>1000</v>
@@ -9083,58 +9095,58 @@
         <v>80</v>
       </c>
       <c r="AP34">
+        <v>7.8</v>
+      </c>
+      <c r="AQ34">
+        <v>8.4</v>
+      </c>
+      <c r="AR34">
+        <v>14.5</v>
+      </c>
+      <c r="AS34">
+        <v>27</v>
+      </c>
+      <c r="AT34">
+        <v>7.8</v>
+      </c>
+      <c r="AU34">
         <v>6.4</v>
       </c>
-      <c r="AQ34">
-        <v>7.2</v>
-      </c>
-      <c r="AR34">
-        <v>11.5</v>
-      </c>
-      <c r="AS34">
-        <v>2.46</v>
-      </c>
-      <c r="AT34">
-        <v>6.2</v>
-      </c>
-      <c r="AU34">
-        <v>5.5</v>
-      </c>
       <c r="AV34">
-        <v>3.15</v>
+        <v>12.5</v>
       </c>
       <c r="AW34">
-        <v>2.46</v>
+        <v>6.6</v>
       </c>
       <c r="AX34">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY34">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ34">
-        <v>2.32</v>
+        <v>16.5</v>
       </c>
       <c r="BA34">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="BB34">
-        <v>2.44</v>
+        <v>6.6</v>
       </c>
       <c r="BC34">
-        <v>2.44</v>
+        <v>26</v>
       </c>
       <c r="BD34">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="BE34">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="BF34">
-        <v>1.94</v>
+        <v>6.4</v>
       </c>
       <c r="BG34">
-        <v>1.97</v>
+        <v>6.8</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9197,42 +9209,42 @@
         <v>1.3</v>
       </c>
       <c r="CB34" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
         <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
         <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F35">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="G35">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="H35">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="I35">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="J35">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="K35">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9241,22 +9253,22 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="O35">
-        <v>1.54</v>
+        <v>1.13</v>
       </c>
       <c r="P35">
-        <v>1.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>1.38</v>
       </c>
       <c r="R35">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="S35">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="T35">
         <v>1.01</v>
@@ -9265,10 +9277,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="W35">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9439,249 +9451,249 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
         <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F36">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="G36">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="H36">
         <v>2.7</v>
       </c>
       <c r="I36">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="J36">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="K36">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L36">
+        <v>1.01</v>
+      </c>
+      <c r="M36">
+        <v>1.01</v>
+      </c>
+      <c r="N36">
+        <v>2.44</v>
+      </c>
+      <c r="O36">
+        <v>1.55</v>
+      </c>
+      <c r="P36">
+        <v>1.44</v>
+      </c>
+      <c r="Q36">
+        <v>2.6</v>
+      </c>
+      <c r="R36">
+        <v>1.13</v>
+      </c>
+      <c r="S36">
+        <v>2.98</v>
+      </c>
+      <c r="T36">
+        <v>1.01</v>
+      </c>
+      <c r="U36">
+        <v>1.01</v>
+      </c>
+      <c r="V36">
         <v>1.45</v>
       </c>
-      <c r="M36">
-        <v>1.08</v>
-      </c>
-      <c r="N36">
-        <v>3.4</v>
-      </c>
-      <c r="O36">
-        <v>1.38</v>
-      </c>
-      <c r="P36">
-        <v>1.8</v>
-      </c>
-      <c r="Q36">
-        <v>2.1</v>
-      </c>
-      <c r="R36">
-        <v>1.3</v>
-      </c>
-      <c r="S36">
-        <v>3.85</v>
-      </c>
-      <c r="T36">
-        <v>1.82</v>
-      </c>
-      <c r="U36">
-        <v>2.08</v>
-      </c>
-      <c r="V36">
-        <v>1.55</v>
-      </c>
       <c r="W36">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="X36">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y36">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z36">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA36">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB36">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC36">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD36">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE36">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF36">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG36">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH36">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI36">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK36">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL36">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM36">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN36">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO36">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP36">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR36">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS36">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AT36">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU36">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV36">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW36">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AX36">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY36">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA36">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB36">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BC36">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BD36">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE36">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BF36">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BG36">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH36">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI36">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ36">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK36">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN36">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO36">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP36">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR36">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS36">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT36">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU36">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV36">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW36">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX36">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY36">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9698,411 +9710,411 @@
         <v>160</v>
       </c>
       <c r="E37" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F37">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="G37">
-        <v>1.88</v>
+        <v>3.05</v>
       </c>
       <c r="H37">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="I37">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="J37">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K37">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="L37">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N37">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O37">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P37">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q37">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="R37">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T37">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V37">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="X37">
+        <v>12.5</v>
+      </c>
+      <c r="Y37">
+        <v>11</v>
+      </c>
+      <c r="Z37">
+        <v>18</v>
+      </c>
+      <c r="AA37">
+        <v>44</v>
+      </c>
+      <c r="AB37">
+        <v>11.5</v>
+      </c>
+      <c r="AC37">
+        <v>7.4</v>
+      </c>
+      <c r="AD37">
+        <v>13</v>
+      </c>
+      <c r="AE37">
+        <v>34</v>
+      </c>
+      <c r="AF37">
+        <v>19.5</v>
+      </c>
+      <c r="AG37">
+        <v>13.5</v>
+      </c>
+      <c r="AH37">
+        <v>18.5</v>
+      </c>
+      <c r="AI37">
+        <v>50</v>
+      </c>
+      <c r="AJ37">
+        <v>50</v>
+      </c>
+      <c r="AK37">
+        <v>38</v>
+      </c>
+      <c r="AL37">
+        <v>50</v>
+      </c>
+      <c r="AM37">
+        <v>110</v>
+      </c>
+      <c r="AN37">
+        <v>36</v>
+      </c>
+      <c r="AO37">
+        <v>32</v>
+      </c>
+      <c r="AP37">
+        <v>11.5</v>
+      </c>
+      <c r="AQ37">
+        <v>9.6</v>
+      </c>
+      <c r="AR37">
+        <v>15.5</v>
+      </c>
+      <c r="AS37">
+        <v>36</v>
+      </c>
+      <c r="AT37">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU37">
+        <v>6.8</v>
+      </c>
+      <c r="AV37">
+        <v>11</v>
+      </c>
+      <c r="AW37">
+        <v>28</v>
+      </c>
+      <c r="AX37">
         <v>17</v>
       </c>
-      <c r="Y37">
-        <v>21</v>
-      </c>
-      <c r="Z37">
-        <v>50</v>
-      </c>
-      <c r="AA37">
-        <v>160</v>
-      </c>
-      <c r="AB37">
+      <c r="AY37">
+        <v>11.5</v>
+      </c>
+      <c r="AZ37">
+        <v>15.5</v>
+      </c>
+      <c r="BA37">
+        <v>40</v>
+      </c>
+      <c r="BB37">
+        <v>42</v>
+      </c>
+      <c r="BC37">
+        <v>30</v>
+      </c>
+      <c r="BD37">
+        <v>34</v>
+      </c>
+      <c r="BE37">
+        <v>11.5</v>
+      </c>
+      <c r="BF37">
+        <v>28</v>
+      </c>
+      <c r="BG37">
+        <v>24</v>
+      </c>
+      <c r="BH37">
+        <v>3.7</v>
+      </c>
+      <c r="BI37">
+        <v>2.6</v>
+      </c>
+      <c r="BJ37">
         <v>10</v>
       </c>
-      <c r="AC37">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD37">
+      <c r="BK37">
+        <v>4.4</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>7.6</v>
+      </c>
+      <c r="BN37">
+        <v>6.2</v>
+      </c>
+      <c r="BO37">
+        <v>5.3</v>
+      </c>
+      <c r="BP37">
         <v>25</v>
       </c>
-      <c r="AE37">
-        <v>90</v>
-      </c>
-      <c r="AF37">
-        <v>13</v>
-      </c>
-      <c r="AG37">
-        <v>10.5</v>
-      </c>
-      <c r="AH37">
-        <v>25</v>
-      </c>
-      <c r="AI37">
-        <v>95</v>
-      </c>
-      <c r="AJ37">
-        <v>24</v>
-      </c>
-      <c r="AK37">
-        <v>24</v>
-      </c>
-      <c r="AL37">
-        <v>46</v>
-      </c>
-      <c r="AM37">
-        <v>150</v>
-      </c>
-      <c r="AN37">
-        <v>15.5</v>
-      </c>
-      <c r="AO37">
-        <v>110</v>
-      </c>
-      <c r="AP37">
-        <v>12</v>
-      </c>
-      <c r="AQ37">
-        <v>14.5</v>
-      </c>
-      <c r="AR37">
-        <v>4.9</v>
-      </c>
-      <c r="AS37">
-        <v>5.2</v>
-      </c>
-      <c r="AT37">
-        <v>7.4</v>
-      </c>
-      <c r="AU37">
-        <v>7.6</v>
-      </c>
-      <c r="AV37">
-        <v>17.5</v>
-      </c>
-      <c r="AW37">
-        <v>5.1</v>
-      </c>
-      <c r="AX37">
-        <v>9.6</v>
-      </c>
-      <c r="AY37">
-        <v>9</v>
-      </c>
-      <c r="AZ37">
-        <v>17.5</v>
-      </c>
-      <c r="BA37">
-        <v>5.2</v>
-      </c>
-      <c r="BB37">
-        <v>17</v>
-      </c>
-      <c r="BC37">
-        <v>17.5</v>
-      </c>
-      <c r="BD37">
-        <v>4.9</v>
-      </c>
-      <c r="BE37">
-        <v>5.1</v>
-      </c>
-      <c r="BF37">
-        <v>11</v>
-      </c>
-      <c r="BG37">
-        <v>5.2</v>
-      </c>
-      <c r="BH37">
-        <v>1000</v>
-      </c>
-      <c r="BI37">
-        <v>1.01</v>
-      </c>
-      <c r="BJ37">
-        <v>1000</v>
-      </c>
-      <c r="BK37">
-        <v>1.01</v>
-      </c>
-      <c r="BL37">
-        <v>1000</v>
-      </c>
-      <c r="BM37">
-        <v>1.01</v>
-      </c>
-      <c r="BN37">
-        <v>1000</v>
-      </c>
-      <c r="BO37">
-        <v>1.01</v>
-      </c>
-      <c r="BP37">
-        <v>1000</v>
-      </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU37">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW37">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ37">
         <v>1000</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB37" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B38" t="s">
         <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
         <v>161</v>
       </c>
       <c r="E38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F38">
-        <v>6.2</v>
+        <v>1.78</v>
       </c>
       <c r="G38">
-        <v>8.800000000000001</v>
+        <v>1.88</v>
       </c>
       <c r="H38">
-        <v>1.43</v>
+        <v>4.9</v>
       </c>
       <c r="I38">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J38">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="K38">
-        <v>5.6</v>
+        <v>3.95</v>
       </c>
       <c r="L38">
         <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N38">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="O38">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="P38">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="Q38">
-        <v>1.56</v>
+        <v>1.99</v>
       </c>
       <c r="R38">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="S38">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="T38">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U38">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V38">
-        <v>3</v>
+        <v>1.22</v>
       </c>
       <c r="W38">
-        <v>1.13</v>
+        <v>2.14</v>
       </c>
       <c r="X38">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="Y38">
+        <v>21</v>
+      </c>
+      <c r="Z38">
+        <v>50</v>
+      </c>
+      <c r="AA38">
+        <v>160</v>
+      </c>
+      <c r="AB38">
+        <v>10</v>
+      </c>
+      <c r="AC38">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD38">
+        <v>25</v>
+      </c>
+      <c r="AE38">
+        <v>90</v>
+      </c>
+      <c r="AF38">
+        <v>13</v>
+      </c>
+      <c r="AG38">
+        <v>10.5</v>
+      </c>
+      <c r="AH38">
+        <v>25</v>
+      </c>
+      <c r="AI38">
+        <v>95</v>
+      </c>
+      <c r="AJ38">
+        <v>24</v>
+      </c>
+      <c r="AK38">
+        <v>24</v>
+      </c>
+      <c r="AL38">
+        <v>46</v>
+      </c>
+      <c r="AM38">
+        <v>150</v>
+      </c>
+      <c r="AN38">
+        <v>15.5</v>
+      </c>
+      <c r="AO38">
+        <v>110</v>
+      </c>
+      <c r="AP38">
+        <v>12</v>
+      </c>
+      <c r="AQ38">
+        <v>14.5</v>
+      </c>
+      <c r="AR38">
+        <v>4.9</v>
+      </c>
+      <c r="AS38">
+        <v>5.2</v>
+      </c>
+      <c r="AT38">
+        <v>7.4</v>
+      </c>
+      <c r="AU38">
+        <v>7.6</v>
+      </c>
+      <c r="AV38">
+        <v>17.5</v>
+      </c>
+      <c r="AW38">
+        <v>5.1</v>
+      </c>
+      <c r="AX38">
+        <v>9.6</v>
+      </c>
+      <c r="AY38">
+        <v>9</v>
+      </c>
+      <c r="AZ38">
+        <v>17.5</v>
+      </c>
+      <c r="BA38">
+        <v>5.2</v>
+      </c>
+      <c r="BB38">
+        <v>17</v>
+      </c>
+      <c r="BC38">
+        <v>17.5</v>
+      </c>
+      <c r="BD38">
+        <v>4.9</v>
+      </c>
+      <c r="BE38">
+        <v>5.1</v>
+      </c>
+      <c r="BF38">
         <v>11</v>
       </c>
-      <c r="Z38">
-        <v>10.5</v>
-      </c>
-      <c r="AA38">
-        <v>13.5</v>
-      </c>
-      <c r="AB38">
-        <v>38</v>
-      </c>
-      <c r="AC38">
-        <v>14.5</v>
-      </c>
-      <c r="AD38">
-        <v>12.5</v>
-      </c>
-      <c r="AE38">
-        <v>15.5</v>
-      </c>
-      <c r="AF38">
-        <v>85</v>
-      </c>
-      <c r="AG38">
-        <v>36</v>
-      </c>
-      <c r="AH38">
-        <v>27</v>
-      </c>
-      <c r="AI38">
-        <v>38</v>
-      </c>
-      <c r="AJ38">
-        <v>260</v>
-      </c>
-      <c r="AK38">
-        <v>120</v>
-      </c>
-      <c r="AL38">
-        <v>100</v>
-      </c>
-      <c r="AM38">
-        <v>130</v>
-      </c>
-      <c r="AN38">
-        <v>130</v>
-      </c>
-      <c r="AO38">
-        <v>5.7</v>
-      </c>
-      <c r="AP38">
-        <v>5.4</v>
-      </c>
-      <c r="AQ38">
-        <v>4.2</v>
-      </c>
-      <c r="AR38">
-        <v>4.1</v>
-      </c>
-      <c r="AS38">
-        <v>4.5</v>
-      </c>
-      <c r="AT38">
-        <v>5.8</v>
-      </c>
-      <c r="AU38">
-        <v>4.6</v>
-      </c>
-      <c r="AV38">
-        <v>4.4</v>
-      </c>
-      <c r="AW38">
-        <v>4.7</v>
-      </c>
-      <c r="AX38">
-        <v>6.2</v>
-      </c>
-      <c r="AY38">
-        <v>5.7</v>
-      </c>
-      <c r="AZ38">
-        <v>5.4</v>
-      </c>
-      <c r="BA38">
-        <v>5.8</v>
-      </c>
-      <c r="BB38">
-        <v>6.6</v>
-      </c>
-      <c r="BC38">
-        <v>6.4</v>
-      </c>
-      <c r="BD38">
-        <v>6.4</v>
-      </c>
-      <c r="BE38">
-        <v>6.4</v>
-      </c>
-      <c r="BF38">
-        <v>6.4</v>
-      </c>
       <c r="BG38">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10165,7 +10177,7 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10182,7 +10194,7 @@
         <v>162</v>
       </c>
       <c r="E39" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F39">
         <v>2.64</v>
@@ -10407,434 +10419,434 @@
         <v>1.01</v>
       </c>
       <c r="CB39" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B40" t="s">
         <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
         <v>163</v>
       </c>
       <c r="E40" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F40">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="G40">
-        <v>1.97</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H40">
-        <v>5.1</v>
+        <v>1.43</v>
       </c>
       <c r="I40">
+        <v>1.5</v>
+      </c>
+      <c r="J40">
+        <v>4.6</v>
+      </c>
+      <c r="K40">
         <v>5.6</v>
       </c>
-      <c r="J40">
-        <v>3.3</v>
-      </c>
-      <c r="K40">
-        <v>3.45</v>
-      </c>
       <c r="L40">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N40">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="O40">
-        <v>1.54</v>
+        <v>1.19</v>
       </c>
       <c r="P40">
+        <v>2.28</v>
+      </c>
+      <c r="Q40">
         <v>1.56</v>
       </c>
-      <c r="Q40">
-        <v>2.62</v>
-      </c>
       <c r="R40">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="S40">
-        <v>5.3</v>
+        <v>2.32</v>
       </c>
       <c r="T40">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="U40">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="V40">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="W40">
-        <v>2.02</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="Y40">
+        <v>11</v>
+      </c>
+      <c r="Z40">
+        <v>10.5</v>
+      </c>
+      <c r="AA40">
         <v>13.5</v>
       </c>
-      <c r="Z40">
-        <v>50</v>
-      </c>
-      <c r="AA40">
-        <v>1000</v>
-      </c>
       <c r="AB40">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="AC40">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AD40">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="AE40">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF40">
-        <v>10.5</v>
+        <v>85</v>
       </c>
       <c r="AG40">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AH40">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AI40">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ40">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="AK40">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="AL40">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AM40">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN40">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="AO40">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AP40">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="AQ40">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR40">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AS40">
-        <v>42</v>
+        <v>4.5</v>
       </c>
       <c r="AT40">
         <v>5.8</v>
       </c>
       <c r="AU40">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV40">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="AW40">
-        <v>36</v>
+        <v>4.7</v>
       </c>
       <c r="AX40">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AY40">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="AZ40">
-        <v>19</v>
+        <v>5.4</v>
       </c>
       <c r="BA40">
-        <v>42</v>
+        <v>5.8</v>
       </c>
       <c r="BB40">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BC40">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD40">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BE40">
-        <v>50</v>
+        <v>6.4</v>
       </c>
       <c r="BF40">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="BG40">
-        <v>44</v>
+        <v>4.7</v>
       </c>
       <c r="BH40">
         <v>1000</v>
       </c>
       <c r="BI40">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
       </c>
       <c r="BK40">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BN40">
         <v>1000</v>
       </c>
       <c r="BO40">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BP40">
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BT40">
         <v>1000</v>
       </c>
       <c r="BU40">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="CB40" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
         <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s">
         <v>164</v>
       </c>
       <c r="E41" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F41">
-        <v>4.1</v>
+        <v>1.08</v>
       </c>
       <c r="G41">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
       <c r="H41">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="I41">
-        <v>2.26</v>
+        <v>50</v>
       </c>
       <c r="J41">
-        <v>3.1</v>
+        <v>7.8</v>
       </c>
       <c r="K41">
-        <v>3.25</v>
+        <v>17</v>
       </c>
       <c r="L41">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N41">
-        <v>2.56</v>
+        <v>7.2</v>
       </c>
       <c r="O41">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="P41">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q41">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="R41">
-        <v>1.19</v>
+        <v>2.12</v>
       </c>
       <c r="S41">
-        <v>4.7</v>
+        <v>1.61</v>
       </c>
       <c r="T41">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="U41">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="V41">
-        <v>1.79</v>
+        <v>1.02</v>
       </c>
       <c r="W41">
-        <v>1.29</v>
+        <v>6</v>
       </c>
       <c r="X41">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="Y41">
-        <v>7.2</v>
+        <v>150</v>
       </c>
       <c r="Z41">
-        <v>12</v>
+        <v>510</v>
       </c>
       <c r="AA41">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB41">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AC41">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AD41">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="AE41">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF41">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="AG41">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AH41">
+        <v>80</v>
+      </c>
+      <c r="AI41">
+        <v>490</v>
+      </c>
+      <c r="AJ41">
+        <v>9.6</v>
+      </c>
+      <c r="AK41">
+        <v>18</v>
+      </c>
+      <c r="AL41">
+        <v>70</v>
+      </c>
+      <c r="AM41">
+        <v>390</v>
+      </c>
+      <c r="AN41">
+        <v>2.46</v>
+      </c>
+      <c r="AO41">
+        <v>1000</v>
+      </c>
+      <c r="AP41">
+        <v>1.01</v>
+      </c>
+      <c r="AQ41">
+        <v>1.01</v>
+      </c>
+      <c r="AR41">
+        <v>1.01</v>
+      </c>
+      <c r="AS41">
+        <v>1.01</v>
+      </c>
+      <c r="AT41">
+        <v>12.5</v>
+      </c>
+      <c r="AU41">
         <v>24</v>
       </c>
-      <c r="AI41">
-        <v>65</v>
-      </c>
-      <c r="AJ41">
-        <v>130</v>
-      </c>
-      <c r="AK41">
-        <v>80</v>
-      </c>
-      <c r="AL41">
-        <v>110</v>
-      </c>
-      <c r="AM41">
-        <v>220</v>
-      </c>
-      <c r="AN41">
-        <v>130</v>
-      </c>
-      <c r="AO41">
-        <v>34</v>
-      </c>
-      <c r="AP41">
+      <c r="AV41">
+        <v>1.01</v>
+      </c>
+      <c r="AW41">
+        <v>1.01</v>
+      </c>
+      <c r="AX41">
         <v>8</v>
       </c>
-      <c r="AQ41">
+      <c r="AY41">
+        <v>14</v>
+      </c>
+      <c r="AZ41">
+        <v>1.01</v>
+      </c>
+      <c r="BA41">
+        <v>1.01</v>
+      </c>
+      <c r="BB41">
         <v>6.4</v>
       </c>
-      <c r="AR41">
-        <v>10.5</v>
-      </c>
-      <c r="AS41">
-        <v>23</v>
-      </c>
-      <c r="AT41">
-        <v>10</v>
-      </c>
-      <c r="AU41">
-        <v>6.4</v>
-      </c>
-      <c r="AV41">
-        <v>10.5</v>
-      </c>
-      <c r="AW41">
-        <v>25</v>
-      </c>
-      <c r="AX41">
-        <v>24</v>
-      </c>
-      <c r="AY41">
-        <v>16</v>
-      </c>
-      <c r="AZ41">
-        <v>21</v>
-      </c>
-      <c r="BA41">
-        <v>50</v>
-      </c>
-      <c r="BB41">
-        <v>13</v>
-      </c>
       <c r="BC41">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BD41">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BE41">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>13</v>
+        <v>1.99</v>
       </c>
       <c r="BG41">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH41">
         <v>1000</v>
       </c>
       <c r="BI41">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BJ41">
         <v>1000</v>
@@ -10870,7 +10882,7 @@
         <v>1000</v>
       </c>
       <c r="BU41">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BV41">
         <v>1000</v>
@@ -10891,249 +10903,733 @@
         <v>1.01</v>
       </c>
       <c r="CB41" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
         <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
         <v>165</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F42">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G42">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="H42">
+        <v>5.1</v>
+      </c>
+      <c r="I42">
+        <v>5.6</v>
+      </c>
+      <c r="J42">
+        <v>3.3</v>
+      </c>
+      <c r="K42">
+        <v>3.55</v>
+      </c>
+      <c r="L42">
+        <v>1.55</v>
+      </c>
+      <c r="M42">
+        <v>1.12</v>
+      </c>
+      <c r="N42">
+        <v>2.7</v>
+      </c>
+      <c r="O42">
+        <v>1.54</v>
+      </c>
+      <c r="P42">
+        <v>1.56</v>
+      </c>
+      <c r="Q42">
+        <v>2.58</v>
+      </c>
+      <c r="R42">
+        <v>1.2</v>
+      </c>
+      <c r="S42">
+        <v>5.4</v>
+      </c>
+      <c r="T42">
+        <v>2.32</v>
+      </c>
+      <c r="U42">
+        <v>1.7</v>
+      </c>
+      <c r="V42">
+        <v>1.22</v>
+      </c>
+      <c r="W42">
+        <v>2.02</v>
+      </c>
+      <c r="X42">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y42">
+        <v>13.5</v>
+      </c>
+      <c r="Z42">
+        <v>65</v>
+      </c>
+      <c r="AA42">
+        <v>1000</v>
+      </c>
+      <c r="AB42">
+        <v>6.4</v>
+      </c>
+      <c r="AC42">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD42">
+        <v>25</v>
+      </c>
+      <c r="AE42">
+        <v>1000</v>
+      </c>
+      <c r="AF42">
+        <v>10.5</v>
+      </c>
+      <c r="AG42">
+        <v>11.5</v>
+      </c>
+      <c r="AH42">
+        <v>32</v>
+      </c>
+      <c r="AI42">
+        <v>1000</v>
+      </c>
+      <c r="AJ42">
+        <v>24</v>
+      </c>
+      <c r="AK42">
+        <v>30</v>
+      </c>
+      <c r="AL42">
+        <v>1000</v>
+      </c>
+      <c r="AM42">
+        <v>1000</v>
+      </c>
+      <c r="AN42">
+        <v>23</v>
+      </c>
+      <c r="AO42">
+        <v>1000</v>
+      </c>
+      <c r="AP42">
+        <v>8</v>
+      </c>
+      <c r="AQ42">
+        <v>11.5</v>
+      </c>
+      <c r="AR42">
+        <v>21</v>
+      </c>
+      <c r="AS42">
+        <v>42</v>
+      </c>
+      <c r="AT42">
+        <v>5.8</v>
+      </c>
+      <c r="AU42">
+        <v>7</v>
+      </c>
+      <c r="AV42">
+        <v>16</v>
+      </c>
+      <c r="AW42">
+        <v>36</v>
+      </c>
+      <c r="AX42">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY42">
+        <v>10</v>
+      </c>
+      <c r="AZ42">
+        <v>19</v>
+      </c>
+      <c r="BA42">
+        <v>42</v>
+      </c>
+      <c r="BB42">
+        <v>15</v>
+      </c>
+      <c r="BC42">
+        <v>17.5</v>
+      </c>
+      <c r="BD42">
+        <v>32</v>
+      </c>
+      <c r="BE42">
+        <v>50</v>
+      </c>
+      <c r="BF42">
+        <v>17.5</v>
+      </c>
+      <c r="BG42">
+        <v>44</v>
+      </c>
+      <c r="BH42">
+        <v>1000</v>
+      </c>
+      <c r="BI42">
+        <v>1.36</v>
+      </c>
+      <c r="BJ42">
+        <v>1000</v>
+      </c>
+      <c r="BK42">
+        <v>1.36</v>
+      </c>
+      <c r="BL42">
+        <v>1000</v>
+      </c>
+      <c r="BM42">
+        <v>1.36</v>
+      </c>
+      <c r="BN42">
+        <v>1000</v>
+      </c>
+      <c r="BO42">
+        <v>1.72</v>
+      </c>
+      <c r="BP42">
+        <v>1000</v>
+      </c>
+      <c r="BQ42">
+        <v>1.36</v>
+      </c>
+      <c r="BR42">
+        <v>1000</v>
+      </c>
+      <c r="BS42">
+        <v>1.36</v>
+      </c>
+      <c r="BT42">
+        <v>1000</v>
+      </c>
+      <c r="BU42">
+        <v>2.22</v>
+      </c>
+      <c r="BV42">
+        <v>1000</v>
+      </c>
+      <c r="BW42">
+        <v>1.36</v>
+      </c>
+      <c r="BX42">
+        <v>1000</v>
+      </c>
+      <c r="BY42">
+        <v>1.36</v>
+      </c>
+      <c r="BZ42">
+        <v>1000</v>
+      </c>
+      <c r="CA42">
+        <v>1.36</v>
+      </c>
+      <c r="CB42" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:80">
+      <c r="A43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" t="s">
+        <v>209</v>
+      </c>
+      <c r="F43">
+        <v>4.1</v>
+      </c>
+      <c r="G43">
+        <v>4.4</v>
+      </c>
+      <c r="H43">
+        <v>2.18</v>
+      </c>
+      <c r="I43">
+        <v>2.28</v>
+      </c>
+      <c r="J43">
+        <v>3.1</v>
+      </c>
+      <c r="K43">
+        <v>3.2</v>
+      </c>
+      <c r="L43">
+        <v>1.52</v>
+      </c>
+      <c r="M43">
+        <v>1.12</v>
+      </c>
+      <c r="N43">
+        <v>2.74</v>
+      </c>
+      <c r="O43">
+        <v>1.51</v>
+      </c>
+      <c r="P43">
+        <v>1.59</v>
+      </c>
+      <c r="Q43">
+        <v>2.54</v>
+      </c>
+      <c r="R43">
+        <v>1.21</v>
+      </c>
+      <c r="S43">
+        <v>5.1</v>
+      </c>
+      <c r="T43">
+        <v>2.1</v>
+      </c>
+      <c r="U43">
+        <v>1.81</v>
+      </c>
+      <c r="V43">
+        <v>1.78</v>
+      </c>
+      <c r="W43">
+        <v>1.29</v>
+      </c>
+      <c r="X43">
+        <v>9</v>
+      </c>
+      <c r="Y43">
+        <v>7.2</v>
+      </c>
+      <c r="Z43">
+        <v>12.5</v>
+      </c>
+      <c r="AA43">
+        <v>30</v>
+      </c>
+      <c r="AB43">
+        <v>12</v>
+      </c>
+      <c r="AC43">
+        <v>7.4</v>
+      </c>
+      <c r="AD43">
+        <v>12</v>
+      </c>
+      <c r="AE43">
+        <v>30</v>
+      </c>
+      <c r="AF43">
+        <v>29</v>
+      </c>
+      <c r="AG43">
+        <v>18.5</v>
+      </c>
+      <c r="AH43">
+        <v>23</v>
+      </c>
+      <c r="AI43">
+        <v>65</v>
+      </c>
+      <c r="AJ43">
+        <v>110</v>
+      </c>
+      <c r="AK43">
+        <v>75</v>
+      </c>
+      <c r="AL43">
+        <v>110</v>
+      </c>
+      <c r="AM43">
+        <v>220</v>
+      </c>
+      <c r="AN43">
+        <v>110</v>
+      </c>
+      <c r="AO43">
+        <v>34</v>
+      </c>
+      <c r="AP43">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ43">
+        <v>6.4</v>
+      </c>
+      <c r="AR43">
+        <v>10.5</v>
+      </c>
+      <c r="AS43">
+        <v>23</v>
+      </c>
+      <c r="AT43">
+        <v>10</v>
+      </c>
+      <c r="AU43">
+        <v>6.4</v>
+      </c>
+      <c r="AV43">
+        <v>10.5</v>
+      </c>
+      <c r="AW43">
+        <v>25</v>
+      </c>
+      <c r="AX43">
+        <v>24</v>
+      </c>
+      <c r="AY43">
+        <v>16</v>
+      </c>
+      <c r="AZ43">
+        <v>21</v>
+      </c>
+      <c r="BA43">
+        <v>50</v>
+      </c>
+      <c r="BB43">
+        <v>13.5</v>
+      </c>
+      <c r="BC43">
+        <v>55</v>
+      </c>
+      <c r="BD43">
+        <v>75</v>
+      </c>
+      <c r="BE43">
+        <v>9.4</v>
+      </c>
+      <c r="BF43">
+        <v>13.5</v>
+      </c>
+      <c r="BG43">
+        <v>21</v>
+      </c>
+      <c r="BH43">
+        <v>1000</v>
+      </c>
+      <c r="BI43">
+        <v>2.34</v>
+      </c>
+      <c r="BJ43">
+        <v>1000</v>
+      </c>
+      <c r="BK43">
+        <v>1.01</v>
+      </c>
+      <c r="BL43">
+        <v>1000</v>
+      </c>
+      <c r="BM43">
+        <v>1.01</v>
+      </c>
+      <c r="BN43">
+        <v>1000</v>
+      </c>
+      <c r="BO43">
+        <v>1.01</v>
+      </c>
+      <c r="BP43">
+        <v>1000</v>
+      </c>
+      <c r="BQ43">
+        <v>1.01</v>
+      </c>
+      <c r="BR43">
+        <v>1000</v>
+      </c>
+      <c r="BS43">
+        <v>1.01</v>
+      </c>
+      <c r="BT43">
+        <v>1000</v>
+      </c>
+      <c r="BU43">
         <v>3.85</v>
       </c>
-      <c r="I42">
-        <v>5</v>
-      </c>
-      <c r="J42">
-        <v>3.15</v>
-      </c>
-      <c r="K42">
+      <c r="BV43">
+        <v>1000</v>
+      </c>
+      <c r="BW43">
+        <v>1.01</v>
+      </c>
+      <c r="BX43">
+        <v>1000</v>
+      </c>
+      <c r="BY43">
+        <v>1.01</v>
+      </c>
+      <c r="BZ43">
+        <v>1000</v>
+      </c>
+      <c r="CA43">
+        <v>1.01</v>
+      </c>
+      <c r="CB43" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:80">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" t="s">
+        <v>210</v>
+      </c>
+      <c r="F44">
+        <v>1.94</v>
+      </c>
+      <c r="G44">
+        <v>2.14</v>
+      </c>
+      <c r="H44">
+        <v>3.85</v>
+      </c>
+      <c r="I44">
+        <v>4.9</v>
+      </c>
+      <c r="J44">
+        <v>3.2</v>
+      </c>
+      <c r="K44">
         <v>4.3</v>
       </c>
-      <c r="L42">
+      <c r="L44">
         <v>1.43</v>
       </c>
-      <c r="M42">
+      <c r="M44">
         <v>1.04</v>
       </c>
-      <c r="N42">
+      <c r="N44">
+        <v>3.45</v>
+      </c>
+      <c r="O44">
+        <v>1.35</v>
+      </c>
+      <c r="P44">
+        <v>1.77</v>
+      </c>
+      <c r="Q44">
+        <v>2.04</v>
+      </c>
+      <c r="R44">
+        <v>1.28</v>
+      </c>
+      <c r="S44">
         <v>3.4</v>
       </c>
-      <c r="O42">
+      <c r="T44">
+        <v>1.77</v>
+      </c>
+      <c r="U44">
+        <v>1.96</v>
+      </c>
+      <c r="V44">
+        <v>1.26</v>
+      </c>
+      <c r="W44">
+        <v>1.87</v>
+      </c>
+      <c r="X44">
+        <v>1000</v>
+      </c>
+      <c r="Y44">
+        <v>42</v>
+      </c>
+      <c r="Z44">
+        <v>1000</v>
+      </c>
+      <c r="AA44">
+        <v>1000</v>
+      </c>
+      <c r="AB44">
+        <v>13</v>
+      </c>
+      <c r="AC44">
+        <v>11.5</v>
+      </c>
+      <c r="AD44">
+        <v>1000</v>
+      </c>
+      <c r="AE44">
+        <v>1000</v>
+      </c>
+      <c r="AF44">
+        <v>23</v>
+      </c>
+      <c r="AG44">
+        <v>19</v>
+      </c>
+      <c r="AH44">
+        <v>1000</v>
+      </c>
+      <c r="AI44">
+        <v>1000</v>
+      </c>
+      <c r="AJ44">
+        <v>1000</v>
+      </c>
+      <c r="AK44">
+        <v>1000</v>
+      </c>
+      <c r="AL44">
+        <v>1000</v>
+      </c>
+      <c r="AM44">
+        <v>1000</v>
+      </c>
+      <c r="AN44">
+        <v>1000</v>
+      </c>
+      <c r="AO44">
+        <v>1000</v>
+      </c>
+      <c r="AP44">
+        <v>1.39</v>
+      </c>
+      <c r="AQ44">
         <v>1.35</v>
       </c>
-      <c r="P42">
-        <v>1.77</v>
-      </c>
-      <c r="Q42">
-        <v>2</v>
-      </c>
-      <c r="R42">
-        <v>1.28</v>
-      </c>
-      <c r="S42">
-        <v>3.3</v>
-      </c>
-      <c r="T42">
-        <v>1.78</v>
-      </c>
-      <c r="U42">
-        <v>1.94</v>
-      </c>
-      <c r="V42">
+      <c r="AR44">
+        <v>1.39</v>
+      </c>
+      <c r="AS44">
+        <v>1.39</v>
+      </c>
+      <c r="AT44">
         <v>1.26</v>
       </c>
-      <c r="W42">
-        <v>1.87</v>
-      </c>
-      <c r="X42">
-        <v>1000</v>
-      </c>
-      <c r="Y42">
-        <v>1000</v>
-      </c>
-      <c r="Z42">
-        <v>1000</v>
-      </c>
-      <c r="AA42">
-        <v>1000</v>
-      </c>
-      <c r="AB42">
-        <v>13</v>
-      </c>
-      <c r="AC42">
-        <v>11.5</v>
-      </c>
-      <c r="AD42">
-        <v>1000</v>
-      </c>
-      <c r="AE42">
-        <v>1000</v>
-      </c>
-      <c r="AF42">
-        <v>1000</v>
-      </c>
-      <c r="AG42">
-        <v>1000</v>
-      </c>
-      <c r="AH42">
-        <v>1000</v>
-      </c>
-      <c r="AI42">
-        <v>1000</v>
-      </c>
-      <c r="AJ42">
-        <v>1000</v>
-      </c>
-      <c r="AK42">
-        <v>1000</v>
-      </c>
-      <c r="AL42">
-        <v>1000</v>
-      </c>
-      <c r="AM42">
-        <v>1000</v>
-      </c>
-      <c r="AN42">
-        <v>1000</v>
-      </c>
-      <c r="AO42">
-        <v>1000</v>
-      </c>
-      <c r="AP42">
-        <v>1.19</v>
-      </c>
-      <c r="AQ42">
-        <v>1.19</v>
-      </c>
-      <c r="AR42">
-        <v>1.19</v>
-      </c>
-      <c r="AS42">
-        <v>1.19</v>
-      </c>
-      <c r="AT42">
-        <v>1.09</v>
-      </c>
-      <c r="AU42">
-        <v>1.08</v>
-      </c>
-      <c r="AV42">
-        <v>1.19</v>
-      </c>
-      <c r="AW42">
-        <v>1.19</v>
-      </c>
-      <c r="AX42">
-        <v>1.19</v>
-      </c>
-      <c r="AY42">
-        <v>1.19</v>
-      </c>
-      <c r="AZ42">
-        <v>1.19</v>
-      </c>
-      <c r="BA42">
-        <v>1.19</v>
-      </c>
-      <c r="BB42">
-        <v>1.19</v>
-      </c>
-      <c r="BC42">
-        <v>1.19</v>
-      </c>
-      <c r="BD42">
-        <v>1.19</v>
-      </c>
-      <c r="BE42">
-        <v>1.19</v>
-      </c>
-      <c r="BF42">
-        <v>1.19</v>
-      </c>
-      <c r="BG42">
-        <v>1.19</v>
-      </c>
-      <c r="BH42">
+      <c r="AU44">
+        <v>1.24</v>
+      </c>
+      <c r="AV44">
+        <v>1.39</v>
+      </c>
+      <c r="AW44">
+        <v>1.39</v>
+      </c>
+      <c r="AX44">
+        <v>1.31</v>
+      </c>
+      <c r="AY44">
+        <v>1.3</v>
+      </c>
+      <c r="AZ44">
+        <v>1.39</v>
+      </c>
+      <c r="BA44">
+        <v>1.39</v>
+      </c>
+      <c r="BB44">
+        <v>1.39</v>
+      </c>
+      <c r="BC44">
+        <v>1.39</v>
+      </c>
+      <c r="BD44">
+        <v>1.39</v>
+      </c>
+      <c r="BE44">
+        <v>1.39</v>
+      </c>
+      <c r="BF44">
+        <v>1.39</v>
+      </c>
+      <c r="BG44">
+        <v>1.39</v>
+      </c>
+      <c r="BH44">
         <v>3.35</v>
       </c>
-      <c r="BI42">
+      <c r="BI44">
         <v>2.68</v>
       </c>
-      <c r="BJ42">
+      <c r="BJ44">
         <v>10.5</v>
       </c>
-      <c r="BK42">
+      <c r="BK44">
         <v>8.4</v>
       </c>
-      <c r="BL42">
-        <v>1000</v>
-      </c>
-      <c r="BM42">
+      <c r="BL44">
+        <v>1000</v>
+      </c>
+      <c r="BM44">
         <v>21</v>
       </c>
-      <c r="BN42">
+      <c r="BN44">
         <v>4.9</v>
       </c>
-      <c r="BO42">
+      <c r="BO44">
         <v>4.1</v>
       </c>
-      <c r="BP42">
+      <c r="BP44">
         <v>15.5</v>
       </c>
-      <c r="BQ42">
+      <c r="BQ44">
         <v>12.5</v>
       </c>
-      <c r="BR42">
+      <c r="BR44">
         <v>32</v>
       </c>
-      <c r="BS42">
+      <c r="BS44">
         <v>26</v>
       </c>
-      <c r="BT42">
+      <c r="BT44">
         <v>7.8</v>
       </c>
-      <c r="BU42">
+      <c r="BU44">
         <v>6.4</v>
       </c>
-      <c r="BV42">
+      <c r="BV44">
         <v>38</v>
       </c>
-      <c r="BW42">
+      <c r="BW44">
         <v>27</v>
       </c>
-      <c r="BX42">
+      <c r="BX44">
         <v>50</v>
       </c>
-      <c r="BY42">
+      <c r="BY44">
         <v>36</v>
       </c>
-      <c r="BZ42">
+      <c r="BZ44">
         <v>30</v>
       </c>
-      <c r="CA42">
+      <c r="CA44">
         <v>21</v>
       </c>
-      <c r="CB42" t="s">
-        <v>207</v>
+      <c r="CB44" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -739,7 +739,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-10-03 16:52:32</t>
+    <t>2026-10-03 19:04:11</t>
   </si>
 </sst>
 </file>
@@ -1336,10 +1336,10 @@
         <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>9.199999999999999</v>
@@ -1348,7 +1348,7 @@
         <v>4.8</v>
       </c>
       <c r="K2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1357,34 +1357,34 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2">
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q2">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
         <v>1.12</v>
       </c>
       <c r="W2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X2">
         <v>19.5</v>
@@ -1402,13 +1402,13 @@
         <v>8.6</v>
       </c>
       <c r="AC2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD2">
         <v>38</v>
       </c>
       <c r="AE2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF2">
         <v>8.800000000000001</v>
@@ -1417,22 +1417,22 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK2">
         <v>16.5</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2">
         <v>7</v>
@@ -1444,34 +1444,34 @@
         <v>16.5</v>
       </c>
       <c r="AQ2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR2">
         <v>55</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU2">
         <v>10</v>
       </c>
       <c r="AV2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA2">
         <v>55</v>
@@ -1483,25 +1483,25 @@
         <v>13.5</v>
       </c>
       <c r="BD2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF2">
         <v>6</v>
       </c>
       <c r="BG2">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BJ2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BK2">
         <v>1.7</v>
@@ -1510,7 +1510,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BN2">
         <v>5.3</v>
@@ -1528,31 +1528,31 @@
         <v>36</v>
       </c>
       <c r="BS2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BT2">
         <v>17.5</v>
       </c>
       <c r="BU2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BZ2">
         <v>21</v>
       </c>
       <c r="CA2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CB2" t="s">
         <v>241</v>
@@ -1578,19 +1578,19 @@
         <v>3.3</v>
       </c>
       <c r="G3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J3">
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1599,16 +1599,16 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O3">
         <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
         <v>1.25</v>
@@ -1617,13 +1617,13 @@
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
         <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W3">
         <v>1.4</v>
@@ -1638,7 +1638,7 @@
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB3">
         <v>11</v>
@@ -1680,19 +1680,19 @@
         <v>70</v>
       </c>
       <c r="AO3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP3">
         <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT3">
         <v>9.199999999999999</v>
@@ -1704,7 +1704,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX3">
         <v>19.5</v>
@@ -1716,13 +1716,13 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB3">
         <v>46</v>
       </c>
       <c r="BC3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BD3">
         <v>46</v>
@@ -1740,7 +1740,7 @@
         <v>2.94</v>
       </c>
       <c r="BI3">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1752,13 +1752,13 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
         <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>22</v>
       </c>
       <c r="BR3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
         <v>34</v>
@@ -1776,7 +1776,7 @@
         <v>5.3</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BV3">
         <v>21</v>
@@ -1785,7 +1785,7 @@
         <v>15</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
         <v>28</v>
@@ -1817,7 +1817,7 @@
         <v>188</v>
       </c>
       <c r="F4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G4">
         <v>5.2</v>
@@ -1835,28 +1835,28 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
         <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
         <v>1.88</v>
@@ -1865,7 +1865,7 @@
         <v>2</v>
       </c>
       <c r="V4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W4">
         <v>1.24</v>
@@ -1874,7 +1874,7 @@
         <v>17</v>
       </c>
       <c r="Y4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z4">
         <v>11.5</v>
@@ -1895,34 +1895,34 @@
         <v>22</v>
       </c>
       <c r="AF4">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AG4">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AH4">
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
         <v>150</v>
       </c>
       <c r="AK4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AM4">
         <v>140</v>
       </c>
       <c r="AN4">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AO4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP4">
         <v>12</v>
@@ -1940,52 +1940,52 @@
         <v>14</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
         <v>9</v>
       </c>
       <c r="AW4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX4">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AY4">
         <v>16</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BB4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC4">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BD4">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF4">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
         <v>11.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
         <v>6.2</v>
@@ -1994,49 +1994,49 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO4">
+        <v>5.3</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>11</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
         <v>11.5</v>
       </c>
-      <c r="BO4">
-        <v>5.1</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>21</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.01</v>
-      </c>
       <c r="BT4">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BW4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="s">
         <v>241</v>
@@ -2059,13 +2059,13 @@
         <v>189</v>
       </c>
       <c r="F5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H5">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I5">
         <v>3.05</v>
@@ -2074,7 +2074,7 @@
         <v>3.75</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -2083,7 +2083,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
         <v>1.25</v>
@@ -2092,16 +2092,16 @@
         <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U5">
         <v>2.42</v>
@@ -2110,22 +2110,22 @@
         <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X5">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z5">
         <v>23</v>
       </c>
       <c r="AA5">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AB5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC5">
         <v>8.800000000000001</v>
@@ -2137,46 +2137,46 @@
         <v>36</v>
       </c>
       <c r="AF5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG5">
         <v>12</v>
       </c>
       <c r="AH5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI5">
         <v>38</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AM5">
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
         <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="AS5">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
         <v>11</v>
@@ -2188,37 +2188,37 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="AX5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BB5">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BC5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BF5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG5">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BH5">
         <v>3.85</v>
@@ -2230,31 +2230,31 @@
         <v>9</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO5">
         <v>5</v>
       </c>
       <c r="BP5">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
         <v>6.4</v>
@@ -2266,7 +2266,7 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BX5">
         <v>36</v>
@@ -2278,7 +2278,7 @@
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>241</v>
@@ -2304,19 +2304,19 @@
         <v>3.35</v>
       </c>
       <c r="G6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H6">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
         <v>1.5</v>
@@ -2325,28 +2325,28 @@
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q6">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
         <v>1.26</v>
       </c>
       <c r="S6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U6">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V6">
         <v>1.66</v>
@@ -2370,7 +2370,7 @@
         <v>11.5</v>
       </c>
       <c r="AC6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
         <v>12.5</v>
@@ -2382,7 +2382,7 @@
         <v>24</v>
       </c>
       <c r="AG6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH6">
         <v>24</v>
@@ -2403,7 +2403,7 @@
         <v>160</v>
       </c>
       <c r="AN6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO6">
         <v>34</v>
@@ -2412,13 +2412,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR6">
         <v>13</v>
       </c>
       <c r="AS6">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT6">
         <v>9.800000000000001</v>
@@ -2430,7 +2430,7 @@
         <v>10</v>
       </c>
       <c r="AW6">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX6">
         <v>20</v>
@@ -2442,25 +2442,25 @@
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC6">
-        <v>5.9</v>
+        <v>34</v>
       </c>
       <c r="BD6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BH6">
         <v>3.05</v>
@@ -2484,10 +2484,10 @@
         <v>6.6</v>
       </c>
       <c r="BO6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP6">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BQ6">
         <v>9.800000000000001</v>
@@ -2549,19 +2549,19 @@
         <v>4.3</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I7">
         <v>2.1</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
         <v>1.06</v>
@@ -2573,10 +2573,10 @@
         <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R7">
         <v>1.37</v>
@@ -2588,7 +2588,7 @@
         <v>1.76</v>
       </c>
       <c r="U7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
         <v>1.9</v>
@@ -2597,52 +2597,52 @@
         <v>1.31</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y7">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AC7">
         <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF7">
         <v>32</v>
       </c>
       <c r="AG7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ7">
         <v>100</v>
       </c>
       <c r="AK7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN7">
         <v>55</v>
@@ -2651,10 +2651,10 @@
         <v>15</v>
       </c>
       <c r="AP7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR7">
         <v>11</v>
@@ -2675,22 +2675,22 @@
         <v>18</v>
       </c>
       <c r="AX7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY7">
         <v>14</v>
       </c>
       <c r="AZ7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA7">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BB7">
         <v>50</v>
       </c>
       <c r="BC7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BD7">
         <v>34</v>
@@ -2699,22 +2699,22 @@
         <v>65</v>
       </c>
       <c r="BF7">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BG7">
         <v>12</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BK7">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2723,46 +2723,46 @@
         <v>21</v>
       </c>
       <c r="BN7">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BO7">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BQ7">
+        <v>25</v>
+      </c>
+      <c r="BR7">
+        <v>44</v>
+      </c>
+      <c r="BS7">
+        <v>32</v>
+      </c>
+      <c r="BT7">
+        <v>5</v>
+      </c>
+      <c r="BU7">
+        <v>4.1</v>
+      </c>
+      <c r="BV7">
+        <v>15</v>
+      </c>
+      <c r="BW7">
+        <v>10.5</v>
+      </c>
+      <c r="BX7">
+        <v>29</v>
+      </c>
+      <c r="BY7">
         <v>21</v>
       </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>21</v>
-      </c>
-      <c r="BT7">
-        <v>6.4</v>
-      </c>
-      <c r="BU7">
-        <v>3.35</v>
-      </c>
-      <c r="BV7">
-        <v>20</v>
-      </c>
-      <c r="BW7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX7">
-        <v>38</v>
-      </c>
-      <c r="BY7">
-        <v>17.5</v>
-      </c>
       <c r="BZ7">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="CA7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CB7" t="s">
         <v>241</v>
@@ -2785,7 +2785,7 @@
         <v>192</v>
       </c>
       <c r="F8">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G8">
         <v>2.36</v>
@@ -2809,142 +2809,142 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P8">
+        <v>1.97</v>
+      </c>
+      <c r="Q8">
         <v>1.96</v>
-      </c>
-      <c r="Q8">
-        <v>1.92</v>
       </c>
       <c r="R8">
         <v>1.36</v>
       </c>
       <c r="S8">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T8">
         <v>1.78</v>
       </c>
       <c r="U8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
         <v>1.73</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB8">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI8">
         <v>55</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8">
-        <v>1.41</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>1.41</v>
+        <v>7.6</v>
       </c>
       <c r="AT8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU8">
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>1.41</v>
+        <v>7.2</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
       </c>
       <c r="AY8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
         <v>16</v>
       </c>
       <c r="BA8">
-        <v>1.37</v>
+        <v>7.2</v>
       </c>
       <c r="BB8">
-        <v>1.41</v>
+        <v>6.8</v>
       </c>
       <c r="BC8">
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>1.41</v>
+        <v>7</v>
       </c>
       <c r="BE8">
-        <v>1.41</v>
+        <v>7.8</v>
       </c>
       <c r="BF8">
         <v>16</v>
       </c>
       <c r="BG8">
-        <v>1.41</v>
+        <v>7.2</v>
       </c>
       <c r="BH8">
         <v>3.5</v>
@@ -2974,13 +2974,13 @@
         <v>18</v>
       </c>
       <c r="BQ8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BR8">
         <v>32</v>
       </c>
       <c r="BS8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BT8">
         <v>7</v>
@@ -3004,7 +3004,7 @@
         <v>28</v>
       </c>
       <c r="CA8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CB8" t="s">
         <v>241</v>
@@ -3027,178 +3027,178 @@
         <v>193</v>
       </c>
       <c r="F9">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="G9">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>11.5</v>
       </c>
       <c r="J9">
-        <v>1.13</v>
+        <v>5.1</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L9">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M9">
         <v>1.02</v>
       </c>
       <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>1.19</v>
+      </c>
+      <c r="P9">
+        <v>2.4</v>
+      </c>
+      <c r="Q9">
+        <v>1.58</v>
+      </c>
+      <c r="R9">
+        <v>1.56</v>
+      </c>
+      <c r="S9">
+        <v>2.46</v>
+      </c>
+      <c r="T9">
+        <v>1.92</v>
+      </c>
+      <c r="U9">
+        <v>1.88</v>
+      </c>
+      <c r="V9">
         <v>1.1</v>
       </c>
-      <c r="O9">
-        <v>1.02</v>
-      </c>
-      <c r="P9">
-        <v>1.51</v>
-      </c>
-      <c r="Q9">
-        <v>1.52</v>
-      </c>
-      <c r="R9">
-        <v>1.18</v>
-      </c>
-      <c r="S9">
-        <v>2.32</v>
-      </c>
-      <c r="T9">
-        <v>1.87</v>
-      </c>
-      <c r="U9">
-        <v>1.83</v>
-      </c>
-      <c r="V9">
-        <v>1.08</v>
-      </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>44</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -3207,46 +3207,46 @@
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
         <v>241</v>
@@ -3269,16 +3269,16 @@
         <v>194</v>
       </c>
       <c r="F10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G10">
         <v>1.42</v>
       </c>
       <c r="H10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="J10">
         <v>5.2</v>
@@ -3287,10 +3287,10 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
         <v>5.9</v>
@@ -3302,13 +3302,13 @@
         <v>2.7</v>
       </c>
       <c r="Q10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R10">
         <v>1.68</v>
       </c>
       <c r="S10">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T10">
         <v>1.75</v>
@@ -3329,40 +3329,40 @@
         <v>42</v>
       </c>
       <c r="Z10">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AA10">
         <v>280</v>
       </c>
       <c r="AB10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC10">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD10">
         <v>38</v>
       </c>
       <c r="AE10">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AF10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH10">
         <v>27</v>
       </c>
       <c r="AI10">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AJ10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK10">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL10">
         <v>34</v>
@@ -3371,34 +3371,34 @@
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AO10">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AP10">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="AQ10">
-        <v>5.2</v>
+        <v>27</v>
       </c>
       <c r="AR10">
-        <v>5.5</v>
+        <v>55</v>
       </c>
       <c r="AS10">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT10">
         <v>10</v>
       </c>
       <c r="AU10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV10">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="AW10">
-        <v>5.4</v>
+        <v>55</v>
       </c>
       <c r="AX10">
         <v>8.800000000000001</v>
@@ -3410,85 +3410,85 @@
         <v>17.5</v>
       </c>
       <c r="BA10">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="BB10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC10">
         <v>10.5</v>
       </c>
       <c r="BD10">
-        <v>5.1</v>
+        <v>17</v>
       </c>
       <c r="BE10">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF10">
         <v>4</v>
       </c>
       <c r="BG10">
-        <v>5.3</v>
+        <v>50</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI10">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK10">
-        <v>1.85</v>
+        <v>6.8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="BN10">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>1.53</v>
+        <v>3.65</v>
       </c>
       <c r="BP10">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BQ10">
         <v>5.3</v>
       </c>
       <c r="BR10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BS10">
-        <v>1.97</v>
+        <v>6</v>
       </c>
       <c r="BT10">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BU10">
-        <v>1.88</v>
+        <v>7.8</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW10">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY10">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="CA10">
-        <v>1.85</v>
+        <v>6.8</v>
       </c>
       <c r="CB10" t="s">
         <v>241</v>
@@ -3514,10 +3514,10 @@
         <v>2.66</v>
       </c>
       <c r="G11">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H11">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I11">
         <v>2.82</v>
@@ -3544,7 +3544,7 @@
         <v>2.1</v>
       </c>
       <c r="Q11">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R11">
         <v>1.43</v>
@@ -3553,7 +3553,7 @@
         <v>3.05</v>
       </c>
       <c r="T11">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U11">
         <v>2.34</v>
@@ -3562,7 +3562,7 @@
         <v>1.55</v>
       </c>
       <c r="W11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X11">
         <v>20</v>
@@ -3604,13 +3604,13 @@
         <v>48</v>
       </c>
       <c r="AK11">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AL11">
         <v>44</v>
       </c>
       <c r="AM11">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN11">
         <v>25</v>
@@ -3628,7 +3628,7 @@
         <v>16</v>
       </c>
       <c r="AS11">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="AT11">
         <v>11</v>
@@ -3652,22 +3652,22 @@
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BB11">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BC11">
         <v>21</v>
       </c>
       <c r="BD11">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BE11">
         <v>5.5</v>
       </c>
       <c r="BF11">
-        <v>16.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG11">
         <v>16.5</v>
@@ -3765,7 +3765,7 @@
         <v>3.6</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
         <v>3.65</v>
@@ -3777,10 +3777,10 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O12">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P12">
         <v>1.91</v>
@@ -3795,16 +3795,16 @@
         <v>3.55</v>
       </c>
       <c r="T12">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V12">
         <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X12">
         <v>14</v>
@@ -3813,10 +3813,10 @@
         <v>13.5</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12">
         <v>10</v>
@@ -3825,10 +3825,10 @@
         <v>8</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF12">
         <v>15</v>
@@ -3837,28 +3837,28 @@
         <v>11.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP12">
         <v>12</v>
@@ -3870,7 +3870,7 @@
         <v>19</v>
       </c>
       <c r="AS12">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12">
         <v>8.6</v>
@@ -3882,7 +3882,7 @@
         <v>13</v>
       </c>
       <c r="AW12">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="AX12">
         <v>12.5</v>
@@ -3894,64 +3894,64 @@
         <v>15</v>
       </c>
       <c r="BA12">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="BB12">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="BC12">
         <v>19</v>
       </c>
       <c r="BD12">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="BE12">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="BF12">
         <v>16.5</v>
       </c>
       <c r="BG12">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI12">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="BJ12">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK12">
-        <v>2.96</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.9</v>
+        <v>12.5</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO12">
-        <v>2.46</v>
+        <v>4.5</v>
       </c>
       <c r="BP12">
         <v>23</v>
       </c>
       <c r="BQ12">
-        <v>1.76</v>
+        <v>7.6</v>
       </c>
       <c r="BR12">
         <v>44</v>
       </c>
       <c r="BS12">
-        <v>1.82</v>
+        <v>9.6</v>
       </c>
       <c r="BT12">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BU12">
         <v>5.1</v>
@@ -3960,19 +3960,19 @@
         <v>40</v>
       </c>
       <c r="BW12">
-        <v>1.81</v>
+        <v>9.4</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY12">
-        <v>1.84</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
         <v>38</v>
       </c>
       <c r="CA12">
-        <v>1.81</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
         <v>241</v>
@@ -3995,25 +3995,25 @@
         <v>197</v>
       </c>
       <c r="F13">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G13">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="H13">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I13">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J13">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L13">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M13">
         <v>1.02</v>
@@ -4022,19 +4022,19 @@
         <v>4.7</v>
       </c>
       <c r="O13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P13">
         <v>2.42</v>
       </c>
       <c r="Q13">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R13">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S13">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
         <v>1.51</v>
@@ -4043,10 +4043,10 @@
         <v>2.4</v>
       </c>
       <c r="V13">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X13">
         <v>27</v>
@@ -4061,7 +4061,7 @@
         <v>34</v>
       </c>
       <c r="AB13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC13">
         <v>10.5</v>
@@ -4103,61 +4103,61 @@
         <v>11.5</v>
       </c>
       <c r="AP13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS13">
         <v>6.6</v>
       </c>
       <c r="AT13">
+        <v>5.9</v>
+      </c>
+      <c r="AU13">
+        <v>5.6</v>
+      </c>
+      <c r="AV13">
+        <v>6.2</v>
+      </c>
+      <c r="AW13">
         <v>6</v>
       </c>
-      <c r="AU13">
-        <v>4.7</v>
-      </c>
-      <c r="AV13">
-        <v>5.1</v>
-      </c>
-      <c r="AW13">
-        <v>6.2</v>
-      </c>
       <c r="AX13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY13">
+        <v>5.4</v>
+      </c>
+      <c r="AZ13">
         <v>5.5</v>
       </c>
-      <c r="AZ13">
-        <v>5.6</v>
-      </c>
       <c r="BA13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC13">
         <v>6.8</v>
       </c>
       <c r="BD13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF13">
         <v>6</v>
       </c>
       <c r="BG13">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI13">
         <v>3.6</v>
@@ -4178,7 +4178,7 @@
         <v>7.2</v>
       </c>
       <c r="BO13">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP13">
         <v>23</v>
@@ -4205,7 +4205,7 @@
         <v>11</v>
       </c>
       <c r="BX13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY13">
         <v>8.800000000000001</v>
@@ -4237,22 +4237,22 @@
         <v>198</v>
       </c>
       <c r="F14">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G14">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H14">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="I14">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4270,28 +4270,28 @@
         <v>2.26</v>
       </c>
       <c r="Q14">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R14">
         <v>1.52</v>
       </c>
       <c r="S14">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="T14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y14">
         <v>16</v>
@@ -4300,16 +4300,16 @@
         <v>22</v>
       </c>
       <c r="AA14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB14">
         <v>16</v>
       </c>
       <c r="AC14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE14">
         <v>28</v>
@@ -4318,25 +4318,25 @@
         <v>22</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH14">
         <v>15.5</v>
       </c>
       <c r="AI14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ14">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL14">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AM14">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN14">
         <v>17.5</v>
@@ -4348,25 +4348,25 @@
         <v>17</v>
       </c>
       <c r="AQ14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR14">
         <v>17.5</v>
       </c>
       <c r="AS14">
-        <v>5.5</v>
+        <v>34</v>
       </c>
       <c r="AT14">
         <v>12.5</v>
       </c>
       <c r="AU14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW14">
-        <v>5.1</v>
+        <v>22</v>
       </c>
       <c r="AX14">
         <v>17</v>
@@ -4375,22 +4375,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ14">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>5.3</v>
+        <v>27</v>
       </c>
       <c r="BB14">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="BC14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BD14">
-        <v>5.3</v>
+        <v>27</v>
       </c>
       <c r="BE14">
-        <v>5.7</v>
+        <v>48</v>
       </c>
       <c r="BF14">
         <v>14</v>
@@ -4408,7 +4408,7 @@
         <v>12.5</v>
       </c>
       <c r="BK14">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4420,43 +4420,43 @@
         <v>8.6</v>
       </c>
       <c r="BO14">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP14">
         <v>26</v>
       </c>
       <c r="BQ14">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BR14">
         <v>38</v>
       </c>
       <c r="BS14">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BT14">
         <v>8.6</v>
       </c>
       <c r="BU14">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BV14">
         <v>28</v>
       </c>
       <c r="BW14">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX14">
         <v>38</v>
       </c>
       <c r="BY14">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BZ14">
         <v>26</v>
       </c>
       <c r="CA14">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="CB14" t="s">
         <v>241</v>
@@ -4479,19 +4479,19 @@
         <v>199</v>
       </c>
       <c r="F15">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="G15">
         <v>990</v>
       </c>
       <c r="H15">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="I15">
         <v>990</v>
       </c>
       <c r="J15">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4506,7 +4506,7 @@
         <v>1.1</v>
       </c>
       <c r="O15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
         <v>1.09</v>
@@ -4518,7 +4518,7 @@
         <v>1.08</v>
       </c>
       <c r="S15">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4527,67 +4527,67 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AM15">
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ15">
         <v>1.03</v>
@@ -4599,10 +4599,10 @@
         <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV15">
         <v>1.03</v>
@@ -4611,7 +4611,7 @@
         <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AY15">
         <v>1.03</v>
@@ -4635,10 +4635,10 @@
         <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4721,16 +4721,16 @@
         <v>200</v>
       </c>
       <c r="F16">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G16">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I16">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J16">
         <v>3.4</v>
@@ -4751,7 +4751,7 @@
         <v>1.33</v>
       </c>
       <c r="P16">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -4766,7 +4766,7 @@
         <v>1.77</v>
       </c>
       <c r="U16">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
         <v>1.52</v>
@@ -4784,10 +4784,10 @@
         <v>19</v>
       </c>
       <c r="AA16">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC16">
         <v>7.6</v>
@@ -4796,7 +4796,7 @@
         <v>13</v>
       </c>
       <c r="AE16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF16">
         <v>18.5</v>
@@ -4805,19 +4805,19 @@
         <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI16">
         <v>46</v>
       </c>
       <c r="AJ16">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK16">
         <v>32</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM16">
         <v>95</v>
@@ -4829,16 +4829,16 @@
         <v>28</v>
       </c>
       <c r="AP16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
         <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AT16">
         <v>10.5</v>
@@ -4850,7 +4850,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AX16">
         <v>16.5</v>
@@ -4859,37 +4859,37 @@
         <v>11</v>
       </c>
       <c r="AZ16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BB16">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BC16">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BD16">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BE16">
         <v>55</v>
       </c>
       <c r="BF16">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BG16">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BJ16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK16">
         <v>6.8</v>
@@ -4898,19 +4898,19 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.53</v>
+        <v>3.55</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP16">
         <v>30</v>
       </c>
       <c r="BQ16">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BR16">
         <v>50</v>
@@ -4922,13 +4922,13 @@
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV16">
         <v>32</v>
       </c>
       <c r="BW16">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BX16">
         <v>50</v>
@@ -4940,7 +4940,7 @@
         <v>40</v>
       </c>
       <c r="CA16">
-        <v>1.48</v>
+        <v>3.25</v>
       </c>
       <c r="CB16" t="s">
         <v>241</v>
@@ -4963,7 +4963,7 @@
         <v>201</v>
       </c>
       <c r="F17">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G17">
         <v>2.6</v>
@@ -4972,7 +4972,7 @@
         <v>2.66</v>
       </c>
       <c r="I17">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="J17">
         <v>3.95</v>
@@ -4990,139 +4990,139 @@
         <v>5.7</v>
       </c>
       <c r="O17">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R17">
         <v>1.63</v>
       </c>
       <c r="S17">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U17">
         <v>2.6</v>
       </c>
       <c r="V17">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W17">
         <v>1.62</v>
       </c>
       <c r="X17">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y17">
+        <v>18</v>
+      </c>
+      <c r="Z17">
+        <v>24</v>
+      </c>
+      <c r="AA17">
+        <v>280</v>
+      </c>
+      <c r="AB17">
+        <v>17</v>
+      </c>
+      <c r="AC17">
+        <v>10.5</v>
+      </c>
+      <c r="AD17">
+        <v>13.5</v>
+      </c>
+      <c r="AE17">
+        <v>28</v>
+      </c>
+      <c r="AF17">
+        <v>24</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>15.5</v>
+      </c>
+      <c r="AI17">
+        <v>36</v>
+      </c>
+      <c r="AJ17">
+        <v>38</v>
+      </c>
+      <c r="AK17">
+        <v>25</v>
+      </c>
+      <c r="AL17">
+        <v>32</v>
+      </c>
+      <c r="AM17">
         <v>250</v>
       </c>
-      <c r="Z17">
-        <v>190</v>
-      </c>
-      <c r="AA17">
-        <v>230</v>
-      </c>
-      <c r="AB17">
-        <v>250</v>
-      </c>
-      <c r="AC17">
-        <v>15</v>
-      </c>
-      <c r="AD17">
-        <v>210</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>25</v>
-      </c>
-      <c r="AH17">
-        <v>230</v>
-      </c>
-      <c r="AI17">
-        <v>220</v>
-      </c>
-      <c r="AJ17">
-        <v>230</v>
-      </c>
-      <c r="AK17">
-        <v>200</v>
-      </c>
-      <c r="AL17">
-        <v>210</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP17">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AQ17">
-        <v>1.22</v>
+        <v>14.5</v>
       </c>
       <c r="AR17">
-        <v>2.86</v>
+        <v>19</v>
       </c>
       <c r="AS17">
-        <v>2.96</v>
+        <v>7.4</v>
       </c>
       <c r="AT17">
-        <v>1.22</v>
+        <v>13.5</v>
       </c>
       <c r="AU17">
-        <v>1.14</v>
+        <v>8.6</v>
       </c>
       <c r="AV17">
-        <v>1.22</v>
+        <v>11</v>
       </c>
       <c r="AW17">
-        <v>1.23</v>
+        <v>21</v>
       </c>
       <c r="AX17">
-        <v>1.23</v>
+        <v>17</v>
       </c>
       <c r="AY17">
-        <v>1.17</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BA17">
-        <v>1.22</v>
+        <v>16</v>
       </c>
       <c r="BB17">
-        <v>1.22</v>
+        <v>16</v>
       </c>
       <c r="BC17">
-        <v>1.22</v>
+        <v>11.5</v>
       </c>
       <c r="BD17">
-        <v>1.22</v>
+        <v>14.5</v>
       </c>
       <c r="BE17">
-        <v>1.23</v>
+        <v>23</v>
       </c>
       <c r="BF17">
-        <v>1.23</v>
+        <v>11.5</v>
       </c>
       <c r="BG17">
-        <v>1.23</v>
+        <v>13.5</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5131,7 +5131,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK17">
         <v>1.01</v>
@@ -5143,43 +5143,43 @@
         <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ17">
         <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW17">
         <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY17">
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA17">
         <v>1.01</v>
@@ -5205,7 +5205,7 @@
         <v>202</v>
       </c>
       <c r="F18">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G18">
         <v>2.02</v>
@@ -5217,7 +5217,7 @@
         <v>4.1</v>
       </c>
       <c r="J18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <v>4.4</v>
@@ -5226,7 +5226,7 @@
         <v>1.28</v>
       </c>
       <c r="M18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
         <v>5.6</v>
@@ -5238,7 +5238,7 @@
         <v>2.56</v>
       </c>
       <c r="Q18">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R18">
         <v>1.63</v>
@@ -5250,7 +5250,7 @@
         <v>1.56</v>
       </c>
       <c r="U18">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V18">
         <v>1.32</v>
@@ -5259,16 +5259,16 @@
         <v>1.98</v>
       </c>
       <c r="X18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y18">
         <v>23</v>
       </c>
       <c r="Z18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA18">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB18">
         <v>14.5</v>
@@ -5289,7 +5289,7 @@
         <v>11.5</v>
       </c>
       <c r="AH18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI18">
         <v>46</v>
@@ -5304,13 +5304,13 @@
         <v>30</v>
       </c>
       <c r="AM18">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="AN18">
         <v>8.800000000000001</v>
       </c>
       <c r="AO18">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="AP18">
         <v>19.5</v>
@@ -5319,10 +5319,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AS18">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT18">
         <v>12</v>
@@ -5334,7 +5334,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX18">
         <v>13</v>
@@ -5346,7 +5346,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB18">
         <v>17</v>
@@ -5358,10 +5358,10 @@
         <v>19.5</v>
       </c>
       <c r="BE18">
+        <v>7.8</v>
+      </c>
+      <c r="BF18">
         <v>7.6</v>
-      </c>
-      <c r="BF18">
-        <v>7.4</v>
       </c>
       <c r="BG18">
         <v>21</v>
@@ -5382,7 +5382,7 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN18">
         <v>5.2</v>
@@ -5391,7 +5391,7 @@
         <v>4.5</v>
       </c>
       <c r="BP18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ18">
         <v>6.4</v>
@@ -5400,31 +5400,31 @@
         <v>22</v>
       </c>
       <c r="BS18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT18">
         <v>7.8</v>
       </c>
       <c r="BU18">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ18">
         <v>15</v>
       </c>
       <c r="CA18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB18" t="s">
         <v>241</v>
@@ -5459,7 +5459,7 @@
         <v>3.15</v>
       </c>
       <c r="J19">
-        <v>1.12</v>
+        <v>2.04</v>
       </c>
       <c r="K19">
         <v>5.3</v>
@@ -5471,7 +5471,7 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O19">
         <v>1.12</v>
@@ -5489,10 +5489,10 @@
         <v>2.06</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
         <v>1.47</v>
@@ -5516,7 +5516,7 @@
         <v>1000</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD19">
         <v>1000</v>
@@ -5603,10 +5603,10 @@
         <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5689,22 +5689,22 @@
         <v>204</v>
       </c>
       <c r="F20">
-        <v>1.15</v>
+        <v>1.64</v>
       </c>
       <c r="G20">
         <v>2.48</v>
       </c>
       <c r="H20">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="I20">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J20">
-        <v>1.99</v>
+        <v>2.74</v>
       </c>
       <c r="K20">
-        <v>950</v>
+        <v>480</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5713,13 +5713,13 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O20">
         <v>1.02</v>
       </c>
       <c r="P20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q20">
         <v>1.03</v>
@@ -5737,64 +5737,64 @@
         <v>2</v>
       </c>
       <c r="V20">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
         <v>1.68</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP20">
         <v>1.03</v>
@@ -5812,7 +5812,7 @@
         <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV20">
         <v>1.03</v>
@@ -5845,10 +5845,10 @@
         <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5937,10 +5937,10 @@
         <v>2.28</v>
       </c>
       <c r="H21">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J21">
         <v>3.15</v>
@@ -5961,7 +5961,7 @@
         <v>1.47</v>
       </c>
       <c r="P21">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q21">
         <v>2.36</v>
@@ -5970,13 +5970,13 @@
         <v>1.23</v>
       </c>
       <c r="S21">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T21">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U21">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V21">
         <v>1.3</v>
@@ -5994,7 +5994,7 @@
         <v>30</v>
       </c>
       <c r="AA21">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AB21">
         <v>7.8</v>
@@ -6006,7 +6006,7 @@
         <v>18</v>
       </c>
       <c r="AE21">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="AF21">
         <v>13</v>
@@ -6018,25 +6018,25 @@
         <v>29</v>
       </c>
       <c r="AI21">
-        <v>140</v>
+        <v>370</v>
       </c>
       <c r="AJ21">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AK21">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AL21">
+        <v>290</v>
+      </c>
+      <c r="AM21">
+        <v>660</v>
+      </c>
+      <c r="AN21">
         <v>55</v>
       </c>
-      <c r="AM21">
-        <v>800</v>
-      </c>
-      <c r="AN21">
-        <v>29</v>
-      </c>
       <c r="AO21">
-        <v>810</v>
+        <v>670</v>
       </c>
       <c r="AP21">
         <v>8.800000000000001</v>
@@ -6045,7 +6045,7 @@
         <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AS21">
         <v>10</v>
@@ -6054,13 +6054,13 @@
         <v>6.6</v>
       </c>
       <c r="AU21">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV21">
         <v>15</v>
       </c>
       <c r="AW21">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="AX21">
         <v>11</v>
@@ -6075,13 +6075,13 @@
         <v>10</v>
       </c>
       <c r="BB21">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BC21">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BD21">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="BE21">
         <v>10</v>
@@ -6090,7 +6090,7 @@
         <v>7.8</v>
       </c>
       <c r="BG21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6173,7 +6173,7 @@
         <v>206</v>
       </c>
       <c r="F22">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G22">
         <v>3.2</v>
@@ -6182,10 +6182,10 @@
         <v>2.2</v>
       </c>
       <c r="I22">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J22">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K22">
         <v>5.6</v>
@@ -6194,31 +6194,31 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N22">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="O22">
         <v>1.11</v>
       </c>
       <c r="P22">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="Q22">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="R22">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S22">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="T22">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="U22">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="V22">
         <v>1.66</v>
@@ -6227,112 +6227,112 @@
         <v>1.45</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6445,7 +6445,7 @@
         <v>1.01</v>
       </c>
       <c r="P23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q23">
         <v>1.28</v>
@@ -6657,22 +6657,22 @@
         <v>208</v>
       </c>
       <c r="F24">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="G24">
         <v>990</v>
       </c>
       <c r="H24">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
       <c r="I24">
         <v>990</v>
       </c>
       <c r="J24">
-        <v>1.12</v>
+        <v>2.2</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>480</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6702,67 +6702,67 @@
         <v>1.11</v>
       </c>
       <c r="U24">
-        <v>1.12</v>
+        <v>2.06</v>
       </c>
       <c r="V24">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP24">
         <v>1.03</v>
@@ -6780,7 +6780,7 @@
         <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV24">
         <v>1.03</v>
@@ -6813,10 +6813,10 @@
         <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6902,16 +6902,16 @@
         <v>1.6</v>
       </c>
       <c r="G25">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I25">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J25">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K25">
         <v>4.6</v>
@@ -6929,34 +6929,34 @@
         <v>1.26</v>
       </c>
       <c r="P25">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q25">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R25">
         <v>1.46</v>
       </c>
       <c r="S25">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T25">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V25">
         <v>1.18</v>
       </c>
       <c r="W25">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="X25">
         <v>19.5</v>
       </c>
       <c r="Y25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z25">
         <v>55</v>
@@ -6968,13 +6968,13 @@
         <v>9.4</v>
       </c>
       <c r="AC25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD25">
         <v>25</v>
       </c>
       <c r="AE25">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AF25">
         <v>10.5</v>
@@ -6986,13 +6986,13 @@
         <v>22</v>
       </c>
       <c r="AI25">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ25">
         <v>15.5</v>
       </c>
       <c r="AK25">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL25">
         <v>36</v>
@@ -7007,28 +7007,28 @@
         <v>120</v>
       </c>
       <c r="AP25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR25">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="AS25">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT25">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU25">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV25">
         <v>20</v>
       </c>
       <c r="AW25">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX25">
         <v>9</v>
@@ -7037,46 +7037,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA25">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB25">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE25">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF25">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG25">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI25">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK25">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL25">
         <v>130</v>
       </c>
       <c r="BM25">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BN25">
         <v>4.2</v>
@@ -7085,40 +7085,40 @@
         <v>3.8</v>
       </c>
       <c r="BP25">
+        <v>10.5</v>
+      </c>
+      <c r="BQ25">
+        <v>7.4</v>
+      </c>
+      <c r="BR25">
+        <v>25</v>
+      </c>
+      <c r="BS25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT25">
         <v>10</v>
       </c>
-      <c r="BQ25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR25">
-        <v>24</v>
-      </c>
-      <c r="BS25">
-        <v>11</v>
-      </c>
-      <c r="BT25">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BU25">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BV25">
         <v>55</v>
       </c>
       <c r="BW25">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BX25">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY25">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BZ25">
         <v>17.5</v>
       </c>
       <c r="CA25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB25" t="s">
         <v>241</v>
@@ -7180,13 +7180,13 @@
         <v>1.99</v>
       </c>
       <c r="S26">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="T26">
         <v>1.74</v>
       </c>
       <c r="U26">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
         <v>4.2</v>
@@ -7261,7 +7261,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT26">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU26">
         <v>15</v>
@@ -7273,7 +7273,7 @@
         <v>11</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY26">
         <v>32</v>
@@ -7285,19 +7285,19 @@
         <v>21</v>
       </c>
       <c r="BB26">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BD26">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BE26">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF26">
-        <v>85</v>
+        <v>8.4</v>
       </c>
       <c r="BG26">
         <v>2.9</v>
@@ -7383,22 +7383,22 @@
         <v>211</v>
       </c>
       <c r="F27">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G27">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H27">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="I27">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="J27">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L27">
         <v>1.29</v>
@@ -7407,34 +7407,34 @@
         <v>1.04</v>
       </c>
       <c r="N27">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="O27">
         <v>1.21</v>
       </c>
       <c r="P27">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q27">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R27">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S27">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T27">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U27">
         <v>2.2</v>
       </c>
       <c r="V27">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="W27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X27">
         <v>26</v>
@@ -7464,16 +7464,16 @@
         <v>55</v>
       </c>
       <c r="AG27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH27">
         <v>19</v>
       </c>
       <c r="AI27">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AJ27">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK27">
         <v>75</v>
@@ -7488,61 +7488,61 @@
         <v>70</v>
       </c>
       <c r="AO27">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP27">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AQ27">
+        <v>9.4</v>
+      </c>
+      <c r="AR27">
+        <v>10</v>
+      </c>
+      <c r="AS27">
+        <v>14.5</v>
+      </c>
+      <c r="AT27">
+        <v>18.5</v>
+      </c>
+      <c r="AU27">
+        <v>8.6</v>
+      </c>
+      <c r="AV27">
+        <v>8.6</v>
+      </c>
+      <c r="AW27">
+        <v>14</v>
+      </c>
+      <c r="AX27">
+        <v>9.4</v>
+      </c>
+      <c r="AY27">
+        <v>17</v>
+      </c>
+      <c r="AZ27">
+        <v>15</v>
+      </c>
+      <c r="BA27">
+        <v>9.4</v>
+      </c>
+      <c r="BB27">
         <v>8</v>
       </c>
-      <c r="AR27">
-        <v>4.8</v>
-      </c>
-      <c r="AS27">
-        <v>5.5</v>
-      </c>
-      <c r="AT27">
-        <v>5.9</v>
-      </c>
-      <c r="AU27">
-        <v>4.6</v>
-      </c>
-      <c r="AV27">
+      <c r="BC27">
+        <v>7.6</v>
+      </c>
+      <c r="BD27">
+        <v>7.6</v>
+      </c>
+      <c r="BE27">
+        <v>7.8</v>
+      </c>
+      <c r="BF27">
         <v>7.4</v>
       </c>
-      <c r="AW27">
-        <v>5.4</v>
-      </c>
-      <c r="AX27">
+      <c r="BG27">
         <v>6.8</v>
-      </c>
-      <c r="AY27">
-        <v>5.8</v>
-      </c>
-      <c r="AZ27">
-        <v>5.6</v>
-      </c>
-      <c r="BA27">
-        <v>6.2</v>
-      </c>
-      <c r="BB27">
-        <v>7.4</v>
-      </c>
-      <c r="BC27">
-        <v>7</v>
-      </c>
-      <c r="BD27">
-        <v>7</v>
-      </c>
-      <c r="BE27">
-        <v>7.2</v>
-      </c>
-      <c r="BF27">
-        <v>7</v>
-      </c>
-      <c r="BG27">
-        <v>5.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7554,7 +7554,7 @@
         <v>13</v>
       </c>
       <c r="BK27">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BL27">
         <v>1000</v>
@@ -7563,7 +7563,7 @@
         <v>2.04</v>
       </c>
       <c r="BN27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BO27">
         <v>1.75</v>
@@ -7572,37 +7572,37 @@
         <v>1000</v>
       </c>
       <c r="BQ27">
+        <v>1.96</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
         <v>1.97</v>
-      </c>
-      <c r="BR27">
-        <v>1000</v>
-      </c>
-      <c r="BS27">
-        <v>1.98</v>
       </c>
       <c r="BT27">
         <v>6</v>
       </c>
       <c r="BU27">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="BV27">
         <v>15</v>
       </c>
       <c r="BW27">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="BX27">
         <v>30</v>
       </c>
       <c r="BY27">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BZ27">
         <v>21</v>
       </c>
       <c r="CA27">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CB27" t="s">
         <v>241</v>
@@ -7625,22 +7625,22 @@
         <v>212</v>
       </c>
       <c r="F28">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="G28">
-        <v>990</v>
+        <v>2.84</v>
       </c>
       <c r="H28">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="J28">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="K28">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7649,22 +7649,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.27</v>
+        <v>3.2</v>
       </c>
       <c r="O28">
         <v>1.36</v>
       </c>
       <c r="P28">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Q28">
         <v>1.38</v>
       </c>
       <c r="R28">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="T28">
         <v>1.11</v>
@@ -7673,10 +7673,10 @@
         <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7733,58 +7733,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7867,22 +7867,22 @@
         <v>213</v>
       </c>
       <c r="F29">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G29">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="H29">
         <v>5.1</v>
       </c>
       <c r="I29">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J29">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K29">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7891,10 +7891,10 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O29">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P29">
         <v>2.18</v>
@@ -7909,16 +7909,16 @@
         <v>2.06</v>
       </c>
       <c r="T29">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="U29">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V29">
         <v>1.16</v>
       </c>
       <c r="W29">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7945,10 +7945,10 @@
         <v>1000</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH29">
         <v>1000</v>
@@ -7957,10 +7957,10 @@
         <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL29">
         <v>1000</v>
@@ -8026,7 +8026,7 @@
         <v>3.75</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8109,22 +8109,22 @@
         <v>214</v>
       </c>
       <c r="F30">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="G30">
         <v>990</v>
       </c>
       <c r="H30">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="I30">
         <v>990</v>
       </c>
       <c r="J30">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="K30">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8139,7 +8139,7 @@
         <v>1.01</v>
       </c>
       <c r="P30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q30">
         <v>1.27</v>
@@ -8148,7 +8148,7 @@
         <v>1.08</v>
       </c>
       <c r="S30">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T30">
         <v>1.11</v>
@@ -8157,7 +8157,7 @@
         <v>1.11</v>
       </c>
       <c r="V30">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="W30">
         <v>1.1</v>
@@ -8217,10 +8217,10 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
         <v>16</v>
@@ -8247,7 +8247,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ30">
-        <v>1.98</v>
+        <v>16</v>
       </c>
       <c r="BA30">
         <v>1.03</v>
@@ -8256,7 +8256,7 @@
         <v>12</v>
       </c>
       <c r="BC30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
         <v>24</v>
@@ -8265,7 +8265,7 @@
         <v>16</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BG30">
         <v>1.01</v>
@@ -8351,19 +8351,19 @@
         <v>215</v>
       </c>
       <c r="F31">
-        <v>1.1</v>
+        <v>1.68</v>
       </c>
       <c r="G31">
         <v>990</v>
       </c>
       <c r="H31">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="I31">
         <v>990</v>
       </c>
       <c r="J31">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K31">
         <v>950</v>
@@ -8375,13 +8375,13 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O31">
         <v>1.22</v>
       </c>
       <c r="P31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q31">
         <v>1.33</v>
@@ -8390,7 +8390,7 @@
         <v>1.07</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>1.27</v>
       </c>
       <c r="T31">
         <v>1.11</v>
@@ -8399,10 +8399,10 @@
         <v>1.11</v>
       </c>
       <c r="V31">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W31">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8441,7 +8441,7 @@
         <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK31">
         <v>1000</v>
@@ -8507,10 +8507,10 @@
         <v>1.03</v>
       </c>
       <c r="BF31">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8617,22 +8617,22 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O32">
         <v>1.21</v>
       </c>
       <c r="P32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q32">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R32">
         <v>1.08</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>2.46</v>
       </c>
       <c r="T32">
         <v>1.11</v>
@@ -8835,22 +8835,22 @@
         <v>217</v>
       </c>
       <c r="F33">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G33">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="H33">
-        <v>1.56</v>
+        <v>2.84</v>
       </c>
       <c r="I33">
-        <v>990</v>
+        <v>23</v>
       </c>
       <c r="J33">
-        <v>1.84</v>
+        <v>2.96</v>
       </c>
       <c r="K33">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8859,13 +8859,13 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O33">
         <v>1.02</v>
       </c>
       <c r="P33">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q33">
         <v>1.03</v>
@@ -8883,10 +8883,10 @@
         <v>1.11</v>
       </c>
       <c r="V33">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="W33">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -8913,10 +8913,10 @@
         <v>1000</v>
       </c>
       <c r="AF33">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG33">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH33">
         <v>1000</v>
@@ -8925,10 +8925,10 @@
         <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK33">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL33">
         <v>1000</v>
@@ -8991,10 +8991,10 @@
         <v>1.03</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BG33">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9083,7 +9083,7 @@
         <v>1.81</v>
       </c>
       <c r="H34">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I34">
         <v>7.6</v>
@@ -9092,7 +9092,7 @@
         <v>3.8</v>
       </c>
       <c r="K34">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -9337,7 +9337,7 @@
         <v>3.65</v>
       </c>
       <c r="L35">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M35">
         <v>1.07</v>
@@ -9388,13 +9388,13 @@
         <v>12.5</v>
       </c>
       <c r="AC35">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE35">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF35">
         <v>19</v>
@@ -9403,7 +9403,7 @@
         <v>13</v>
       </c>
       <c r="AH35">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI35">
         <v>120</v>
@@ -9412,7 +9412,7 @@
         <v>110</v>
       </c>
       <c r="AK35">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL35">
         <v>120</v>
@@ -9421,10 +9421,10 @@
         <v>1000</v>
       </c>
       <c r="AN35">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AO35">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP35">
         <v>13</v>
@@ -9439,7 +9439,7 @@
         <v>24</v>
       </c>
       <c r="AT35">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU35">
         <v>7</v>
@@ -9451,7 +9451,7 @@
         <v>19</v>
       </c>
       <c r="AX35">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY35">
         <v>10.5</v>
@@ -9460,10 +9460,10 @@
         <v>14</v>
       </c>
       <c r="BA35">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BB35">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC35">
         <v>19.5</v>
@@ -9472,13 +9472,13 @@
         <v>30</v>
       </c>
       <c r="BE35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BF35">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG35">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9564,10 +9564,10 @@
         <v>1.62</v>
       </c>
       <c r="G36">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="H36">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="I36">
         <v>8.199999999999999</v>
@@ -9639,10 +9639,10 @@
         <v>1000</v>
       </c>
       <c r="AF36">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH36">
         <v>1000</v>
@@ -9651,10 +9651,10 @@
         <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL36">
         <v>1000</v>
@@ -9669,58 +9669,58 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AR36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT36">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AV36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AW36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AX36">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AY36">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AZ36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BA36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BB36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC36">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9812,7 +9812,7 @@
         <v>3.45</v>
       </c>
       <c r="I37">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J37">
         <v>3.4</v>
@@ -9821,28 +9821,28 @@
         <v>3.5</v>
       </c>
       <c r="L37">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M37">
         <v>1.08</v>
       </c>
       <c r="N37">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O37">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P37">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q37">
         <v>2.12</v>
       </c>
       <c r="R37">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S37">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T37">
         <v>1.87</v>
@@ -9851,13 +9851,13 @@
         <v>2.08</v>
       </c>
       <c r="V37">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
         <v>1.72</v>
       </c>
       <c r="X37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y37">
         <v>12.5</v>
@@ -9878,7 +9878,7 @@
         <v>15</v>
       </c>
       <c r="AE37">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF37">
         <v>14.5</v>
@@ -9899,7 +9899,7 @@
         <v>28</v>
       </c>
       <c r="AL37">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM37">
         <v>110</v>
@@ -9908,7 +9908,7 @@
         <v>23</v>
       </c>
       <c r="AO37">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP37">
         <v>11</v>
@@ -9929,7 +9929,7 @@
         <v>7</v>
       </c>
       <c r="AV37">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW37">
         <v>38</v>
@@ -9956,73 +9956,73 @@
         <v>38</v>
       </c>
       <c r="BE37">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF37">
         <v>19.5</v>
       </c>
       <c r="BG37">
+        <v>38</v>
+      </c>
+      <c r="BH37">
+        <v>3.15</v>
+      </c>
+      <c r="BI37">
+        <v>2.94</v>
+      </c>
+      <c r="BJ37">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK37">
+        <v>8.6</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>14.5</v>
+      </c>
+      <c r="BN37">
+        <v>5.2</v>
+      </c>
+      <c r="BO37">
+        <v>4.6</v>
+      </c>
+      <c r="BP37">
+        <v>18</v>
+      </c>
+      <c r="BQ37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR37">
         <v>34</v>
       </c>
-      <c r="BH37">
-        <v>3.5</v>
-      </c>
-      <c r="BI37">
-        <v>2.72</v>
-      </c>
-      <c r="BJ37">
+      <c r="BS37">
+        <v>11</v>
+      </c>
+      <c r="BT37">
+        <v>6.6</v>
+      </c>
+      <c r="BU37">
+        <v>5.8</v>
+      </c>
+      <c r="BV37">
+        <v>29</v>
+      </c>
+      <c r="BW37">
+        <v>10.5</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
         <v>11.5</v>
       </c>
-      <c r="BK37">
-        <v>8</v>
-      </c>
-      <c r="BL37">
-        <v>1000</v>
-      </c>
-      <c r="BM37">
-        <v>6</v>
-      </c>
-      <c r="BN37">
-        <v>6</v>
-      </c>
-      <c r="BO37">
-        <v>4.1</v>
-      </c>
-      <c r="BP37">
-        <v>21</v>
-      </c>
-      <c r="BQ37">
-        <v>4.6</v>
-      </c>
-      <c r="BR37">
-        <v>40</v>
-      </c>
-      <c r="BS37">
-        <v>5.2</v>
-      </c>
-      <c r="BT37">
-        <v>7.4</v>
-      </c>
-      <c r="BU37">
-        <v>5.6</v>
-      </c>
-      <c r="BV37">
-        <v>34</v>
-      </c>
-      <c r="BW37">
-        <v>5.1</v>
-      </c>
-      <c r="BX37">
-        <v>1000</v>
-      </c>
-      <c r="BY37">
-        <v>5.3</v>
-      </c>
       <c r="BZ37">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="CA37">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="CB37" t="s">
         <v>241</v>
@@ -10045,19 +10045,19 @@
         <v>222</v>
       </c>
       <c r="F38">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G38">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H38">
         <v>12.5</v>
       </c>
       <c r="I38">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J38">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K38">
         <v>7.8</v>
@@ -10069,7 +10069,7 @@
         <v>1.02</v>
       </c>
       <c r="N38">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O38">
         <v>1.13</v>
@@ -10081,28 +10081,28 @@
         <v>1.4</v>
       </c>
       <c r="R38">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S38">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T38">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U38">
         <v>2.06</v>
       </c>
       <c r="V38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W38">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X38">
         <v>40</v>
       </c>
       <c r="Y38">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z38">
         <v>170</v>
@@ -10114,19 +10114,19 @@
         <v>13.5</v>
       </c>
       <c r="AC38">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AD38">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AE38">
         <v>180</v>
       </c>
       <c r="AF38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG38">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH38">
         <v>29</v>
@@ -10135,7 +10135,7 @@
         <v>1000</v>
       </c>
       <c r="AJ38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK38">
         <v>13.5</v>
@@ -10156,7 +10156,7 @@
         <v>34</v>
       </c>
       <c r="AQ38">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AR38">
         <v>42</v>
@@ -10168,10 +10168,10 @@
         <v>12.5</v>
       </c>
       <c r="AU38">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AV38">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AW38">
         <v>44</v>
@@ -10195,13 +10195,13 @@
         <v>11.5</v>
       </c>
       <c r="BD38">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE38">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BF38">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG38">
         <v>44</v>
@@ -10287,10 +10287,10 @@
         <v>223</v>
       </c>
       <c r="F39">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G39">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H39">
         <v>6</v>
@@ -10308,22 +10308,22 @@
         <v>1.59</v>
       </c>
       <c r="M39">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N39">
         <v>2.72</v>
       </c>
       <c r="O39">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P39">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q39">
         <v>2.62</v>
       </c>
       <c r="R39">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S39">
         <v>5.4</v>
@@ -10341,7 +10341,7 @@
         <v>2.22</v>
       </c>
       <c r="X39">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>15</v>
@@ -10452,10 +10452,10 @@
         <v>2.72</v>
       </c>
       <c r="BI39">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ39">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BK39">
         <v>10.5</v>
@@ -10464,16 +10464,16 @@
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BN39">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BO39">
         <v>3.65</v>
       </c>
       <c r="BP39">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BQ39">
         <v>11</v>
@@ -10482,31 +10482,31 @@
         <v>46</v>
       </c>
       <c r="BS39">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT39">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU39">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV39">
         <v>90</v>
       </c>
       <c r="BW39">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BX39">
         <v>110</v>
       </c>
       <c r="BY39">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ39">
         <v>44</v>
       </c>
       <c r="CA39">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB39" t="s">
         <v>241</v>
@@ -10529,58 +10529,58 @@
         <v>224</v>
       </c>
       <c r="F40">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="G40">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="H40">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J40">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K40">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="L40">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M40">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N40">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="O40">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="P40">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Q40">
         <v>2.06</v>
       </c>
       <c r="R40">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S40">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T40">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U40">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V40">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W40">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10619,10 +10619,10 @@
         <v>1000</v>
       </c>
       <c r="AJ40">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK40">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL40">
         <v>1000</v>
@@ -10637,64 +10637,64 @@
         <v>1000</v>
       </c>
       <c r="AP40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40">
         <v>1.01</v>
       </c>
       <c r="BG40">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BH40">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI40">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
@@ -10771,31 +10771,31 @@
         <v>225</v>
       </c>
       <c r="F41">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="G41">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H41">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I41">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J41">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K41">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L41">
         <v>1.49</v>
       </c>
       <c r="M41">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N41">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="O41">
         <v>1.46</v>
@@ -10807,16 +10807,16 @@
         <v>2.36</v>
       </c>
       <c r="R41">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S41">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T41">
         <v>1.98</v>
       </c>
       <c r="U41">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="V41">
         <v>1.56</v>
@@ -10825,118 +10825,118 @@
         <v>1.43</v>
       </c>
       <c r="X41">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y41">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="Z41">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA41">
-        <v>880</v>
+        <v>740</v>
       </c>
       <c r="AB41">
         <v>10.5</v>
       </c>
       <c r="AC41">
+        <v>7.4</v>
+      </c>
+      <c r="AD41">
+        <v>13</v>
+      </c>
+      <c r="AE41">
+        <v>44</v>
+      </c>
+      <c r="AF41">
+        <v>21</v>
+      </c>
+      <c r="AG41">
+        <v>14.5</v>
+      </c>
+      <c r="AH41">
+        <v>21</v>
+      </c>
+      <c r="AI41">
+        <v>70</v>
+      </c>
+      <c r="AJ41">
+        <v>900</v>
+      </c>
+      <c r="AK41">
+        <v>50</v>
+      </c>
+      <c r="AL41">
+        <v>70</v>
+      </c>
+      <c r="AM41">
+        <v>810</v>
+      </c>
+      <c r="AN41">
+        <v>65</v>
+      </c>
+      <c r="AO41">
+        <v>46</v>
+      </c>
+      <c r="AP41">
         <v>8.6</v>
       </c>
-      <c r="AD41">
+      <c r="AQ41">
+        <v>7.6</v>
+      </c>
+      <c r="AR41">
         <v>14</v>
       </c>
-      <c r="AE41">
-        <v>36</v>
-      </c>
-      <c r="AF41">
-        <v>23</v>
-      </c>
-      <c r="AG41">
-        <v>16</v>
-      </c>
-      <c r="AH41">
-        <v>22</v>
-      </c>
-      <c r="AI41">
-        <v>60</v>
-      </c>
-      <c r="AJ41">
-        <v>870</v>
-      </c>
-      <c r="AK41">
-        <v>870</v>
-      </c>
-      <c r="AL41">
-        <v>85</v>
-      </c>
-      <c r="AM41">
-        <v>900</v>
-      </c>
-      <c r="AN41">
-        <v>55</v>
-      </c>
-      <c r="AO41">
+      <c r="AS41">
+        <v>30</v>
+      </c>
+      <c r="AT41">
+        <v>8.6</v>
+      </c>
+      <c r="AU41">
+        <v>6.2</v>
+      </c>
+      <c r="AV41">
+        <v>11</v>
+      </c>
+      <c r="AW41">
+        <v>26</v>
+      </c>
+      <c r="AX41">
+        <v>16.5</v>
+      </c>
+      <c r="AY41">
+        <v>12</v>
+      </c>
+      <c r="AZ41">
+        <v>15.5</v>
+      </c>
+      <c r="BA41">
+        <v>10</v>
+      </c>
+      <c r="BB41">
+        <v>8.6</v>
+      </c>
+      <c r="BC41">
+        <v>34</v>
+      </c>
+      <c r="BD41">
+        <v>10.5</v>
+      </c>
+      <c r="BE41">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF41">
         <v>38</v>
       </c>
-      <c r="AP41">
-        <v>7.8</v>
-      </c>
-      <c r="AQ41">
-        <v>6.8</v>
-      </c>
-      <c r="AR41">
-        <v>12</v>
-      </c>
-      <c r="AS41">
-        <v>5</v>
-      </c>
-      <c r="AT41">
-        <v>7.6</v>
-      </c>
-      <c r="AU41">
-        <v>5.7</v>
-      </c>
-      <c r="AV41">
-        <v>9.4</v>
-      </c>
-      <c r="AW41">
-        <v>4.8</v>
-      </c>
-      <c r="AX41">
-        <v>15</v>
-      </c>
-      <c r="AY41">
-        <v>11</v>
-      </c>
-      <c r="AZ41">
-        <v>15</v>
-      </c>
-      <c r="BA41">
-        <v>5.1</v>
-      </c>
-      <c r="BB41">
-        <v>5.2</v>
-      </c>
-      <c r="BC41">
-        <v>5.1</v>
-      </c>
-      <c r="BD41">
-        <v>5.2</v>
-      </c>
-      <c r="BE41">
-        <v>4.3</v>
-      </c>
-      <c r="BF41">
-        <v>5.1</v>
-      </c>
       <c r="BG41">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="BH41">
         <v>3.45</v>
       </c>
       <c r="BI41">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ41">
         <v>15</v>
@@ -10954,7 +10954,7 @@
         <v>8.6</v>
       </c>
       <c r="BO41">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP41">
         <v>40</v>
@@ -11013,10 +11013,10 @@
         <v>226</v>
       </c>
       <c r="F42">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G42">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H42">
         <v>3.2</v>
@@ -11025,61 +11025,61 @@
         <v>3.3</v>
       </c>
       <c r="J42">
+        <v>3.45</v>
+      </c>
+      <c r="K42">
         <v>3.55</v>
-      </c>
-      <c r="K42">
-        <v>3.6</v>
       </c>
       <c r="L42">
         <v>1.4</v>
       </c>
       <c r="M42">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N42">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O42">
         <v>1.3</v>
       </c>
       <c r="P42">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q42">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R42">
         <v>1.42</v>
       </c>
       <c r="S42">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T42">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="U42">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
         <v>1.43</v>
       </c>
       <c r="W42">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X42">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z42">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA42">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB42">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC42">
         <v>8.199999999999999</v>
@@ -11088,7 +11088,7 @@
         <v>14.5</v>
       </c>
       <c r="AE42">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF42">
         <v>16.5</v>
@@ -11097,7 +11097,7 @@
         <v>11.5</v>
       </c>
       <c r="AH42">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI42">
         <v>55</v>
@@ -11118,25 +11118,25 @@
         <v>17.5</v>
       </c>
       <c r="AO42">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP42">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ42">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR42">
         <v>20</v>
       </c>
       <c r="AS42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT42">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU42">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV42">
         <v>13</v>
@@ -11145,28 +11145,28 @@
         <v>10.5</v>
       </c>
       <c r="AX42">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY42">
         <v>10</v>
       </c>
       <c r="AZ42">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA42">
         <v>36</v>
       </c>
       <c r="BB42">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC42">
         <v>21</v>
       </c>
       <c r="BD42">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE42">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF42">
         <v>14</v>
@@ -11184,7 +11184,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK42">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL42">
         <v>1000</v>
@@ -11193,7 +11193,7 @@
         <v>21</v>
       </c>
       <c r="BN42">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO42">
         <v>4.9</v>
@@ -11255,13 +11255,13 @@
         <v>227</v>
       </c>
       <c r="F43">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G43">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H43">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I43">
         <v>34</v>
@@ -11291,31 +11291,31 @@
         <v>1.3</v>
       </c>
       <c r="R43">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="S43">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="T43">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U43">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V43">
         <v>1.03</v>
       </c>
       <c r="W43">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="X43">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y43">
         <v>110</v>
       </c>
       <c r="Z43">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AA43">
         <v>1000</v>
@@ -11330,7 +11330,7 @@
         <v>110</v>
       </c>
       <c r="AE43">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AF43">
         <v>11</v>
@@ -11351,10 +11351,10 @@
         <v>16.5</v>
       </c>
       <c r="AL43">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM43">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN43">
         <v>2.74</v>
@@ -11363,28 +11363,28 @@
         <v>600</v>
       </c>
       <c r="AP43">
-        <v>36</v>
+        <v>6.2</v>
       </c>
       <c r="AQ43">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR43">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS43">
         <v>7</v>
       </c>
       <c r="AT43">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV43">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW43">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX43">
         <v>7.8</v>
@@ -11393,10 +11393,10 @@
         <v>12</v>
       </c>
       <c r="AZ43">
-        <v>36</v>
+        <v>6.2</v>
       </c>
       <c r="BA43">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB43">
         <v>7.4</v>
@@ -11405,16 +11405,16 @@
         <v>12.5</v>
       </c>
       <c r="BD43">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BE43">
         <v>6.8</v>
       </c>
       <c r="BF43">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BG43">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -11500,13 +11500,13 @@
         <v>2.28</v>
       </c>
       <c r="G44">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H44">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I44">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J44">
         <v>3.1</v>
@@ -11515,7 +11515,7 @@
         <v>3.3</v>
       </c>
       <c r="L44">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M44">
         <v>1.11</v>
@@ -11530,7 +11530,7 @@
         <v>1.66</v>
       </c>
       <c r="Q44">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
         <v>1.25</v>
@@ -11539,7 +11539,7 @@
         <v>4.6</v>
       </c>
       <c r="T44">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U44">
         <v>1.9</v>
@@ -11563,7 +11563,7 @@
         <v>95</v>
       </c>
       <c r="AB44">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC44">
         <v>7.4</v>
@@ -11578,7 +11578,7 @@
         <v>14</v>
       </c>
       <c r="AG44">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH44">
         <v>22</v>
@@ -11596,7 +11596,7 @@
         <v>55</v>
       </c>
       <c r="AM44">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN44">
         <v>29</v>
@@ -11611,10 +11611,10 @@
         <v>10</v>
       </c>
       <c r="AR44">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS44">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT44">
         <v>7.2</v>
@@ -11626,7 +11626,7 @@
         <v>14</v>
       </c>
       <c r="AW44">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="AX44">
         <v>12</v>
@@ -11638,25 +11638,25 @@
         <v>18</v>
       </c>
       <c r="BA44">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB44">
+        <v>7.8</v>
+      </c>
+      <c r="BC44">
+        <v>7.8</v>
+      </c>
+      <c r="BD44">
+        <v>8.4</v>
+      </c>
+      <c r="BE44">
         <v>9.6</v>
       </c>
-      <c r="BB44">
-        <v>24</v>
-      </c>
-      <c r="BC44">
-        <v>21</v>
-      </c>
-      <c r="BD44">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE44">
-        <v>10</v>
-      </c>
       <c r="BF44">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BG44">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -11739,10 +11739,10 @@
         <v>229</v>
       </c>
       <c r="F45">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G45">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H45">
         <v>3.1</v>
@@ -11751,58 +11751,58 @@
         <v>3.25</v>
       </c>
       <c r="J45">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K45">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L45">
         <v>1.52</v>
       </c>
       <c r="M45">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N45">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="O45">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P45">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q45">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R45">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S45">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T45">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U45">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V45">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W45">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X45">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y45">
         <v>9.4</v>
       </c>
       <c r="Z45">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA45">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="AB45">
         <v>8.6</v>
@@ -11811,25 +11811,25 @@
         <v>7.2</v>
       </c>
       <c r="AD45">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE45">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF45">
         <v>16.5</v>
       </c>
       <c r="AG45">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH45">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI45">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ45">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK45">
         <v>40</v>
@@ -11838,22 +11838,22 @@
         <v>65</v>
       </c>
       <c r="AM45">
-        <v>860</v>
+        <v>1000</v>
       </c>
       <c r="AN45">
         <v>44</v>
       </c>
       <c r="AO45">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP45">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ45">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR45">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS45">
         <v>28</v>
@@ -11868,10 +11868,10 @@
         <v>13</v>
       </c>
       <c r="AW45">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AX45">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY45">
         <v>11.5</v>
@@ -11880,25 +11880,25 @@
         <v>19</v>
       </c>
       <c r="BA45">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB45">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC45">
+        <v>28</v>
+      </c>
+      <c r="BD45">
+        <v>44</v>
+      </c>
+      <c r="BE45">
+        <v>80</v>
+      </c>
+      <c r="BF45">
         <v>32</v>
       </c>
-      <c r="BD45">
-        <v>32</v>
-      </c>
-      <c r="BE45">
-        <v>44</v>
-      </c>
-      <c r="BF45">
-        <v>36</v>
-      </c>
       <c r="BG45">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BH45">
         <v>1000</v>
@@ -11981,58 +11981,58 @@
         <v>230</v>
       </c>
       <c r="F46">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G46">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H46">
         <v>3.9</v>
       </c>
       <c r="I46">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J46">
         <v>4.1</v>
       </c>
       <c r="K46">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L46">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M46">
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P46">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q46">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="R46">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="S46">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="T46">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U46">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V46">
         <v>1.26</v>
       </c>
       <c r="W46">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X46">
         <v>34</v>
@@ -12044,7 +12044,7 @@
         <v>46</v>
       </c>
       <c r="AA46">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB46">
         <v>17</v>
@@ -12101,37 +12101,37 @@
         <v>1.03</v>
       </c>
       <c r="AT46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU46">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV46">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW46">
         <v>1.03</v>
       </c>
       <c r="AX46">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY46">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ46">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA46">
         <v>1.03</v>
       </c>
       <c r="BB46">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC46">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD46">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE46">
         <v>1.03</v>
@@ -12223,7 +12223,7 @@
         <v>231</v>
       </c>
       <c r="F47">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -12232,157 +12232,157 @@
         <v>4.2</v>
       </c>
       <c r="I47">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J47">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K47">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M47">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N47">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O47">
         <v>1.28</v>
       </c>
       <c r="P47">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q47">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="R47">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S47">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="T47">
-        <v>1.02</v>
+        <v>1.7</v>
       </c>
       <c r="U47">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V47">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W47">
         <v>2</v>
       </c>
       <c r="X47">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y47">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Z47">
         <v>50</v>
       </c>
       <c r="AA47">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB47">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC47">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD47">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AE47">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF47">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AG47">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH47">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AI47">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ47">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AK47">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL47">
         <v>50</v>
       </c>
       <c r="AM47">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN47">
+        <v>13</v>
+      </c>
+      <c r="AO47">
+        <v>500</v>
+      </c>
+      <c r="AP47">
+        <v>11.5</v>
+      </c>
+      <c r="AQ47">
+        <v>14</v>
+      </c>
+      <c r="AR47">
+        <v>21</v>
+      </c>
+      <c r="AS47">
+        <v>8</v>
+      </c>
+      <c r="AT47">
+        <v>7.8</v>
+      </c>
+      <c r="AU47">
+        <v>7.4</v>
+      </c>
+      <c r="AV47">
+        <v>15.5</v>
+      </c>
+      <c r="AW47">
+        <v>7.6</v>
+      </c>
+      <c r="AX47">
+        <v>10</v>
+      </c>
+      <c r="AY47">
+        <v>8.6</v>
+      </c>
+      <c r="AZ47">
+        <v>15.5</v>
+      </c>
+      <c r="BA47">
+        <v>7.6</v>
+      </c>
+      <c r="BB47">
         <v>17.5</v>
       </c>
-      <c r="AO47">
-        <v>85</v>
-      </c>
-      <c r="AP47">
-        <v>1.03</v>
-      </c>
-      <c r="AQ47">
-        <v>11</v>
-      </c>
-      <c r="AR47">
-        <v>1.03</v>
-      </c>
-      <c r="AS47">
-        <v>1.01</v>
-      </c>
-      <c r="AT47">
-        <v>6</v>
-      </c>
-      <c r="AU47">
-        <v>5.7</v>
-      </c>
-      <c r="AV47">
-        <v>11.5</v>
-      </c>
-      <c r="AW47">
-        <v>1.01</v>
-      </c>
-      <c r="AX47">
+      <c r="BC47">
+        <v>16.5</v>
+      </c>
+      <c r="BD47">
+        <v>21</v>
+      </c>
+      <c r="BE47">
+        <v>8</v>
+      </c>
+      <c r="BF47">
+        <v>10</v>
+      </c>
+      <c r="BG47">
         <v>7.6</v>
-      </c>
-      <c r="AY47">
-        <v>6.6</v>
-      </c>
-      <c r="AZ47">
-        <v>11.5</v>
-      </c>
-      <c r="BA47">
-        <v>1.01</v>
-      </c>
-      <c r="BB47">
-        <v>13</v>
-      </c>
-      <c r="BC47">
-        <v>12</v>
-      </c>
-      <c r="BD47">
-        <v>1.03</v>
-      </c>
-      <c r="BE47">
-        <v>1.01</v>
-      </c>
-      <c r="BF47">
-        <v>7.8</v>
-      </c>
-      <c r="BG47">
-        <v>1.01</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12465,22 +12465,22 @@
         <v>232</v>
       </c>
       <c r="F48">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G48">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H48">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="I48">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J48">
         <v>2.8</v>
       </c>
       <c r="K48">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L48">
         <v>1.01</v>
@@ -12489,88 +12489,88 @@
         <v>1.01</v>
       </c>
       <c r="N48">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="P48">
         <v>1.45</v>
       </c>
       <c r="Q48">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R48">
         <v>1.15</v>
       </c>
       <c r="S48">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="T48">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U48">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V48">
+        <v>1.49</v>
+      </c>
+      <c r="W48">
         <v>1.45</v>
       </c>
-      <c r="W48">
-        <v>1.42</v>
-      </c>
       <c r="X48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA48">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ48">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP48">
         <v>1.03</v>
@@ -12579,7 +12579,7 @@
         <v>1.03</v>
       </c>
       <c r="AR48">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS48">
         <v>1.03</v>
@@ -12588,10 +12588,10 @@
         <v>1.03</v>
       </c>
       <c r="AU48">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV48">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW48">
         <v>1.03</v>
@@ -12600,7 +12600,7 @@
         <v>1.03</v>
       </c>
       <c r="AY48">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ48">
         <v>1.03</v>
@@ -12621,10 +12621,10 @@
         <v>1.03</v>
       </c>
       <c r="BF48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -12725,19 +12725,19 @@
         <v>3.4</v>
       </c>
       <c r="L49">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M49">
         <v>1.08</v>
       </c>
       <c r="N49">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O49">
         <v>1.36</v>
       </c>
       <c r="P49">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q49">
         <v>2.06</v>
@@ -12779,7 +12779,7 @@
         <v>7.4</v>
       </c>
       <c r="AD49">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE49">
         <v>32</v>
@@ -12794,7 +12794,7 @@
         <v>17.5</v>
       </c>
       <c r="AI49">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ49">
         <v>48</v>
@@ -12806,7 +12806,7 @@
         <v>55</v>
       </c>
       <c r="AM49">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AN49">
         <v>32</v>
@@ -12833,7 +12833,7 @@
         <v>6.4</v>
       </c>
       <c r="AV49">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW49">
         <v>28</v>
@@ -12857,10 +12857,10 @@
         <v>30</v>
       </c>
       <c r="BD49">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BE49">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="BF49">
         <v>26</v>
@@ -12884,7 +12884,7 @@
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN49">
         <v>6.2</v>
@@ -12896,7 +12896,7 @@
         <v>24</v>
       </c>
       <c r="BQ49">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR49">
         <v>44</v>
@@ -12914,7 +12914,7 @@
         <v>21</v>
       </c>
       <c r="BW49">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX49">
         <v>36</v>
@@ -12926,7 +12926,7 @@
         <v>34</v>
       </c>
       <c r="CA49">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB49" t="s">
         <v>241</v>
@@ -12949,7 +12949,7 @@
         <v>234</v>
       </c>
       <c r="F50">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G50">
         <v>1.88</v>
@@ -12958,13 +12958,13 @@
         <v>5</v>
       </c>
       <c r="I50">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J50">
         <v>3.65</v>
       </c>
       <c r="K50">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L50">
         <v>1.38</v>
@@ -13009,7 +13009,7 @@
         <v>21</v>
       </c>
       <c r="Z50">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA50">
         <v>160</v>
@@ -13042,7 +13042,7 @@
         <v>24</v>
       </c>
       <c r="AK50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL50">
         <v>46</v>
@@ -13051,7 +13051,7 @@
         <v>150</v>
       </c>
       <c r="AN50">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO50">
         <v>110</v>
@@ -13063,10 +13063,10 @@
         <v>14.5</v>
       </c>
       <c r="AR50">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS50">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT50">
         <v>7.4</v>
@@ -13078,7 +13078,7 @@
         <v>17.5</v>
       </c>
       <c r="AW50">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX50">
         <v>9.6</v>
@@ -13087,10 +13087,10 @@
         <v>9</v>
       </c>
       <c r="AZ50">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA50">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB50">
         <v>17</v>
@@ -13099,10 +13099,10 @@
         <v>17.5</v>
       </c>
       <c r="BD50">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE50">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF50">
         <v>11</v>
@@ -13114,19 +13114,19 @@
         <v>1000</v>
       </c>
       <c r="BI50">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="BJ50">
         <v>15</v>
       </c>
       <c r="BK50">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="BN50">
         <v>6</v>
@@ -13138,16 +13138,16 @@
         <v>18.5</v>
       </c>
       <c r="BQ50">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="BR50">
         <v>40</v>
       </c>
       <c r="BS50">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="BT50">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BU50">
         <v>5.3</v>
@@ -13156,19 +13156,19 @@
         <v>1000</v>
       </c>
       <c r="BW50">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="BX50">
         <v>1000</v>
       </c>
       <c r="BY50">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="BZ50">
         <v>34</v>
       </c>
       <c r="CA50">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="CB50" t="s">
         <v>241</v>
@@ -13191,7 +13191,7 @@
         <v>235</v>
       </c>
       <c r="F51">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G51">
         <v>7.8</v>
@@ -13221,7 +13221,7 @@
         <v>1.21</v>
       </c>
       <c r="P51">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q51">
         <v>1.58</v>
@@ -13311,7 +13311,7 @@
         <v>12</v>
       </c>
       <c r="AT51">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AU51">
         <v>10</v>
@@ -13344,7 +13344,7 @@
         <v>5.3</v>
       </c>
       <c r="BE51">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF51">
         <v>5.4</v>
@@ -13439,7 +13439,7 @@
         <v>1.13</v>
       </c>
       <c r="H52">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I52">
         <v>46</v>
@@ -13469,28 +13469,28 @@
         <v>1.27</v>
       </c>
       <c r="R52">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S52">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="T52">
         <v>2.42</v>
       </c>
       <c r="U52">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V52">
         <v>1.02</v>
       </c>
       <c r="W52">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X52">
         <v>65</v>
       </c>
       <c r="Y52">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="Z52">
         <v>500</v>
@@ -13675,19 +13675,19 @@
         <v>237</v>
       </c>
       <c r="F53">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="G53">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H53">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I53">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J53">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K53">
         <v>3.45</v>
@@ -13696,25 +13696,25 @@
         <v>1.41</v>
       </c>
       <c r="M53">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N53">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="O53">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P53">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Q53">
         <v>2.28</v>
       </c>
       <c r="R53">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="S53">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="T53">
         <v>1.9</v>
@@ -13729,58 +13729,58 @@
         <v>1.44</v>
       </c>
       <c r="X53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA53">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ53">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP53">
         <v>1.03</v>
@@ -13831,10 +13831,10 @@
         <v>1.03</v>
       </c>
       <c r="BF53">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BG53">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13917,10 +13917,10 @@
         <v>238</v>
       </c>
       <c r="F54">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G54">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H54">
         <v>5.4</v>
@@ -13929,10 +13929,10 @@
         <v>5.9</v>
       </c>
       <c r="J54">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K54">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L54">
         <v>1.56</v>
@@ -13941,16 +13941,16 @@
         <v>1.12</v>
       </c>
       <c r="N54">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O54">
         <v>1.54</v>
       </c>
       <c r="P54">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q54">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R54">
         <v>1.21</v>
@@ -13959,7 +13959,7 @@
         <v>5.4</v>
       </c>
       <c r="T54">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U54">
         <v>1.71</v>
@@ -13968,7 +13968,7 @@
         <v>1.2</v>
       </c>
       <c r="W54">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X54">
         <v>9.199999999999999</v>
@@ -13977,10 +13977,10 @@
         <v>13.5</v>
       </c>
       <c r="Z54">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AA54">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB54">
         <v>6.4</v>
@@ -13989,10 +13989,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD54">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE54">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AF54">
         <v>9.6</v>
@@ -14001,28 +14001,28 @@
         <v>11.5</v>
       </c>
       <c r="AH54">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AI54">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AJ54">
         <v>22</v>
       </c>
       <c r="AK54">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL54">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AM54">
         <v>1000</v>
       </c>
       <c r="AN54">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO54">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AP54">
         <v>8.199999999999999</v>
@@ -14031,7 +14031,7 @@
         <v>12</v>
       </c>
       <c r="AR54">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AS54">
         <v>44</v>
@@ -14040,13 +14040,13 @@
         <v>5.7</v>
       </c>
       <c r="AU54">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV54">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AW54">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AX54">
         <v>8.6</v>
@@ -14055,28 +14055,28 @@
         <v>10</v>
       </c>
       <c r="AZ54">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA54">
         <v>42</v>
       </c>
       <c r="BB54">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC54">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BD54">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BE54">
         <v>90</v>
       </c>
       <c r="BF54">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG54">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -14174,7 +14174,7 @@
         <v>3.15</v>
       </c>
       <c r="K55">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L55">
         <v>1.52</v>
@@ -14183,10 +14183,10 @@
         <v>1.12</v>
       </c>
       <c r="N55">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="O55">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P55">
         <v>1.59</v>
@@ -14216,67 +14216,67 @@
         <v>11.5</v>
       </c>
       <c r="Y55">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z55">
         <v>12</v>
       </c>
       <c r="AA55">
-        <v>29</v>
+        <v>900</v>
       </c>
       <c r="AB55">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC55">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AD55">
-        <v>120</v>
+        <v>16.5</v>
       </c>
       <c r="AE55">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AF55">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AG55">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AH55">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AI55">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ55">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK55">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL55">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM55">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN55">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AO55">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AP55">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ55">
         <v>6.6</v>
       </c>
       <c r="AR55">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS55">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT55">
         <v>10.5</v>
@@ -14285,13 +14285,13 @@
         <v>6.8</v>
       </c>
       <c r="AV55">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW55">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX55">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AY55">
         <v>16</v>
@@ -14300,22 +14300,22 @@
         <v>21</v>
       </c>
       <c r="BA55">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB55">
+        <v>9.4</v>
+      </c>
+      <c r="BC55">
+        <v>9.4</v>
+      </c>
+      <c r="BD55">
         <v>9.6</v>
       </c>
-      <c r="BB55">
-        <v>10</v>
-      </c>
-      <c r="BC55">
-        <v>55</v>
-      </c>
-      <c r="BD55">
-        <v>10</v>
-      </c>
       <c r="BE55">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF55">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BF55">
-        <v>9.6</v>
       </c>
       <c r="BG55">
         <v>21</v>
@@ -14324,61 +14324,61 @@
         <v>1000</v>
       </c>
       <c r="BI55">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="BJ55">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK55">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="BL55">
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="BN55">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO55">
-        <v>4.7</v>
+        <v>1.12</v>
       </c>
       <c r="BP55">
         <v>1000</v>
       </c>
       <c r="BQ55">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="BR55">
         <v>1000</v>
       </c>
       <c r="BS55">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="BT55">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU55">
-        <v>3.95</v>
+        <v>1.12</v>
       </c>
       <c r="BV55">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW55">
-        <v>1.59</v>
+        <v>2.96</v>
       </c>
       <c r="BX55">
         <v>1000</v>
       </c>
       <c r="BY55">
-        <v>1.66</v>
+        <v>3.3</v>
       </c>
       <c r="BZ55">
         <v>1000</v>
       </c>
       <c r="CA55">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="CB55" t="s">
         <v>241</v>
@@ -14401,13 +14401,13 @@
         <v>240</v>
       </c>
       <c r="F56">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G56">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H56">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I56">
         <v>4.3</v>
@@ -14425,16 +14425,16 @@
         <v>1.08</v>
       </c>
       <c r="N56">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O56">
         <v>1.37</v>
       </c>
       <c r="P56">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q56">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R56">
         <v>1.32</v>
@@ -14449,19 +14449,19 @@
         <v>2.04</v>
       </c>
       <c r="V56">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W56">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X56">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y56">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z56">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA56">
         <v>110</v>
@@ -14473,7 +14473,7 @@
         <v>8</v>
       </c>
       <c r="AD56">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE56">
         <v>65</v>
@@ -14491,7 +14491,7 @@
         <v>75</v>
       </c>
       <c r="AJ56">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK56">
         <v>27</v>
@@ -14503,22 +14503,22 @@
         <v>140</v>
       </c>
       <c r="AN56">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO56">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP56">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ56">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR56">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS56">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT56">
         <v>7.8</v>
@@ -14527,40 +14527,40 @@
         <v>7.2</v>
       </c>
       <c r="AV56">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW56">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX56">
         <v>11</v>
       </c>
       <c r="AY56">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ56">
         <v>17</v>
       </c>
       <c r="BA56">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB56">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BC56">
         <v>19.5</v>
       </c>
       <c r="BD56">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE56">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF56">
         <v>14.5</v>
       </c>
       <c r="BG56">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH56">
         <v>3.35</v>
@@ -14602,7 +14602,7 @@
         <v>7.8</v>
       </c>
       <c r="BU56">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV56">
         <v>38</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -739,7 +739,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-10-03 19:04:11</t>
+    <t>2026-10-03 21:16:40</t>
   </si>
 </sst>
 </file>
@@ -1336,19 +1336,19 @@
         <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1363,10 +1363,10 @@
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R2">
         <v>1.47</v>
@@ -1378,46 +1378,46 @@
         <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
         <v>1.12</v>
       </c>
       <c r="W2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X2">
         <v>19.5</v>
       </c>
       <c r="Y2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Z2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA2">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
         <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE2">
         <v>170</v>
       </c>
       <c r="AF2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>140</v>
@@ -1426,31 +1426,31 @@
         <v>12.5</v>
       </c>
       <c r="AK2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO2">
         <v>220</v>
       </c>
       <c r="AP2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ2">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="AS2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT2">
         <v>7.8</v>
@@ -1459,22 +1459,22 @@
         <v>10</v>
       </c>
       <c r="AV2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AW2">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="BB2">
         <v>10.5</v>
@@ -1483,76 +1483,76 @@
         <v>13.5</v>
       </c>
       <c r="BD2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BE2">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="BF2">
         <v>6</v>
       </c>
       <c r="BG2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI2">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.9</v>
+        <v>140</v>
       </c>
       <c r="BN2">
+        <v>3.9</v>
+      </c>
+      <c r="BO2">
+        <v>3.5</v>
+      </c>
+      <c r="BP2">
+        <v>9</v>
+      </c>
+      <c r="BQ2">
         <v>5.3</v>
       </c>
-      <c r="BO2">
-        <v>2.68</v>
-      </c>
-      <c r="BP2">
+      <c r="BR2">
+        <v>26</v>
+      </c>
+      <c r="BS2">
+        <v>8.4</v>
+      </c>
+      <c r="BT2">
         <v>12.5</v>
       </c>
-      <c r="BQ2">
-        <v>5.4</v>
-      </c>
-      <c r="BR2">
-        <v>36</v>
-      </c>
-      <c r="BS2">
-        <v>1.81</v>
-      </c>
-      <c r="BT2">
-        <v>17.5</v>
-      </c>
       <c r="BU2">
-        <v>1.72</v>
+        <v>6.2</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW2">
-        <v>1.9</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.87</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="CA2">
-        <v>1.75</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>241</v>
@@ -1575,73 +1575,73 @@
         <v>187</v>
       </c>
       <c r="F3">
+        <v>3.25</v>
+      </c>
+      <c r="G3">
+        <v>3.4</v>
+      </c>
+      <c r="H3">
+        <v>2.46</v>
+      </c>
+      <c r="I3">
+        <v>2.54</v>
+      </c>
+      <c r="J3">
         <v>3.3</v>
       </c>
-      <c r="G3">
-        <v>3.55</v>
-      </c>
-      <c r="H3">
-        <v>2.4</v>
-      </c>
-      <c r="I3">
-        <v>2.5</v>
-      </c>
-      <c r="J3">
-        <v>3.2</v>
-      </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
         <v>2.4</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V3">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y3">
         <v>8.6</v>
       </c>
       <c r="Z3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
@@ -1653,10 +1653,10 @@
         <v>34</v>
       </c>
       <c r="AF3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3">
         <v>21</v>
@@ -1665,25 +1665,25 @@
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>7.4</v>
@@ -1698,7 +1698,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
         <v>10.5</v>
@@ -1707,94 +1707,94 @@
         <v>26</v>
       </c>
       <c r="AX3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY3">
         <v>13</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA3">
+        <v>38</v>
+      </c>
+      <c r="BB3">
         <v>42</v>
       </c>
-      <c r="BB3">
-        <v>46</v>
-      </c>
       <c r="BC3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD3">
         <v>46</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BG3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH3">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BI3">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
         <v>32</v>
       </c>
       <c r="BQ3">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BT3">
         <v>5.3</v>
       </c>
       <c r="BU3">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
         <v>21</v>
       </c>
       <c r="BW3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
         <v>42</v>
       </c>
       <c r="CA3">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="s">
         <v>241</v>
@@ -1832,40 +1832,40 @@
         <v>3.75</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O4">
         <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T4">
         <v>1.88</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W4">
         <v>1.24</v>
@@ -1916,7 +1916,7 @@
         <v>110</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AN4">
         <v>120</v>
@@ -1937,10 +1937,10 @@
         <v>17</v>
       </c>
       <c r="AT4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
         <v>9</v>
@@ -1970,10 +1970,10 @@
         <v>11</v>
       </c>
       <c r="BE4">
+        <v>11.5</v>
+      </c>
+      <c r="BF4">
         <v>11</v>
-      </c>
-      <c r="BF4">
-        <v>11.5</v>
       </c>
       <c r="BG4">
         <v>11.5</v>
@@ -2000,7 +2000,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -2062,13 +2062,13 @@
         <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="H5">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="I5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>3.75</v>
@@ -2077,7 +2077,7 @@
         <v>3.9</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -2086,31 +2086,31 @@
         <v>4.6</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
         <v>1.48</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T5">
         <v>1.62</v>
       </c>
       <c r="U5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X5">
         <v>19.5</v>
@@ -2131,7 +2131,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
         <v>36</v>
@@ -2146,25 +2146,25 @@
         <v>16.5</v>
       </c>
       <c r="AI5">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
         <v>36</v>
       </c>
       <c r="AK5">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL5">
         <v>50</v>
       </c>
       <c r="AM5">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO5">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AP5">
         <v>16.5</v>
@@ -2176,13 +2176,13 @@
         <v>17.5</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="AT5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
         <v>11.5</v>
@@ -2200,25 +2200,25 @@
         <v>13.5</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BB5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC5">
         <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BE5">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
         <v>14.5</v>
       </c>
       <c r="BG5">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BH5">
         <v>3.85</v>
@@ -2230,7 +2230,7 @@
         <v>9</v>
       </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2251,10 +2251,10 @@
         <v>8</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT5">
         <v>6.4</v>
@@ -2266,13 +2266,13 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
@@ -2304,22 +2304,22 @@
         <v>3.35</v>
       </c>
       <c r="G6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H6">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J6">
         <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M6">
         <v>1.1</v>
@@ -2328,10 +2328,10 @@
         <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2340,55 +2340,55 @@
         <v>1.26</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T6">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U6">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V6">
         <v>1.66</v>
       </c>
       <c r="W6">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
         <v>18</v>
       </c>
       <c r="AA6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE6">
         <v>38</v>
       </c>
       <c r="AF6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AG6">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH6">
         <v>24</v>
       </c>
       <c r="AI6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
         <v>85</v>
@@ -2403,13 +2403,13 @@
         <v>160</v>
       </c>
       <c r="AN6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6">
         <v>7.8</v>
@@ -2418,7 +2418,7 @@
         <v>13</v>
       </c>
       <c r="AS6">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="AT6">
         <v>9.800000000000001</v>
@@ -2427,10 +2427,10 @@
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AX6">
         <v>20</v>
@@ -2442,31 +2442,31 @@
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BB6">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC6">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="BD6">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BE6">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH6">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI6">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
@@ -2478,28 +2478,28 @@
         <v>190</v>
       </c>
       <c r="BM6">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN6">
         <v>6.6</v>
       </c>
       <c r="BO6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP6">
         <v>30</v>
       </c>
       <c r="BQ6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BR6">
         <v>60</v>
       </c>
       <c r="BS6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU6">
         <v>4.6</v>
@@ -2508,19 +2508,19 @@
         <v>19.5</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6">
         <v>38</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6">
         <v>38</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB6" t="s">
         <v>241</v>
@@ -2549,31 +2549,31 @@
         <v>4.3</v>
       </c>
       <c r="H7">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>2.1</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M7">
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O7">
         <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q7">
         <v>1.89</v>
@@ -2588,7 +2588,7 @@
         <v>1.76</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V7">
         <v>1.9</v>
@@ -2600,7 +2600,7 @@
         <v>16</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z7">
         <v>14</v>
@@ -2609,7 +2609,7 @@
         <v>26</v>
       </c>
       <c r="AB7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC7">
         <v>8.800000000000001</v>
@@ -2630,10 +2630,10 @@
         <v>19</v>
       </c>
       <c r="AI7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK7">
         <v>60</v>
@@ -2714,31 +2714,31 @@
         <v>10</v>
       </c>
       <c r="BK7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
         <v>7.8</v>
       </c>
       <c r="BO7">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
         <v>36</v>
       </c>
       <c r="BQ7">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>44</v>
       </c>
       <c r="BS7">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
         <v>5</v>
@@ -2750,19 +2750,19 @@
         <v>15</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>29</v>
       </c>
       <c r="BY7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>25</v>
       </c>
       <c r="CA7">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>241</v>
@@ -2785,7 +2785,7 @@
         <v>192</v>
       </c>
       <c r="F8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G8">
         <v>2.36</v>
@@ -2797,13 +2797,13 @@
         <v>3.6</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2815,22 +2815,22 @@
         <v>1.32</v>
       </c>
       <c r="P8">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q8">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="R8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8">
         <v>3.5</v>
       </c>
       <c r="T8">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V8">
         <v>1.4</v>
@@ -2857,10 +2857,10 @@
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>15.5</v>
@@ -2878,7 +2878,7 @@
         <v>36</v>
       </c>
       <c r="AK8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL8">
         <v>44</v>
@@ -2887,10 +2887,10 @@
         <v>110</v>
       </c>
       <c r="AN8">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AO8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP8">
         <v>12.5</v>
@@ -2902,10 +2902,10 @@
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU8">
         <v>7</v>
@@ -2914,7 +2914,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
@@ -2926,34 +2926,34 @@
         <v>16</v>
       </c>
       <c r="BA8">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BC8">
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE8">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF8">
         <v>16</v>
       </c>
       <c r="BG8">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
         <v>6.8</v>
@@ -2962,49 +2962,49 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BN8">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO8">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8">
         <v>32</v>
       </c>
       <c r="BS8">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="BT8">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BX8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY8">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BZ8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA8">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB8" t="s">
         <v>241</v>
@@ -3027,13 +3027,13 @@
         <v>193</v>
       </c>
       <c r="F9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G9">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="H9">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I9">
         <v>11.5</v>
@@ -3048,13 +3048,13 @@
         <v>1.29</v>
       </c>
       <c r="M9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
         <v>2.4</v>
@@ -3063,16 +3063,16 @@
         <v>1.58</v>
       </c>
       <c r="R9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S9">
         <v>2.46</v>
       </c>
       <c r="T9">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U9">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V9">
         <v>1.1</v>
@@ -3090,7 +3090,7 @@
         <v>420</v>
       </c>
       <c r="AA9">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB9">
         <v>10.5</v>
@@ -3099,13 +3099,13 @@
         <v>13.5</v>
       </c>
       <c r="AD9">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AE9">
         <v>400</v>
       </c>
       <c r="AF9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG9">
         <v>11.5</v>
@@ -3144,13 +3144,13 @@
         <v>38</v>
       </c>
       <c r="AS9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT9">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU9">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AV9">
         <v>18</v>
@@ -3162,7 +3162,7 @@
         <v>7.6</v>
       </c>
       <c r="AY9">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
         <v>17.5</v>
@@ -3171,7 +3171,7 @@
         <v>30</v>
       </c>
       <c r="BB9">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC9">
         <v>8.6</v>
@@ -3183,7 +3183,7 @@
         <v>44</v>
       </c>
       <c r="BF9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG9">
         <v>55</v>
@@ -3192,7 +3192,7 @@
         <v>4.5</v>
       </c>
       <c r="BI9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9">
         <v>12</v>
@@ -3278,52 +3278,52 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K10">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L10">
         <v>1.25</v>
       </c>
       <c r="M10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P10">
         <v>2.7</v>
       </c>
       <c r="Q10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R10">
         <v>1.68</v>
       </c>
       <c r="S10">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T10">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U10">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W10">
         <v>3.35</v>
       </c>
       <c r="X10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y10">
         <v>42</v>
@@ -3374,7 +3374,7 @@
         <v>4.9</v>
       </c>
       <c r="AO10">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP10">
         <v>18</v>
@@ -3386,7 +3386,7 @@
         <v>55</v>
       </c>
       <c r="AS10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT10">
         <v>10</v>
@@ -3407,19 +3407,19 @@
         <v>9</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB10">
         <v>10.5</v>
       </c>
       <c r="BC10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE10">
         <v>55</v>
@@ -3479,7 +3479,7 @@
         <v>7.4</v>
       </c>
       <c r="BX10">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BY10">
         <v>7.2</v>
@@ -3517,19 +3517,19 @@
         <v>2.8</v>
       </c>
       <c r="H11">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I11">
         <v>2.82</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
         <v>3.85</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M11">
         <v>1.06</v>
@@ -3544,7 +3544,7 @@
         <v>2.1</v>
       </c>
       <c r="Q11">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R11">
         <v>1.43</v>
@@ -3559,7 +3559,7 @@
         <v>2.34</v>
       </c>
       <c r="V11">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W11">
         <v>1.55</v>
@@ -3604,7 +3604,7 @@
         <v>48</v>
       </c>
       <c r="AK11">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AL11">
         <v>44</v>
@@ -3637,10 +3637,10 @@
         <v>7.4</v>
       </c>
       <c r="AV11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AX11">
         <v>17</v>
@@ -3652,85 +3652,85 @@
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="BB11">
         <v>18</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="BD11">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="BE11">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF11">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BG11">
         <v>16.5</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI11">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BK11">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.92</v>
+        <v>10</v>
       </c>
       <c r="BN11">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BO11">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR11">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BU11">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BV11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX11">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.81</v>
+        <v>7.6</v>
       </c>
       <c r="CB11" t="s">
         <v>241</v>
@@ -3753,31 +3753,31 @@
         <v>196</v>
       </c>
       <c r="F12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G12">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M12">
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
         <v>1.34</v>
@@ -3789,7 +3789,7 @@
         <v>1.98</v>
       </c>
       <c r="R12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S12">
         <v>3.55</v>
@@ -3798,13 +3798,13 @@
         <v>1.78</v>
       </c>
       <c r="U12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X12">
         <v>14</v>
@@ -3813,7 +3813,7 @@
         <v>13.5</v>
       </c>
       <c r="Z12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA12">
         <v>900</v>
@@ -3837,16 +3837,16 @@
         <v>11.5</v>
       </c>
       <c r="AH12">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI12">
         <v>55</v>
       </c>
       <c r="AJ12">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AK12">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL12">
         <v>42</v>
@@ -3870,19 +3870,19 @@
         <v>19</v>
       </c>
       <c r="AS12">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV12">
         <v>13</v>
       </c>
       <c r="AW12">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX12">
         <v>12.5</v>
@@ -3894,7 +3894,7 @@
         <v>15</v>
       </c>
       <c r="BA12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB12">
         <v>14.5</v>
@@ -3903,25 +3903,25 @@
         <v>19</v>
       </c>
       <c r="BD12">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF12">
         <v>16.5</v>
       </c>
       <c r="BG12">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH12">
         <v>3.4</v>
       </c>
       <c r="BI12">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK12">
         <v>6</v>
@@ -3930,25 +3930,25 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN12">
         <v>5.2</v>
       </c>
       <c r="BO12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP12">
         <v>23</v>
       </c>
       <c r="BQ12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR12">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT12">
         <v>6.8</v>
@@ -3960,19 +3960,19 @@
         <v>40</v>
       </c>
       <c r="BW12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX12">
         <v>55</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ12">
         <v>38</v>
       </c>
       <c r="CA12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="s">
         <v>241</v>
@@ -3998,16 +3998,16 @@
         <v>2.98</v>
       </c>
       <c r="G13">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="H13">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I13">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
         <v>4.6</v>
@@ -4016,37 +4016,37 @@
         <v>1.27</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O13">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q13">
         <v>1.51</v>
       </c>
       <c r="R13">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U13">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="V13">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W13">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X13">
         <v>27</v>
@@ -4103,61 +4103,61 @@
         <v>11.5</v>
       </c>
       <c r="AP13">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AQ13">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR13">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="AS13">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AT13">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AU13">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV13">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AX13">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AY13">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="AZ13">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BB13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC13">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BD13">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BE13">
         <v>7.4</v>
       </c>
       <c r="BF13">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BG13">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI13">
         <v>3.6</v>
@@ -4166,7 +4166,7 @@
         <v>9</v>
       </c>
       <c r="BK13">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -4175,28 +4175,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN13">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BO13">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
         <v>16.5</v>
       </c>
       <c r="BR13">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BS13">
         <v>20</v>
       </c>
       <c r="BT13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV13">
         <v>15.5</v>
@@ -4205,13 +4205,13 @@
         <v>11</v>
       </c>
       <c r="BX13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BY13">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BZ13">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="CA13">
         <v>11.5</v>
@@ -4237,25 +4237,25 @@
         <v>198</v>
       </c>
       <c r="F14">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G14">
+        <v>2.74</v>
+      </c>
+      <c r="H14">
         <v>2.8</v>
       </c>
-      <c r="H14">
-        <v>2.78</v>
-      </c>
       <c r="I14">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M14">
         <v>1.05</v>
@@ -4264,13 +4264,13 @@
         <v>4.7</v>
       </c>
       <c r="O14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
         <v>2.26</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R14">
         <v>1.52</v>
@@ -4279,7 +4279,7 @@
         <v>2.56</v>
       </c>
       <c r="T14">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U14">
         <v>2.48</v>
@@ -4288,10 +4288,10 @@
         <v>1.51</v>
       </c>
       <c r="W14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y14">
         <v>16</v>
@@ -4300,13 +4300,13 @@
         <v>22</v>
       </c>
       <c r="AA14">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AB14">
         <v>16</v>
       </c>
       <c r="AC14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD14">
         <v>13</v>
@@ -4315,7 +4315,7 @@
         <v>28</v>
       </c>
       <c r="AF14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG14">
         <v>13</v>
@@ -4351,7 +4351,7 @@
         <v>13</v>
       </c>
       <c r="AR14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS14">
         <v>34</v>
@@ -4360,7 +4360,7 @@
         <v>12.5</v>
       </c>
       <c r="AU14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV14">
         <v>11</v>
@@ -4375,16 +4375,16 @@
         <v>10.5</v>
       </c>
       <c r="AZ14">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB14">
         <v>34</v>
       </c>
       <c r="BC14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD14">
         <v>27</v>
@@ -4393,19 +4393,19 @@
         <v>48</v>
       </c>
       <c r="BF14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ14">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BK14">
         <v>5.4</v>
@@ -4417,31 +4417,31 @@
         <v>21</v>
       </c>
       <c r="BN14">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO14">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BP14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BQ14">
         <v>11</v>
       </c>
       <c r="BR14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
         <v>15.5</v>
       </c>
       <c r="BT14">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU14">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BW14">
         <v>11.5</v>
@@ -4453,7 +4453,7 @@
         <v>16</v>
       </c>
       <c r="BZ14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="CA14">
         <v>11</v>
@@ -4479,22 +4479,22 @@
         <v>199</v>
       </c>
       <c r="F15">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="G15">
-        <v>990</v>
+        <v>2.6</v>
       </c>
       <c r="H15">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>990</v>
+        <v>18.5</v>
       </c>
       <c r="J15">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4506,7 +4506,7 @@
         <v>1.1</v>
       </c>
       <c r="O15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P15">
         <v>1.09</v>
@@ -4518,7 +4518,7 @@
         <v>1.08</v>
       </c>
       <c r="S15">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4530,64 +4530,64 @@
         <v>1.2</v>
       </c>
       <c r="W15">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="X15">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Y15">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="Z15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AA15">
         <v>900</v>
       </c>
       <c r="AB15">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AC15">
         <v>42</v>
       </c>
       <c r="AD15">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AE15">
-        <v>440</v>
+        <v>260</v>
       </c>
       <c r="AF15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG15">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AH15">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="AI15">
-        <v>540</v>
+        <v>350</v>
       </c>
       <c r="AJ15">
         <v>900</v>
       </c>
       <c r="AK15">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="AL15">
-        <v>450</v>
+        <v>180</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN15">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP15">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
         <v>1.03</v>
@@ -4599,7 +4599,7 @@
         <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
         <v>4.9</v>
@@ -4611,7 +4611,7 @@
         <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
         <v>1.03</v>
@@ -4635,7 +4635,7 @@
         <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>5.9</v>
+        <v>1.55</v>
       </c>
       <c r="BG15">
         <v>1.55</v>
@@ -4644,61 +4644,61 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>241</v>
@@ -4739,7 +4739,7 @@
         <v>3.5</v>
       </c>
       <c r="L16">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M16">
         <v>1.07</v>
@@ -4823,7 +4823,7 @@
         <v>95</v>
       </c>
       <c r="AN16">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AO16">
         <v>28</v>
@@ -4838,7 +4838,7 @@
         <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT16">
         <v>10.5</v>
@@ -4850,7 +4850,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AX16">
         <v>16.5</v>
@@ -4859,7 +4859,7 @@
         <v>11</v>
       </c>
       <c r="AZ16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA16">
         <v>28</v>
@@ -4868,79 +4868,79 @@
         <v>30</v>
       </c>
       <c r="BC16">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BD16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE16">
         <v>55</v>
       </c>
       <c r="BF16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG16">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI16">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="BJ16">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BK16">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM16">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO16">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP16">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BQ16">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR16">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BS16">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU16">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV16">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BW16">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX16">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BY16">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="BZ16">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="CA16">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="CB16" t="s">
         <v>241</v>
@@ -4969,7 +4969,7 @@
         <v>2.6</v>
       </c>
       <c r="H17">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I17">
         <v>2.92</v>
@@ -4987,7 +4987,7 @@
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O17">
         <v>1.19</v>
@@ -4999,10 +4999,10 @@
         <v>1.55</v>
       </c>
       <c r="R17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S17">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T17">
         <v>1.53</v>
@@ -5128,19 +5128,19 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BJ17">
         <v>11.5</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BN17">
         <v>8</v>
@@ -5152,13 +5152,13 @@
         <v>23</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BR17">
         <v>34</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BT17">
         <v>8.6</v>
@@ -5170,19 +5170,19 @@
         <v>26</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BX17">
         <v>34</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BZ17">
         <v>21</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="CB17" t="s">
         <v>241</v>
@@ -5262,7 +5262,7 @@
         <v>27</v>
       </c>
       <c r="Y18">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z18">
         <v>38</v>
@@ -5295,7 +5295,7 @@
         <v>46</v>
       </c>
       <c r="AJ18">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK18">
         <v>19.5</v>
@@ -5322,7 +5322,7 @@
         <v>16</v>
       </c>
       <c r="AS18">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT18">
         <v>12</v>
@@ -5334,7 +5334,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX18">
         <v>13</v>
@@ -5346,19 +5346,19 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB18">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BC18">
         <v>15.5</v>
       </c>
       <c r="BD18">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BE18">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF18">
         <v>7.6</v>
@@ -5376,7 +5376,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK18">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5504,46 +5504,46 @@
         <v>1000</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AC19">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AM19">
         <v>1000</v>
@@ -5555,52 +5555,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BF19">
         <v>1.55</v>
@@ -5689,22 +5689,22 @@
         <v>204</v>
       </c>
       <c r="F20">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G20">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H20">
         <v>2.62</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J20">
         <v>2.74</v>
       </c>
       <c r="K20">
-        <v>480</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5740,7 +5740,7 @@
         <v>1.25</v>
       </c>
       <c r="W20">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X20">
         <v>28</v>
@@ -5854,61 +5854,61 @@
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>241</v>
@@ -5943,7 +5943,7 @@
         <v>4.4</v>
       </c>
       <c r="J21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K21">
         <v>3.4</v>
@@ -5961,7 +5961,7 @@
         <v>1.47</v>
       </c>
       <c r="P21">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q21">
         <v>2.36</v>
@@ -5976,7 +5976,7 @@
         <v>2.04</v>
       </c>
       <c r="U21">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V21">
         <v>1.3</v>
@@ -6021,7 +6021,7 @@
         <v>370</v>
       </c>
       <c r="AJ21">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AK21">
         <v>48</v>
@@ -6030,13 +6030,13 @@
         <v>290</v>
       </c>
       <c r="AM21">
-        <v>660</v>
+        <v>580</v>
       </c>
       <c r="AN21">
         <v>55</v>
       </c>
       <c r="AO21">
-        <v>670</v>
+        <v>590</v>
       </c>
       <c r="AP21">
         <v>8.800000000000001</v>
@@ -6045,7 +6045,7 @@
         <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS21">
         <v>10</v>
@@ -6069,7 +6069,7 @@
         <v>10</v>
       </c>
       <c r="AZ21">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA21">
         <v>10</v>
@@ -6078,7 +6078,7 @@
         <v>11.5</v>
       </c>
       <c r="BC21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD21">
         <v>9.4</v>
@@ -6173,7 +6173,7 @@
         <v>206</v>
       </c>
       <c r="F22">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G22">
         <v>3.2</v>
@@ -6194,19 +6194,19 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="O22">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P22">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="Q22">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R22">
         <v>1.83</v>
@@ -6224,7 +6224,7 @@
         <v>1.66</v>
       </c>
       <c r="W22">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X22">
         <v>48</v>
@@ -6242,7 +6242,7 @@
         <v>30</v>
       </c>
       <c r="AC22">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD22">
         <v>16</v>
@@ -6275,118 +6275,118 @@
         <v>48</v>
       </c>
       <c r="AN22">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO22">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP22">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AQ22">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AR22">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AS22">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AT22">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AU22">
         <v>5.8</v>
       </c>
       <c r="AV22">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AW22">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AX22">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AY22">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AZ22">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BA22">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BB22">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BC22">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BD22">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BE22">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BF22">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BG22">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6445,7 +6445,7 @@
         <v>1.01</v>
       </c>
       <c r="P23">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q23">
         <v>1.28</v>
@@ -6463,10 +6463,10 @@
         <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6657,22 +6657,22 @@
         <v>208</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="G24">
         <v>990</v>
       </c>
       <c r="H24">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="I24">
-        <v>990</v>
+        <v>2.86</v>
       </c>
       <c r="J24">
         <v>2.2</v>
       </c>
       <c r="K24">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6705,64 +6705,64 @@
         <v>2.06</v>
       </c>
       <c r="V24">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.27</v>
       </c>
       <c r="X24">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="Y24">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
         <v>900</v>
       </c>
       <c r="AB24">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AC24">
         <v>42</v>
       </c>
       <c r="AD24">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AE24">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF24">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AG24">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH24">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AI24">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AJ24">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="AK24">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AL24">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
         <v>1.03</v>
@@ -6816,67 +6816,67 @@
         <v>1.55</v>
       </c>
       <c r="BG24">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
         <v>241</v>
@@ -6905,10 +6905,10 @@
         <v>1.66</v>
       </c>
       <c r="H25">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J25">
         <v>4.2</v>
@@ -6923,25 +6923,25 @@
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O25">
         <v>1.26</v>
       </c>
       <c r="P25">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q25">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R25">
         <v>1.46</v>
       </c>
       <c r="S25">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T25">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="U25">
         <v>2.04</v>
@@ -6953,7 +6953,7 @@
         <v>2.5</v>
       </c>
       <c r="X25">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y25">
         <v>23</v>
@@ -6962,7 +6962,7 @@
         <v>55</v>
       </c>
       <c r="AA25">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB25">
         <v>9.4</v>
@@ -6971,10 +6971,10 @@
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE25">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF25">
         <v>10.5</v>
@@ -7004,7 +7004,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO25">
-        <v>120</v>
+        <v>530</v>
       </c>
       <c r="AP25">
         <v>16</v>
@@ -7016,10 +7016,10 @@
         <v>42</v>
       </c>
       <c r="AS25">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT25">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU25">
         <v>8.800000000000001</v>
@@ -7028,7 +7028,7 @@
         <v>20</v>
       </c>
       <c r="AW25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX25">
         <v>9</v>
@@ -7040,7 +7040,7 @@
         <v>17.5</v>
       </c>
       <c r="BA25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB25">
         <v>13</v>
@@ -7049,19 +7049,19 @@
         <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BE25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF25">
         <v>7.4</v>
       </c>
       <c r="BG25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH25">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI25">
         <v>3.45</v>
@@ -7076,7 +7076,7 @@
         <v>130</v>
       </c>
       <c r="BM25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN25">
         <v>4.2</v>
@@ -7088,7 +7088,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ25">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR25">
         <v>25</v>
@@ -7112,13 +7112,13 @@
         <v>60</v>
       </c>
       <c r="BY25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ25">
         <v>17.5</v>
       </c>
       <c r="CA25">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="CB25" t="s">
         <v>241</v>
@@ -7150,7 +7150,7 @@
         <v>1.26</v>
       </c>
       <c r="I26">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="J26">
         <v>6.8</v>
@@ -7174,13 +7174,13 @@
         <v>3.45</v>
       </c>
       <c r="Q26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R26">
         <v>1.99</v>
       </c>
       <c r="S26">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="T26">
         <v>1.74</v>
@@ -7237,10 +7237,10 @@
         <v>160</v>
       </c>
       <c r="AL26">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AM26">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="AN26">
         <v>140</v>
@@ -7261,7 +7261,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT26">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AU26">
         <v>15</v>
@@ -7297,7 +7297,7 @@
         <v>8.4</v>
       </c>
       <c r="BF26">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG26">
         <v>2.9</v>
@@ -7306,55 +7306,55 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7401,7 +7401,7 @@
         <v>4.7</v>
       </c>
       <c r="L27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M27">
         <v>1.04</v>
@@ -7428,7 +7428,7 @@
         <v>1.67</v>
       </c>
       <c r="U27">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V27">
         <v>2.28</v>
@@ -7461,7 +7461,7 @@
         <v>17.5</v>
       </c>
       <c r="AF27">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AG27">
         <v>21</v>
@@ -7470,22 +7470,22 @@
         <v>19</v>
       </c>
       <c r="AI27">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AJ27">
         <v>900</v>
       </c>
       <c r="AK27">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AL27">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="AM27">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN27">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="AO27">
         <v>8.199999999999999</v>
@@ -7494,7 +7494,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ27">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="AR27">
         <v>10</v>
@@ -7545,64 +7545,64 @@
         <v>6.8</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI27">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ27">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK27">
-        <v>1.76</v>
+        <v>6.2</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>2.04</v>
+        <v>9</v>
       </c>
       <c r="BN27">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO27">
-        <v>1.75</v>
+        <v>6.8</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.96</v>
+        <v>8</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.97</v>
+        <v>8</v>
       </c>
       <c r="BT27">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BU27">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BV27">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BW27">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX27">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BY27">
-        <v>1.91</v>
+        <v>6.8</v>
       </c>
       <c r="BZ27">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="CA27">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="CB27" t="s">
         <v>241</v>
@@ -7631,7 +7631,7 @@
         <v>2.84</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I28">
         <v>4.2</v>
@@ -7640,13 +7640,13 @@
         <v>3.1</v>
       </c>
       <c r="K28">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N28">
         <v>3.2</v>
@@ -7655,22 +7655,22 @@
         <v>1.36</v>
       </c>
       <c r="P28">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="Q28">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="R28">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="S28">
         <v>3.5</v>
       </c>
       <c r="T28">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U28">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="V28">
         <v>1.31</v>
@@ -7679,112 +7679,112 @@
         <v>1.54</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF28">
-        <v>1.41</v>
+        <v>6</v>
       </c>
       <c r="BG28">
-        <v>1.56</v>
+        <v>4.1</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7870,7 +7870,7 @@
         <v>1.47</v>
       </c>
       <c r="G29">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H29">
         <v>5.1</v>
@@ -7891,196 +7891,196 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O29">
         <v>1.14</v>
       </c>
       <c r="P29">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="Q29">
         <v>1.4</v>
       </c>
       <c r="R29">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="S29">
         <v>2.06</v>
       </c>
       <c r="T29">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U29">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="V29">
         <v>1.16</v>
       </c>
       <c r="W29">
+        <v>2.72</v>
+      </c>
+      <c r="X29">
+        <v>44</v>
+      </c>
+      <c r="Y29">
+        <v>42</v>
+      </c>
+      <c r="Z29">
+        <v>70</v>
+      </c>
+      <c r="AA29">
+        <v>170</v>
+      </c>
+      <c r="AB29">
+        <v>18</v>
+      </c>
+      <c r="AC29">
+        <v>14</v>
+      </c>
+      <c r="AD29">
+        <v>29</v>
+      </c>
+      <c r="AE29">
+        <v>75</v>
+      </c>
+      <c r="AF29">
+        <v>15.5</v>
+      </c>
+      <c r="AG29">
+        <v>13</v>
+      </c>
+      <c r="AH29">
+        <v>22</v>
+      </c>
+      <c r="AI29">
+        <v>65</v>
+      </c>
+      <c r="AJ29">
+        <v>18</v>
+      </c>
+      <c r="AK29">
+        <v>16.5</v>
+      </c>
+      <c r="AL29">
+        <v>28</v>
+      </c>
+      <c r="AM29">
+        <v>75</v>
+      </c>
+      <c r="AN29">
+        <v>4.8</v>
+      </c>
+      <c r="AO29">
+        <v>55</v>
+      </c>
+      <c r="AP29">
+        <v>5.4</v>
+      </c>
+      <c r="AQ29">
+        <v>5.3</v>
+      </c>
+      <c r="AR29">
+        <v>5.6</v>
+      </c>
+      <c r="AS29">
+        <v>5.9</v>
+      </c>
+      <c r="AT29">
+        <v>4.5</v>
+      </c>
+      <c r="AU29">
+        <v>6.2</v>
+      </c>
+      <c r="AV29">
+        <v>5</v>
+      </c>
+      <c r="AW29">
+        <v>5.6</v>
+      </c>
+      <c r="AX29">
+        <v>4.4</v>
+      </c>
+      <c r="AY29">
+        <v>6.2</v>
+      </c>
+      <c r="AZ29">
+        <v>4.8</v>
+      </c>
+      <c r="BA29">
+        <v>5.6</v>
+      </c>
+      <c r="BB29">
+        <v>4.5</v>
+      </c>
+      <c r="BC29">
+        <v>4.4</v>
+      </c>
+      <c r="BD29">
+        <v>5</v>
+      </c>
+      <c r="BE29">
+        <v>5.6</v>
+      </c>
+      <c r="BF29">
         <v>2.68</v>
       </c>
-      <c r="X29">
-        <v>1000</v>
-      </c>
-      <c r="Y29">
-        <v>1000</v>
-      </c>
-      <c r="Z29">
-        <v>1000</v>
-      </c>
-      <c r="AA29">
-        <v>1000</v>
-      </c>
-      <c r="AB29">
-        <v>1000</v>
-      </c>
-      <c r="AC29">
-        <v>1000</v>
-      </c>
-      <c r="AD29">
-        <v>1000</v>
-      </c>
-      <c r="AE29">
-        <v>1000</v>
-      </c>
-      <c r="AF29">
-        <v>40</v>
-      </c>
-      <c r="AG29">
-        <v>36</v>
-      </c>
-      <c r="AH29">
-        <v>1000</v>
-      </c>
-      <c r="AI29">
-        <v>1000</v>
-      </c>
-      <c r="AJ29">
-        <v>900</v>
-      </c>
-      <c r="AK29">
-        <v>65</v>
-      </c>
-      <c r="AL29">
-        <v>1000</v>
-      </c>
-      <c r="AM29">
-        <v>1000</v>
-      </c>
-      <c r="AN29">
-        <v>1000</v>
-      </c>
-      <c r="AO29">
-        <v>1000</v>
-      </c>
-      <c r="AP29">
-        <v>1.03</v>
-      </c>
-      <c r="AQ29">
-        <v>1.03</v>
-      </c>
-      <c r="AR29">
-        <v>1.03</v>
-      </c>
-      <c r="AS29">
-        <v>1.03</v>
-      </c>
-      <c r="AT29">
-        <v>1.03</v>
-      </c>
-      <c r="AU29">
-        <v>1.03</v>
-      </c>
-      <c r="AV29">
-        <v>1.03</v>
-      </c>
-      <c r="AW29">
-        <v>1.03</v>
-      </c>
-      <c r="AX29">
-        <v>1.03</v>
-      </c>
-      <c r="AY29">
-        <v>1.03</v>
-      </c>
-      <c r="AZ29">
-        <v>1.03</v>
-      </c>
-      <c r="BA29">
-        <v>1.03</v>
-      </c>
-      <c r="BB29">
-        <v>1.03</v>
-      </c>
-      <c r="BC29">
-        <v>1.03</v>
-      </c>
-      <c r="BD29">
-        <v>1.03</v>
-      </c>
-      <c r="BE29">
-        <v>1.03</v>
-      </c>
-      <c r="BF29">
-        <v>3.75</v>
-      </c>
       <c r="BG29">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -8109,22 +8109,22 @@
         <v>214</v>
       </c>
       <c r="F30">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="G30">
-        <v>990</v>
+        <v>1.96</v>
       </c>
       <c r="H30">
-        <v>1.38</v>
+        <v>3.7</v>
       </c>
       <c r="I30">
-        <v>990</v>
+        <v>7.4</v>
       </c>
       <c r="J30">
-        <v>1.29</v>
+        <v>3.6</v>
       </c>
       <c r="K30">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8133,34 +8133,34 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="O30">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P30">
+        <v>1.86</v>
+      </c>
+      <c r="Q30">
+        <v>1.16</v>
+      </c>
+      <c r="R30">
         <v>1.09</v>
       </c>
-      <c r="Q30">
+      <c r="S30">
         <v>1.27</v>
-      </c>
-      <c r="R30">
-        <v>1.08</v>
-      </c>
-      <c r="S30">
-        <v>1.53</v>
       </c>
       <c r="T30">
         <v>1.11</v>
       </c>
       <c r="U30">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V30">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>2.04</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8178,7 +8178,7 @@
         <v>1000</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD30">
         <v>1000</v>
@@ -8190,7 +8190,7 @@
         <v>1000</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AH30">
         <v>1000</v>
@@ -8202,7 +8202,7 @@
         <v>1000</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL30">
         <v>1000</v>
@@ -8217,46 +8217,46 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR30">
         <v>16</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT30">
         <v>7.4</v>
       </c>
       <c r="AU30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV30">
-        <v>1.98</v>
+        <v>16</v>
       </c>
       <c r="AW30">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AX30">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY30">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ30">
-        <v>16</v>
+        <v>1.97</v>
       </c>
       <c r="BA30">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BB30">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD30">
         <v>24</v>
@@ -8265,10 +8265,10 @@
         <v>16</v>
       </c>
       <c r="BF30">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8351,22 +8351,22 @@
         <v>215</v>
       </c>
       <c r="F31">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="G31">
-        <v>990</v>
+        <v>2.94</v>
       </c>
       <c r="H31">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="I31">
-        <v>990</v>
+        <v>13.5</v>
       </c>
       <c r="J31">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K31">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8381,13 +8381,13 @@
         <v>1.22</v>
       </c>
       <c r="P31">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q31">
         <v>1.33</v>
       </c>
       <c r="R31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S31">
         <v>1.27</v>
@@ -8402,61 +8402,61 @@
         <v>1.27</v>
       </c>
       <c r="W31">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ31">
         <v>900</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP31">
         <v>1.03</v>
@@ -8471,10 +8471,10 @@
         <v>1.03</v>
       </c>
       <c r="AT31">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AU31">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV31">
         <v>1.03</v>
@@ -8507,10 +8507,10 @@
         <v>1.03</v>
       </c>
       <c r="BF31">
-        <v>1.27</v>
+        <v>5.5</v>
       </c>
       <c r="BG31">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8623,7 +8623,7 @@
         <v>1.21</v>
       </c>
       <c r="P32">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Q32">
         <v>1.21</v>
@@ -8758,55 +8758,55 @@
         <v>1000</v>
       </c>
       <c r="BI32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ32">
         <v>0</v>
@@ -8838,16 +8838,16 @@
         <v>1.49</v>
       </c>
       <c r="G33">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H33">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="I33">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="J33">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K33">
         <v>5.6</v>
@@ -8859,13 +8859,13 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O33">
         <v>1.02</v>
       </c>
       <c r="P33">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q33">
         <v>1.03</v>
@@ -8886,61 +8886,61 @@
         <v>1.16</v>
       </c>
       <c r="W33">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="X33">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y33">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z33">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AB33">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC33">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD33">
         <v>1000</v>
       </c>
       <c r="AE33">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF33">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG33">
+        <v>500</v>
+      </c>
+      <c r="AH33">
         <v>36</v>
       </c>
-      <c r="AH33">
-        <v>1000</v>
-      </c>
       <c r="AI33">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ33">
         <v>900</v>
       </c>
       <c r="AK33">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL33">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM33">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO33">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP33">
         <v>1.03</v>
@@ -8958,7 +8958,7 @@
         <v>1.03</v>
       </c>
       <c r="AU33">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AV33">
         <v>1.03</v>
@@ -8991,70 +8991,70 @@
         <v>1.03</v>
       </c>
       <c r="BF33">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="BG33">
-        <v>2.86</v>
+        <v>1.55</v>
       </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="s">
         <v>241</v>
@@ -9131,58 +9131,58 @@
         <v>2.24</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AA34">
         <v>1000</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AE34">
         <v>1000</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AI34">
         <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM34">
         <v>1000</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP34">
         <v>1.03</v>
@@ -9197,10 +9197,10 @@
         <v>1.03</v>
       </c>
       <c r="AT34">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU34">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AV34">
         <v>1.03</v>
@@ -9209,7 +9209,7 @@
         <v>1.03</v>
       </c>
       <c r="AX34">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AY34">
         <v>1.03</v>
@@ -9233,70 +9233,70 @@
         <v>1.03</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH34">
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB34" t="s">
         <v>241</v>
@@ -9319,7 +9319,7 @@
         <v>219</v>
       </c>
       <c r="F35">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G35">
         <v>2.9</v>
@@ -9343,7 +9343,7 @@
         <v>1.07</v>
       </c>
       <c r="N35">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O35">
         <v>1.32</v>
@@ -9367,34 +9367,34 @@
         <v>2.22</v>
       </c>
       <c r="V35">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W35">
         <v>1.53</v>
       </c>
       <c r="X35">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y35">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z35">
         <v>18</v>
       </c>
       <c r="AA35">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AB35">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC35">
         <v>8</v>
       </c>
       <c r="AD35">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE35">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AF35">
         <v>19</v>
@@ -9403,28 +9403,28 @@
         <v>13</v>
       </c>
       <c r="AH35">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI35">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ35">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AK35">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL35">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AM35">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN35">
         <v>40</v>
       </c>
       <c r="AO35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP35">
         <v>13</v>
@@ -9433,13 +9433,13 @@
         <v>10.5</v>
       </c>
       <c r="AR35">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU35">
         <v>7</v>
@@ -9448,37 +9448,37 @@
         <v>11</v>
       </c>
       <c r="AW35">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX35">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ35">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA35">
         <v>30</v>
       </c>
       <c r="BB35">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC35">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD35">
         <v>30</v>
       </c>
       <c r="BE35">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BF35">
         <v>20</v>
       </c>
       <c r="BG35">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9561,16 +9561,16 @@
         <v>220</v>
       </c>
       <c r="F36">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G36">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H36">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I36">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J36">
         <v>3.6</v>
@@ -9609,172 +9609,172 @@
         <v>1.11</v>
       </c>
       <c r="V36">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W36">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE36">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF36">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG36">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AH36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI36">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ36">
         <v>900</v>
       </c>
       <c r="AK36">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM36">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO36">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP36">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AQ36">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AR36">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AS36">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AT36">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AU36">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AV36">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AW36">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AX36">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AY36">
+        <v>1.21</v>
+      </c>
+      <c r="AZ36">
+        <v>1.23</v>
+      </c>
+      <c r="BA36">
+        <v>1.25</v>
+      </c>
+      <c r="BB36">
+        <v>1.24</v>
+      </c>
+      <c r="BC36">
+        <v>1.23</v>
+      </c>
+      <c r="BD36">
+        <v>1.24</v>
+      </c>
+      <c r="BE36">
+        <v>1.25</v>
+      </c>
+      <c r="BF36">
+        <v>1.22</v>
+      </c>
+      <c r="BG36">
+        <v>1.55</v>
+      </c>
+      <c r="BH36">
+        <v>1000</v>
+      </c>
+      <c r="BI36">
         <v>1.04</v>
       </c>
-      <c r="AZ36">
-        <v>1.07</v>
-      </c>
-      <c r="BA36">
-        <v>1.07</v>
-      </c>
-      <c r="BB36">
-        <v>1.07</v>
-      </c>
-      <c r="BC36">
-        <v>1.06</v>
-      </c>
-      <c r="BD36">
-        <v>1.07</v>
-      </c>
-      <c r="BE36">
-        <v>1.07</v>
-      </c>
-      <c r="BF36">
-        <v>1.07</v>
-      </c>
-      <c r="BG36">
-        <v>1.07</v>
-      </c>
-      <c r="BH36">
-        <v>1000</v>
-      </c>
-      <c r="BI36">
-        <v>1.01</v>
-      </c>
       <c r="BJ36">
         <v>1000</v>
       </c>
       <c r="BK36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN36">
         <v>1000</v>
       </c>
       <c r="BO36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP36">
         <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT36">
         <v>1000</v>
       </c>
       <c r="BU36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36">
         <v>0</v>
@@ -9803,16 +9803,16 @@
         <v>221</v>
       </c>
       <c r="F37">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="G37">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H37">
         <v>3.45</v>
       </c>
       <c r="I37">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J37">
         <v>3.4</v>
@@ -9827,25 +9827,25 @@
         <v>1.08</v>
       </c>
       <c r="N37">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P37">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q37">
         <v>2.12</v>
       </c>
       <c r="R37">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S37">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T37">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U37">
         <v>2.08</v>
@@ -9854,7 +9854,7 @@
         <v>1.38</v>
       </c>
       <c r="W37">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X37">
         <v>12</v>
@@ -9905,10 +9905,10 @@
         <v>110</v>
       </c>
       <c r="AN37">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO37">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP37">
         <v>11</v>
@@ -9947,7 +9947,7 @@
         <v>48</v>
       </c>
       <c r="BB37">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="BC37">
         <v>23</v>
@@ -9956,13 +9956,13 @@
         <v>38</v>
       </c>
       <c r="BE37">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BF37">
         <v>19.5</v>
       </c>
       <c r="BG37">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH37">
         <v>3.15</v>
@@ -9980,10 +9980,10 @@
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN37">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO37">
         <v>4.6</v>
@@ -9998,31 +9998,31 @@
         <v>34</v>
       </c>
       <c r="BS37">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT37">
         <v>6.6</v>
       </c>
       <c r="BU37">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV37">
         <v>29</v>
       </c>
       <c r="BW37">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX37">
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ37">
         <v>32</v>
       </c>
       <c r="CA37">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB37" t="s">
         <v>241</v>
@@ -10045,10 +10045,10 @@
         <v>222</v>
       </c>
       <c r="F38">
+        <v>1.24</v>
+      </c>
+      <c r="G38">
         <v>1.26</v>
-      </c>
-      <c r="G38">
-        <v>1.27</v>
       </c>
       <c r="H38">
         <v>12.5</v>
@@ -10060,7 +10060,7 @@
         <v>7.4</v>
       </c>
       <c r="K38">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>1.22</v>
@@ -10072,31 +10072,31 @@
         <v>7.8</v>
       </c>
       <c r="O38">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P38">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q38">
         <v>1.4</v>
       </c>
       <c r="R38">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S38">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T38">
         <v>1.9</v>
       </c>
       <c r="U38">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W38">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X38">
         <v>40</v>
@@ -10114,13 +10114,13 @@
         <v>13.5</v>
       </c>
       <c r="AC38">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AD38">
         <v>55</v>
       </c>
       <c r="AE38">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AF38">
         <v>10</v>
@@ -10129,13 +10129,13 @@
         <v>11.5</v>
       </c>
       <c r="AH38">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI38">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK38">
         <v>13.5</v>
@@ -10144,13 +10144,13 @@
         <v>30</v>
       </c>
       <c r="AM38">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN38">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AO38">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP38">
         <v>34</v>
@@ -10165,7 +10165,7 @@
         <v>55</v>
       </c>
       <c r="AT38">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU38">
         <v>15.5</v>
@@ -10174,7 +10174,7 @@
         <v>40</v>
       </c>
       <c r="AW38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX38">
         <v>9.199999999999999</v>
@@ -10183,28 +10183,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA38">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB38">
         <v>9.6</v>
       </c>
       <c r="BC38">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD38">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE38">
         <v>65</v>
       </c>
       <c r="BF38">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH38">
         <v>5.8</v>
@@ -10246,7 +10246,7 @@
         <v>1000</v>
       </c>
       <c r="BU38">
-        <v>8.6</v>
+        <v>2.04</v>
       </c>
       <c r="BV38">
         <v>1000</v>
@@ -10290,7 +10290,7 @@
         <v>1.77</v>
       </c>
       <c r="G39">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H39">
         <v>6</v>
@@ -10314,31 +10314,31 @@
         <v>2.72</v>
       </c>
       <c r="O39">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P39">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q39">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S39">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T39">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U39">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V39">
         <v>1.17</v>
       </c>
       <c r="W39">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X39">
         <v>9</v>
@@ -10347,16 +10347,16 @@
         <v>15</v>
       </c>
       <c r="Z39">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB39">
         <v>6</v>
       </c>
       <c r="AC39">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD39">
         <v>27</v>
@@ -10428,7 +10428,7 @@
         <v>26</v>
       </c>
       <c r="BA39">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="BB39">
         <v>16.5</v>
@@ -10437,7 +10437,7 @@
         <v>21</v>
       </c>
       <c r="BD39">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE39">
         <v>50</v>
@@ -10595,7 +10595,7 @@
         <v>1000</v>
       </c>
       <c r="AB40">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC40">
         <v>1000</v>
@@ -10607,10 +10607,10 @@
         <v>1000</v>
       </c>
       <c r="AF40">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG40">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH40">
         <v>1000</v>
@@ -10622,16 +10622,16 @@
         <v>900</v>
       </c>
       <c r="AK40">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL40">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM40">
         <v>1000</v>
       </c>
       <c r="AN40">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO40">
         <v>1000</v>
@@ -10694,61 +10694,61 @@
         <v>1000</v>
       </c>
       <c r="BI40">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
       </c>
       <c r="BK40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN40">
         <v>1000</v>
       </c>
       <c r="BO40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP40">
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT40">
         <v>1000</v>
       </c>
       <c r="BU40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB40" t="s">
         <v>241</v>
@@ -10774,7 +10774,7 @@
         <v>3.05</v>
       </c>
       <c r="G41">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H41">
         <v>2.58</v>
@@ -10783,10 +10783,10 @@
         <v>2.76</v>
       </c>
       <c r="J41">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K41">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L41">
         <v>1.49</v>
@@ -10795,34 +10795,34 @@
         <v>1.11</v>
       </c>
       <c r="N41">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O41">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P41">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q41">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R41">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S41">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T41">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U41">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V41">
         <v>1.56</v>
       </c>
       <c r="W41">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X41">
         <v>10</v>
@@ -10834,10 +10834,10 @@
         <v>17</v>
       </c>
       <c r="AA41">
-        <v>740</v>
+        <v>900</v>
       </c>
       <c r="AB41">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC41">
         <v>7.4</v>
@@ -10855,7 +10855,7 @@
         <v>14.5</v>
       </c>
       <c r="AH41">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI41">
         <v>70</v>
@@ -10864,13 +10864,13 @@
         <v>900</v>
       </c>
       <c r="AK41">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL41">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM41">
-        <v>810</v>
+        <v>720</v>
       </c>
       <c r="AN41">
         <v>65</v>
@@ -10888,7 +10888,7 @@
         <v>14</v>
       </c>
       <c r="AS41">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AT41">
         <v>8.6</v>
@@ -10900,37 +10900,37 @@
         <v>11</v>
       </c>
       <c r="AW41">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AX41">
         <v>16.5</v>
       </c>
       <c r="AY41">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ41">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA41">
         <v>10</v>
       </c>
       <c r="BB41">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BC41">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BD41">
         <v>10.5</v>
       </c>
       <c r="BE41">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF41">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BG41">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BH41">
         <v>3.45</v>
@@ -10939,58 +10939,58 @@
         <v>2.34</v>
       </c>
       <c r="BJ41">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK41">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
       <c r="BN41">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO41">
-        <v>4.5</v>
+        <v>1.71</v>
       </c>
       <c r="BP41">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ41">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="BR41">
         <v>1000</v>
       </c>
       <c r="BS41">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="BT41">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU41">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="BV41">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW41">
-        <v>3.1</v>
+        <v>1.47</v>
       </c>
       <c r="BX41">
         <v>1000</v>
       </c>
       <c r="BY41">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="BZ41">
         <v>1000</v>
       </c>
       <c r="CA41">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="CB41" t="s">
         <v>241</v>
@@ -11013,7 +11013,7 @@
         <v>226</v>
       </c>
       <c r="F42">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G42">
         <v>2.44</v>
@@ -11049,10 +11049,10 @@
         <v>1.9</v>
       </c>
       <c r="R42">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S42">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T42">
         <v>1.75</v>
@@ -11076,19 +11076,19 @@
         <v>23</v>
       </c>
       <c r="AA42">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB42">
         <v>11.5</v>
       </c>
       <c r="AC42">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD42">
         <v>14.5</v>
       </c>
       <c r="AE42">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF42">
         <v>16.5</v>
@@ -11106,7 +11106,7 @@
         <v>32</v>
       </c>
       <c r="AK42">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL42">
         <v>34</v>
@@ -11121,7 +11121,7 @@
         <v>32</v>
       </c>
       <c r="AP42">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ42">
         <v>12.5</v>
@@ -11136,13 +11136,13 @@
         <v>10.5</v>
       </c>
       <c r="AU42">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV42">
         <v>13</v>
       </c>
       <c r="AW42">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX42">
         <v>14.5</v>
@@ -11151,13 +11151,13 @@
         <v>10</v>
       </c>
       <c r="AZ42">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA42">
         <v>36</v>
       </c>
       <c r="BB42">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC42">
         <v>21</v>
@@ -11294,13 +11294,13 @@
         <v>1.98</v>
       </c>
       <c r="S43">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="T43">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U43">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V43">
         <v>1.03</v>
@@ -11399,7 +11399,7 @@
         <v>6.8</v>
       </c>
       <c r="BB43">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC43">
         <v>12.5</v>
@@ -11497,22 +11497,22 @@
         <v>228</v>
       </c>
       <c r="F44">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G44">
         <v>2.4</v>
       </c>
       <c r="H44">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I44">
         <v>3.9</v>
       </c>
       <c r="J44">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K44">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L44">
         <v>1.48</v>
@@ -11521,16 +11521,16 @@
         <v>1.11</v>
       </c>
       <c r="N44">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O44">
         <v>1.46</v>
       </c>
       <c r="P44">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q44">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R44">
         <v>1.25</v>
@@ -11539,13 +11539,13 @@
         <v>4.6</v>
       </c>
       <c r="T44">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U44">
         <v>1.9</v>
       </c>
       <c r="V44">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
         <v>1.71</v>
@@ -11563,13 +11563,13 @@
         <v>95</v>
       </c>
       <c r="AB44">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC44">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD44">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE44">
         <v>60</v>
@@ -11578,7 +11578,7 @@
         <v>14</v>
       </c>
       <c r="AG44">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH44">
         <v>22</v>
@@ -11599,10 +11599,10 @@
         <v>500</v>
       </c>
       <c r="AN44">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO44">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP44">
         <v>9</v>
@@ -11620,13 +11620,13 @@
         <v>7.2</v>
       </c>
       <c r="AU44">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV44">
         <v>14</v>
       </c>
       <c r="AW44">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX44">
         <v>12</v>
@@ -11638,16 +11638,16 @@
         <v>18</v>
       </c>
       <c r="BA44">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB44">
         <v>7.8</v>
       </c>
       <c r="BC44">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BD44">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE44">
         <v>9.6</v>
@@ -11656,7 +11656,7 @@
         <v>17</v>
       </c>
       <c r="BG44">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -11716,7 +11716,7 @@
         <v>46</v>
       </c>
       <c r="CA44">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CB44" t="s">
         <v>241</v>
@@ -11739,22 +11739,22 @@
         <v>229</v>
       </c>
       <c r="F45">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="G45">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H45">
+        <v>2.98</v>
+      </c>
+      <c r="I45">
         <v>3.1</v>
       </c>
-      <c r="I45">
-        <v>3.25</v>
-      </c>
       <c r="J45">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K45">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L45">
         <v>1.52</v>
@@ -11769,7 +11769,7 @@
         <v>1.55</v>
       </c>
       <c r="P45">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q45">
         <v>2.62</v>
@@ -11778,7 +11778,7 @@
         <v>1.21</v>
       </c>
       <c r="S45">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T45">
         <v>2.12</v>
@@ -11787,37 +11787,37 @@
         <v>1.84</v>
       </c>
       <c r="V45">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W45">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X45">
         <v>8.800000000000001</v>
       </c>
       <c r="Y45">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z45">
         <v>19.5</v>
       </c>
       <c r="AA45">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="AB45">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC45">
         <v>7.2</v>
       </c>
       <c r="AD45">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE45">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF45">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG45">
         <v>13.5</v>
@@ -11826,10 +11826,10 @@
         <v>23</v>
       </c>
       <c r="AI45">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ45">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AK45">
         <v>40</v>
@@ -11841,25 +11841,25 @@
         <v>1000</v>
       </c>
       <c r="AN45">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AO45">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP45">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ45">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR45">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS45">
         <v>28</v>
       </c>
       <c r="AT45">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU45">
         <v>6.4</v>
@@ -11871,7 +11871,7 @@
         <v>34</v>
       </c>
       <c r="AX45">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY45">
         <v>11.5</v>
@@ -11984,13 +11984,13 @@
         <v>1.76</v>
       </c>
       <c r="G46">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H46">
         <v>3.9</v>
       </c>
       <c r="I46">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J46">
         <v>4.1</v>
@@ -12002,7 +12002,7 @@
         <v>1.23</v>
       </c>
       <c r="M46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N46">
         <v>2.72</v>
@@ -12014,13 +12014,13 @@
         <v>2.48</v>
       </c>
       <c r="Q46">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R46">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S46">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="T46">
         <v>1.54</v>
@@ -12053,7 +12053,7 @@
         <v>13</v>
       </c>
       <c r="AD46">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE46">
         <v>55</v>
@@ -12095,10 +12095,10 @@
         <v>16.5</v>
       </c>
       <c r="AR46">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS46">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT46">
         <v>11</v>
@@ -12110,7 +12110,7 @@
         <v>13.5</v>
       </c>
       <c r="AW46">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX46">
         <v>11</v>
@@ -12122,7 +12122,7 @@
         <v>12</v>
       </c>
       <c r="BA46">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB46">
         <v>15.5</v>
@@ -12134,13 +12134,13 @@
         <v>19</v>
       </c>
       <c r="BE46">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF46">
         <v>5.7</v>
       </c>
       <c r="BG46">
-        <v>22</v>
+        <v>3.95</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12226,7 +12226,7 @@
         <v>1.82</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H47">
         <v>4.2</v>
@@ -12241,13 +12241,13 @@
         <v>4.1</v>
       </c>
       <c r="L47">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M47">
         <v>1.06</v>
       </c>
       <c r="N47">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O47">
         <v>1.28</v>
@@ -12256,19 +12256,19 @@
         <v>1.96</v>
       </c>
       <c r="Q47">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R47">
         <v>1.38</v>
       </c>
       <c r="S47">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T47">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="U47">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="V47">
         <v>1.24</v>
@@ -12465,64 +12465,64 @@
         <v>232</v>
       </c>
       <c r="F48">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="G48">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H48">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I48">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J48">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K48">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="L48">
         <v>1.01</v>
       </c>
       <c r="M48">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O48">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P48">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q48">
         <v>2.62</v>
       </c>
       <c r="R48">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S48">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T48">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U48">
         <v>1.7</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W48">
         <v>1.45</v>
       </c>
       <c r="X48">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y48">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="Z48">
         <v>500</v>
@@ -12534,7 +12534,7 @@
         <v>500</v>
       </c>
       <c r="AC48">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD48">
         <v>500</v>
@@ -12573,58 +12573,58 @@
         <v>500</v>
       </c>
       <c r="AP48">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ48">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AR48">
         <v>12</v>
       </c>
       <c r="AS48">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AT48">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU48">
-        <v>5.7</v>
+        <v>1.31</v>
       </c>
       <c r="AV48">
-        <v>12</v>
+        <v>1.57</v>
       </c>
       <c r="AW48">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AX48">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AY48">
-        <v>12</v>
+        <v>1.49</v>
       </c>
       <c r="AZ48">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BA48">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="BB48">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="BC48">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BD48">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="BE48">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BF48">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="BG48">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -12707,10 +12707,10 @@
         <v>233</v>
       </c>
       <c r="F49">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G49">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H49">
         <v>2.74</v>
@@ -12719,13 +12719,13 @@
         <v>2.78</v>
       </c>
       <c r="J49">
+        <v>3.3</v>
+      </c>
+      <c r="K49">
         <v>3.35</v>
       </c>
-      <c r="K49">
-        <v>3.4</v>
-      </c>
       <c r="L49">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M49">
         <v>1.08</v>
@@ -12737,10 +12737,10 @@
         <v>1.36</v>
       </c>
       <c r="P49">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q49">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R49">
         <v>1.31</v>
@@ -12809,10 +12809,10 @@
         <v>110</v>
       </c>
       <c r="AN49">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO49">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP49">
         <v>11</v>
@@ -12827,7 +12827,7 @@
         <v>36</v>
       </c>
       <c r="AT49">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU49">
         <v>6.4</v>
@@ -12851,7 +12851,7 @@
         <v>40</v>
       </c>
       <c r="BB49">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BC49">
         <v>30</v>
@@ -12878,7 +12878,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK49">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BL49">
         <v>1000</v>
@@ -12964,10 +12964,10 @@
         <v>3.65</v>
       </c>
       <c r="K50">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L50">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M50">
         <v>1.07</v>
@@ -13015,10 +13015,10 @@
         <v>160</v>
       </c>
       <c r="AB50">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC50">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="AD50">
         <v>25</v>
@@ -13063,10 +13063,10 @@
         <v>14.5</v>
       </c>
       <c r="AR50">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AS50">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT50">
         <v>7.4</v>
@@ -13078,7 +13078,7 @@
         <v>17.5</v>
       </c>
       <c r="AW50">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX50">
         <v>9.6</v>
@@ -13090,7 +13090,7 @@
         <v>18</v>
       </c>
       <c r="BA50">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB50">
         <v>17</v>
@@ -13099,76 +13099,76 @@
         <v>17.5</v>
       </c>
       <c r="BD50">
+        <v>4.7</v>
+      </c>
+      <c r="BE50">
         <v>4.9</v>
-      </c>
-      <c r="BE50">
-        <v>5</v>
       </c>
       <c r="BF50">
         <v>11</v>
       </c>
       <c r="BG50">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH50">
         <v>1000</v>
       </c>
       <c r="BI50">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BJ50">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK50">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BN50">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO50">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BP50">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ50">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BR50">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS50">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BT50">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU50">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV50">
         <v>1000</v>
       </c>
       <c r="BW50">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BX50">
         <v>1000</v>
       </c>
       <c r="BY50">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA50">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="s">
         <v>241</v>
@@ -13209,7 +13209,7 @@
         <v>5.2</v>
       </c>
       <c r="L51">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M51">
         <v>1.04</v>
@@ -13230,10 +13230,10 @@
         <v>1.54</v>
       </c>
       <c r="S51">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T51">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U51">
         <v>2.12</v>
@@ -13254,7 +13254,7 @@
         <v>11</v>
       </c>
       <c r="AA51">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AB51">
         <v>29</v>
@@ -13272,13 +13272,13 @@
         <v>75</v>
       </c>
       <c r="AG51">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AH51">
         <v>26</v>
       </c>
       <c r="AI51">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ51">
         <v>220</v>
@@ -13311,7 +13311,7 @@
         <v>12</v>
       </c>
       <c r="AT51">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AU51">
         <v>10</v>
@@ -13323,7 +13323,7 @@
         <v>13</v>
       </c>
       <c r="AX51">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY51">
         <v>21</v>
@@ -13332,22 +13332,22 @@
         <v>17.5</v>
       </c>
       <c r="BA51">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="BB51">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC51">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD51">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BE51">
+        <v>6</v>
+      </c>
+      <c r="BF51">
         <v>5.8</v>
-      </c>
-      <c r="BF51">
-        <v>5.4</v>
       </c>
       <c r="BG51">
         <v>5.6</v>
@@ -13451,7 +13451,7 @@
         <v>17</v>
       </c>
       <c r="L52">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M52">
         <v>1.01</v>
@@ -13469,10 +13469,10 @@
         <v>1.27</v>
       </c>
       <c r="R52">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S52">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="T52">
         <v>2.42</v>
@@ -13520,7 +13520,7 @@
         <v>85</v>
       </c>
       <c r="AI52">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="AJ52">
         <v>9.199999999999999</v>
@@ -13532,7 +13532,7 @@
         <v>75</v>
       </c>
       <c r="AM52">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="AN52">
         <v>2.5</v>
@@ -13556,7 +13556,7 @@
         <v>11.5</v>
       </c>
       <c r="AU52">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV52">
         <v>6.2</v>
@@ -13598,61 +13598,61 @@
         <v>1000</v>
       </c>
       <c r="BI52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ52">
         <v>1000</v>
       </c>
       <c r="BK52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL52">
         <v>1000</v>
       </c>
       <c r="BM52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN52">
         <v>1000</v>
       </c>
       <c r="BO52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP52">
         <v>1000</v>
       </c>
       <c r="BQ52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR52">
         <v>1000</v>
       </c>
       <c r="BS52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT52">
         <v>1000</v>
       </c>
       <c r="BU52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV52">
         <v>1000</v>
       </c>
       <c r="BW52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX52">
         <v>1000</v>
       </c>
       <c r="BY52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ52">
         <v>1000</v>
       </c>
       <c r="CA52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB52" t="s">
         <v>241</v>
@@ -13675,16 +13675,16 @@
         <v>237</v>
       </c>
       <c r="F53">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="G53">
         <v>3.3</v>
       </c>
       <c r="H53">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I53">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J53">
         <v>2.92</v>
@@ -13699,22 +13699,22 @@
         <v>1.06</v>
       </c>
       <c r="N53">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O53">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P53">
         <v>1.58</v>
       </c>
       <c r="Q53">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="R53">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S53">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T53">
         <v>1.9</v>
@@ -13840,61 +13840,61 @@
         <v>1000</v>
       </c>
       <c r="BI53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ53">
         <v>1000</v>
       </c>
       <c r="BK53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL53">
         <v>1000</v>
       </c>
       <c r="BM53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN53">
         <v>1000</v>
       </c>
       <c r="BO53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP53">
         <v>1000</v>
       </c>
       <c r="BQ53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR53">
         <v>1000</v>
       </c>
       <c r="BS53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT53">
         <v>1000</v>
       </c>
       <c r="BU53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV53">
         <v>1000</v>
       </c>
       <c r="BW53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX53">
         <v>1000</v>
       </c>
       <c r="BY53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ53">
         <v>1000</v>
       </c>
       <c r="CA53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB53" t="s">
         <v>241</v>
@@ -13941,16 +13941,16 @@
         <v>1.12</v>
       </c>
       <c r="N54">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O54">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P54">
         <v>1.6</v>
       </c>
       <c r="Q54">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R54">
         <v>1.21</v>
@@ -13959,7 +13959,7 @@
         <v>5.4</v>
       </c>
       <c r="T54">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U54">
         <v>1.71</v>
@@ -13971,7 +13971,7 @@
         <v>2.12</v>
       </c>
       <c r="X54">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y54">
         <v>13.5</v>
@@ -13989,13 +13989,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD54">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE54">
         <v>690</v>
       </c>
       <c r="AF54">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG54">
         <v>11.5</v>
@@ -14055,13 +14055,13 @@
         <v>10</v>
       </c>
       <c r="AZ54">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BA54">
         <v>42</v>
       </c>
       <c r="BB54">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC54">
         <v>17</v>
@@ -14165,115 +14165,115 @@
         <v>4.5</v>
       </c>
       <c r="H55">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I55">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J55">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K55">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L55">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="M55">
         <v>1.12</v>
       </c>
       <c r="N55">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O55">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="P55">
         <v>1.59</v>
       </c>
       <c r="Q55">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R55">
         <v>1.21</v>
       </c>
       <c r="S55">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T55">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U55">
         <v>1.8</v>
       </c>
       <c r="V55">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W55">
         <v>1.28</v>
       </c>
       <c r="X55">
+        <v>9</v>
+      </c>
+      <c r="Y55">
+        <v>7.2</v>
+      </c>
+      <c r="Z55">
         <v>11.5</v>
       </c>
-      <c r="Y55">
-        <v>7.6</v>
-      </c>
-      <c r="Z55">
+      <c r="AA55">
+        <v>30</v>
+      </c>
+      <c r="AB55">
         <v>12</v>
       </c>
-      <c r="AA55">
-        <v>900</v>
-      </c>
-      <c r="AB55">
-        <v>16.5</v>
-      </c>
       <c r="AC55">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AD55">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE55">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AF55">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AG55">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AH55">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AI55">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ55">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK55">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL55">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AM55">
         <v>500</v>
       </c>
       <c r="AN55">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AO55">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AP55">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ55">
         <v>6.6</v>
       </c>
       <c r="AR55">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS55">
         <v>22</v>
@@ -14288,10 +14288,10 @@
         <v>10</v>
       </c>
       <c r="AW55">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="AX55">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY55">
         <v>16</v>
@@ -14300,22 +14300,22 @@
         <v>21</v>
       </c>
       <c r="BA55">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BB55">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC55">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD55">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BE55">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BF55">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BG55">
         <v>21</v>
@@ -14401,7 +14401,7 @@
         <v>240</v>
       </c>
       <c r="F56">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G56">
         <v>2.14</v>
@@ -14416,7 +14416,7 @@
         <v>3.45</v>
       </c>
       <c r="K56">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L56">
         <v>1.42</v>
@@ -14431,7 +14431,7 @@
         <v>1.37</v>
       </c>
       <c r="P56">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q56">
         <v>2.08</v>
@@ -14443,10 +14443,10 @@
         <v>3.85</v>
       </c>
       <c r="T56">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U56">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V56">
         <v>1.31</v>
@@ -14455,7 +14455,7 @@
         <v>1.88</v>
       </c>
       <c r="X56">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y56">
         <v>14.5</v>
@@ -14479,7 +14479,7 @@
         <v>65</v>
       </c>
       <c r="AF56">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG56">
         <v>11</v>
@@ -14515,10 +14515,10 @@
         <v>12</v>
       </c>
       <c r="AR56">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS56">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT56">
         <v>7.8</v>
@@ -14530,7 +14530,7 @@
         <v>15</v>
       </c>
       <c r="AW56">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX56">
         <v>11</v>
@@ -14542,7 +14542,7 @@
         <v>17</v>
       </c>
       <c r="BA56">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB56">
         <v>21</v>
@@ -14551,16 +14551,16 @@
         <v>19.5</v>
       </c>
       <c r="BD56">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE56">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF56">
         <v>14.5</v>
       </c>
       <c r="BG56">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH56">
         <v>3.35</v>
@@ -14602,7 +14602,7 @@
         <v>7.8</v>
       </c>
       <c r="BU56">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV56">
         <v>38</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-04.xlsx
@@ -739,7 +739,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-10-03 21:16:40</t>
+    <t>2026-10-03 23:29:48</t>
   </si>
 </sst>
 </file>
@@ -1333,226 +1333,226 @@
         <v>186</v>
       </c>
       <c r="F2">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="G2">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="I2">
-        <v>9.4</v>
+        <v>680</v>
       </c>
       <c r="J2">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="K2">
-        <v>5.3</v>
+        <v>750</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="P2">
-        <v>2.2</v>
+        <v>1.02</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="R2">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>2.96</v>
+        <v>1.03</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>11.5</v>
+        <v>990</v>
       </c>
       <c r="AD2">
-        <v>34</v>
+        <v>990</v>
       </c>
       <c r="AE2">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>990</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>990</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>3.9</v>
+        <v>590</v>
       </c>
       <c r="BO2">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>910</v>
       </c>
       <c r="BS2">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>12.5</v>
+        <v>690</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>15.5</v>
+        <v>960</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>241</v>
@@ -1575,226 +1575,226 @@
         <v>187</v>
       </c>
       <c r="F3">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="H3">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="I3">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="L3">
+        <v>2.42</v>
+      </c>
+      <c r="M3">
+        <v>1.19</v>
+      </c>
+      <c r="N3">
+        <v>2.06</v>
+      </c>
+      <c r="O3">
+        <v>1.86</v>
+      </c>
+      <c r="P3">
+        <v>1.34</v>
+      </c>
+      <c r="Q3">
+        <v>3.55</v>
+      </c>
+      <c r="R3">
+        <v>1.11</v>
+      </c>
+      <c r="S3">
+        <v>9.6</v>
+      </c>
+      <c r="T3">
+        <v>2.56</v>
+      </c>
+      <c r="U3">
+        <v>1.54</v>
+      </c>
+      <c r="V3">
         <v>1.53</v>
       </c>
-      <c r="M3">
-        <v>1.11</v>
-      </c>
-      <c r="N3">
-        <v>2.88</v>
-      </c>
-      <c r="O3">
-        <v>1.47</v>
-      </c>
-      <c r="P3">
-        <v>1.65</v>
-      </c>
-      <c r="Q3">
-        <v>2.4</v>
-      </c>
-      <c r="R3">
-        <v>1.24</v>
-      </c>
-      <c r="S3">
-        <v>4.7</v>
-      </c>
-      <c r="T3">
-        <v>2.02</v>
-      </c>
-      <c r="U3">
-        <v>1.89</v>
-      </c>
-      <c r="V3">
-        <v>1.64</v>
-      </c>
       <c r="W3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="Y3">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="Z3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA3">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AF3">
+        <v>20</v>
+      </c>
+      <c r="AG3">
+        <v>22</v>
+      </c>
+      <c r="AH3">
+        <v>42</v>
+      </c>
+      <c r="AI3">
+        <v>150</v>
+      </c>
+      <c r="AJ3">
+        <v>80</v>
+      </c>
+      <c r="AK3">
+        <v>80</v>
+      </c>
+      <c r="AL3">
+        <v>150</v>
+      </c>
+      <c r="AM3">
+        <v>430</v>
+      </c>
+      <c r="AN3">
+        <v>120</v>
+      </c>
+      <c r="AO3">
+        <v>90</v>
+      </c>
+      <c r="AP3">
+        <v>5.5</v>
+      </c>
+      <c r="AQ3">
+        <v>5.9</v>
+      </c>
+      <c r="AR3">
+        <v>14</v>
+      </c>
+      <c r="AS3">
+        <v>40</v>
+      </c>
+      <c r="AT3">
+        <v>6.8</v>
+      </c>
+      <c r="AU3">
+        <v>6.8</v>
+      </c>
+      <c r="AV3">
+        <v>14</v>
+      </c>
+      <c r="AW3">
+        <v>48</v>
+      </c>
+      <c r="AX3">
+        <v>16.5</v>
+      </c>
+      <c r="AY3">
+        <v>15.5</v>
+      </c>
+      <c r="AZ3">
+        <v>30</v>
+      </c>
+      <c r="BA3">
+        <v>85</v>
+      </c>
+      <c r="BB3">
+        <v>60</v>
+      </c>
+      <c r="BC3">
+        <v>55</v>
+      </c>
+      <c r="BD3">
+        <v>100</v>
+      </c>
+      <c r="BE3">
+        <v>230</v>
+      </c>
+      <c r="BF3">
+        <v>90</v>
+      </c>
+      <c r="BG3">
+        <v>60</v>
+      </c>
+      <c r="BH3">
+        <v>1.73</v>
+      </c>
+      <c r="BI3">
+        <v>1.61</v>
+      </c>
+      <c r="BJ3">
+        <v>29</v>
+      </c>
+      <c r="BK3">
         <v>23</v>
       </c>
-      <c r="AG3">
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
         <v>15</v>
       </c>
-      <c r="AH3">
-        <v>21</v>
-      </c>
-      <c r="AI3">
-        <v>65</v>
-      </c>
-      <c r="AJ3">
-        <v>75</v>
-      </c>
-      <c r="AK3">
-        <v>60</v>
-      </c>
-      <c r="AL3">
-        <v>75</v>
-      </c>
-      <c r="AM3">
-        <v>170</v>
-      </c>
-      <c r="AN3">
-        <v>60</v>
-      </c>
-      <c r="AO3">
-        <v>34</v>
-      </c>
-      <c r="AP3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ3">
+      <c r="BN3">
         <v>7.4</v>
       </c>
-      <c r="AR3">
-        <v>12.5</v>
-      </c>
-      <c r="AS3">
-        <v>28</v>
-      </c>
-      <c r="AT3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU3">
+      <c r="BO3">
+        <v>6.2</v>
+      </c>
+      <c r="BP3">
+        <v>85</v>
+      </c>
+      <c r="BQ3">
+        <v>50</v>
+      </c>
+      <c r="BR3">
+        <v>910</v>
+      </c>
+      <c r="BS3">
+        <v>14.5</v>
+      </c>
+      <c r="BT3">
         <v>6.6</v>
       </c>
-      <c r="AV3">
-        <v>10.5</v>
-      </c>
-      <c r="AW3">
-        <v>26</v>
-      </c>
-      <c r="AX3">
-        <v>19</v>
-      </c>
-      <c r="AY3">
-        <v>13</v>
-      </c>
-      <c r="AZ3">
-        <v>19</v>
-      </c>
-      <c r="BA3">
+      <c r="BU3">
+        <v>5.6</v>
+      </c>
+      <c r="BV3">
+        <v>70</v>
+      </c>
+      <c r="BW3">
         <v>38</v>
       </c>
-      <c r="BB3">
-        <v>42</v>
-      </c>
-      <c r="BC3">
-        <v>38</v>
-      </c>
-      <c r="BD3">
-        <v>46</v>
-      </c>
-      <c r="BE3">
-        <v>110</v>
-      </c>
-      <c r="BF3">
-        <v>44</v>
-      </c>
-      <c r="BG3">
-        <v>23</v>
-      </c>
-      <c r="BH3">
-        <v>2.9</v>
-      </c>
-      <c r="BI3">
-        <v>2.7</v>
-      </c>
-      <c r="BJ3">
-        <v>10.5</v>
-      </c>
-      <c r="BK3">
-        <v>6.4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
+      <c r="BX3">
+        <v>950</v>
+      </c>
+      <c r="BY3">
         <v>14.5</v>
       </c>
-      <c r="BN3">
-        <v>6.4</v>
-      </c>
-      <c r="BO3">
-        <v>5.5</v>
-      </c>
-      <c r="BP3">
-        <v>32</v>
-      </c>
-      <c r="BQ3">
-        <v>10.5</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>12</v>
-      </c>
-      <c r="BT3">
-        <v>5.3</v>
-      </c>
-      <c r="BU3">
-        <v>4.6</v>
-      </c>
-      <c r="BV3">
-        <v>21</v>
-      </c>
-      <c r="BW3">
-        <v>9</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>11.5</v>
-      </c>
       <c r="BZ3">
-        <v>42</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="s">
         <v>241</v>
@@ -1817,67 +1817,67 @@
         <v>188</v>
       </c>
       <c r="F4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G4">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H4">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I4">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J4">
         <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
         <v>1.89</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
         <v>1.34</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T4">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W4">
         <v>1.24</v>
       </c>
       <c r="X4">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
         <v>8.4</v>
       </c>
       <c r="Z4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA4">
         <v>22</v>
@@ -1886,7 +1886,7 @@
         <v>17</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
@@ -1895,7 +1895,7 @@
         <v>22</v>
       </c>
       <c r="AF4">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AG4">
         <v>21</v>
@@ -1904,31 +1904,31 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AK4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL4">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AM4">
-        <v>190</v>
+        <v>520</v>
       </c>
       <c r="AN4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AO4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AP4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR4">
         <v>9.800000000000001</v>
@@ -1937,7 +1937,7 @@
         <v>17</v>
       </c>
       <c r="AT4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
@@ -1946,40 +1946,40 @@
         <v>9</v>
       </c>
       <c r="AW4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY4">
         <v>16</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>100</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI4">
         <v>3.05</v>
@@ -1988,31 +1988,31 @@
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>130</v>
       </c>
       <c r="BN4">
         <v>8.199999999999999</v>
       </c>
       <c r="BO4">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BT4">
         <v>4.5</v>
@@ -2021,22 +2021,22 @@
         <v>4</v>
       </c>
       <c r="BV4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>241</v>
@@ -2059,49 +2059,49 @@
         <v>189</v>
       </c>
       <c r="F5">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G5">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H5">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J5">
         <v>3.75</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
         <v>2.22</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R5">
         <v>1.48</v>
       </c>
       <c r="S5">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="T5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
         <v>2.46</v>
@@ -2110,25 +2110,25 @@
         <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y5">
         <v>15</v>
       </c>
       <c r="Z5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
         <v>13.5</v>
@@ -2143,7 +2143,7 @@
         <v>12</v>
       </c>
       <c r="AH5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI5">
         <v>55</v>
@@ -2152,19 +2152,19 @@
         <v>36</v>
       </c>
       <c r="AK5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL5">
         <v>50</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO5">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AP5">
         <v>16.5</v>
@@ -2176,7 +2176,7 @@
         <v>17.5</v>
       </c>
       <c r="AS5">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -2194,10 +2194,10 @@
         <v>15.5</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA5">
         <v>30</v>
@@ -2206,16 +2206,16 @@
         <v>25</v>
       </c>
       <c r="BC5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE5">
         <v>10.5</v>
       </c>
       <c r="BF5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG5">
         <v>20</v>
@@ -2224,19 +2224,19 @@
         <v>3.85</v>
       </c>
       <c r="BI5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN5">
         <v>5.7</v>
@@ -2245,19 +2245,19 @@
         <v>5</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU5">
         <v>5.6</v>
@@ -2266,19 +2266,19 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="s">
         <v>241</v>
@@ -2301,40 +2301,40 @@
         <v>190</v>
       </c>
       <c r="F6">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H6">
         <v>2.38</v>
       </c>
       <c r="I6">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="J6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
         <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M6">
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
         <v>1.43</v>
       </c>
       <c r="P6">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q6">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R6">
         <v>1.26</v>
@@ -2343,25 +2343,25 @@
         <v>4.5</v>
       </c>
       <c r="T6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U6">
         <v>1.97</v>
       </c>
       <c r="V6">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W6">
         <v>1.4</v>
       </c>
       <c r="X6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y6">
         <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA6">
         <v>42</v>
@@ -2406,7 +2406,7 @@
         <v>70</v>
       </c>
       <c r="AO6">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AP6">
         <v>9.800000000000001</v>
@@ -2424,7 +2424,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
         <v>10.5</v>
@@ -2442,7 +2442,7 @@
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB6">
         <v>7.2</v>
@@ -2460,7 +2460,7 @@
         <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2487,7 +2487,7 @@
         <v>5.7</v>
       </c>
       <c r="BP6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ6">
         <v>11</v>
@@ -2505,10 +2505,10 @@
         <v>4.6</v>
       </c>
       <c r="BV6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX6">
         <v>38</v>
@@ -2546,55 +2546,55 @@
         <v>3.85</v>
       </c>
       <c r="G7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7">
         <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O7">
         <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R7">
         <v>1.37</v>
       </c>
       <c r="S7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T7">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U7">
         <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X7">
         <v>16</v>
@@ -2609,13 +2609,13 @@
         <v>26</v>
       </c>
       <c r="AB7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC7">
         <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE7">
         <v>23</v>
@@ -2642,7 +2642,7 @@
         <v>65</v>
       </c>
       <c r="AM7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN7">
         <v>55</v>
@@ -2675,16 +2675,16 @@
         <v>18</v>
       </c>
       <c r="AX7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY7">
         <v>14</v>
       </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB7">
         <v>50</v>
@@ -2693,13 +2693,13 @@
         <v>36</v>
       </c>
       <c r="BD7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BG7">
         <v>12</v>
@@ -2714,31 +2714,31 @@
         <v>10</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN7">
         <v>7.8</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP7">
         <v>36</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7">
         <v>44</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT7">
         <v>5</v>
@@ -2750,19 +2750,19 @@
         <v>15</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX7">
         <v>29</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7">
         <v>25</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
         <v>241</v>
@@ -2785,43 +2785,43 @@
         <v>192</v>
       </c>
       <c r="F8">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G8">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H8">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I8">
+        <v>3.55</v>
+      </c>
+      <c r="J8">
         <v>3.6</v>
       </c>
-      <c r="J8">
-        <v>3.45</v>
-      </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>1.32</v>
       </c>
       <c r="P8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R8">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S8">
         <v>3.5</v>
@@ -2830,91 +2830,91 @@
         <v>1.77</v>
       </c>
       <c r="U8">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X8">
         <v>15</v>
       </c>
       <c r="Y8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z8">
         <v>26</v>
       </c>
       <c r="AA8">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB8">
         <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
+        <v>15</v>
+      </c>
+      <c r="AE8">
+        <v>42</v>
+      </c>
+      <c r="AF8">
         <v>14.5</v>
       </c>
-      <c r="AE8">
-        <v>46</v>
-      </c>
-      <c r="AF8">
-        <v>15.5</v>
-      </c>
       <c r="AG8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH8">
+        <v>17.5</v>
+      </c>
+      <c r="AI8">
+        <v>50</v>
+      </c>
+      <c r="AJ8">
+        <v>30</v>
+      </c>
+      <c r="AK8">
+        <v>24</v>
+      </c>
+      <c r="AL8">
+        <v>38</v>
+      </c>
+      <c r="AM8">
+        <v>95</v>
+      </c>
+      <c r="AN8">
         <v>18</v>
       </c>
-      <c r="AI8">
-        <v>55</v>
-      </c>
-      <c r="AJ8">
-        <v>36</v>
-      </c>
-      <c r="AK8">
-        <v>26</v>
-      </c>
-      <c r="AL8">
-        <v>44</v>
-      </c>
-      <c r="AM8">
-        <v>110</v>
-      </c>
-      <c r="AN8">
-        <v>19.5</v>
-      </c>
       <c r="AO8">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP8">
+        <v>13.5</v>
+      </c>
+      <c r="AQ8">
         <v>12.5</v>
-      </c>
-      <c r="AQ8">
-        <v>11.5</v>
       </c>
       <c r="AR8">
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="AT8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW8">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
@@ -2926,43 +2926,43 @@
         <v>16</v>
       </c>
       <c r="BA8">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB8">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD8">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BE8">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="BF8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG8">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BH8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI8">
         <v>3.1</v>
       </c>
       <c r="BJ8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN8">
         <v>5.2</v>
@@ -2974,19 +2974,19 @@
         <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BR8">
         <v>32</v>
       </c>
       <c r="BS8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT8">
         <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV8">
         <v>28</v>
@@ -2995,13 +2995,13 @@
         <v>10</v>
       </c>
       <c r="BX8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY8">
         <v>11</v>
       </c>
       <c r="BZ8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA8">
         <v>9.800000000000001</v>
@@ -3045,7 +3045,7 @@
         <v>6.4</v>
       </c>
       <c r="L9">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="M9">
         <v>1.04</v>
@@ -3069,7 +3069,7 @@
         <v>2.46</v>
       </c>
       <c r="T9">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U9">
         <v>1.9</v>
@@ -3111,7 +3111,7 @@
         <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI9">
         <v>460</v>
@@ -3198,13 +3198,13 @@
         <v>12</v>
       </c>
       <c r="BK9">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN9">
         <v>4.1</v>
@@ -3216,37 +3216,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BQ9">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BR9">
         <v>23</v>
       </c>
       <c r="BS9">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="BT9">
         <v>13.5</v>
       </c>
       <c r="BU9">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>12.5</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="CB9" t="s">
         <v>241</v>
@@ -3269,7 +3269,7 @@
         <v>194</v>
       </c>
       <c r="F10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G10">
         <v>1.42</v>
@@ -3296,25 +3296,25 @@
         <v>6</v>
       </c>
       <c r="O10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q10">
         <v>1.49</v>
       </c>
       <c r="R10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S10">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="T10">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
         <v>1.12</v>
@@ -3332,7 +3332,7 @@
         <v>130</v>
       </c>
       <c r="AA10">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB10">
         <v>13</v>
@@ -3341,19 +3341,19 @@
         <v>14.5</v>
       </c>
       <c r="AD10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE10">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="AF10">
+        <v>11.5</v>
+      </c>
+      <c r="AG10">
         <v>11</v>
       </c>
-      <c r="AG10">
-        <v>11.5</v>
-      </c>
       <c r="AH10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI10">
         <v>230</v>
@@ -3362,16 +3362,16 @@
         <v>13.5</v>
       </c>
       <c r="AK10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM10">
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO10">
         <v>130</v>
@@ -3386,13 +3386,13 @@
         <v>55</v>
       </c>
       <c r="AS10">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10">
         <v>10</v>
       </c>
       <c r="AU10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV10">
         <v>25</v>
@@ -3401,16 +3401,16 @@
         <v>55</v>
       </c>
       <c r="AX10">
+        <v>9</v>
+      </c>
+      <c r="AY10">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AY10">
-        <v>9</v>
       </c>
       <c r="AZ10">
         <v>19</v>
       </c>
       <c r="BA10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB10">
         <v>10.5</v>
@@ -3511,25 +3511,25 @@
         <v>195</v>
       </c>
       <c r="F11">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G11">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H11">
         <v>2.64</v>
       </c>
       <c r="I11">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
         <v>3.85</v>
       </c>
       <c r="L11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M11">
         <v>1.06</v>
@@ -3547,10 +3547,10 @@
         <v>1.82</v>
       </c>
       <c r="R11">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T11">
         <v>1.67</v>
@@ -3559,19 +3559,19 @@
         <v>2.34</v>
       </c>
       <c r="V11">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W11">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y11">
         <v>15</v>
       </c>
       <c r="Z11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA11">
         <v>46</v>
@@ -3580,16 +3580,16 @@
         <v>15</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG11">
         <v>12.5</v>
@@ -3598,7 +3598,7 @@
         <v>18.5</v>
       </c>
       <c r="AI11">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ11">
         <v>48</v>
@@ -3613,7 +3613,7 @@
         <v>320</v>
       </c>
       <c r="AN11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO11">
         <v>25</v>
@@ -3652,25 +3652,25 @@
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB11">
         <v>18</v>
       </c>
       <c r="BC11">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BD11">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="BE11">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG11">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BH11">
         <v>4.1</v>
@@ -3765,7 +3765,7 @@
         <v>3.7</v>
       </c>
       <c r="J12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
         <v>3.7</v>
@@ -3777,16 +3777,16 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O12">
         <v>1.34</v>
       </c>
       <c r="P12">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q12">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R12">
         <v>1.35</v>
@@ -3795,10 +3795,10 @@
         <v>3.55</v>
       </c>
       <c r="T12">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U12">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V12">
         <v>1.37</v>
@@ -3807,7 +3807,7 @@
         <v>1.74</v>
       </c>
       <c r="X12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y12">
         <v>13.5</v>
@@ -3816,7 +3816,7 @@
         <v>26</v>
       </c>
       <c r="AA12">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB12">
         <v>10</v>
@@ -3861,7 +3861,7 @@
         <v>50</v>
       </c>
       <c r="AP12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12">
         <v>11.5</v>
@@ -3870,7 +3870,7 @@
         <v>19</v>
       </c>
       <c r="AS12">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AT12">
         <v>8.800000000000001</v>
@@ -3882,7 +3882,7 @@
         <v>13</v>
       </c>
       <c r="AW12">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX12">
         <v>12.5</v>
@@ -3894,25 +3894,25 @@
         <v>15</v>
       </c>
       <c r="BA12">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BB12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC12">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BD12">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BE12">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG12">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BH12">
         <v>3.4</v>
@@ -3995,16 +3995,16 @@
         <v>197</v>
       </c>
       <c r="F13">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="G13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H13">
         <v>2.1</v>
       </c>
       <c r="I13">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J13">
         <v>3.8</v>
@@ -4019,31 +4019,31 @@
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O13">
         <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R13">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S13">
         <v>2.32</v>
       </c>
       <c r="T13">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="U13">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V13">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="W13">
         <v>1.4</v>
@@ -4118,7 +4118,7 @@
         <v>15.5</v>
       </c>
       <c r="AU13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV13">
         <v>9.800000000000001</v>
@@ -4139,7 +4139,7 @@
         <v>20</v>
       </c>
       <c r="BB13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC13">
         <v>16</v>
@@ -4154,46 +4154,46 @@
         <v>16.5</v>
       </c>
       <c r="BG13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI13">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="BJ13">
         <v>9</v>
       </c>
       <c r="BK13">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BN13">
         <v>7.8</v>
       </c>
       <c r="BO13">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BP13">
         <v>25</v>
       </c>
       <c r="BQ13">
-        <v>16.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="BT13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU13">
         <v>4.5</v>
@@ -4202,19 +4202,19 @@
         <v>15.5</v>
       </c>
       <c r="BW13">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="BX13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY13">
-        <v>17</v>
+        <v>5.3</v>
       </c>
       <c r="BZ13">
         <v>17.5</v>
       </c>
       <c r="CA13">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="CB13" t="s">
         <v>241</v>
@@ -4237,25 +4237,25 @@
         <v>198</v>
       </c>
       <c r="F14">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G14">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="H14">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="I14">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J14">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
         <v>3.7</v>
       </c>
       <c r="L14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M14">
         <v>1.05</v>
@@ -4276,19 +4276,19 @@
         <v>1.52</v>
       </c>
       <c r="S14">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T14">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U14">
         <v>2.48</v>
       </c>
       <c r="V14">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X14">
         <v>22</v>
@@ -4315,7 +4315,7 @@
         <v>28</v>
       </c>
       <c r="AF14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG14">
         <v>13</v>
@@ -4327,7 +4327,7 @@
         <v>36</v>
       </c>
       <c r="AJ14">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AK14">
         <v>32</v>
@@ -4351,13 +4351,13 @@
         <v>13</v>
       </c>
       <c r="AR14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS14">
         <v>34</v>
       </c>
       <c r="AT14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU14">
         <v>7.4</v>
@@ -4372,7 +4372,7 @@
         <v>17</v>
       </c>
       <c r="AY14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ14">
         <v>13.5</v>
@@ -4384,7 +4384,7 @@
         <v>34</v>
       </c>
       <c r="BC14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD14">
         <v>27</v>
@@ -4396,7 +4396,7 @@
         <v>13.5</v>
       </c>
       <c r="BG14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH14">
         <v>4.3</v>
@@ -4414,7 +4414,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BN14">
         <v>6.2</v>
@@ -4426,13 +4426,13 @@
         <v>19</v>
       </c>
       <c r="BQ14">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="BT14">
         <v>6.4</v>
@@ -4441,22 +4441,22 @@
         <v>5.2</v>
       </c>
       <c r="BV14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW14">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BX14">
         <v>38</v>
       </c>
       <c r="BY14">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14">
         <v>19</v>
       </c>
       <c r="CA14">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="CB14" t="s">
         <v>241</v>
@@ -4479,13 +4479,13 @@
         <v>199</v>
       </c>
       <c r="F15">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G15">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I15">
         <v>18.5</v>
@@ -4518,7 +4518,7 @@
         <v>1.08</v>
       </c>
       <c r="S15">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4530,13 +4530,13 @@
         <v>1.2</v>
       </c>
       <c r="W15">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="X15">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y15">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z15">
         <v>120</v>
@@ -4545,25 +4545,25 @@
         <v>900</v>
       </c>
       <c r="AB15">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AC15">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AD15">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="AE15">
         <v>260</v>
       </c>
       <c r="AF15">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AG15">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="AH15">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI15">
         <v>350</v>
@@ -4572,7 +4572,7 @@
         <v>900</v>
       </c>
       <c r="AK15">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AL15">
         <v>180</v>
@@ -4587,52 +4587,52 @@
         <v>600</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AU15">
         <v>4.9</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BF15">
         <v>1.55</v>
@@ -4724,7 +4724,7 @@
         <v>2.72</v>
       </c>
       <c r="G16">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H16">
         <v>2.84</v>
@@ -4838,7 +4838,7 @@
         <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT16">
         <v>10.5</v>
@@ -4862,43 +4862,43 @@
         <v>15</v>
       </c>
       <c r="BA16">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB16">
         <v>30</v>
       </c>
       <c r="BC16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE16">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BF16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG16">
         <v>22</v>
       </c>
       <c r="BH16">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BI16">
         <v>3.1</v>
       </c>
       <c r="BJ16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK16">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL16">
         <v>140</v>
       </c>
       <c r="BM16">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BN16">
         <v>6.6</v>
@@ -4910,13 +4910,13 @@
         <v>22</v>
       </c>
       <c r="BQ16">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR16">
         <v>36</v>
       </c>
       <c r="BS16">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BT16">
         <v>6.2</v>
@@ -4928,19 +4928,19 @@
         <v>23</v>
       </c>
       <c r="BW16">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BX16">
         <v>36</v>
       </c>
       <c r="BY16">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ16">
         <v>29</v>
       </c>
       <c r="CA16">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CB16" t="s">
         <v>241</v>
@@ -4963,16 +4963,16 @@
         <v>201</v>
       </c>
       <c r="F17">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G17">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H17">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I17">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="J17">
         <v>3.95</v>
@@ -4981,10 +4981,10 @@
         <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
         <v>5.5</v>
@@ -4993,28 +4993,28 @@
         <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R17">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S17">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T17">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U17">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V17">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W17">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X17">
         <v>27</v>
@@ -5041,7 +5041,7 @@
         <v>28</v>
       </c>
       <c r="AF17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG17">
         <v>13</v>
@@ -5050,7 +5050,7 @@
         <v>15.5</v>
       </c>
       <c r="AI17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ17">
         <v>38</v>
@@ -5059,16 +5059,16 @@
         <v>25</v>
       </c>
       <c r="AL17">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM17">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN17">
+        <v>13</v>
+      </c>
+      <c r="AO17">
         <v>15.5</v>
-      </c>
-      <c r="AO17">
-        <v>16.5</v>
       </c>
       <c r="AP17">
         <v>21</v>
@@ -5077,19 +5077,19 @@
         <v>14.5</v>
       </c>
       <c r="AR17">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS17">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU17">
         <v>8.6</v>
       </c>
       <c r="AV17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW17">
         <v>21</v>
@@ -5101,88 +5101,88 @@
         <v>10.5</v>
       </c>
       <c r="AZ17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA17">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BB17">
         <v>16</v>
       </c>
       <c r="BC17">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BD17">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BE17">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BF17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG17">
         <v>13.5</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI17">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ17">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>1.78</v>
+        <v>5.6</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.06</v>
+        <v>9</v>
       </c>
       <c r="BN17">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BO17">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BP17">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BQ17">
-        <v>1.93</v>
+        <v>6.4</v>
       </c>
       <c r="BR17">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS17">
-        <v>1.99</v>
+        <v>7.2</v>
       </c>
       <c r="BT17">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BU17">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV17">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="BW17">
-        <v>1.95</v>
+        <v>6.6</v>
       </c>
       <c r="BX17">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BY17">
-        <v>1.99</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="CA17">
-        <v>1.92</v>
+        <v>6.2</v>
       </c>
       <c r="CB17" t="s">
         <v>241</v>
@@ -5214,7 +5214,7 @@
         <v>3.75</v>
       </c>
       <c r="I18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -5226,7 +5226,7 @@
         <v>1.28</v>
       </c>
       <c r="M18">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
         <v>5.6</v>
@@ -5241,37 +5241,37 @@
         <v>1.55</v>
       </c>
       <c r="R18">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S18">
         <v>2.36</v>
       </c>
       <c r="T18">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U18">
         <v>2.56</v>
       </c>
       <c r="V18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
         <v>1.98</v>
       </c>
       <c r="X18">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Y18">
         <v>25</v>
       </c>
       <c r="Z18">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA18">
         <v>900</v>
       </c>
       <c r="AB18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC18">
         <v>10.5</v>
@@ -5301,16 +5301,16 @@
         <v>19.5</v>
       </c>
       <c r="AL18">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM18">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN18">
         <v>8.800000000000001</v>
       </c>
       <c r="AO18">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AP18">
         <v>19.5</v>
@@ -5319,10 +5319,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AS18">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="AT18">
         <v>12</v>
@@ -5334,19 +5334,19 @@
         <v>14.5</v>
       </c>
       <c r="AW18">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="AX18">
         <v>13</v>
       </c>
       <c r="AY18">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18">
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BB18">
         <v>19.5</v>
@@ -5355,10 +5355,10 @@
         <v>15.5</v>
       </c>
       <c r="BD18">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BE18">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="BF18">
         <v>7.6</v>
@@ -5367,7 +5367,7 @@
         <v>21</v>
       </c>
       <c r="BH18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI18">
         <v>4</v>
@@ -5376,55 +5376,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK18">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN18">
         <v>5.2</v>
       </c>
       <c r="BO18">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR18">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT18">
         <v>7.8</v>
       </c>
       <c r="BU18">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ18">
         <v>15</v>
       </c>
       <c r="CA18">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB18" t="s">
         <v>241</v>
@@ -5450,217 +5450,217 @@
         <v>2.38</v>
       </c>
       <c r="G19">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="H19">
         <v>2.56</v>
       </c>
       <c r="I19">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="J19">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="K19">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="O19">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P19">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="Q19">
+        <v>1.43</v>
+      </c>
+      <c r="R19">
+        <v>1.75</v>
+      </c>
+      <c r="S19">
+        <v>2.08</v>
+      </c>
+      <c r="T19">
         <v>1.41</v>
       </c>
-      <c r="R19">
-        <v>1.73</v>
-      </c>
-      <c r="S19">
-        <v>2.06</v>
-      </c>
-      <c r="T19">
-        <v>1.11</v>
-      </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W19">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y19">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="Z19">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="AA19">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AB19">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="AC19">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="AD19">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="AE19">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="AF19">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="AG19">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="AH19">
-        <v>160</v>
+        <v>16.5</v>
       </c>
       <c r="AI19">
-        <v>230</v>
+        <v>32</v>
       </c>
       <c r="AJ19">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AK19">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="AL19">
-        <v>210</v>
+        <v>32</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ19">
-        <v>1.17</v>
+        <v>15.5</v>
       </c>
       <c r="AR19">
-        <v>1.18</v>
+        <v>18.5</v>
       </c>
       <c r="AS19">
-        <v>1.19</v>
+        <v>4.9</v>
       </c>
       <c r="AT19">
-        <v>1.18</v>
+        <v>14.5</v>
       </c>
       <c r="AU19">
-        <v>1.17</v>
+        <v>8.6</v>
       </c>
       <c r="AV19">
-        <v>1.18</v>
+        <v>10.5</v>
       </c>
       <c r="AW19">
-        <v>1.19</v>
+        <v>18.5</v>
       </c>
       <c r="AX19">
-        <v>1.18</v>
+        <v>17</v>
       </c>
       <c r="AY19">
-        <v>1.17</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>1.18</v>
+        <v>11</v>
       </c>
       <c r="BA19">
-        <v>1.19</v>
+        <v>20</v>
       </c>
       <c r="BB19">
-        <v>1.19</v>
+        <v>4.8</v>
       </c>
       <c r="BC19">
-        <v>1.19</v>
+        <v>17</v>
       </c>
       <c r="BD19">
-        <v>1.19</v>
+        <v>20</v>
       </c>
       <c r="BE19">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="BF19">
-        <v>1.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5689,226 +5689,226 @@
         <v>204</v>
       </c>
       <c r="F20">
-        <v>1.66</v>
+        <v>2.48</v>
       </c>
       <c r="G20">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="H20">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="I20">
-        <v>990</v>
+        <v>3.05</v>
       </c>
       <c r="J20">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
+        <v>3.85</v>
+      </c>
+      <c r="O20">
         <v>1.25</v>
       </c>
-      <c r="O20">
-        <v>1.02</v>
-      </c>
       <c r="P20">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="Q20">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="R20">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S20">
-        <v>1.05</v>
+        <v>2.68</v>
       </c>
       <c r="T20">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="V20">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="X20">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Y20">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="Z20">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="AA20">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB20">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AC20">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="AE20">
         <v>260</v>
       </c>
       <c r="AF20">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AG20">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="AH20">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AI20">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AJ20">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AK20">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AL20">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AM20">
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AO20">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU20">
         <v>5.1</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF20">
-        <v>2.86</v>
+        <v>5.9</v>
       </c>
       <c r="BG20">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB20" t="s">
         <v>241</v>
@@ -5934,16 +5934,16 @@
         <v>2.12</v>
       </c>
       <c r="G21">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H21">
         <v>4</v>
       </c>
       <c r="I21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K21">
         <v>3.4</v>
@@ -5955,19 +5955,19 @@
         <v>1.11</v>
       </c>
       <c r="N21">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O21">
         <v>1.47</v>
       </c>
       <c r="P21">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q21">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S21">
         <v>4.8</v>
@@ -5982,7 +5982,7 @@
         <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X21">
         <v>10.5</v>
@@ -5991,7 +5991,7 @@
         <v>12.5</v>
       </c>
       <c r="Z21">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="AA21">
         <v>900</v>
@@ -6024,7 +6024,7 @@
         <v>110</v>
       </c>
       <c r="AK21">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL21">
         <v>290</v>
@@ -6033,10 +6033,10 @@
         <v>580</v>
       </c>
       <c r="AN21">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO21">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="AP21">
         <v>8.800000000000001</v>
@@ -6048,7 +6048,7 @@
         <v>13.5</v>
       </c>
       <c r="AS21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT21">
         <v>6.6</v>
@@ -6060,7 +6060,7 @@
         <v>15</v>
       </c>
       <c r="AW21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX21">
         <v>11</v>
@@ -6081,19 +6081,19 @@
         <v>13.5</v>
       </c>
       <c r="BD21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI21">
         <v>2.6</v>
@@ -6173,40 +6173,40 @@
         <v>206</v>
       </c>
       <c r="F22">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G22">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I22">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J22">
         <v>4.2</v>
       </c>
       <c r="K22">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M22">
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="O22">
         <v>1.12</v>
       </c>
       <c r="P22">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="Q22">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R22">
         <v>1.83</v>
@@ -6215,16 +6215,16 @@
         <v>1.82</v>
       </c>
       <c r="T22">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U22">
         <v>3.05</v>
       </c>
       <c r="V22">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X22">
         <v>48</v>
@@ -6335,58 +6335,58 @@
         <v>3.25</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO22">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6415,22 +6415,22 @@
         <v>207</v>
       </c>
       <c r="F23">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="G23">
-        <v>990</v>
+        <v>2.24</v>
       </c>
       <c r="H23">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="I23">
         <v>990</v>
       </c>
       <c r="J23">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6439,22 +6439,22 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O23">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P23">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Q23">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="R23">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="S23">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="T23">
         <v>1.11</v>
@@ -6463,172 +6463,172 @@
         <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="X23">
         <v>1000</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE23">
         <v>1000</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI23">
         <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM23">
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO23">
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AQ23">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AR23">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AS23">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AT23">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AU23">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AV23">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AW23">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AX23">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AY23">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AZ23">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BA23">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BB23">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BC23">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BD23">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BE23">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6657,166 +6657,166 @@
         <v>208</v>
       </c>
       <c r="F24">
-        <v>2.26</v>
+        <v>3.25</v>
       </c>
       <c r="G24">
-        <v>990</v>
+        <v>4</v>
       </c>
       <c r="H24">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="I24">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="J24">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="K24">
-        <v>500</v>
+        <v>3.85</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O24">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="P24">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q24">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="R24">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S24">
         <v>1.05</v>
       </c>
       <c r="T24">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U24">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="W24">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X24">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA24">
         <v>900</v>
       </c>
       <c r="AB24">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AC24">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD24">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE24">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF24">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AG24">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AH24">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AI24">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AJ24">
         <v>900</v>
       </c>
       <c r="AK24">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AQ24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AR24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AT24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AU24">
-        <v>4.9</v>
+        <v>1.05</v>
       </c>
       <c r="AV24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AX24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AY24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AZ24">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BC24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BF24">
         <v>1.55</v>
       </c>
       <c r="BG24">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6905,7 +6905,7 @@
         <v>1.66</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I25">
         <v>6.6</v>
@@ -6914,7 +6914,7 @@
         <v>4.2</v>
       </c>
       <c r="K25">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L25">
         <v>1.36</v>
@@ -6932,16 +6932,16 @@
         <v>2.18</v>
       </c>
       <c r="Q25">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R25">
         <v>1.46</v>
       </c>
       <c r="S25">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T25">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="U25">
         <v>2.04</v>
@@ -7010,7 +7010,7 @@
         <v>16</v>
       </c>
       <c r="AQ25">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR25">
         <v>42</v>
@@ -7025,10 +7025,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV25">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AW25">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AX25">
         <v>9</v>
@@ -7040,19 +7040,19 @@
         <v>17.5</v>
       </c>
       <c r="BA25">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="BB25">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC25">
         <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE25">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF25">
         <v>7.4</v>
@@ -7494,7 +7494,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ27">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AR27">
         <v>10</v>
@@ -7566,7 +7566,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO27">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BP27">
         <v>1000</v>
@@ -7628,16 +7628,16 @@
         <v>2.18</v>
       </c>
       <c r="G28">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H28">
         <v>2.96</v>
       </c>
       <c r="I28">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K28">
         <v>4.2</v>
@@ -7649,88 +7649,88 @@
         <v>1.07</v>
       </c>
       <c r="N28">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O28">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P28">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="Q28">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="R28">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S28">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T28">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="U28">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="V28">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X28">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y28">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z28">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA28">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB28">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC28">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD28">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE28">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AF28">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH28">
+        <v>21</v>
+      </c>
+      <c r="AI28">
+        <v>60</v>
+      </c>
+      <c r="AJ28">
+        <v>36</v>
+      </c>
+      <c r="AK28">
+        <v>28</v>
+      </c>
+      <c r="AL28">
+        <v>46</v>
+      </c>
+      <c r="AM28">
+        <v>110</v>
+      </c>
+      <c r="AN28">
         <v>23</v>
       </c>
-      <c r="AI28">
-        <v>70</v>
-      </c>
-      <c r="AJ28">
-        <v>42</v>
-      </c>
-      <c r="AK28">
-        <v>34</v>
-      </c>
-      <c r="AL28">
-        <v>55</v>
-      </c>
-      <c r="AM28">
-        <v>440</v>
-      </c>
-      <c r="AN28">
-        <v>29</v>
-      </c>
       <c r="AO28">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AP28">
         <v>5.6</v>
@@ -7739,10 +7739,10 @@
         <v>6.2</v>
       </c>
       <c r="AR28">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AS28">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT28">
         <v>5.6</v>
@@ -7751,100 +7751,100 @@
         <v>4.4</v>
       </c>
       <c r="AV28">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AW28">
+        <v>4.6</v>
+      </c>
+      <c r="AX28">
+        <v>4</v>
+      </c>
+      <c r="AY28">
+        <v>7.6</v>
+      </c>
+      <c r="AZ28">
         <v>4.1</v>
       </c>
-      <c r="AX28">
-        <v>3.6</v>
-      </c>
-      <c r="AY28">
-        <v>3.4</v>
-      </c>
-      <c r="AZ28">
-        <v>3.75</v>
-      </c>
       <c r="BA28">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB28">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC28">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BD28">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE28">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF28">
         <v>6</v>
       </c>
       <c r="BG28">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="s">
         <v>241</v>
@@ -7867,22 +7867,22 @@
         <v>213</v>
       </c>
       <c r="F29">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="G29">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H29">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I29">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J29">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K29">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7891,46 +7891,46 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="O29">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="P29">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="Q29">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R29">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="S29">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="T29">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U29">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
         <v>1.16</v>
       </c>
       <c r="W29">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="X29">
         <v>44</v>
       </c>
       <c r="Y29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z29">
         <v>70</v>
       </c>
       <c r="AA29">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AB29">
         <v>18</v>
@@ -7939,10 +7939,10 @@
         <v>14</v>
       </c>
       <c r="AD29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE29">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF29">
         <v>15.5</v>
@@ -7951,10 +7951,10 @@
         <v>13</v>
       </c>
       <c r="AH29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI29">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ29">
         <v>18</v>
@@ -7963,70 +7963,70 @@
         <v>16.5</v>
       </c>
       <c r="AL29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM29">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN29">
         <v>4.8</v>
       </c>
       <c r="AO29">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP29">
+        <v>5.8</v>
+      </c>
+      <c r="AQ29">
+        <v>5.7</v>
+      </c>
+      <c r="AR29">
+        <v>6</v>
+      </c>
+      <c r="AS29">
+        <v>6.4</v>
+      </c>
+      <c r="AT29">
+        <v>4.8</v>
+      </c>
+      <c r="AU29">
+        <v>11.5</v>
+      </c>
+      <c r="AV29">
         <v>5.4</v>
       </c>
-      <c r="AQ29">
-        <v>5.3</v>
-      </c>
-      <c r="AR29">
-        <v>5.6</v>
-      </c>
-      <c r="AS29">
-        <v>5.9</v>
-      </c>
-      <c r="AT29">
-        <v>4.5</v>
-      </c>
-      <c r="AU29">
-        <v>6.2</v>
-      </c>
-      <c r="AV29">
+      <c r="AW29">
+        <v>6</v>
+      </c>
+      <c r="AX29">
+        <v>4.6</v>
+      </c>
+      <c r="AY29">
+        <v>9.6</v>
+      </c>
+      <c r="AZ29">
         <v>5</v>
       </c>
-      <c r="AW29">
-        <v>5.6</v>
-      </c>
-      <c r="AX29">
-        <v>4.4</v>
-      </c>
-      <c r="AY29">
-        <v>6.2</v>
-      </c>
-      <c r="AZ29">
+      <c r="BA29">
+        <v>6</v>
+      </c>
+      <c r="BB29">
         <v>4.8</v>
       </c>
-      <c r="BA29">
-        <v>5.6</v>
-      </c>
-      <c r="BB29">
-        <v>4.5</v>
-      </c>
       <c r="BC29">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD29">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BE29">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF29">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="BG29">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8112,19 +8112,19 @@
         <v>1.55</v>
       </c>
       <c r="G30">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="H30">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I30">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="J30">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8145,7 +8145,7 @@
         <v>1.16</v>
       </c>
       <c r="R30">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="S30">
         <v>1.27</v>
@@ -8154,13 +8154,13 @@
         <v>1.11</v>
       </c>
       <c r="U30">
-        <v>1.12</v>
+        <v>1.86</v>
       </c>
       <c r="V30">
         <v>1.19</v>
       </c>
       <c r="W30">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8178,7 +8178,7 @@
         <v>1000</v>
       </c>
       <c r="AC30">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD30">
         <v>1000</v>
@@ -8190,7 +8190,7 @@
         <v>1000</v>
       </c>
       <c r="AG30">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AH30">
         <v>1000</v>
@@ -8232,7 +8232,7 @@
         <v>7.4</v>
       </c>
       <c r="AU30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AV30">
         <v>16</v>
@@ -8256,7 +8256,7 @@
         <v>10</v>
       </c>
       <c r="BC30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BD30">
         <v>24</v>
@@ -8274,61 +8274,61 @@
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30">
         <v>1000</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="s">
         <v>241</v>
@@ -8351,19 +8351,19 @@
         <v>215</v>
       </c>
       <c r="F31">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G31">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="H31">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I31">
         <v>13.5</v>
       </c>
       <c r="J31">
-        <v>3.15</v>
+        <v>2.32</v>
       </c>
       <c r="K31">
         <v>8.4</v>
@@ -8375,22 +8375,22 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>1.11</v>
+        <v>2.82</v>
       </c>
       <c r="O31">
         <v>1.22</v>
       </c>
       <c r="P31">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Q31">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R31">
         <v>1.08</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T31">
         <v>1.11</v>
@@ -8402,13 +8402,13 @@
         <v>1.27</v>
       </c>
       <c r="W31">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X31">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y31">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z31">
         <v>500</v>
@@ -8417,13 +8417,13 @@
         <v>900</v>
       </c>
       <c r="AB31">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC31">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD31">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE31">
         <v>500</v>
@@ -8432,10 +8432,10 @@
         <v>500</v>
       </c>
       <c r="AG31">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH31">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI31">
         <v>500</v>
@@ -8459,118 +8459,118 @@
         <v>500</v>
       </c>
       <c r="AP31">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ31">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AR31">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AS31">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="AT31">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU31">
         <v>4.9</v>
       </c>
       <c r="AV31">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AW31">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="AX31">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AY31">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AZ31">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="BA31">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="BB31">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="BC31">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="BD31">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="BE31">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BF31">
         <v>5.5</v>
       </c>
       <c r="BG31">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="BH31">
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN31">
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP31">
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT31">
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="s">
         <v>241</v>
@@ -8593,19 +8593,19 @@
         <v>216</v>
       </c>
       <c r="F32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G32">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H32">
         <v>1.02</v>
       </c>
       <c r="I32">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J32">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K32">
         <v>950</v>
@@ -8623,10 +8623,10 @@
         <v>1.21</v>
       </c>
       <c r="P32">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Q32">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R32">
         <v>1.08</v>
@@ -8641,7 +8641,7 @@
         <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32">
         <v>1.01</v>
@@ -8701,52 +8701,52 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
         <v>1.01</v>
@@ -8838,10 +8838,10 @@
         <v>1.49</v>
       </c>
       <c r="G33">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="I33">
         <v>7.2</v>
@@ -8886,13 +8886,13 @@
         <v>1.16</v>
       </c>
       <c r="W33">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="X33">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Y33">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Z33">
         <v>85</v>
@@ -8901,10 +8901,10 @@
         <v>470</v>
       </c>
       <c r="AB33">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC33">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD33">
         <v>1000</v>
@@ -8916,10 +8916,10 @@
         <v>500</v>
       </c>
       <c r="AG33">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH33">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AI33">
         <v>160</v>
@@ -8937,64 +8937,64 @@
         <v>260</v>
       </c>
       <c r="AN33">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO33">
         <v>80</v>
       </c>
       <c r="AP33">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="AQ33">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="AR33">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="AS33">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AT33">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AU33">
+        <v>5.6</v>
+      </c>
+      <c r="AV33">
+        <v>1.79</v>
+      </c>
+      <c r="AW33">
+        <v>1.78</v>
+      </c>
+      <c r="AX33">
         <v>2.5</v>
       </c>
-      <c r="AV33">
-        <v>1.03</v>
-      </c>
-      <c r="AW33">
-        <v>1.03</v>
-      </c>
-      <c r="AX33">
-        <v>1.03</v>
-      </c>
       <c r="AY33">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AZ33">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="BA33">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="BB33">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="BC33">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="BD33">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="BE33">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="BF33">
         <v>2.42</v>
       </c>
       <c r="BG33">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9131,10 +9131,10 @@
         <v>2.24</v>
       </c>
       <c r="X34">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="Y34">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Z34">
         <v>470</v>
@@ -9143,13 +9143,13 @@
         <v>1000</v>
       </c>
       <c r="AB34">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AC34">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AD34">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AE34">
         <v>1000</v>
@@ -9158,10 +9158,10 @@
         <v>85</v>
       </c>
       <c r="AG34">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AH34">
-        <v>190</v>
+        <v>950</v>
       </c>
       <c r="AI34">
         <v>1000</v>
@@ -9185,55 +9185,55 @@
         <v>140</v>
       </c>
       <c r="AP34">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AQ34">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AR34">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AS34">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AT34">
         <v>5.1</v>
       </c>
       <c r="AU34">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="AV34">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AW34">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AX34">
         <v>2.5</v>
       </c>
       <c r="AY34">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AZ34">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BA34">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BB34">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="BC34">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BD34">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BE34">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BF34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BG34">
         <v>1.55</v>
@@ -9364,7 +9364,7 @@
         <v>1.77</v>
       </c>
       <c r="U35">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
         <v>1.55</v>
@@ -9412,7 +9412,7 @@
         <v>95</v>
       </c>
       <c r="AK35">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL35">
         <v>95</v>
@@ -9421,10 +9421,10 @@
         <v>190</v>
       </c>
       <c r="AN35">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO35">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP35">
         <v>13</v>
@@ -9436,7 +9436,7 @@
         <v>15.5</v>
       </c>
       <c r="AS35">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT35">
         <v>10.5</v>
@@ -9463,7 +9463,7 @@
         <v>30</v>
       </c>
       <c r="BB35">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BC35">
         <v>20</v>
@@ -9472,7 +9472,7 @@
         <v>30</v>
       </c>
       <c r="BE35">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF35">
         <v>20</v>
@@ -9564,7 +9564,7 @@
         <v>1.63</v>
       </c>
       <c r="G36">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H36">
         <v>6.2</v>
@@ -9576,16 +9576,16 @@
         <v>3.6</v>
       </c>
       <c r="K36">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M36">
         <v>1.09</v>
       </c>
       <c r="N36">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="O36">
         <v>1.4</v>
@@ -9597,139 +9597,139 @@
         <v>2.2</v>
       </c>
       <c r="R36">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S36">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="T36">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U36">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V36">
         <v>1.15</v>
       </c>
       <c r="W36">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X36">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="Y36">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="Z36">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AA36">
         <v>700</v>
       </c>
       <c r="AB36">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="AC36">
-        <v>500</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD36">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AE36">
         <v>700</v>
       </c>
       <c r="AF36">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="AG36">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH36">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AI36">
         <v>700</v>
       </c>
       <c r="AJ36">
-        <v>900</v>
+        <v>18</v>
       </c>
       <c r="AK36">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AL36">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM36">
         <v>700</v>
       </c>
       <c r="AN36">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AO36">
         <v>700</v>
       </c>
       <c r="AP36">
-        <v>1.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ36">
-        <v>1.24</v>
+        <v>13.5</v>
       </c>
       <c r="AR36">
-        <v>1.25</v>
+        <v>7.4</v>
       </c>
       <c r="AS36">
-        <v>1.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT36">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU36">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="AV36">
-        <v>1.24</v>
+        <v>20</v>
       </c>
       <c r="AW36">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="AX36">
-        <v>1.22</v>
+        <v>7</v>
       </c>
       <c r="AY36">
-        <v>1.21</v>
+        <v>8</v>
       </c>
       <c r="AZ36">
-        <v>1.23</v>
+        <v>19.5</v>
       </c>
       <c r="BA36">
-        <v>1.25</v>
+        <v>7.8</v>
       </c>
       <c r="BB36">
-        <v>1.24</v>
+        <v>13</v>
       </c>
       <c r="BC36">
-        <v>1.23</v>
+        <v>15.5</v>
       </c>
       <c r="BD36">
-        <v>1.24</v>
+        <v>7.2</v>
       </c>
       <c r="BE36">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="BF36">
-        <v>1.22</v>
+        <v>10.5</v>
       </c>
       <c r="BG36">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BH36">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI36">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BJ36">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK36">
         <v>1.04</v>
@@ -9741,25 +9741,25 @@
         <v>1.04</v>
       </c>
       <c r="BN36">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO36">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP36">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ36">
         <v>1.04</v>
       </c>
       <c r="BR36">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS36">
         <v>1.04</v>
       </c>
       <c r="BT36">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU36">
         <v>1.04</v>
@@ -9803,13 +9803,13 @@
         <v>221</v>
       </c>
       <c r="F37">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G37">
         <v>2.36</v>
       </c>
       <c r="H37">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I37">
         <v>3.65</v>
@@ -9833,7 +9833,7 @@
         <v>1.37</v>
       </c>
       <c r="P37">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q37">
         <v>2.12</v>
@@ -9878,10 +9878,10 @@
         <v>15</v>
       </c>
       <c r="AE37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF37">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG37">
         <v>11.5</v>
@@ -9890,7 +9890,7 @@
         <v>19.5</v>
       </c>
       <c r="AI37">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ37">
         <v>32</v>
@@ -9923,7 +9923,7 @@
         <v>55</v>
       </c>
       <c r="AT37">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -9956,7 +9956,7 @@
         <v>38</v>
       </c>
       <c r="BE37">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF37">
         <v>19.5</v>
@@ -10051,7 +10051,7 @@
         <v>1.26</v>
       </c>
       <c r="H38">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I38">
         <v>14.5</v>
@@ -10072,7 +10072,7 @@
         <v>7.8</v>
       </c>
       <c r="O38">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P38">
         <v>3.25</v>
@@ -10087,7 +10087,7 @@
         <v>2.02</v>
       </c>
       <c r="T38">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U38">
         <v>2.04</v>
@@ -10117,22 +10117,22 @@
         <v>17.5</v>
       </c>
       <c r="AD38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AE38">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF38">
         <v>10</v>
       </c>
       <c r="AG38">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH38">
         <v>30</v>
       </c>
       <c r="AI38">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AJ38">
         <v>10</v>
@@ -10141,13 +10141,13 @@
         <v>13.5</v>
       </c>
       <c r="AL38">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM38">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN38">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AO38">
         <v>170</v>
@@ -10162,22 +10162,22 @@
         <v>42</v>
       </c>
       <c r="AS38">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AT38">
         <v>12</v>
       </c>
       <c r="AU38">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AV38">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW38">
         <v>46</v>
       </c>
       <c r="AX38">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY38">
         <v>10.5</v>
@@ -10189,13 +10189,13 @@
         <v>42</v>
       </c>
       <c r="BB38">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC38">
         <v>12</v>
       </c>
       <c r="BD38">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE38">
         <v>65</v>
@@ -10210,61 +10210,61 @@
         <v>5.8</v>
       </c>
       <c r="BI38">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="BJ38">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK38">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>2.04</v>
+        <v>4.3</v>
       </c>
       <c r="BN38">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO38">
-        <v>1.41</v>
+        <v>3.35</v>
       </c>
       <c r="BP38">
         <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>1.66</v>
+        <v>5.1</v>
       </c>
       <c r="BR38">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS38">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="BT38">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU38">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>2.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>2.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ38">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA38">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="CB38" t="s">
         <v>241</v>
@@ -10287,10 +10287,10 @@
         <v>223</v>
       </c>
       <c r="F39">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G39">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H39">
         <v>6</v>
@@ -10311,22 +10311,22 @@
         <v>1.12</v>
       </c>
       <c r="N39">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O39">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P39">
         <v>1.58</v>
       </c>
       <c r="Q39">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R39">
         <v>1.2</v>
       </c>
       <c r="S39">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T39">
         <v>2.42</v>
@@ -10338,7 +10338,7 @@
         <v>1.17</v>
       </c>
       <c r="W39">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X39">
         <v>9</v>
@@ -10368,10 +10368,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG39">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH39">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI39">
         <v>160</v>
@@ -10380,7 +10380,7 @@
         <v>19</v>
       </c>
       <c r="AK39">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL39">
         <v>65</v>
@@ -10395,7 +10395,7 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ39">
         <v>13</v>
@@ -10428,7 +10428,7 @@
         <v>26</v>
       </c>
       <c r="BA39">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BB39">
         <v>16.5</v>
@@ -10440,7 +10440,7 @@
         <v>40</v>
       </c>
       <c r="BE39">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="BF39">
         <v>16.5</v>
@@ -10532,10 +10532,10 @@
         <v>2.04</v>
       </c>
       <c r="G40">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H40">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I40">
         <v>4.5</v>
@@ -10544,7 +10544,7 @@
         <v>2.84</v>
       </c>
       <c r="K40">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="L40">
         <v>1.39</v>
@@ -10580,7 +10580,7 @@
         <v>1.3</v>
       </c>
       <c r="W40">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10595,7 +10595,7 @@
         <v>1000</v>
       </c>
       <c r="AB40">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC40">
         <v>1000</v>
@@ -10610,7 +10610,7 @@
         <v>500</v>
       </c>
       <c r="AG40">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH40">
         <v>1000</v>
@@ -10676,7 +10676,7 @@
         <v>1.03</v>
       </c>
       <c r="BC40">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD40">
         <v>1.03</v>
@@ -10685,10 +10685,10 @@
         <v>1.03</v>
       </c>
       <c r="BF40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG40">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10834,7 +10834,7 @@
         <v>17</v>
       </c>
       <c r="AA41">
-        <v>900</v>
+        <v>410</v>
       </c>
       <c r="AB41">
         <v>10</v>
@@ -10870,7 +10870,7 @@
         <v>80</v>
       </c>
       <c r="AM41">
-        <v>720</v>
+        <v>640</v>
       </c>
       <c r="AN41">
         <v>65</v>
@@ -10912,16 +10912,16 @@
         <v>17.5</v>
       </c>
       <c r="BA41">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="BB41">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BC41">
         <v>25</v>
       </c>
       <c r="BD41">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BE41">
         <v>9</v>
@@ -11019,7 +11019,7 @@
         <v>2.44</v>
       </c>
       <c r="H42">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I42">
         <v>3.3</v>
@@ -11046,7 +11046,7 @@
         <v>2.04</v>
       </c>
       <c r="Q42">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R42">
         <v>1.41</v>
@@ -11076,7 +11076,7 @@
         <v>23</v>
       </c>
       <c r="AA42">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AB42">
         <v>11.5</v>
@@ -11130,7 +11130,7 @@
         <v>20</v>
       </c>
       <c r="AS42">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AT42">
         <v>10.5</v>
@@ -11142,7 +11142,7 @@
         <v>13</v>
       </c>
       <c r="AW42">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AX42">
         <v>14.5</v>
@@ -11157,16 +11157,16 @@
         <v>36</v>
       </c>
       <c r="BB42">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="BC42">
         <v>21</v>
       </c>
       <c r="BD42">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BE42">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="BF42">
         <v>14</v>
@@ -11190,7 +11190,7 @@
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BN42">
         <v>5.3</v>
@@ -11208,7 +11208,7 @@
         <v>29</v>
       </c>
       <c r="BS42">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="BT42">
         <v>6.4</v>
@@ -11220,19 +11220,19 @@
         <v>25</v>
       </c>
       <c r="BW42">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX42">
         <v>36</v>
       </c>
       <c r="BY42">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BZ42">
         <v>25</v>
       </c>
       <c r="CA42">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB42" t="s">
         <v>241</v>
@@ -11258,7 +11258,7 @@
         <v>1.13</v>
       </c>
       <c r="G43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H43">
         <v>23</v>
@@ -11267,7 +11267,7 @@
         <v>34</v>
       </c>
       <c r="J43">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="K43">
         <v>13</v>
@@ -11306,13 +11306,13 @@
         <v>1.03</v>
       </c>
       <c r="W43">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="X43">
         <v>60</v>
       </c>
       <c r="Y43">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="Z43">
         <v>320</v>
@@ -11327,7 +11327,7 @@
         <v>28</v>
       </c>
       <c r="AD43">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AE43">
         <v>490</v>
@@ -11351,7 +11351,7 @@
         <v>16.5</v>
       </c>
       <c r="AL43">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AM43">
         <v>260</v>
@@ -11375,7 +11375,7 @@
         <v>7</v>
       </c>
       <c r="AT43">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU43">
         <v>21</v>
@@ -11387,7 +11387,7 @@
         <v>6.8</v>
       </c>
       <c r="AX43">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY43">
         <v>12</v>
@@ -11399,7 +11399,7 @@
         <v>6.8</v>
       </c>
       <c r="BB43">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC43">
         <v>12.5</v>
@@ -11420,61 +11420,61 @@
         <v>1000</v>
       </c>
       <c r="BI43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN43">
         <v>1000</v>
       </c>
       <c r="BO43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP43">
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT43">
         <v>1000</v>
       </c>
       <c r="BU43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV43">
         <v>1000</v>
       </c>
       <c r="BW43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ43">
         <v>1000</v>
       </c>
       <c r="CA43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB43" t="s">
         <v>241</v>
@@ -11506,7 +11506,7 @@
         <v>3.6</v>
       </c>
       <c r="I44">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J44">
         <v>3.2</v>
@@ -11659,64 +11659,64 @@
         <v>9</v>
       </c>
       <c r="BH44">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI44">
-        <v>1.98</v>
+        <v>2.64</v>
       </c>
       <c r="BJ44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK44">
-        <v>1.72</v>
+        <v>7.4</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>1.98</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN44">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BO44">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP44">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BQ44">
-        <v>1.82</v>
+        <v>6.6</v>
       </c>
       <c r="BR44">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BS44">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT44">
+        <v>7.2</v>
+      </c>
+      <c r="BU44">
+        <v>5.8</v>
+      </c>
+      <c r="BV44">
+        <v>36</v>
+      </c>
+      <c r="BW44">
+        <v>8</v>
+      </c>
+      <c r="BX44">
+        <v>55</v>
+      </c>
+      <c r="BY44">
+        <v>8.6</v>
+      </c>
+      <c r="BZ44">
+        <v>40</v>
+      </c>
+      <c r="CA44">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BU44">
-        <v>5</v>
-      </c>
-      <c r="BV44">
-        <v>40</v>
-      </c>
-      <c r="BW44">
-        <v>1.89</v>
-      </c>
-      <c r="BX44">
-        <v>1000</v>
-      </c>
-      <c r="BY44">
-        <v>1.92</v>
-      </c>
-      <c r="BZ44">
-        <v>46</v>
-      </c>
-      <c r="CA44">
-        <v>1.91</v>
       </c>
       <c r="CB44" t="s">
         <v>241</v>
@@ -11769,10 +11769,10 @@
         <v>1.55</v>
       </c>
       <c r="P45">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q45">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R45">
         <v>1.21</v>
@@ -11784,7 +11784,7 @@
         <v>2.12</v>
       </c>
       <c r="U45">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V45">
         <v>1.47</v>
@@ -11829,13 +11829,13 @@
         <v>70</v>
       </c>
       <c r="AJ45">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK45">
         <v>40</v>
       </c>
       <c r="AL45">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM45">
         <v>1000</v>
@@ -11856,7 +11856,7 @@
         <v>16</v>
       </c>
       <c r="AS45">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AT45">
         <v>7.8</v>
@@ -11874,7 +11874,7 @@
         <v>15</v>
       </c>
       <c r="AY45">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ45">
         <v>19</v>
@@ -11898,7 +11898,7 @@
         <v>32</v>
       </c>
       <c r="BG45">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BH45">
         <v>1000</v>
@@ -11990,7 +11990,7 @@
         <v>3.9</v>
       </c>
       <c r="I46">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J46">
         <v>4.1</v>
@@ -11999,19 +11999,19 @@
         <v>4.8</v>
       </c>
       <c r="L46">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M46">
         <v>1.02</v>
       </c>
       <c r="N46">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="O46">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P46">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q46">
         <v>1.5</v>
@@ -12026,10 +12026,10 @@
         <v>1.54</v>
       </c>
       <c r="U46">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="V46">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W46">
         <v>2.08</v>
@@ -12044,46 +12044,46 @@
         <v>46</v>
       </c>
       <c r="AA46">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AB46">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC46">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD46">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE46">
         <v>55</v>
       </c>
       <c r="AF46">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG46">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH46">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI46">
         <v>55</v>
       </c>
       <c r="AJ46">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK46">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL46">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AM46">
         <v>75</v>
       </c>
       <c r="AN46">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AO46">
         <v>38</v>
@@ -12092,115 +12092,115 @@
         <v>20</v>
       </c>
       <c r="AQ46">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AR46">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="AS46">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT46">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU46">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV46">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW46">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="AX46">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY46">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ46">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA46">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BB46">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC46">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD46">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE46">
-        <v>4.1</v>
+        <v>42</v>
       </c>
       <c r="BF46">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG46">
-        <v>3.95</v>
+        <v>22</v>
       </c>
       <c r="BH46">
         <v>1000</v>
       </c>
       <c r="BI46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ46">
         <v>1000</v>
       </c>
       <c r="BK46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL46">
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN46">
         <v>1000</v>
       </c>
       <c r="BO46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP46">
         <v>1000</v>
       </c>
       <c r="BQ46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR46">
         <v>1000</v>
       </c>
       <c r="BS46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT46">
         <v>1000</v>
       </c>
       <c r="BU46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV46">
         <v>1000</v>
       </c>
       <c r="BW46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX46">
         <v>1000</v>
       </c>
       <c r="BY46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ46">
         <v>1000</v>
       </c>
       <c r="CA46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB46" t="s">
         <v>241</v>
@@ -12388,61 +12388,61 @@
         <v>1000</v>
       </c>
       <c r="BI47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ47">
         <v>1000</v>
       </c>
       <c r="BK47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL47">
         <v>1000</v>
       </c>
       <c r="BM47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN47">
         <v>1000</v>
       </c>
       <c r="BO47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP47">
         <v>1000</v>
       </c>
       <c r="BQ47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR47">
         <v>1000</v>
       </c>
       <c r="BS47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT47">
         <v>1000</v>
       </c>
       <c r="BU47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV47">
         <v>1000</v>
       </c>
       <c r="BW47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX47">
         <v>1000</v>
       </c>
       <c r="BY47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ47">
         <v>1000</v>
       </c>
       <c r="CA47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB47" t="s">
         <v>241</v>
@@ -12471,40 +12471,40 @@
         <v>3.25</v>
       </c>
       <c r="H48">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I48">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J48">
         <v>2.82</v>
       </c>
       <c r="K48">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L48">
         <v>1.01</v>
       </c>
       <c r="M48">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="N48">
         <v>2.52</v>
       </c>
       <c r="O48">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P48">
         <v>1.46</v>
       </c>
       <c r="Q48">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="R48">
         <v>1.16</v>
       </c>
       <c r="S48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48">
         <v>2.08</v>
@@ -12513,7 +12513,7 @@
         <v>1.7</v>
       </c>
       <c r="V48">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
         <v>1.45</v>
@@ -12531,13 +12531,13 @@
         <v>900</v>
       </c>
       <c r="AB48">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC48">
         <v>970</v>
       </c>
       <c r="AD48">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE48">
         <v>500</v>
@@ -12546,10 +12546,10 @@
         <v>500</v>
       </c>
       <c r="AG48">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH48">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI48">
         <v>500</v>
@@ -12579,7 +12579,7 @@
         <v>1.34</v>
       </c>
       <c r="AR48">
-        <v>12</v>
+        <v>1.57</v>
       </c>
       <c r="AS48">
         <v>1.57</v>
@@ -12600,7 +12600,7 @@
         <v>1.57</v>
       </c>
       <c r="AY48">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AZ48">
         <v>1.57</v>
@@ -12618,7 +12618,7 @@
         <v>1.49</v>
       </c>
       <c r="BE48">
-        <v>1.57</v>
+        <v>24</v>
       </c>
       <c r="BF48">
         <v>1.49</v>
@@ -12630,61 +12630,61 @@
         <v>1000</v>
       </c>
       <c r="BI48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ48">
         <v>1000</v>
       </c>
       <c r="BK48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN48">
         <v>1000</v>
       </c>
       <c r="BO48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP48">
         <v>1000</v>
       </c>
       <c r="BQ48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR48">
         <v>1000</v>
       </c>
       <c r="BS48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT48">
         <v>1000</v>
       </c>
       <c r="BU48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV48">
         <v>1000</v>
       </c>
       <c r="BW48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX48">
         <v>1000</v>
       </c>
       <c r="BY48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ48">
         <v>1000</v>
       </c>
       <c r="CA48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB48" t="s">
         <v>241</v>
@@ -12710,22 +12710,22 @@
         <v>2.94</v>
       </c>
       <c r="G49">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>2.74</v>
       </c>
       <c r="I49">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J49">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K49">
         <v>3.35</v>
       </c>
       <c r="L49">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M49">
         <v>1.08</v>
@@ -12743,19 +12743,19 @@
         <v>2.08</v>
       </c>
       <c r="R49">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S49">
         <v>3.75</v>
       </c>
       <c r="T49">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U49">
         <v>2.08</v>
       </c>
       <c r="V49">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
         <v>1.5</v>
@@ -12779,7 +12779,7 @@
         <v>7.4</v>
       </c>
       <c r="AD49">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE49">
         <v>32</v>
@@ -12788,13 +12788,13 @@
         <v>19.5</v>
       </c>
       <c r="AG49">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH49">
         <v>17.5</v>
       </c>
       <c r="AI49">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ49">
         <v>48</v>
@@ -12809,7 +12809,7 @@
         <v>110</v>
       </c>
       <c r="AN49">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO49">
         <v>29</v>
@@ -12827,13 +12827,13 @@
         <v>36</v>
       </c>
       <c r="AT49">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU49">
         <v>6.4</v>
       </c>
       <c r="AV49">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW49">
         <v>28</v>
@@ -12842,7 +12842,7 @@
         <v>16.5</v>
       </c>
       <c r="AY49">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ49">
         <v>16</v>
@@ -12851,7 +12851,7 @@
         <v>40</v>
       </c>
       <c r="BB49">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BC49">
         <v>30</v>
@@ -12860,13 +12860,13 @@
         <v>14</v>
       </c>
       <c r="BE49">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="BF49">
         <v>26</v>
       </c>
       <c r="BG49">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH49">
         <v>3.65</v>
@@ -12902,7 +12902,7 @@
         <v>44</v>
       </c>
       <c r="BS49">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT49">
         <v>5.9</v>
@@ -12920,10 +12920,10 @@
         <v>36</v>
       </c>
       <c r="BY49">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ49">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="CA49">
         <v>6.4</v>
@@ -12973,7 +12973,7 @@
         <v>1.07</v>
       </c>
       <c r="N50">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O50">
         <v>1.34</v>
@@ -13114,61 +13114,61 @@
         <v>1000</v>
       </c>
       <c r="BI50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ50">
         <v>1000</v>
       </c>
       <c r="BK50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN50">
         <v>1000</v>
       </c>
       <c r="BO50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP50">
         <v>1000</v>
       </c>
       <c r="BQ50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR50">
         <v>1000</v>
       </c>
       <c r="BS50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT50">
         <v>1000</v>
       </c>
       <c r="BU50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV50">
         <v>1000</v>
       </c>
       <c r="BW50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX50">
         <v>1000</v>
       </c>
       <c r="BY50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ50">
         <v>1000</v>
       </c>
       <c r="CA50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB50" t="s">
         <v>241</v>
@@ -13194,19 +13194,19 @@
         <v>6.2</v>
       </c>
       <c r="G51">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H51">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="I51">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="J51">
         <v>4.6</v>
       </c>
       <c r="K51">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L51">
         <v>1.27</v>
@@ -13233,19 +13233,19 @@
         <v>2.56</v>
       </c>
       <c r="T51">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U51">
         <v>2.12</v>
       </c>
       <c r="V51">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X51">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y51">
         <v>13</v>
@@ -13260,7 +13260,7 @@
         <v>29</v>
       </c>
       <c r="AC51">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD51">
         <v>10.5</v>
@@ -13269,31 +13269,31 @@
         <v>16</v>
       </c>
       <c r="AF51">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG51">
         <v>27</v>
       </c>
       <c r="AH51">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI51">
         <v>34</v>
       </c>
       <c r="AJ51">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AK51">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AL51">
         <v>90</v>
       </c>
       <c r="AM51">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AN51">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AO51">
         <v>6.8</v>
@@ -13311,19 +13311,19 @@
         <v>12</v>
       </c>
       <c r="AT51">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU51">
         <v>10</v>
       </c>
       <c r="AV51">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW51">
         <v>13</v>
       </c>
       <c r="AX51">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY51">
         <v>21</v>
@@ -13335,82 +13335,82 @@
         <v>25</v>
       </c>
       <c r="BB51">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BC51">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BD51">
+        <v>6.8</v>
+      </c>
+      <c r="BE51">
+        <v>7.4</v>
+      </c>
+      <c r="BF51">
+        <v>7</v>
+      </c>
+      <c r="BG51">
         <v>5.7</v>
       </c>
-      <c r="BE51">
-        <v>6</v>
-      </c>
-      <c r="BF51">
-        <v>5.8</v>
-      </c>
-      <c r="BG51">
-        <v>5.6</v>
-      </c>
       <c r="BH51">
         <v>1000</v>
       </c>
       <c r="BI51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ51">
         <v>1000</v>
       </c>
       <c r="BK51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL51">
         <v>1000</v>
       </c>
       <c r="BM51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN51">
         <v>1000</v>
       </c>
       <c r="BO51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP51">
         <v>1000</v>
       </c>
       <c r="BQ51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR51">
         <v>1000</v>
       </c>
       <c r="BS51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT51">
         <v>1000</v>
       </c>
       <c r="BU51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV51">
         <v>1000</v>
       </c>
       <c r="BW51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX51">
         <v>1000</v>
       </c>
       <c r="BY51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ51">
         <v>1000</v>
       </c>
       <c r="CA51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB51" t="s">
         <v>241</v>
@@ -13490,7 +13490,7 @@
         <v>65</v>
       </c>
       <c r="Y52">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="Z52">
         <v>500</v>
@@ -13505,7 +13505,7 @@
         <v>38</v>
       </c>
       <c r="AD52">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="AE52">
         <v>1000</v>
@@ -13541,7 +13541,7 @@
         <v>1000</v>
       </c>
       <c r="AP52">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ52">
         <v>6.2</v>
@@ -13550,7 +13550,7 @@
         <v>6.4</v>
       </c>
       <c r="AS52">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT52">
         <v>11.5</v>
@@ -13562,7 +13562,7 @@
         <v>6.2</v>
       </c>
       <c r="AW52">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX52">
         <v>7.4</v>
@@ -13675,46 +13675,46 @@
         <v>237</v>
       </c>
       <c r="F53">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G53">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H53">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I53">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J53">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K53">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L53">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M53">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N53">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="O53">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P53">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Q53">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="R53">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="S53">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="T53">
         <v>1.9</v>
@@ -13723,118 +13723,118 @@
         <v>1.88</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W53">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X53">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="Y53">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="Z53">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AA53">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB53">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AC53">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="AD53">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AE53">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AF53">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AG53">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AH53">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AI53">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AJ53">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AK53">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AL53">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM53">
         <v>500</v>
       </c>
       <c r="AN53">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO53">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AP53">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ53">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR53">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS53">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT53">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU53">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV53">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW53">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX53">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY53">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ53">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA53">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB53">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC53">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD53">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE53">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF53">
-        <v>1.89</v>
+        <v>4.7</v>
       </c>
       <c r="BG53">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13920,7 +13920,7 @@
         <v>1.83</v>
       </c>
       <c r="G54">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H54">
         <v>5.4</v>
@@ -13932,7 +13932,7 @@
         <v>3.35</v>
       </c>
       <c r="K54">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L54">
         <v>1.56</v>
@@ -13959,7 +13959,7 @@
         <v>5.4</v>
       </c>
       <c r="T54">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U54">
         <v>1.71</v>
@@ -13968,7 +13968,7 @@
         <v>1.2</v>
       </c>
       <c r="W54">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X54">
         <v>9</v>
@@ -14082,22 +14082,22 @@
         <v>1000</v>
       </c>
       <c r="BI54">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BJ54">
         <v>1000</v>
       </c>
       <c r="BK54">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BL54">
         <v>1000</v>
       </c>
       <c r="BM54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BN54">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO54">
         <v>1.53</v>
@@ -14106,37 +14106,37 @@
         <v>1000</v>
       </c>
       <c r="BQ54">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BR54">
         <v>1000</v>
       </c>
       <c r="BS54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BT54">
         <v>1000</v>
       </c>
       <c r="BU54">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BV54">
         <v>1000</v>
       </c>
       <c r="BW54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BX54">
         <v>1000</v>
       </c>
       <c r="BY54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BZ54">
         <v>1000</v>
       </c>
       <c r="CA54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CB54" t="s">
         <v>241</v>
@@ -14177,22 +14177,22 @@
         <v>3.2</v>
       </c>
       <c r="L55">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="M55">
         <v>1.12</v>
       </c>
       <c r="N55">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O55">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P55">
         <v>1.59</v>
       </c>
       <c r="Q55">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R55">
         <v>1.21</v>
@@ -14201,7 +14201,7 @@
         <v>5.3</v>
       </c>
       <c r="T55">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U55">
         <v>1.8</v>
@@ -14288,10 +14288,10 @@
         <v>10</v>
       </c>
       <c r="AW55">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX55">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY55">
         <v>16</v>
@@ -14303,19 +14303,19 @@
         <v>50</v>
       </c>
       <c r="BB55">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC55">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="BD55">
+        <v>75</v>
+      </c>
+      <c r="BE55">
+        <v>14.5</v>
+      </c>
+      <c r="BF55">
         <v>16</v>
-      </c>
-      <c r="BE55">
-        <v>15</v>
-      </c>
-      <c r="BF55">
-        <v>16.5</v>
       </c>
       <c r="BG55">
         <v>21</v>
@@ -14446,10 +14446,10 @@
         <v>1.87</v>
       </c>
       <c r="U56">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V56">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W56">
         <v>1.88</v>
